--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,33 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Norway Eliteserien</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>Strømsgodset</t>
+  </si>
+  <si>
+    <t>Rosenborg</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['39', '49']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +806,212 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7785174</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2">
+        <v>3.75</v>
+      </c>
+      <c r="R2">
+        <v>2.3</v>
+      </c>
+      <c r="S2">
+        <v>2.63</v>
+      </c>
+      <c r="T2">
+        <v>1.3</v>
+      </c>
+      <c r="U2">
+        <v>3.4</v>
+      </c>
+      <c r="V2">
+        <v>2.5</v>
+      </c>
+      <c r="W2">
+        <v>1.5</v>
+      </c>
+      <c r="X2">
+        <v>6</v>
+      </c>
+      <c r="Y2">
+        <v>1.13</v>
+      </c>
+      <c r="Z2">
+        <v>3.3</v>
+      </c>
+      <c r="AA2">
+        <v>3.68</v>
+      </c>
+      <c r="AB2">
+        <v>2.02</v>
+      </c>
+      <c r="AC2">
+        <v>1.04</v>
+      </c>
+      <c r="AD2">
+        <v>10</v>
+      </c>
+      <c r="AE2">
+        <v>1.2</v>
+      </c>
+      <c r="AF2">
+        <v>4.33</v>
+      </c>
+      <c r="AG2">
+        <v>1.6</v>
+      </c>
+      <c r="AH2">
+        <v>2.15</v>
+      </c>
+      <c r="AI2">
+        <v>1.53</v>
+      </c>
+      <c r="AJ2">
+        <v>2.38</v>
+      </c>
+      <c r="AK2">
+        <v>1.77</v>
+      </c>
+      <c r="AL2">
+        <v>1.28</v>
+      </c>
+      <c r="AM2">
+        <v>1.29</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>3</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>6</v>
+      </c>
+      <c r="AW2">
+        <v>5</v>
+      </c>
+      <c r="AX2">
+        <v>10</v>
+      </c>
+      <c r="AY2">
+        <v>13</v>
+      </c>
+      <c r="AZ2">
+        <v>19</v>
+      </c>
+      <c r="BA2">
+        <v>2</v>
+      </c>
+      <c r="BB2">
+        <v>5</v>
+      </c>
+      <c r="BC2">
+        <v>7</v>
+      </c>
+      <c r="BD2">
+        <v>2.4</v>
+      </c>
+      <c r="BE2">
+        <v>7</v>
+      </c>
+      <c r="BF2">
+        <v>1.67</v>
+      </c>
+      <c r="BG2">
+        <v>1.15</v>
+      </c>
+      <c r="BH2">
+        <v>4.8</v>
+      </c>
+      <c r="BI2">
+        <v>1.26</v>
+      </c>
+      <c r="BJ2">
+        <v>3.4</v>
+      </c>
+      <c r="BK2">
+        <v>1.45</v>
+      </c>
+      <c r="BL2">
+        <v>2.55</v>
+      </c>
+      <c r="BM2">
+        <v>1.71</v>
+      </c>
+      <c r="BN2">
+        <v>2</v>
+      </c>
+      <c r="BO2">
+        <v>2.08</v>
+      </c>
+      <c r="BP2">
+        <v>1.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -229,13 +229,37 @@
     <t>Strømsgodset</t>
   </si>
   <si>
+    <t>Fredrikstad</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
+    <t>Brann</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
     <t>['90']</t>
   </si>
   <si>
+    <t>['10', '23', '83']</t>
+  </si>
+  <si>
+    <t>['41', '66', '80']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['63']</t>
   </si>
 </sst>
 </file>
@@ -597,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP2"/>
+  <dimension ref="A1:BP4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -829,7 +853,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -850,10 +874,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -967,10 +991,10 @@
         <v>2</v>
       </c>
       <c r="BB2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD2">
         <v>2.4</v>
@@ -1010,6 +1034,418 @@
       </c>
       <c r="BP2">
         <v>1.66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7785175</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45745.58333333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3">
+        <v>3.75</v>
+      </c>
+      <c r="R3">
+        <v>2.1</v>
+      </c>
+      <c r="S3">
+        <v>2.88</v>
+      </c>
+      <c r="T3">
+        <v>1.4</v>
+      </c>
+      <c r="U3">
+        <v>2.75</v>
+      </c>
+      <c r="V3">
+        <v>3</v>
+      </c>
+      <c r="W3">
+        <v>1.36</v>
+      </c>
+      <c r="X3">
+        <v>8</v>
+      </c>
+      <c r="Y3">
+        <v>1.08</v>
+      </c>
+      <c r="Z3">
+        <v>3.31</v>
+      </c>
+      <c r="AA3">
+        <v>3.36</v>
+      </c>
+      <c r="AB3">
+        <v>2.12</v>
+      </c>
+      <c r="AC3">
+        <v>1.06</v>
+      </c>
+      <c r="AD3">
+        <v>8.5</v>
+      </c>
+      <c r="AE3">
+        <v>1.3</v>
+      </c>
+      <c r="AF3">
+        <v>3.35</v>
+      </c>
+      <c r="AG3">
+        <v>1.92</v>
+      </c>
+      <c r="AH3">
+        <v>1.82</v>
+      </c>
+      <c r="AI3">
+        <v>1.75</v>
+      </c>
+      <c r="AJ3">
+        <v>2</v>
+      </c>
+      <c r="AK3">
+        <v>1.62</v>
+      </c>
+      <c r="AL3">
+        <v>1.31</v>
+      </c>
+      <c r="AM3">
+        <v>1.35</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>6</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>3</v>
+      </c>
+      <c r="AY3">
+        <v>7</v>
+      </c>
+      <c r="AZ3">
+        <v>3</v>
+      </c>
+      <c r="BA3">
+        <v>3</v>
+      </c>
+      <c r="BB3">
+        <v>7</v>
+      </c>
+      <c r="BC3">
+        <v>10</v>
+      </c>
+      <c r="BD3">
+        <v>2.17</v>
+      </c>
+      <c r="BE3">
+        <v>6.75</v>
+      </c>
+      <c r="BF3">
+        <v>1.82</v>
+      </c>
+      <c r="BG3">
+        <v>1.25</v>
+      </c>
+      <c r="BH3">
+        <v>3.55</v>
+      </c>
+      <c r="BI3">
+        <v>1.44</v>
+      </c>
+      <c r="BJ3">
+        <v>2.55</v>
+      </c>
+      <c r="BK3">
+        <v>1.77</v>
+      </c>
+      <c r="BL3">
+        <v>1.95</v>
+      </c>
+      <c r="BM3">
+        <v>2.08</v>
+      </c>
+      <c r="BN3">
+        <v>1.65</v>
+      </c>
+      <c r="BO3">
+        <v>2.65</v>
+      </c>
+      <c r="BP3">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7785176</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45746.39583333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>4</v>
+      </c>
+      <c r="O4" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>2.25</v>
+      </c>
+      <c r="S4">
+        <v>3.4</v>
+      </c>
+      <c r="T4">
+        <v>1.33</v>
+      </c>
+      <c r="U4">
+        <v>3.25</v>
+      </c>
+      <c r="V4">
+        <v>2.63</v>
+      </c>
+      <c r="W4">
+        <v>1.44</v>
+      </c>
+      <c r="X4">
+        <v>6.5</v>
+      </c>
+      <c r="Y4">
+        <v>1.11</v>
+      </c>
+      <c r="Z4">
+        <v>2.33</v>
+      </c>
+      <c r="AA4">
+        <v>3.62</v>
+      </c>
+      <c r="AB4">
+        <v>2.75</v>
+      </c>
+      <c r="AC4">
+        <v>1.04</v>
+      </c>
+      <c r="AD4">
+        <v>10</v>
+      </c>
+      <c r="AE4">
+        <v>1.22</v>
+      </c>
+      <c r="AF4">
+        <v>4</v>
+      </c>
+      <c r="AG4">
+        <v>1.75</v>
+      </c>
+      <c r="AH4">
+        <v>1.91</v>
+      </c>
+      <c r="AI4">
+        <v>1.62</v>
+      </c>
+      <c r="AJ4">
+        <v>2.2</v>
+      </c>
+      <c r="AK4">
+        <v>1.42</v>
+      </c>
+      <c r="AL4">
+        <v>1.29</v>
+      </c>
+      <c r="AM4">
+        <v>1.55</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>6</v>
+      </c>
+      <c r="AW4">
+        <v>10</v>
+      </c>
+      <c r="AX4">
+        <v>8</v>
+      </c>
+      <c r="AY4">
+        <v>20</v>
+      </c>
+      <c r="AZ4">
+        <v>16</v>
+      </c>
+      <c r="BA4">
+        <v>8</v>
+      </c>
+      <c r="BB4">
+        <v>6</v>
+      </c>
+      <c r="BC4">
+        <v>14</v>
+      </c>
+      <c r="BD4">
+        <v>1.9</v>
+      </c>
+      <c r="BE4">
+        <v>6.75</v>
+      </c>
+      <c r="BF4">
+        <v>2.07</v>
+      </c>
+      <c r="BG4">
+        <v>1.2</v>
+      </c>
+      <c r="BH4">
+        <v>3.95</v>
+      </c>
+      <c r="BI4">
+        <v>1.35</v>
+      </c>
+      <c r="BJ4">
+        <v>2.9</v>
+      </c>
+      <c r="BK4">
+        <v>1.57</v>
+      </c>
+      <c r="BL4">
+        <v>2.23</v>
+      </c>
+      <c r="BM4">
+        <v>1.77</v>
+      </c>
+      <c r="BN4">
+        <v>1.95</v>
+      </c>
+      <c r="BO4">
+        <v>2.38</v>
+      </c>
+      <c r="BP4">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="99">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -235,6 +235,21 @@
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>HamKam</t>
+  </si>
+  <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Molde</t>
+  </si>
+  <si>
+    <t>Tromsø</t>
+  </si>
+  <si>
+    <t>Bryne</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -244,6 +259,21 @@
     <t>Viking</t>
   </si>
   <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
     <t>['90']</t>
   </si>
   <si>
@@ -253,13 +283,34 @@
     <t>['41', '66', '80']</t>
   </si>
   <si>
+    <t>['4', '59']</t>
+  </si>
+  <si>
+    <t>['45+2', '63', '77']</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>['63']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['5', '64']</t>
+  </si>
+  <si>
+    <t>['35']</t>
   </si>
 </sst>
 </file>
@@ -621,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP4"/>
+  <dimension ref="A1:BP9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -853,7 +904,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -874,10 +925,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1059,7 +1110,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1080,10 +1131,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="Q3">
         <v>3.75</v>
@@ -1265,7 +1316,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1286,10 +1337,10 @@
         <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1446,6 +1497,1036 @@
       </c>
       <c r="BP4">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7785177</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45746.5</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5" t="s">
+        <v>89</v>
+      </c>
+      <c r="P5" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q5">
+        <v>2.5</v>
+      </c>
+      <c r="R5">
+        <v>2.25</v>
+      </c>
+      <c r="S5">
+        <v>4.33</v>
+      </c>
+      <c r="T5">
+        <v>1.36</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <v>2.63</v>
+      </c>
+      <c r="W5">
+        <v>1.44</v>
+      </c>
+      <c r="X5">
+        <v>7</v>
+      </c>
+      <c r="Y5">
+        <v>1.1</v>
+      </c>
+      <c r="Z5">
+        <v>1.84</v>
+      </c>
+      <c r="AA5">
+        <v>3.57</v>
+      </c>
+      <c r="AB5">
+        <v>4.1</v>
+      </c>
+      <c r="AC5">
+        <v>1.05</v>
+      </c>
+      <c r="AD5">
+        <v>9</v>
+      </c>
+      <c r="AE5">
+        <v>1.28</v>
+      </c>
+      <c r="AF5">
+        <v>3.65</v>
+      </c>
+      <c r="AG5">
+        <v>1.8</v>
+      </c>
+      <c r="AH5">
+        <v>1.94</v>
+      </c>
+      <c r="AI5">
+        <v>1.7</v>
+      </c>
+      <c r="AJ5">
+        <v>2.05</v>
+      </c>
+      <c r="AK5">
+        <v>1.22</v>
+      </c>
+      <c r="AL5">
+        <v>1.28</v>
+      </c>
+      <c r="AM5">
+        <v>1.9</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>6</v>
+      </c>
+      <c r="AW5">
+        <v>4</v>
+      </c>
+      <c r="AX5">
+        <v>9</v>
+      </c>
+      <c r="AY5">
+        <v>10</v>
+      </c>
+      <c r="AZ5">
+        <v>16</v>
+      </c>
+      <c r="BA5">
+        <v>1</v>
+      </c>
+      <c r="BB5">
+        <v>6</v>
+      </c>
+      <c r="BC5">
+        <v>7</v>
+      </c>
+      <c r="BD5">
+        <v>1.5</v>
+      </c>
+      <c r="BE5">
+        <v>7</v>
+      </c>
+      <c r="BF5">
+        <v>2.8</v>
+      </c>
+      <c r="BG5">
+        <v>1.18</v>
+      </c>
+      <c r="BH5">
+        <v>4.3</v>
+      </c>
+      <c r="BI5">
+        <v>1.3</v>
+      </c>
+      <c r="BJ5">
+        <v>3.05</v>
+      </c>
+      <c r="BK5">
+        <v>1.5</v>
+      </c>
+      <c r="BL5">
+        <v>2.33</v>
+      </c>
+      <c r="BM5">
+        <v>1.77</v>
+      </c>
+      <c r="BN5">
+        <v>1.95</v>
+      </c>
+      <c r="BO5">
+        <v>2.23</v>
+      </c>
+      <c r="BP5">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7785178</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45746.5</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q6">
+        <v>2.88</v>
+      </c>
+      <c r="R6">
+        <v>2.1</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>1.44</v>
+      </c>
+      <c r="U6">
+        <v>2.63</v>
+      </c>
+      <c r="V6">
+        <v>3.25</v>
+      </c>
+      <c r="W6">
+        <v>1.33</v>
+      </c>
+      <c r="X6">
+        <v>9</v>
+      </c>
+      <c r="Y6">
+        <v>1.07</v>
+      </c>
+      <c r="Z6">
+        <v>2.16</v>
+      </c>
+      <c r="AA6">
+        <v>3.21</v>
+      </c>
+      <c r="AB6">
+        <v>3.37</v>
+      </c>
+      <c r="AC6">
+        <v>1.06</v>
+      </c>
+      <c r="AD6">
+        <v>8.5</v>
+      </c>
+      <c r="AE6">
+        <v>1.35</v>
+      </c>
+      <c r="AF6">
+        <v>3.1</v>
+      </c>
+      <c r="AG6">
+        <v>1.95</v>
+      </c>
+      <c r="AH6">
+        <v>1.7</v>
+      </c>
+      <c r="AI6">
+        <v>1.8</v>
+      </c>
+      <c r="AJ6">
+        <v>1.95</v>
+      </c>
+      <c r="AK6">
+        <v>1.31</v>
+      </c>
+      <c r="AL6">
+        <v>1.32</v>
+      </c>
+      <c r="AM6">
+        <v>1.66</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>5</v>
+      </c>
+      <c r="AV6">
+        <v>4</v>
+      </c>
+      <c r="AW6">
+        <v>8</v>
+      </c>
+      <c r="AX6">
+        <v>7</v>
+      </c>
+      <c r="AY6">
+        <v>14</v>
+      </c>
+      <c r="AZ6">
+        <v>11</v>
+      </c>
+      <c r="BA6">
+        <v>4</v>
+      </c>
+      <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
+        <v>9</v>
+      </c>
+      <c r="BD6">
+        <v>1.57</v>
+      </c>
+      <c r="BE6">
+        <v>8</v>
+      </c>
+      <c r="BF6">
+        <v>2.75</v>
+      </c>
+      <c r="BG6">
+        <v>1.28</v>
+      </c>
+      <c r="BH6">
+        <v>3.25</v>
+      </c>
+      <c r="BI6">
+        <v>1.52</v>
+      </c>
+      <c r="BJ6">
+        <v>2.37</v>
+      </c>
+      <c r="BK6">
+        <v>1.85</v>
+      </c>
+      <c r="BL6">
+        <v>1.85</v>
+      </c>
+      <c r="BM6">
+        <v>2.38</v>
+      </c>
+      <c r="BN6">
+        <v>1.54</v>
+      </c>
+      <c r="BO6">
+        <v>3.12</v>
+      </c>
+      <c r="BP6">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7785179</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45746.5</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q7">
+        <v>1.91</v>
+      </c>
+      <c r="R7">
+        <v>2.5</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <v>1.29</v>
+      </c>
+      <c r="U7">
+        <v>3.5</v>
+      </c>
+      <c r="V7">
+        <v>2.25</v>
+      </c>
+      <c r="W7">
+        <v>1.57</v>
+      </c>
+      <c r="X7">
+        <v>5.5</v>
+      </c>
+      <c r="Y7">
+        <v>1.14</v>
+      </c>
+      <c r="Z7">
+        <v>1.42</v>
+      </c>
+      <c r="AA7">
+        <v>4.8</v>
+      </c>
+      <c r="AB7">
+        <v>6.3</v>
+      </c>
+      <c r="AC7">
+        <v>1.03</v>
+      </c>
+      <c r="AD7">
+        <v>11</v>
+      </c>
+      <c r="AE7">
+        <v>1.17</v>
+      </c>
+      <c r="AF7">
+        <v>5</v>
+      </c>
+      <c r="AG7">
+        <v>1.54</v>
+      </c>
+      <c r="AH7">
+        <v>2.38</v>
+      </c>
+      <c r="AI7">
+        <v>1.75</v>
+      </c>
+      <c r="AJ7">
+        <v>2</v>
+      </c>
+      <c r="AK7">
+        <v>1.12</v>
+      </c>
+      <c r="AL7">
+        <v>1.18</v>
+      </c>
+      <c r="AM7">
+        <v>2.65</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>3</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>3</v>
+      </c>
+      <c r="AV7">
+        <v>6</v>
+      </c>
+      <c r="AW7">
+        <v>5</v>
+      </c>
+      <c r="AX7">
+        <v>5</v>
+      </c>
+      <c r="AY7">
+        <v>8</v>
+      </c>
+      <c r="AZ7">
+        <v>11</v>
+      </c>
+      <c r="BA7">
+        <v>8</v>
+      </c>
+      <c r="BB7">
+        <v>1</v>
+      </c>
+      <c r="BC7">
+        <v>9</v>
+      </c>
+      <c r="BD7">
+        <v>1.36</v>
+      </c>
+      <c r="BE7">
+        <v>7</v>
+      </c>
+      <c r="BF7">
+        <v>3.4</v>
+      </c>
+      <c r="BG7">
+        <v>1.25</v>
+      </c>
+      <c r="BH7">
+        <v>3.4</v>
+      </c>
+      <c r="BI7">
+        <v>1.46</v>
+      </c>
+      <c r="BJ7">
+        <v>2.5</v>
+      </c>
+      <c r="BK7">
+        <v>1.7</v>
+      </c>
+      <c r="BL7">
+        <v>2.05</v>
+      </c>
+      <c r="BM7">
+        <v>2.12</v>
+      </c>
+      <c r="BN7">
+        <v>1.63</v>
+      </c>
+      <c r="BO7">
+        <v>2.65</v>
+      </c>
+      <c r="BP7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7785180</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45746.5</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q8">
+        <v>2.3</v>
+      </c>
+      <c r="R8">
+        <v>2.2</v>
+      </c>
+      <c r="S8">
+        <v>5</v>
+      </c>
+      <c r="T8">
+        <v>1.4</v>
+      </c>
+      <c r="U8">
+        <v>2.75</v>
+      </c>
+      <c r="V8">
+        <v>2.75</v>
+      </c>
+      <c r="W8">
+        <v>1.4</v>
+      </c>
+      <c r="X8">
+        <v>8</v>
+      </c>
+      <c r="Y8">
+        <v>1.08</v>
+      </c>
+      <c r="Z8">
+        <v>1.65</v>
+      </c>
+      <c r="AA8">
+        <v>3.53</v>
+      </c>
+      <c r="AB8">
+        <v>5.5</v>
+      </c>
+      <c r="AC8">
+        <v>1.05</v>
+      </c>
+      <c r="AD8">
+        <v>9</v>
+      </c>
+      <c r="AE8">
+        <v>1.3</v>
+      </c>
+      <c r="AF8">
+        <v>3.45</v>
+      </c>
+      <c r="AG8">
+        <v>1.85</v>
+      </c>
+      <c r="AH8">
+        <v>1.89</v>
+      </c>
+      <c r="AI8">
+        <v>1.8</v>
+      </c>
+      <c r="AJ8">
+        <v>1.95</v>
+      </c>
+      <c r="AK8">
+        <v>1.18</v>
+      </c>
+      <c r="AL8">
+        <v>1.26</v>
+      </c>
+      <c r="AM8">
+        <v>2.1</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>3</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>8</v>
+      </c>
+      <c r="AV8">
+        <v>4</v>
+      </c>
+      <c r="AW8">
+        <v>6</v>
+      </c>
+      <c r="AX8">
+        <v>2</v>
+      </c>
+      <c r="AY8">
+        <v>14</v>
+      </c>
+      <c r="AZ8">
+        <v>6</v>
+      </c>
+      <c r="BA8">
+        <v>8</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BC8">
+        <v>10</v>
+      </c>
+      <c r="BD8">
+        <v>1.48</v>
+      </c>
+      <c r="BE8">
+        <v>7</v>
+      </c>
+      <c r="BF8">
+        <v>2.9</v>
+      </c>
+      <c r="BG8">
+        <v>1.22</v>
+      </c>
+      <c r="BH8">
+        <v>3.8</v>
+      </c>
+      <c r="BI8">
+        <v>1.38</v>
+      </c>
+      <c r="BJ8">
+        <v>2.75</v>
+      </c>
+      <c r="BK8">
+        <v>1.64</v>
+      </c>
+      <c r="BL8">
+        <v>2.12</v>
+      </c>
+      <c r="BM8">
+        <v>1.95</v>
+      </c>
+      <c r="BN8">
+        <v>1.77</v>
+      </c>
+      <c r="BO8">
+        <v>2.48</v>
+      </c>
+      <c r="BP8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7785181</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45746.59375</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>91</v>
+      </c>
+      <c r="P9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9">
+        <v>6.5</v>
+      </c>
+      <c r="R9">
+        <v>2.63</v>
+      </c>
+      <c r="S9">
+        <v>1.83</v>
+      </c>
+      <c r="T9">
+        <v>1.25</v>
+      </c>
+      <c r="U9">
+        <v>3.75</v>
+      </c>
+      <c r="V9">
+        <v>2.2</v>
+      </c>
+      <c r="W9">
+        <v>1.62</v>
+      </c>
+      <c r="X9">
+        <v>5</v>
+      </c>
+      <c r="Y9">
+        <v>1.17</v>
+      </c>
+      <c r="Z9">
+        <v>7.1</v>
+      </c>
+      <c r="AA9">
+        <v>5</v>
+      </c>
+      <c r="AB9">
+        <v>1.37</v>
+      </c>
+      <c r="AC9">
+        <v>1.01</v>
+      </c>
+      <c r="AD9">
+        <v>17</v>
+      </c>
+      <c r="AE9">
+        <v>1.14</v>
+      </c>
+      <c r="AF9">
+        <v>5.5</v>
+      </c>
+      <c r="AG9">
+        <v>1.45</v>
+      </c>
+      <c r="AH9">
+        <v>2.63</v>
+      </c>
+      <c r="AI9">
+        <v>1.7</v>
+      </c>
+      <c r="AJ9">
+        <v>2.05</v>
+      </c>
+      <c r="AK9">
+        <v>3</v>
+      </c>
+      <c r="AL9">
+        <v>1.16</v>
+      </c>
+      <c r="AM9">
+        <v>1.1</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>3</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>-1</v>
+      </c>
+      <c r="AV9">
+        <v>-1</v>
+      </c>
+      <c r="AW9">
+        <v>-1</v>
+      </c>
+      <c r="AX9">
+        <v>-1</v>
+      </c>
+      <c r="AY9">
+        <v>-1</v>
+      </c>
+      <c r="AZ9">
+        <v>-1</v>
+      </c>
+      <c r="BA9">
+        <v>-1</v>
+      </c>
+      <c r="BB9">
+        <v>-1</v>
+      </c>
+      <c r="BC9">
+        <v>-1</v>
+      </c>
+      <c r="BD9">
+        <v>3.55</v>
+      </c>
+      <c r="BE9">
+        <v>7.5</v>
+      </c>
+      <c r="BF9">
+        <v>1.33</v>
+      </c>
+      <c r="BG9">
+        <v>1.22</v>
+      </c>
+      <c r="BH9">
+        <v>3.8</v>
+      </c>
+      <c r="BI9">
+        <v>1.38</v>
+      </c>
+      <c r="BJ9">
+        <v>2.7</v>
+      </c>
+      <c r="BK9">
+        <v>1.7</v>
+      </c>
+      <c r="BL9">
+        <v>2.05</v>
+      </c>
+      <c r="BM9">
+        <v>1.98</v>
+      </c>
+      <c r="BN9">
+        <v>1.73</v>
+      </c>
+      <c r="BO9">
+        <v>2.45</v>
+      </c>
+      <c r="BP9">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -1454,10 +1454,10 @@
         <v>8</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD4">
         <v>1.9</v>
@@ -2275,13 +2275,13 @@
         <v>6</v>
       </c>
       <c r="BA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB8">
         <v>2</v>
       </c>
       <c r="BC8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD8">
         <v>1.48</v>
@@ -2463,31 +2463,31 @@
         <v>0</v>
       </c>
       <c r="AU9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AV9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AW9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AX9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AY9">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AZ9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BA9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BC9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="BD9">
         <v>3.55</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -250,6 +250,9 @@
     <t>Bryne</t>
   </si>
   <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
     <t>Rosenborg</t>
   </si>
   <si>
@@ -271,9 +274,6 @@
     <t>Haugesund</t>
   </si>
   <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>['90']</t>
   </si>
   <si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>['37']</t>
+  </si>
+  <si>
+    <t>['5', '59', '75']</t>
+  </si>
+  <si>
+    <t>['40']</t>
   </si>
   <si>
     <t>['39', '49']</t>
@@ -672,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP9"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -904,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -928,7 +934,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1110,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1316,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1340,7 +1346,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1522,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1546,7 +1552,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1728,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1752,7 +1758,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -1934,7 +1940,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1958,7 +1964,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2140,7 +2146,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2346,7 +2352,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2370,7 +2376,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -2527,6 +2533,418 @@
       </c>
       <c r="BP9">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7785184</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>3</v>
+      </c>
+      <c r="O10" t="s">
+        <v>93</v>
+      </c>
+      <c r="P10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q10">
+        <v>1.62</v>
+      </c>
+      <c r="R10">
+        <v>2.88</v>
+      </c>
+      <c r="S10">
+        <v>8.5</v>
+      </c>
+      <c r="T10">
+        <v>1.22</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
+      </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
+      <c r="W10">
+        <v>1.73</v>
+      </c>
+      <c r="X10">
+        <v>4.33</v>
+      </c>
+      <c r="Y10">
+        <v>1.2</v>
+      </c>
+      <c r="Z10">
+        <v>1.21</v>
+      </c>
+      <c r="AA10">
+        <v>7</v>
+      </c>
+      <c r="AB10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>1.13</v>
+      </c>
+      <c r="AF10">
+        <v>6.31</v>
+      </c>
+      <c r="AG10">
+        <v>1.36</v>
+      </c>
+      <c r="AH10">
+        <v>2.99</v>
+      </c>
+      <c r="AI10">
+        <v>1.91</v>
+      </c>
+      <c r="AJ10">
+        <v>1.91</v>
+      </c>
+      <c r="AK10">
+        <v>1.04</v>
+      </c>
+      <c r="AL10">
+        <v>1.11</v>
+      </c>
+      <c r="AM10">
+        <v>3.95</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>3</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>-1</v>
+      </c>
+      <c r="AV10">
+        <v>-1</v>
+      </c>
+      <c r="AW10">
+        <v>-1</v>
+      </c>
+      <c r="AX10">
+        <v>-1</v>
+      </c>
+      <c r="AY10">
+        <v>-1</v>
+      </c>
+      <c r="AZ10">
+        <v>-1</v>
+      </c>
+      <c r="BA10">
+        <v>-1</v>
+      </c>
+      <c r="BB10">
+        <v>-1</v>
+      </c>
+      <c r="BC10">
+        <v>-1</v>
+      </c>
+      <c r="BD10">
+        <v>1.12</v>
+      </c>
+      <c r="BE10">
+        <v>14.25</v>
+      </c>
+      <c r="BF10">
+        <v>7.5</v>
+      </c>
+      <c r="BG10">
+        <v>1.08</v>
+      </c>
+      <c r="BH10">
+        <v>5.5</v>
+      </c>
+      <c r="BI10">
+        <v>1.2</v>
+      </c>
+      <c r="BJ10">
+        <v>3.72</v>
+      </c>
+      <c r="BK10">
+        <v>1.39</v>
+      </c>
+      <c r="BL10">
+        <v>2.67</v>
+      </c>
+      <c r="BM10">
+        <v>1.73</v>
+      </c>
+      <c r="BN10">
+        <v>2</v>
+      </c>
+      <c r="BO10">
+        <v>2.07</v>
+      </c>
+      <c r="BP10">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7785182</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45752.54166666666</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q11">
+        <v>2.3</v>
+      </c>
+      <c r="R11">
+        <v>2.25</v>
+      </c>
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
+        <v>1.36</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <v>2.75</v>
+      </c>
+      <c r="W11">
+        <v>1.4</v>
+      </c>
+      <c r="X11">
+        <v>7</v>
+      </c>
+      <c r="Y11">
+        <v>1.1</v>
+      </c>
+      <c r="Z11">
+        <v>1.66</v>
+      </c>
+      <c r="AA11">
+        <v>3.82</v>
+      </c>
+      <c r="AB11">
+        <v>4.8</v>
+      </c>
+      <c r="AC11">
+        <v>1.05</v>
+      </c>
+      <c r="AD11">
+        <v>9.5</v>
+      </c>
+      <c r="AE11">
+        <v>1.28</v>
+      </c>
+      <c r="AF11">
+        <v>3.55</v>
+      </c>
+      <c r="AG11">
+        <v>1.8</v>
+      </c>
+      <c r="AH11">
+        <v>1.94</v>
+      </c>
+      <c r="AI11">
+        <v>1.8</v>
+      </c>
+      <c r="AJ11">
+        <v>1.95</v>
+      </c>
+      <c r="AK11">
+        <v>1.17</v>
+      </c>
+      <c r="AL11">
+        <v>1.22</v>
+      </c>
+      <c r="AM11">
+        <v>2.1</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>3</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>4</v>
+      </c>
+      <c r="AW11">
+        <v>10</v>
+      </c>
+      <c r="AX11">
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <v>17</v>
+      </c>
+      <c r="AZ11">
+        <v>5</v>
+      </c>
+      <c r="BA11">
+        <v>8</v>
+      </c>
+      <c r="BB11">
+        <v>6</v>
+      </c>
+      <c r="BC11">
+        <v>14</v>
+      </c>
+      <c r="BD11">
+        <v>1.28</v>
+      </c>
+      <c r="BE11">
+        <v>10.25</v>
+      </c>
+      <c r="BF11">
+        <v>4.6</v>
+      </c>
+      <c r="BG11">
+        <v>1.23</v>
+      </c>
+      <c r="BH11">
+        <v>3.42</v>
+      </c>
+      <c r="BI11">
+        <v>1.46</v>
+      </c>
+      <c r="BJ11">
+        <v>2.45</v>
+      </c>
+      <c r="BK11">
+        <v>1.85</v>
+      </c>
+      <c r="BL11">
+        <v>1.85</v>
+      </c>
+      <c r="BM11">
+        <v>2.3</v>
+      </c>
+      <c r="BN11">
+        <v>1.52</v>
+      </c>
+      <c r="BO11">
+        <v>3.05</v>
+      </c>
+      <c r="BP11">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -2675,31 +2675,31 @@
         <v>0</v>
       </c>
       <c r="AU10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AX10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AY10">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AZ10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BA10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD10">
         <v>1.12</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="111">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -259,21 +259,21 @@
     <t>Brann</t>
   </si>
   <si>
+    <t>Sarpsborg 08</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>Haugesund</t>
+  </si>
+  <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
     <t>Viking</t>
   </si>
   <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
-    <t>Sandefjord</t>
-  </si>
-  <si>
-    <t>Sarpsborg 08</t>
-  </si>
-  <si>
-    <t>Haugesund</t>
-  </si>
-  <si>
     <t>['90']</t>
   </si>
   <si>
@@ -301,6 +301,21 @@
     <t>['40']</t>
   </si>
   <si>
+    <t>['62', '74', '78']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['23', '41', '80']</t>
+  </si>
+  <si>
+    <t>['43', '87']</t>
+  </si>
+  <si>
+    <t>['39', '74', '83']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -317,6 +332,21 @@
   </si>
   <si>
     <t>['35']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['15', '25', '48', '79', '90+2']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -934,7 +964,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1322,7 +1352,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -1346,7 +1376,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1528,7 +1558,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1552,7 +1582,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1734,7 +1764,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1758,7 +1788,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -1940,7 +1970,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1964,7 +1994,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2146,7 +2176,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I8">
         <v>1</v>
@@ -2376,7 +2406,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -2945,6 +2975,1242 @@
       </c>
       <c r="BP11">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7785183</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45753.39583333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>3</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>4</v>
+      </c>
+      <c r="O12" t="s">
+        <v>95</v>
+      </c>
+      <c r="P12" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q12">
+        <v>2.2</v>
+      </c>
+      <c r="R12">
+        <v>2.38</v>
+      </c>
+      <c r="S12">
+        <v>5</v>
+      </c>
+      <c r="T12">
+        <v>1.33</v>
+      </c>
+      <c r="U12">
+        <v>3.25</v>
+      </c>
+      <c r="V12">
+        <v>2.63</v>
+      </c>
+      <c r="W12">
+        <v>1.44</v>
+      </c>
+      <c r="X12">
+        <v>6.5</v>
+      </c>
+      <c r="Y12">
+        <v>1.11</v>
+      </c>
+      <c r="Z12">
+        <v>1.58</v>
+      </c>
+      <c r="AA12">
+        <v>4.1</v>
+      </c>
+      <c r="AB12">
+        <v>5.1</v>
+      </c>
+      <c r="AC12">
+        <v>1.04</v>
+      </c>
+      <c r="AD12">
+        <v>10</v>
+      </c>
+      <c r="AE12">
+        <v>1.22</v>
+      </c>
+      <c r="AF12">
+        <v>4</v>
+      </c>
+      <c r="AG12">
+        <v>1.65</v>
+      </c>
+      <c r="AH12">
+        <v>2.05</v>
+      </c>
+      <c r="AI12">
+        <v>1.75</v>
+      </c>
+      <c r="AJ12">
+        <v>2</v>
+      </c>
+      <c r="AK12">
+        <v>1.15</v>
+      </c>
+      <c r="AL12">
+        <v>1.18</v>
+      </c>
+      <c r="AM12">
+        <v>2.3</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>6</v>
+      </c>
+      <c r="AV12">
+        <v>2</v>
+      </c>
+      <c r="AW12">
+        <v>7</v>
+      </c>
+      <c r="AX12">
+        <v>2</v>
+      </c>
+      <c r="AY12">
+        <v>16</v>
+      </c>
+      <c r="AZ12">
+        <v>4</v>
+      </c>
+      <c r="BA12">
+        <v>5</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>5</v>
+      </c>
+      <c r="BD12">
+        <v>1.45</v>
+      </c>
+      <c r="BE12">
+        <v>7</v>
+      </c>
+      <c r="BF12">
+        <v>3.05</v>
+      </c>
+      <c r="BG12">
+        <v>1.24</v>
+      </c>
+      <c r="BH12">
+        <v>3.65</v>
+      </c>
+      <c r="BI12">
+        <v>1.42</v>
+      </c>
+      <c r="BJ12">
+        <v>2.65</v>
+      </c>
+      <c r="BK12">
+        <v>1.68</v>
+      </c>
+      <c r="BL12">
+        <v>2.05</v>
+      </c>
+      <c r="BM12">
+        <v>2.02</v>
+      </c>
+      <c r="BN12">
+        <v>1.68</v>
+      </c>
+      <c r="BO12">
+        <v>2.55</v>
+      </c>
+      <c r="BP12">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7785188</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13" t="s">
+        <v>96</v>
+      </c>
+      <c r="P13" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>2.2</v>
+      </c>
+      <c r="S13">
+        <v>3.5</v>
+      </c>
+      <c r="T13">
+        <v>1.36</v>
+      </c>
+      <c r="U13">
+        <v>3</v>
+      </c>
+      <c r="V13">
+        <v>2.63</v>
+      </c>
+      <c r="W13">
+        <v>1.44</v>
+      </c>
+      <c r="X13">
+        <v>7</v>
+      </c>
+      <c r="Y13">
+        <v>1.1</v>
+      </c>
+      <c r="Z13">
+        <v>2.18</v>
+      </c>
+      <c r="AA13">
+        <v>3.51</v>
+      </c>
+      <c r="AB13">
+        <v>3.06</v>
+      </c>
+      <c r="AC13">
+        <v>1.05</v>
+      </c>
+      <c r="AD13">
+        <v>9.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.25</v>
+      </c>
+      <c r="AF13">
+        <v>3.7</v>
+      </c>
+      <c r="AG13">
+        <v>1.79</v>
+      </c>
+      <c r="AH13">
+        <v>1.95</v>
+      </c>
+      <c r="AI13">
+        <v>1.67</v>
+      </c>
+      <c r="AJ13">
+        <v>2.1</v>
+      </c>
+      <c r="AK13">
+        <v>1.38</v>
+      </c>
+      <c r="AL13">
+        <v>1.29</v>
+      </c>
+      <c r="AM13">
+        <v>1.58</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1</v>
+      </c>
+      <c r="AQ13">
+        <v>1</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>4</v>
+      </c>
+      <c r="AW13">
+        <v>6</v>
+      </c>
+      <c r="AX13">
+        <v>5</v>
+      </c>
+      <c r="AY13">
+        <v>10</v>
+      </c>
+      <c r="AZ13">
+        <v>9</v>
+      </c>
+      <c r="BA13">
+        <v>8</v>
+      </c>
+      <c r="BB13">
+        <v>3</v>
+      </c>
+      <c r="BC13">
+        <v>11</v>
+      </c>
+      <c r="BD13">
+        <v>1.82</v>
+      </c>
+      <c r="BE13">
+        <v>6.75</v>
+      </c>
+      <c r="BF13">
+        <v>2.2</v>
+      </c>
+      <c r="BG13">
+        <v>1.24</v>
+      </c>
+      <c r="BH13">
+        <v>3.55</v>
+      </c>
+      <c r="BI13">
+        <v>1.42</v>
+      </c>
+      <c r="BJ13">
+        <v>2.65</v>
+      </c>
+      <c r="BK13">
+        <v>1.68</v>
+      </c>
+      <c r="BL13">
+        <v>2.05</v>
+      </c>
+      <c r="BM13">
+        <v>2.05</v>
+      </c>
+      <c r="BN13">
+        <v>1.68</v>
+      </c>
+      <c r="BO13">
+        <v>2.55</v>
+      </c>
+      <c r="BP13">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7785187</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P14" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q14">
+        <v>4</v>
+      </c>
+      <c r="R14">
+        <v>2.3</v>
+      </c>
+      <c r="S14">
+        <v>2.6</v>
+      </c>
+      <c r="T14">
+        <v>1.33</v>
+      </c>
+      <c r="U14">
+        <v>3.25</v>
+      </c>
+      <c r="V14">
+        <v>2.63</v>
+      </c>
+      <c r="W14">
+        <v>1.44</v>
+      </c>
+      <c r="X14">
+        <v>6.5</v>
+      </c>
+      <c r="Y14">
+        <v>1.11</v>
+      </c>
+      <c r="Z14">
+        <v>3.36</v>
+      </c>
+      <c r="AA14">
+        <v>3.85</v>
+      </c>
+      <c r="AB14">
+        <v>1.95</v>
+      </c>
+      <c r="AC14">
+        <v>1.04</v>
+      </c>
+      <c r="AD14">
+        <v>10</v>
+      </c>
+      <c r="AE14">
+        <v>1.22</v>
+      </c>
+      <c r="AF14">
+        <v>4.2</v>
+      </c>
+      <c r="AG14">
+        <v>1.65</v>
+      </c>
+      <c r="AH14">
+        <v>2</v>
+      </c>
+      <c r="AI14">
+        <v>1.62</v>
+      </c>
+      <c r="AJ14">
+        <v>2.2</v>
+      </c>
+      <c r="AK14">
+        <v>1.77</v>
+      </c>
+      <c r="AL14">
+        <v>1.22</v>
+      </c>
+      <c r="AM14">
+        <v>1.3</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>9</v>
+      </c>
+      <c r="AV14">
+        <v>3</v>
+      </c>
+      <c r="AW14">
+        <v>15</v>
+      </c>
+      <c r="AX14">
+        <v>12</v>
+      </c>
+      <c r="AY14">
+        <v>28</v>
+      </c>
+      <c r="AZ14">
+        <v>17</v>
+      </c>
+      <c r="BA14">
+        <v>1</v>
+      </c>
+      <c r="BB14">
+        <v>9</v>
+      </c>
+      <c r="BC14">
+        <v>10</v>
+      </c>
+      <c r="BD14">
+        <v>2.43</v>
+      </c>
+      <c r="BE14">
+        <v>7</v>
+      </c>
+      <c r="BF14">
+        <v>1.65</v>
+      </c>
+      <c r="BG14">
+        <v>1.22</v>
+      </c>
+      <c r="BH14">
+        <v>3.8</v>
+      </c>
+      <c r="BI14">
+        <v>1.38</v>
+      </c>
+      <c r="BJ14">
+        <v>2.8</v>
+      </c>
+      <c r="BK14">
+        <v>1.61</v>
+      </c>
+      <c r="BL14">
+        <v>2.15</v>
+      </c>
+      <c r="BM14">
+        <v>1.97</v>
+      </c>
+      <c r="BN14">
+        <v>1.74</v>
+      </c>
+      <c r="BO14">
+        <v>2.43</v>
+      </c>
+      <c r="BP14">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7785185</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15" t="s">
+        <v>91</v>
+      </c>
+      <c r="P15" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q15">
+        <v>3.25</v>
+      </c>
+      <c r="R15">
+        <v>2.2</v>
+      </c>
+      <c r="S15">
+        <v>3.25</v>
+      </c>
+      <c r="T15">
+        <v>1.4</v>
+      </c>
+      <c r="U15">
+        <v>2.75</v>
+      </c>
+      <c r="V15">
+        <v>2.75</v>
+      </c>
+      <c r="W15">
+        <v>1.4</v>
+      </c>
+      <c r="X15">
+        <v>8</v>
+      </c>
+      <c r="Y15">
+        <v>1.08</v>
+      </c>
+      <c r="Z15">
+        <v>2.66</v>
+      </c>
+      <c r="AA15">
+        <v>2.96</v>
+      </c>
+      <c r="AB15">
+        <v>2.8</v>
+      </c>
+      <c r="AC15">
+        <v>1.06</v>
+      </c>
+      <c r="AD15">
+        <v>8.5</v>
+      </c>
+      <c r="AE15">
+        <v>1.28</v>
+      </c>
+      <c r="AF15">
+        <v>3.5</v>
+      </c>
+      <c r="AG15">
+        <v>1.87</v>
+      </c>
+      <c r="AH15">
+        <v>1.87</v>
+      </c>
+      <c r="AI15">
+        <v>1.7</v>
+      </c>
+      <c r="AJ15">
+        <v>2.05</v>
+      </c>
+      <c r="AK15">
+        <v>1.44</v>
+      </c>
+      <c r="AL15">
+        <v>1.3</v>
+      </c>
+      <c r="AM15">
+        <v>1.48</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>3</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>4</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>10</v>
+      </c>
+      <c r="AX15">
+        <v>14</v>
+      </c>
+      <c r="AY15">
+        <v>15</v>
+      </c>
+      <c r="AZ15">
+        <v>28</v>
+      </c>
+      <c r="BA15">
+        <v>4</v>
+      </c>
+      <c r="BB15">
+        <v>10</v>
+      </c>
+      <c r="BC15">
+        <v>14</v>
+      </c>
+      <c r="BD15">
+        <v>1.94</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
+        <v>2.07</v>
+      </c>
+      <c r="BG15">
+        <v>1.4</v>
+      </c>
+      <c r="BH15">
+        <v>2.7</v>
+      </c>
+      <c r="BI15">
+        <v>1.67</v>
+      </c>
+      <c r="BJ15">
+        <v>2.07</v>
+      </c>
+      <c r="BK15">
+        <v>2.07</v>
+      </c>
+      <c r="BL15">
+        <v>1.67</v>
+      </c>
+      <c r="BM15">
+        <v>2.65</v>
+      </c>
+      <c r="BN15">
+        <v>1.42</v>
+      </c>
+      <c r="BO15">
+        <v>3.45</v>
+      </c>
+      <c r="BP15">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7785186</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45753.5</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>98</v>
+      </c>
+      <c r="P16" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q16">
+        <v>2.6</v>
+      </c>
+      <c r="R16">
+        <v>2.2</v>
+      </c>
+      <c r="S16">
+        <v>4.33</v>
+      </c>
+      <c r="T16">
+        <v>1.36</v>
+      </c>
+      <c r="U16">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>2.75</v>
+      </c>
+      <c r="W16">
+        <v>1.4</v>
+      </c>
+      <c r="X16">
+        <v>8</v>
+      </c>
+      <c r="Y16">
+        <v>1.08</v>
+      </c>
+      <c r="Z16">
+        <v>1.88</v>
+      </c>
+      <c r="AA16">
+        <v>3.76</v>
+      </c>
+      <c r="AB16">
+        <v>3.66</v>
+      </c>
+      <c r="AC16">
+        <v>1.05</v>
+      </c>
+      <c r="AD16">
+        <v>9.5</v>
+      </c>
+      <c r="AE16">
+        <v>1.28</v>
+      </c>
+      <c r="AF16">
+        <v>3.65</v>
+      </c>
+      <c r="AG16">
+        <v>1.8</v>
+      </c>
+      <c r="AH16">
+        <v>1.94</v>
+      </c>
+      <c r="AI16">
+        <v>1.75</v>
+      </c>
+      <c r="AJ16">
+        <v>2</v>
+      </c>
+      <c r="AK16">
+        <v>1.25</v>
+      </c>
+      <c r="AL16">
+        <v>1.29</v>
+      </c>
+      <c r="AM16">
+        <v>1.83</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>3</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>4</v>
+      </c>
+      <c r="AW16">
+        <v>8</v>
+      </c>
+      <c r="AX16">
+        <v>6</v>
+      </c>
+      <c r="AY16">
+        <v>17</v>
+      </c>
+      <c r="AZ16">
+        <v>11</v>
+      </c>
+      <c r="BA16">
+        <v>8</v>
+      </c>
+      <c r="BB16">
+        <v>1</v>
+      </c>
+      <c r="BC16">
+        <v>9</v>
+      </c>
+      <c r="BD16">
+        <v>1.65</v>
+      </c>
+      <c r="BE16">
+        <v>6.75</v>
+      </c>
+      <c r="BF16">
+        <v>2.5</v>
+      </c>
+      <c r="BG16">
+        <v>1.24</v>
+      </c>
+      <c r="BH16">
+        <v>3.65</v>
+      </c>
+      <c r="BI16">
+        <v>1.4</v>
+      </c>
+      <c r="BJ16">
+        <v>2.65</v>
+      </c>
+      <c r="BK16">
+        <v>1.66</v>
+      </c>
+      <c r="BL16">
+        <v>2.07</v>
+      </c>
+      <c r="BM16">
+        <v>2.05</v>
+      </c>
+      <c r="BN16">
+        <v>1.68</v>
+      </c>
+      <c r="BO16">
+        <v>2.55</v>
+      </c>
+      <c r="BP16">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7785189</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45753.59375</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>4</v>
+      </c>
+      <c r="O17" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q17">
+        <v>2.25</v>
+      </c>
+      <c r="R17">
+        <v>2.3</v>
+      </c>
+      <c r="S17">
+        <v>5</v>
+      </c>
+      <c r="T17">
+        <v>1.36</v>
+      </c>
+      <c r="U17">
+        <v>3</v>
+      </c>
+      <c r="V17">
+        <v>2.63</v>
+      </c>
+      <c r="W17">
+        <v>1.44</v>
+      </c>
+      <c r="X17">
+        <v>7</v>
+      </c>
+      <c r="Y17">
+        <v>1.1</v>
+      </c>
+      <c r="Z17">
+        <v>1.69</v>
+      </c>
+      <c r="AA17">
+        <v>4</v>
+      </c>
+      <c r="AB17">
+        <v>4.33</v>
+      </c>
+      <c r="AC17">
+        <v>1.04</v>
+      </c>
+      <c r="AD17">
+        <v>10</v>
+      </c>
+      <c r="AE17">
+        <v>1.25</v>
+      </c>
+      <c r="AF17">
+        <v>3.85</v>
+      </c>
+      <c r="AG17">
+        <v>1.79</v>
+      </c>
+      <c r="AH17">
+        <v>1.95</v>
+      </c>
+      <c r="AI17">
+        <v>1.75</v>
+      </c>
+      <c r="AJ17">
+        <v>2</v>
+      </c>
+      <c r="AK17">
+        <v>1.18</v>
+      </c>
+      <c r="AL17">
+        <v>1.2</v>
+      </c>
+      <c r="AM17">
+        <v>2.15</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>3</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>4</v>
+      </c>
+      <c r="AV17">
+        <v>2</v>
+      </c>
+      <c r="AW17">
+        <v>14</v>
+      </c>
+      <c r="AX17">
+        <v>4</v>
+      </c>
+      <c r="AY17">
+        <v>23</v>
+      </c>
+      <c r="AZ17">
+        <v>8</v>
+      </c>
+      <c r="BA17">
+        <v>5</v>
+      </c>
+      <c r="BB17">
+        <v>1</v>
+      </c>
+      <c r="BC17">
+        <v>6</v>
+      </c>
+      <c r="BD17">
+        <v>1.5</v>
+      </c>
+      <c r="BE17">
+        <v>6.75</v>
+      </c>
+      <c r="BF17">
+        <v>2.9</v>
+      </c>
+      <c r="BG17">
+        <v>1.23</v>
+      </c>
+      <c r="BH17">
+        <v>3.7</v>
+      </c>
+      <c r="BI17">
+        <v>1.38</v>
+      </c>
+      <c r="BJ17">
+        <v>2.7</v>
+      </c>
+      <c r="BK17">
+        <v>1.64</v>
+      </c>
+      <c r="BL17">
+        <v>2.1</v>
+      </c>
+      <c r="BM17">
+        <v>1.98</v>
+      </c>
+      <c r="BN17">
+        <v>1.72</v>
+      </c>
+      <c r="BO17">
+        <v>2.48</v>
+      </c>
+      <c r="BP17">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -3341,13 +3341,13 @@
         <v>9</v>
       </c>
       <c r="BA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB13">
         <v>3</v>
       </c>
       <c r="BC13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD13">
         <v>1.82</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="112">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>['39', '74', '83']</t>
+  </si>
+  <si>
+    <t>['39', '76']</t>
   </si>
   <si>
     <t>['39', '49']</t>
@@ -708,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP17"/>
+  <dimension ref="A1:BP18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -964,7 +967,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1376,7 +1379,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1582,7 +1585,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1788,7 +1791,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -1994,7 +1997,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2406,7 +2409,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3024,7 +3027,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3230,7 +3233,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3311,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3642,7 +3645,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -3848,7 +3851,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4054,7 +4057,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4211,6 +4214,212 @@
       </c>
       <c r="BP17">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7785190</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45756.58333333334</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+      <c r="G18" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+      <c r="O18" t="s">
+        <v>100</v>
+      </c>
+      <c r="P18" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q18">
+        <v>3.1</v>
+      </c>
+      <c r="R18">
+        <v>2.1</v>
+      </c>
+      <c r="S18">
+        <v>3.5</v>
+      </c>
+      <c r="T18">
+        <v>1.4</v>
+      </c>
+      <c r="U18">
+        <v>2.75</v>
+      </c>
+      <c r="V18">
+        <v>3</v>
+      </c>
+      <c r="W18">
+        <v>1.36</v>
+      </c>
+      <c r="X18">
+        <v>8</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>2.37</v>
+      </c>
+      <c r="AA18">
+        <v>3.28</v>
+      </c>
+      <c r="AB18">
+        <v>2.92</v>
+      </c>
+      <c r="AC18">
+        <v>1.06</v>
+      </c>
+      <c r="AD18">
+        <v>8.5</v>
+      </c>
+      <c r="AE18">
+        <v>1.33</v>
+      </c>
+      <c r="AF18">
+        <v>3.25</v>
+      </c>
+      <c r="AG18">
+        <v>1.98</v>
+      </c>
+      <c r="AH18">
+        <v>1.77</v>
+      </c>
+      <c r="AI18">
+        <v>1.75</v>
+      </c>
+      <c r="AJ18">
+        <v>2</v>
+      </c>
+      <c r="AK18">
+        <v>1.42</v>
+      </c>
+      <c r="AL18">
+        <v>1.32</v>
+      </c>
+      <c r="AM18">
+        <v>1.5</v>
+      </c>
+      <c r="AN18">
+        <v>3</v>
+      </c>
+      <c r="AO18">
+        <v>1</v>
+      </c>
+      <c r="AP18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>0.5</v>
+      </c>
+      <c r="AR18">
+        <v>0.92</v>
+      </c>
+      <c r="AS18">
+        <v>1.2</v>
+      </c>
+      <c r="AT18">
+        <v>2.12</v>
+      </c>
+      <c r="AU18">
+        <v>5</v>
+      </c>
+      <c r="AV18">
+        <v>4</v>
+      </c>
+      <c r="AW18">
+        <v>8</v>
+      </c>
+      <c r="AX18">
+        <v>5</v>
+      </c>
+      <c r="AY18">
+        <v>14</v>
+      </c>
+      <c r="AZ18">
+        <v>10</v>
+      </c>
+      <c r="BA18">
+        <v>6</v>
+      </c>
+      <c r="BB18">
+        <v>5</v>
+      </c>
+      <c r="BC18">
+        <v>11</v>
+      </c>
+      <c r="BD18">
+        <v>1.93</v>
+      </c>
+      <c r="BE18">
+        <v>6.75</v>
+      </c>
+      <c r="BF18">
+        <v>2.05</v>
+      </c>
+      <c r="BG18">
+        <v>1.21</v>
+      </c>
+      <c r="BH18">
+        <v>3.9</v>
+      </c>
+      <c r="BI18">
+        <v>1.38</v>
+      </c>
+      <c r="BJ18">
+        <v>2.8</v>
+      </c>
+      <c r="BK18">
+        <v>1.63</v>
+      </c>
+      <c r="BL18">
+        <v>2.15</v>
+      </c>
+      <c r="BM18">
+        <v>1.96</v>
+      </c>
+      <c r="BN18">
+        <v>1.74</v>
+      </c>
+      <c r="BO18">
+        <v>2.43</v>
+      </c>
+      <c r="BP18">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="116">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -319,6 +319,12 @@
     <t>['39', '76']</t>
   </si>
   <si>
+    <t>['47', '58', '66']</t>
+  </si>
+  <si>
+    <t>['45+3', '70']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -350,6 +356,12 @@
   </si>
   <si>
     <t>['29']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
 </sst>
 </file>
@@ -711,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP18"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -967,7 +979,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1379,7 +1391,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1585,7 +1597,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1791,7 +1803,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -1997,7 +2009,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2409,7 +2421,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3027,7 +3039,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3233,7 +3245,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3645,7 +3657,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -3726,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="AQ15">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -3851,7 +3863,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4057,7 +4069,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4420,6 +4432,418 @@
       </c>
       <c r="BP18">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7785191</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45757.58333333334</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>3</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
+      <c r="O19" t="s">
+        <v>101</v>
+      </c>
+      <c r="P19" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q19">
+        <v>1.91</v>
+      </c>
+      <c r="R19">
+        <v>2.63</v>
+      </c>
+      <c r="S19">
+        <v>6</v>
+      </c>
+      <c r="T19">
+        <v>1.25</v>
+      </c>
+      <c r="U19">
+        <v>3.75</v>
+      </c>
+      <c r="V19">
+        <v>2.2</v>
+      </c>
+      <c r="W19">
+        <v>1.62</v>
+      </c>
+      <c r="X19">
+        <v>5</v>
+      </c>
+      <c r="Y19">
+        <v>1.17</v>
+      </c>
+      <c r="Z19">
+        <v>1.43</v>
+      </c>
+      <c r="AA19">
+        <v>4.9</v>
+      </c>
+      <c r="AB19">
+        <v>6</v>
+      </c>
+      <c r="AC19">
+        <v>1.01</v>
+      </c>
+      <c r="AD19">
+        <v>17</v>
+      </c>
+      <c r="AE19">
+        <v>1.1</v>
+      </c>
+      <c r="AF19">
+        <v>5.15</v>
+      </c>
+      <c r="AG19">
+        <v>1.47</v>
+      </c>
+      <c r="AH19">
+        <v>2.57</v>
+      </c>
+      <c r="AI19">
+        <v>1.62</v>
+      </c>
+      <c r="AJ19">
+        <v>2.2</v>
+      </c>
+      <c r="AK19">
+        <v>1.11</v>
+      </c>
+      <c r="AL19">
+        <v>1.17</v>
+      </c>
+      <c r="AM19">
+        <v>2.82</v>
+      </c>
+      <c r="AN19">
+        <v>3</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>3</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>2.02</v>
+      </c>
+      <c r="AS19">
+        <v>1.76</v>
+      </c>
+      <c r="AT19">
+        <v>3.78</v>
+      </c>
+      <c r="AU19">
+        <v>7</v>
+      </c>
+      <c r="AV19">
+        <v>5</v>
+      </c>
+      <c r="AW19">
+        <v>11</v>
+      </c>
+      <c r="AX19">
+        <v>10</v>
+      </c>
+      <c r="AY19">
+        <v>20</v>
+      </c>
+      <c r="AZ19">
+        <v>18</v>
+      </c>
+      <c r="BA19">
+        <v>11</v>
+      </c>
+      <c r="BB19">
+        <v>9</v>
+      </c>
+      <c r="BC19">
+        <v>20</v>
+      </c>
+      <c r="BD19">
+        <v>1.35</v>
+      </c>
+      <c r="BE19">
+        <v>7.5</v>
+      </c>
+      <c r="BF19">
+        <v>3.45</v>
+      </c>
+      <c r="BG19">
+        <v>1.23</v>
+      </c>
+      <c r="BH19">
+        <v>3.65</v>
+      </c>
+      <c r="BI19">
+        <v>1.4</v>
+      </c>
+      <c r="BJ19">
+        <v>2.65</v>
+      </c>
+      <c r="BK19">
+        <v>1.65</v>
+      </c>
+      <c r="BL19">
+        <v>2.08</v>
+      </c>
+      <c r="BM19">
+        <v>2</v>
+      </c>
+      <c r="BN19">
+        <v>1.71</v>
+      </c>
+      <c r="BO19">
+        <v>2.55</v>
+      </c>
+      <c r="BP19">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7785192</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45757.58333333334</v>
+      </c>
+      <c r="F20">
+        <v>17</v>
+      </c>
+      <c r="G20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="s">
+        <v>102</v>
+      </c>
+      <c r="P20" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q20">
+        <v>1.9</v>
+      </c>
+      <c r="R20">
+        <v>2.5</v>
+      </c>
+      <c r="S20">
+        <v>5.25</v>
+      </c>
+      <c r="T20">
+        <v>1.25</v>
+      </c>
+      <c r="U20">
+        <v>3.65</v>
+      </c>
+      <c r="V20">
+        <v>2.1</v>
+      </c>
+      <c r="W20">
+        <v>1.65</v>
+      </c>
+      <c r="X20">
+        <v>4.5</v>
+      </c>
+      <c r="Y20">
+        <v>1.13</v>
+      </c>
+      <c r="Z20">
+        <v>1.44</v>
+      </c>
+      <c r="AA20">
+        <v>4.5</v>
+      </c>
+      <c r="AB20">
+        <v>6.6</v>
+      </c>
+      <c r="AC20">
+        <v>1.01</v>
+      </c>
+      <c r="AD20">
+        <v>17</v>
+      </c>
+      <c r="AE20">
+        <v>1.15</v>
+      </c>
+      <c r="AF20">
+        <v>5.25</v>
+      </c>
+      <c r="AG20">
+        <v>1.48</v>
+      </c>
+      <c r="AH20">
+        <v>2.54</v>
+      </c>
+      <c r="AI20">
+        <v>1.57</v>
+      </c>
+      <c r="AJ20">
+        <v>2.2</v>
+      </c>
+      <c r="AK20">
+        <v>1.12</v>
+      </c>
+      <c r="AL20">
+        <v>1.15</v>
+      </c>
+      <c r="AM20">
+        <v>2.55</v>
+      </c>
+      <c r="AN20">
+        <v>3</v>
+      </c>
+      <c r="AO20">
+        <v>3</v>
+      </c>
+      <c r="AP20">
+        <v>3</v>
+      </c>
+      <c r="AQ20">
+        <v>1.5</v>
+      </c>
+      <c r="AR20">
+        <v>1.82</v>
+      </c>
+      <c r="AS20">
+        <v>2.56</v>
+      </c>
+      <c r="AT20">
+        <v>4.38</v>
+      </c>
+      <c r="AU20">
+        <v>4</v>
+      </c>
+      <c r="AV20">
+        <v>4</v>
+      </c>
+      <c r="AW20">
+        <v>14</v>
+      </c>
+      <c r="AX20">
+        <v>7</v>
+      </c>
+      <c r="AY20">
+        <v>22</v>
+      </c>
+      <c r="AZ20">
+        <v>12</v>
+      </c>
+      <c r="BA20">
+        <v>9</v>
+      </c>
+      <c r="BB20">
+        <v>10</v>
+      </c>
+      <c r="BC20">
+        <v>19</v>
+      </c>
+      <c r="BD20">
+        <v>1.44</v>
+      </c>
+      <c r="BE20">
+        <v>7</v>
+      </c>
+      <c r="BF20">
+        <v>3.15</v>
+      </c>
+      <c r="BG20">
+        <v>1.24</v>
+      </c>
+      <c r="BH20">
+        <v>3.55</v>
+      </c>
+      <c r="BI20">
+        <v>1.42</v>
+      </c>
+      <c r="BJ20">
+        <v>2.63</v>
+      </c>
+      <c r="BK20">
+        <v>1.68</v>
+      </c>
+      <c r="BL20">
+        <v>2.05</v>
+      </c>
+      <c r="BM20">
+        <v>2.05</v>
+      </c>
+      <c r="BN20">
+        <v>1.68</v>
+      </c>
+      <c r="BO20">
+        <v>2.55</v>
+      </c>
+      <c r="BP20">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="196">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t>['74']</t>
+  </si>
+  <si>
+    <t>['5', '40', '47']</t>
   </si>
   <si>
     <t>['39', '49']</t>
@@ -960,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP79"/>
+  <dimension ref="A1:BP80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1216,7 +1219,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1503,7 +1506,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ3">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1628,7 +1631,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1834,7 +1837,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2040,7 +2043,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2246,7 +2249,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2658,7 +2661,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -2942,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ10">
         <v>0.8</v>
@@ -3276,7 +3279,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3482,7 +3485,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3894,7 +3897,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4100,7 +4103,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4306,7 +4309,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4718,7 +4721,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4924,7 +4927,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5130,7 +5133,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5336,7 +5339,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5542,7 +5545,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5623,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR23">
         <v>1.32</v>
@@ -5748,7 +5751,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5954,7 +5957,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6160,7 +6163,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6366,7 +6369,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6572,7 +6575,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7062,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ30">
         <v>0.4</v>
@@ -7190,7 +7193,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7602,7 +7605,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8014,7 +8017,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8220,7 +8223,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8426,7 +8429,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8632,7 +8635,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9044,7 +9047,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9125,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR40">
         <v>2.08</v>
@@ -9456,7 +9459,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9662,7 +9665,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10486,7 +10489,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10692,7 +10695,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10898,7 +10901,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q49">
         <v>3.4</v>
@@ -11104,7 +11107,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11516,7 +11519,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11722,7 +11725,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11928,7 +11931,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -12340,7 +12343,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12546,7 +12549,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12752,7 +12755,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13164,7 +13167,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13370,7 +13373,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13654,7 +13657,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ62">
         <v>2</v>
@@ -13782,7 +13785,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14194,7 +14197,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14400,7 +14403,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14606,7 +14609,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14687,7 +14690,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ67">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AR67">
         <v>1.35</v>
@@ -14812,7 +14815,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15018,7 +15021,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15224,7 +15227,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15302,7 +15305,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ70">
         <v>2.5</v>
@@ -15430,7 +15433,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15636,7 +15639,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15842,7 +15845,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16048,7 +16051,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16254,7 +16257,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16460,7 +16463,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16666,7 +16669,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16872,7 +16875,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17078,7 +17081,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17235,6 +17238,212 @@
       </c>
       <c r="BP79">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7785254</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45829.54166666666</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>3</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>3</v>
+      </c>
+      <c r="O80" t="s">
+        <v>139</v>
+      </c>
+      <c r="P80" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q80">
+        <v>1.95</v>
+      </c>
+      <c r="R80">
+        <v>2.63</v>
+      </c>
+      <c r="S80">
+        <v>5</v>
+      </c>
+      <c r="T80">
+        <v>1.22</v>
+      </c>
+      <c r="U80">
+        <v>4</v>
+      </c>
+      <c r="V80">
+        <v>2</v>
+      </c>
+      <c r="W80">
+        <v>1.73</v>
+      </c>
+      <c r="X80">
+        <v>4.33</v>
+      </c>
+      <c r="Y80">
+        <v>1.2</v>
+      </c>
+      <c r="Z80">
+        <v>1.44</v>
+      </c>
+      <c r="AA80">
+        <v>4.6</v>
+      </c>
+      <c r="AB80">
+        <v>4.8</v>
+      </c>
+      <c r="AC80">
+        <v>1.02</v>
+      </c>
+      <c r="AD80">
+        <v>21</v>
+      </c>
+      <c r="AE80">
+        <v>1.12</v>
+      </c>
+      <c r="AF80">
+        <v>5.75</v>
+      </c>
+      <c r="AG80">
+        <v>1.42</v>
+      </c>
+      <c r="AH80">
+        <v>2.74</v>
+      </c>
+      <c r="AI80">
+        <v>1.53</v>
+      </c>
+      <c r="AJ80">
+        <v>2.38</v>
+      </c>
+      <c r="AK80">
+        <v>1.15</v>
+      </c>
+      <c r="AL80">
+        <v>1.18</v>
+      </c>
+      <c r="AM80">
+        <v>2.5</v>
+      </c>
+      <c r="AN80">
+        <v>2.25</v>
+      </c>
+      <c r="AO80">
+        <v>2.25</v>
+      </c>
+      <c r="AP80">
+        <v>2.4</v>
+      </c>
+      <c r="AQ80">
+        <v>1.8</v>
+      </c>
+      <c r="AR80">
+        <v>2.02</v>
+      </c>
+      <c r="AS80">
+        <v>1.79</v>
+      </c>
+      <c r="AT80">
+        <v>3.81</v>
+      </c>
+      <c r="AU80">
+        <v>5</v>
+      </c>
+      <c r="AV80">
+        <v>0</v>
+      </c>
+      <c r="AW80">
+        <v>0</v>
+      </c>
+      <c r="AX80">
+        <v>0</v>
+      </c>
+      <c r="AY80">
+        <v>5</v>
+      </c>
+      <c r="AZ80">
+        <v>0</v>
+      </c>
+      <c r="BA80">
+        <v>9</v>
+      </c>
+      <c r="BB80">
+        <v>2</v>
+      </c>
+      <c r="BC80">
+        <v>11</v>
+      </c>
+      <c r="BD80">
+        <v>1.44</v>
+      </c>
+      <c r="BE80">
+        <v>7</v>
+      </c>
+      <c r="BF80">
+        <v>3.05</v>
+      </c>
+      <c r="BG80">
+        <v>1.17</v>
+      </c>
+      <c r="BH80">
+        <v>4.3</v>
+      </c>
+      <c r="BI80">
+        <v>1.3</v>
+      </c>
+      <c r="BJ80">
+        <v>3.05</v>
+      </c>
+      <c r="BK80">
+        <v>1.5</v>
+      </c>
+      <c r="BL80">
+        <v>2.35</v>
+      </c>
+      <c r="BM80">
+        <v>1.82</v>
+      </c>
+      <c r="BN80">
+        <v>1.86</v>
+      </c>
+      <c r="BO80">
+        <v>2.23</v>
+      </c>
+      <c r="BP80">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -436,6 +436,27 @@
     <t>['5', '40', '47']</t>
   </si>
   <si>
+    <t>['23', '42']</t>
+  </si>
+  <si>
+    <t>['8', '58', '86']</t>
+  </si>
+  <si>
+    <t>['21', '33', '35', '84']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['53', '59', '70', '82', '9002']</t>
+  </si>
+  <si>
+    <t>['7', '60', '80']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -602,6 +623,18 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['7', '80', '84']</t>
+  </si>
+  <si>
+    <t>['4503']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
+    <t>['21', '26', '47']</t>
   </si>
 </sst>
 </file>
@@ -963,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP80"/>
+  <dimension ref="A1:BP87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1219,7 +1252,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1300,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1631,7 +1664,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1709,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ4">
         <v>2.5</v>
@@ -1837,7 +1870,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1915,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
         <v>1.43</v>
@@ -2043,7 +2076,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2121,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ6">
         <v>0.6</v>
@@ -2249,7 +2282,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2661,7 +2694,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3154,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3279,7 +3312,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3360,7 +3393,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3485,7 +3518,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3772,7 +3805,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3897,7 +3930,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -3978,7 +4011,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ15">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4103,7 +4136,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4181,10 +4214,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4309,7 +4342,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4387,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ17">
         <v>0.4</v>
@@ -4721,7 +4754,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4799,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ19">
         <v>1.43</v>
@@ -4927,7 +4960,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5008,7 +5041,7 @@
         <v>2</v>
       </c>
       <c r="AQ20">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR20">
         <v>1.82</v>
@@ -5133,7 +5166,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5339,7 +5372,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5417,10 +5450,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR22">
         <v>1.7</v>
@@ -5545,7 +5578,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5751,7 +5784,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5957,7 +5990,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6163,7 +6196,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6241,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ26">
         <v>2.5</v>
@@ -6369,7 +6402,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6447,7 +6480,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
         <v>1.8</v>
@@ -6575,7 +6608,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6862,7 +6895,7 @@
         <v>2</v>
       </c>
       <c r="AQ29">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7193,7 +7226,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7274,7 +7307,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR31">
         <v>1.79</v>
@@ -7480,7 +7513,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR32">
         <v>1.53</v>
@@ -7605,7 +7638,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7683,7 +7716,7 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ33">
         <v>1.17</v>
@@ -8017,7 +8050,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8098,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.51</v>
@@ -8223,7 +8256,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8301,10 +8334,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR36">
         <v>2</v>
@@ -8429,7 +8462,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8507,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -8635,7 +8668,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8919,7 +8952,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ39">
         <v>0.4</v>
@@ -9047,7 +9080,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9125,7 +9158,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ40">
         <v>1.8</v>
@@ -9331,7 +9364,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ41">
         <v>1.8</v>
@@ -9459,7 +9492,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9665,7 +9698,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10158,7 +10191,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR45">
         <v>2.27</v>
@@ -10364,7 +10397,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR46">
         <v>1.95</v>
@@ -10489,7 +10522,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10570,7 +10603,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ47">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR47">
         <v>1.44</v>
@@ -10695,7 +10728,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10773,10 +10806,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -10901,7 +10934,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="Q49">
         <v>3.4</v>
@@ -10979,10 +11012,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR49">
         <v>1.56</v>
@@ -11107,7 +11140,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11519,7 +11552,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11725,7 +11758,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11803,7 +11836,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ53">
         <v>0.6</v>
@@ -11931,7 +11964,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -12343,7 +12376,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12549,7 +12582,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12630,7 +12663,7 @@
         <v>0</v>
       </c>
       <c r="AQ57">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -12755,7 +12788,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13167,7 +13200,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13245,7 +13278,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AQ60">
         <v>0.8</v>
@@ -13373,7 +13406,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13454,7 +13487,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AR61">
         <v>1.27</v>
@@ -13660,7 +13693,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ62">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR62">
         <v>2.13</v>
@@ -13785,7 +13818,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13863,10 +13896,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ63">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR63">
         <v>1.3</v>
@@ -14072,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR64">
         <v>1.85</v>
@@ -14197,7 +14230,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14275,7 +14308,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ65">
         <v>2.5</v>
@@ -14403,7 +14436,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14484,7 +14517,7 @@
         <v>3</v>
       </c>
       <c r="AQ66">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.95</v>
@@ -14609,7 +14642,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14815,7 +14848,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -14893,7 +14926,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ68">
         <v>1.17</v>
@@ -15021,7 +15054,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15102,7 +15135,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ69">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR69">
         <v>1.11</v>
@@ -15227,7 +15260,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15433,7 +15466,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15514,7 +15547,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AR71">
         <v>1.99</v>
@@ -15639,7 +15672,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15845,7 +15878,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16051,7 +16084,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16257,7 +16290,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16463,7 +16496,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16669,7 +16702,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16875,7 +16908,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17081,7 +17114,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17444,6 +17477,1448 @@
       </c>
       <c r="BP80">
         <v>1.57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7785261</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45830.39583333334</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81" t="s">
+        <v>72</v>
+      </c>
+      <c r="H81" t="s">
+        <v>75</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>3</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>3</v>
+      </c>
+      <c r="N81">
+        <v>5</v>
+      </c>
+      <c r="O81" t="s">
+        <v>140</v>
+      </c>
+      <c r="P81" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q81">
+        <v>3</v>
+      </c>
+      <c r="R81">
+        <v>2.3</v>
+      </c>
+      <c r="S81">
+        <v>3.25</v>
+      </c>
+      <c r="T81">
+        <v>1.33</v>
+      </c>
+      <c r="U81">
+        <v>3.25</v>
+      </c>
+      <c r="V81">
+        <v>2.5</v>
+      </c>
+      <c r="W81">
+        <v>1.5</v>
+      </c>
+      <c r="X81">
+        <v>6</v>
+      </c>
+      <c r="Y81">
+        <v>1.13</v>
+      </c>
+      <c r="Z81">
+        <v>2.37</v>
+      </c>
+      <c r="AA81">
+        <v>3.29</v>
+      </c>
+      <c r="AB81">
+        <v>2.54</v>
+      </c>
+      <c r="AC81">
+        <v>1.04</v>
+      </c>
+      <c r="AD81">
+        <v>10</v>
+      </c>
+      <c r="AE81">
+        <v>1.22</v>
+      </c>
+      <c r="AF81">
+        <v>4</v>
+      </c>
+      <c r="AG81">
+        <v>1.59</v>
+      </c>
+      <c r="AH81">
+        <v>2.2</v>
+      </c>
+      <c r="AI81">
+        <v>1.62</v>
+      </c>
+      <c r="AJ81">
+        <v>2.2</v>
+      </c>
+      <c r="AK81">
+        <v>1.44</v>
+      </c>
+      <c r="AL81">
+        <v>1.28</v>
+      </c>
+      <c r="AM81">
+        <v>1.53</v>
+      </c>
+      <c r="AN81">
+        <v>1</v>
+      </c>
+      <c r="AO81">
+        <v>1.4</v>
+      </c>
+      <c r="AP81">
+        <v>0.8</v>
+      </c>
+      <c r="AQ81">
+        <v>1.67</v>
+      </c>
+      <c r="AR81">
+        <v>2.19</v>
+      </c>
+      <c r="AS81">
+        <v>1.51</v>
+      </c>
+      <c r="AT81">
+        <v>3.7</v>
+      </c>
+      <c r="AU81">
+        <v>8</v>
+      </c>
+      <c r="AV81">
+        <v>7</v>
+      </c>
+      <c r="AW81">
+        <v>7</v>
+      </c>
+      <c r="AX81">
+        <v>11</v>
+      </c>
+      <c r="AY81">
+        <v>15</v>
+      </c>
+      <c r="AZ81">
+        <v>18</v>
+      </c>
+      <c r="BA81">
+        <v>5</v>
+      </c>
+      <c r="BB81">
+        <v>7</v>
+      </c>
+      <c r="BC81">
+        <v>12</v>
+      </c>
+      <c r="BD81">
+        <v>1.96</v>
+      </c>
+      <c r="BE81">
+        <v>6.75</v>
+      </c>
+      <c r="BF81">
+        <v>1.98</v>
+      </c>
+      <c r="BG81">
+        <v>1.22</v>
+      </c>
+      <c r="BH81">
+        <v>3.8</v>
+      </c>
+      <c r="BI81">
+        <v>1.38</v>
+      </c>
+      <c r="BJ81">
+        <v>2.7</v>
+      </c>
+      <c r="BK81">
+        <v>1.65</v>
+      </c>
+      <c r="BL81">
+        <v>2.1</v>
+      </c>
+      <c r="BM81">
+        <v>1.98</v>
+      </c>
+      <c r="BN81">
+        <v>1.72</v>
+      </c>
+      <c r="BO81">
+        <v>2.48</v>
+      </c>
+      <c r="BP81">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7785258</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F82">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>82</v>
+      </c>
+      <c r="H82" t="s">
+        <v>83</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>3</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>3</v>
+      </c>
+      <c r="O82" t="s">
+        <v>141</v>
+      </c>
+      <c r="P82" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q82">
+        <v>1.8</v>
+      </c>
+      <c r="R82">
+        <v>2.63</v>
+      </c>
+      <c r="S82">
+        <v>7</v>
+      </c>
+      <c r="T82">
+        <v>1.25</v>
+      </c>
+      <c r="U82">
+        <v>3.75</v>
+      </c>
+      <c r="V82">
+        <v>2.25</v>
+      </c>
+      <c r="W82">
+        <v>1.57</v>
+      </c>
+      <c r="X82">
+        <v>5.5</v>
+      </c>
+      <c r="Y82">
+        <v>1.14</v>
+      </c>
+      <c r="Z82">
+        <v>1.34</v>
+      </c>
+      <c r="AA82">
+        <v>4.5</v>
+      </c>
+      <c r="AB82">
+        <v>6.5</v>
+      </c>
+      <c r="AC82">
+        <v>1.01</v>
+      </c>
+      <c r="AD82">
+        <v>17</v>
+      </c>
+      <c r="AE82">
+        <v>1.17</v>
+      </c>
+      <c r="AF82">
+        <v>5</v>
+      </c>
+      <c r="AG82">
+        <v>1.5</v>
+      </c>
+      <c r="AH82">
+        <v>2.48</v>
+      </c>
+      <c r="AI82">
+        <v>1.8</v>
+      </c>
+      <c r="AJ82">
+        <v>1.95</v>
+      </c>
+      <c r="AK82">
+        <v>1.1</v>
+      </c>
+      <c r="AL82">
+        <v>1.16</v>
+      </c>
+      <c r="AM82">
+        <v>2.9</v>
+      </c>
+      <c r="AN82">
+        <v>3</v>
+      </c>
+      <c r="AO82">
+        <v>0</v>
+      </c>
+      <c r="AP82">
+        <v>3</v>
+      </c>
+      <c r="AQ82">
+        <v>0</v>
+      </c>
+      <c r="AR82">
+        <v>2.07</v>
+      </c>
+      <c r="AS82">
+        <v>0.95</v>
+      </c>
+      <c r="AT82">
+        <v>3.02</v>
+      </c>
+      <c r="AU82">
+        <v>11</v>
+      </c>
+      <c r="AV82">
+        <v>8</v>
+      </c>
+      <c r="AW82">
+        <v>2</v>
+      </c>
+      <c r="AX82">
+        <v>11</v>
+      </c>
+      <c r="AY82">
+        <v>13</v>
+      </c>
+      <c r="AZ82">
+        <v>19</v>
+      </c>
+      <c r="BA82">
+        <v>3</v>
+      </c>
+      <c r="BB82">
+        <v>8</v>
+      </c>
+      <c r="BC82">
+        <v>11</v>
+      </c>
+      <c r="BD82">
+        <v>1.29</v>
+      </c>
+      <c r="BE82">
+        <v>8</v>
+      </c>
+      <c r="BF82">
+        <v>3.9</v>
+      </c>
+      <c r="BG82">
+        <v>1.2</v>
+      </c>
+      <c r="BH82">
+        <v>4</v>
+      </c>
+      <c r="BI82">
+        <v>1.34</v>
+      </c>
+      <c r="BJ82">
+        <v>2.9</v>
+      </c>
+      <c r="BK82">
+        <v>1.57</v>
+      </c>
+      <c r="BL82">
+        <v>2.23</v>
+      </c>
+      <c r="BM82">
+        <v>1.9</v>
+      </c>
+      <c r="BN82">
+        <v>1.79</v>
+      </c>
+      <c r="BO82">
+        <v>2.32</v>
+      </c>
+      <c r="BP82">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7785257</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>84</v>
+      </c>
+      <c r="H83" t="s">
+        <v>79</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>4</v>
+      </c>
+      <c r="L83">
+        <v>4</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>5</v>
+      </c>
+      <c r="O83" t="s">
+        <v>142</v>
+      </c>
+      <c r="P83" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q83">
+        <v>4.75</v>
+      </c>
+      <c r="R83">
+        <v>2.4</v>
+      </c>
+      <c r="S83">
+        <v>2.2</v>
+      </c>
+      <c r="T83">
+        <v>1.3</v>
+      </c>
+      <c r="U83">
+        <v>3.4</v>
+      </c>
+      <c r="V83">
+        <v>2.38</v>
+      </c>
+      <c r="W83">
+        <v>1.53</v>
+      </c>
+      <c r="X83">
+        <v>6</v>
+      </c>
+      <c r="Y83">
+        <v>1.13</v>
+      </c>
+      <c r="Z83">
+        <v>4.2</v>
+      </c>
+      <c r="AA83">
+        <v>3.78</v>
+      </c>
+      <c r="AB83">
+        <v>1.62</v>
+      </c>
+      <c r="AC83">
+        <v>1.04</v>
+      </c>
+      <c r="AD83">
+        <v>10</v>
+      </c>
+      <c r="AE83">
+        <v>1.2</v>
+      </c>
+      <c r="AF83">
+        <v>4.33</v>
+      </c>
+      <c r="AG83">
+        <v>1.56</v>
+      </c>
+      <c r="AH83">
+        <v>2.27</v>
+      </c>
+      <c r="AI83">
+        <v>1.67</v>
+      </c>
+      <c r="AJ83">
+        <v>2.1</v>
+      </c>
+      <c r="AK83">
+        <v>2.05</v>
+      </c>
+      <c r="AL83">
+        <v>1.23</v>
+      </c>
+      <c r="AM83">
+        <v>1.21</v>
+      </c>
+      <c r="AN83">
+        <v>0.75</v>
+      </c>
+      <c r="AO83">
+        <v>2</v>
+      </c>
+      <c r="AP83">
+        <v>1.2</v>
+      </c>
+      <c r="AQ83">
+        <v>1.67</v>
+      </c>
+      <c r="AR83">
+        <v>1.44</v>
+      </c>
+      <c r="AS83">
+        <v>1.21</v>
+      </c>
+      <c r="AT83">
+        <v>2.65</v>
+      </c>
+      <c r="AU83">
+        <v>9</v>
+      </c>
+      <c r="AV83">
+        <v>6</v>
+      </c>
+      <c r="AW83">
+        <v>4</v>
+      </c>
+      <c r="AX83">
+        <v>7</v>
+      </c>
+      <c r="AY83">
+        <v>13</v>
+      </c>
+      <c r="AZ83">
+        <v>13</v>
+      </c>
+      <c r="BA83">
+        <v>3</v>
+      </c>
+      <c r="BB83">
+        <v>9</v>
+      </c>
+      <c r="BC83">
+        <v>12</v>
+      </c>
+      <c r="BD83">
+        <v>3.15</v>
+      </c>
+      <c r="BE83">
+        <v>7</v>
+      </c>
+      <c r="BF83">
+        <v>1.42</v>
+      </c>
+      <c r="BG83">
+        <v>1.22</v>
+      </c>
+      <c r="BH83">
+        <v>3.8</v>
+      </c>
+      <c r="BI83">
+        <v>1.38</v>
+      </c>
+      <c r="BJ83">
+        <v>2.8</v>
+      </c>
+      <c r="BK83">
+        <v>1.61</v>
+      </c>
+      <c r="BL83">
+        <v>2.15</v>
+      </c>
+      <c r="BM83">
+        <v>1.97</v>
+      </c>
+      <c r="BN83">
+        <v>1.74</v>
+      </c>
+      <c r="BO83">
+        <v>2.43</v>
+      </c>
+      <c r="BP83">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7785259</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84" t="s">
+        <v>143</v>
+      </c>
+      <c r="P84" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q84">
+        <v>2.1</v>
+      </c>
+      <c r="R84">
+        <v>2.4</v>
+      </c>
+      <c r="S84">
+        <v>5</v>
+      </c>
+      <c r="T84">
+        <v>1.29</v>
+      </c>
+      <c r="U84">
+        <v>3.5</v>
+      </c>
+      <c r="V84">
+        <v>2.38</v>
+      </c>
+      <c r="W84">
+        <v>1.53</v>
+      </c>
+      <c r="X84">
+        <v>5.5</v>
+      </c>
+      <c r="Y84">
+        <v>1.14</v>
+      </c>
+      <c r="Z84">
+        <v>1.56</v>
+      </c>
+      <c r="AA84">
+        <v>3.9</v>
+      </c>
+      <c r="AB84">
+        <v>4.5</v>
+      </c>
+      <c r="AC84">
+        <v>1.03</v>
+      </c>
+      <c r="AD84">
+        <v>11</v>
+      </c>
+      <c r="AE84">
+        <v>1.2</v>
+      </c>
+      <c r="AF84">
+        <v>4.33</v>
+      </c>
+      <c r="AG84">
+        <v>1.58</v>
+      </c>
+      <c r="AH84">
+        <v>2.22</v>
+      </c>
+      <c r="AI84">
+        <v>1.67</v>
+      </c>
+      <c r="AJ84">
+        <v>2.1</v>
+      </c>
+      <c r="AK84">
+        <v>1.18</v>
+      </c>
+      <c r="AL84">
+        <v>1.22</v>
+      </c>
+      <c r="AM84">
+        <v>2.25</v>
+      </c>
+      <c r="AN84">
+        <v>1</v>
+      </c>
+      <c r="AO84">
+        <v>0.75</v>
+      </c>
+      <c r="AP84">
+        <v>1</v>
+      </c>
+      <c r="AQ84">
+        <v>0.8</v>
+      </c>
+      <c r="AR84">
+        <v>1.74</v>
+      </c>
+      <c r="AS84">
+        <v>1.09</v>
+      </c>
+      <c r="AT84">
+        <v>2.83</v>
+      </c>
+      <c r="AU84">
+        <v>5</v>
+      </c>
+      <c r="AV84">
+        <v>3</v>
+      </c>
+      <c r="AW84">
+        <v>3</v>
+      </c>
+      <c r="AX84">
+        <v>7</v>
+      </c>
+      <c r="AY84">
+        <v>8</v>
+      </c>
+      <c r="AZ84">
+        <v>10</v>
+      </c>
+      <c r="BA84">
+        <v>3</v>
+      </c>
+      <c r="BB84">
+        <v>2</v>
+      </c>
+      <c r="BC84">
+        <v>5</v>
+      </c>
+      <c r="BD84">
+        <v>1.49</v>
+      </c>
+      <c r="BE84">
+        <v>7</v>
+      </c>
+      <c r="BF84">
+        <v>2.9</v>
+      </c>
+      <c r="BG84">
+        <v>1.22</v>
+      </c>
+      <c r="BH84">
+        <v>3.7</v>
+      </c>
+      <c r="BI84">
+        <v>1.38</v>
+      </c>
+      <c r="BJ84">
+        <v>2.7</v>
+      </c>
+      <c r="BK84">
+        <v>1.64</v>
+      </c>
+      <c r="BL84">
+        <v>2.1</v>
+      </c>
+      <c r="BM84">
+        <v>2</v>
+      </c>
+      <c r="BN84">
+        <v>1.71</v>
+      </c>
+      <c r="BO84">
+        <v>2.5</v>
+      </c>
+      <c r="BP84">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7785255</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F85">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>73</v>
+      </c>
+      <c r="H85" t="s">
+        <v>76</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>3</v>
+      </c>
+      <c r="N85">
+        <v>4</v>
+      </c>
+      <c r="O85" t="s">
+        <v>144</v>
+      </c>
+      <c r="P85" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q85">
+        <v>3.75</v>
+      </c>
+      <c r="R85">
+        <v>2.25</v>
+      </c>
+      <c r="S85">
+        <v>2.75</v>
+      </c>
+      <c r="T85">
+        <v>1.36</v>
+      </c>
+      <c r="U85">
+        <v>3</v>
+      </c>
+      <c r="V85">
+        <v>2.63</v>
+      </c>
+      <c r="W85">
+        <v>1.44</v>
+      </c>
+      <c r="X85">
+        <v>7</v>
+      </c>
+      <c r="Y85">
+        <v>1.1</v>
+      </c>
+      <c r="Z85">
+        <v>3.16</v>
+      </c>
+      <c r="AA85">
+        <v>3.25</v>
+      </c>
+      <c r="AB85">
+        <v>2.02</v>
+      </c>
+      <c r="AC85">
+        <v>1.05</v>
+      </c>
+      <c r="AD85">
+        <v>9.5</v>
+      </c>
+      <c r="AE85">
+        <v>1.28</v>
+      </c>
+      <c r="AF85">
+        <v>3.65</v>
+      </c>
+      <c r="AG85">
+        <v>1.79</v>
+      </c>
+      <c r="AH85">
+        <v>1.91</v>
+      </c>
+      <c r="AI85">
+        <v>1.7</v>
+      </c>
+      <c r="AJ85">
+        <v>2.05</v>
+      </c>
+      <c r="AK85">
+        <v>1.71</v>
+      </c>
+      <c r="AL85">
+        <v>1.28</v>
+      </c>
+      <c r="AM85">
+        <v>1.32</v>
+      </c>
+      <c r="AN85">
+        <v>1.75</v>
+      </c>
+      <c r="AO85">
+        <v>1.75</v>
+      </c>
+      <c r="AP85">
+        <v>1.4</v>
+      </c>
+      <c r="AQ85">
+        <v>2</v>
+      </c>
+      <c r="AR85">
+        <v>1.38</v>
+      </c>
+      <c r="AS85">
+        <v>1.15</v>
+      </c>
+      <c r="AT85">
+        <v>2.53</v>
+      </c>
+      <c r="AU85">
+        <v>5</v>
+      </c>
+      <c r="AV85">
+        <v>5</v>
+      </c>
+      <c r="AW85">
+        <v>6</v>
+      </c>
+      <c r="AX85">
+        <v>0</v>
+      </c>
+      <c r="AY85">
+        <v>11</v>
+      </c>
+      <c r="AZ85">
+        <v>5</v>
+      </c>
+      <c r="BA85">
+        <v>6</v>
+      </c>
+      <c r="BB85">
+        <v>2</v>
+      </c>
+      <c r="BC85">
+        <v>8</v>
+      </c>
+      <c r="BD85">
+        <v>2.4</v>
+      </c>
+      <c r="BE85">
+        <v>6.75</v>
+      </c>
+      <c r="BF85">
+        <v>1.68</v>
+      </c>
+      <c r="BG85">
+        <v>1.23</v>
+      </c>
+      <c r="BH85">
+        <v>3.65</v>
+      </c>
+      <c r="BI85">
+        <v>1.41</v>
+      </c>
+      <c r="BJ85">
+        <v>2.65</v>
+      </c>
+      <c r="BK85">
+        <v>1.67</v>
+      </c>
+      <c r="BL85">
+        <v>2.07</v>
+      </c>
+      <c r="BM85">
+        <v>2.02</v>
+      </c>
+      <c r="BN85">
+        <v>1.7</v>
+      </c>
+      <c r="BO85">
+        <v>2.55</v>
+      </c>
+      <c r="BP85">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7785256</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86" t="s">
+        <v>74</v>
+      </c>
+      <c r="H86" t="s">
+        <v>70</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>5</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>5</v>
+      </c>
+      <c r="O86" t="s">
+        <v>145</v>
+      </c>
+      <c r="P86" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q86">
+        <v>2.75</v>
+      </c>
+      <c r="R86">
+        <v>2.2</v>
+      </c>
+      <c r="S86">
+        <v>3.75</v>
+      </c>
+      <c r="T86">
+        <v>1.36</v>
+      </c>
+      <c r="U86">
+        <v>3</v>
+      </c>
+      <c r="V86">
+        <v>2.63</v>
+      </c>
+      <c r="W86">
+        <v>1.44</v>
+      </c>
+      <c r="X86">
+        <v>7</v>
+      </c>
+      <c r="Y86">
+        <v>1.1</v>
+      </c>
+      <c r="Z86">
+        <v>2.08</v>
+      </c>
+      <c r="AA86">
+        <v>3.39</v>
+      </c>
+      <c r="AB86">
+        <v>2.9</v>
+      </c>
+      <c r="AC86">
+        <v>1.05</v>
+      </c>
+      <c r="AD86">
+        <v>9.5</v>
+      </c>
+      <c r="AE86">
+        <v>1.28</v>
+      </c>
+      <c r="AF86">
+        <v>3.55</v>
+      </c>
+      <c r="AG86">
+        <v>1.86</v>
+      </c>
+      <c r="AH86">
+        <v>1.84</v>
+      </c>
+      <c r="AI86">
+        <v>1.7</v>
+      </c>
+      <c r="AJ86">
+        <v>2.05</v>
+      </c>
+      <c r="AK86">
+        <v>1.35</v>
+      </c>
+      <c r="AL86">
+        <v>1.29</v>
+      </c>
+      <c r="AM86">
+        <v>1.65</v>
+      </c>
+      <c r="AN86">
+        <v>0.75</v>
+      </c>
+      <c r="AO86">
+        <v>1.5</v>
+      </c>
+      <c r="AP86">
+        <v>1.2</v>
+      </c>
+      <c r="AQ86">
+        <v>1.2</v>
+      </c>
+      <c r="AR86">
+        <v>1.15</v>
+      </c>
+      <c r="AS86">
+        <v>1.67</v>
+      </c>
+      <c r="AT86">
+        <v>2.82</v>
+      </c>
+      <c r="AU86">
+        <v>6</v>
+      </c>
+      <c r="AV86">
+        <v>2</v>
+      </c>
+      <c r="AW86">
+        <v>8</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+      <c r="AY86">
+        <v>14</v>
+      </c>
+      <c r="AZ86">
+        <v>10</v>
+      </c>
+      <c r="BA86">
+        <v>6</v>
+      </c>
+      <c r="BB86">
+        <v>2</v>
+      </c>
+      <c r="BC86">
+        <v>8</v>
+      </c>
+      <c r="BD86">
+        <v>1.7</v>
+      </c>
+      <c r="BE86">
+        <v>6.75</v>
+      </c>
+      <c r="BF86">
+        <v>2.4</v>
+      </c>
+      <c r="BG86">
+        <v>1.24</v>
+      </c>
+      <c r="BH86">
+        <v>3.55</v>
+      </c>
+      <c r="BI86">
+        <v>1.43</v>
+      </c>
+      <c r="BJ86">
+        <v>2.6</v>
+      </c>
+      <c r="BK86">
+        <v>1.7</v>
+      </c>
+      <c r="BL86">
+        <v>2.02</v>
+      </c>
+      <c r="BM86">
+        <v>2.08</v>
+      </c>
+      <c r="BN86">
+        <v>1.65</v>
+      </c>
+      <c r="BO86">
+        <v>2.65</v>
+      </c>
+      <c r="BP86">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7785260</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45830.59375</v>
+      </c>
+      <c r="F87">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>85</v>
+      </c>
+      <c r="H87" t="s">
+        <v>71</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" t="s">
+        <v>146</v>
+      </c>
+      <c r="P87" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q87">
+        <v>2.1</v>
+      </c>
+      <c r="R87">
+        <v>2.5</v>
+      </c>
+      <c r="S87">
+        <v>5</v>
+      </c>
+      <c r="T87">
+        <v>1.29</v>
+      </c>
+      <c r="U87">
+        <v>3.5</v>
+      </c>
+      <c r="V87">
+        <v>2.25</v>
+      </c>
+      <c r="W87">
+        <v>1.57</v>
+      </c>
+      <c r="X87">
+        <v>5.5</v>
+      </c>
+      <c r="Y87">
+        <v>1.14</v>
+      </c>
+      <c r="Z87">
+        <v>1.52</v>
+      </c>
+      <c r="AA87">
+        <v>3.95</v>
+      </c>
+      <c r="AB87">
+        <v>4.8</v>
+      </c>
+      <c r="AC87">
+        <v>1.03</v>
+      </c>
+      <c r="AD87">
+        <v>11</v>
+      </c>
+      <c r="AE87">
+        <v>1.2</v>
+      </c>
+      <c r="AF87">
+        <v>4.5</v>
+      </c>
+      <c r="AG87">
+        <v>1.55</v>
+      </c>
+      <c r="AH87">
+        <v>2.29</v>
+      </c>
+      <c r="AI87">
+        <v>1.67</v>
+      </c>
+      <c r="AJ87">
+        <v>2.1</v>
+      </c>
+      <c r="AK87">
+        <v>1.18</v>
+      </c>
+      <c r="AL87">
+        <v>1.21</v>
+      </c>
+      <c r="AM87">
+        <v>2.25</v>
+      </c>
+      <c r="AN87">
+        <v>2.33</v>
+      </c>
+      <c r="AO87">
+        <v>1</v>
+      </c>
+      <c r="AP87">
+        <v>2.43</v>
+      </c>
+      <c r="AQ87">
+        <v>0.8</v>
+      </c>
+      <c r="AR87">
+        <v>2.49</v>
+      </c>
+      <c r="AS87">
+        <v>1.17</v>
+      </c>
+      <c r="AT87">
+        <v>3.66</v>
+      </c>
+      <c r="AU87">
+        <v>5</v>
+      </c>
+      <c r="AV87">
+        <v>2</v>
+      </c>
+      <c r="AW87">
+        <v>9</v>
+      </c>
+      <c r="AX87">
+        <v>9</v>
+      </c>
+      <c r="AY87">
+        <v>14</v>
+      </c>
+      <c r="AZ87">
+        <v>11</v>
+      </c>
+      <c r="BA87">
+        <v>6</v>
+      </c>
+      <c r="BB87">
+        <v>6</v>
+      </c>
+      <c r="BC87">
+        <v>12</v>
+      </c>
+      <c r="BD87">
+        <v>1.46</v>
+      </c>
+      <c r="BE87">
+        <v>7</v>
+      </c>
+      <c r="BF87">
+        <v>3</v>
+      </c>
+      <c r="BG87">
+        <v>1.18</v>
+      </c>
+      <c r="BH87">
+        <v>4.1</v>
+      </c>
+      <c r="BI87">
+        <v>1.32</v>
+      </c>
+      <c r="BJ87">
+        <v>3.05</v>
+      </c>
+      <c r="BK87">
+        <v>1.53</v>
+      </c>
+      <c r="BL87">
+        <v>2.3</v>
+      </c>
+      <c r="BM87">
+        <v>1.83</v>
+      </c>
+      <c r="BN87">
+        <v>1.85</v>
+      </c>
+      <c r="BO87">
+        <v>2.25</v>
+      </c>
+      <c r="BP87">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -17010,13 +17010,13 @@
         <v>2</v>
       </c>
       <c r="AX78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY78">
         <v>4</v>
       </c>
       <c r="AZ78">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA78">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -457,6 +457,9 @@
     <t>['7', '60', '80']</t>
   </si>
   <si>
+    <t>['70']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -551,9 +554,6 @@
   </si>
   <si>
     <t>['5', '90+2', '90+4']</t>
-  </si>
-  <si>
-    <t>['70']</t>
   </si>
   <si>
     <t>['39']</t>
@@ -996,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP87"/>
+  <dimension ref="A1:BP88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1252,7 +1252,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1664,7 +1664,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1745,7 +1745,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ4">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2076,7 +2076,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2282,7 +2282,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2694,7 +2694,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11">
         <v>0.8</v>
@@ -3312,7 +3312,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3518,7 +3518,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3930,7 +3930,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4136,7 +4136,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4342,7 +4342,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4754,7 +4754,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4960,7 +4960,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5166,7 +5166,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5372,7 +5372,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5578,7 +5578,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5784,7 +5784,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5990,7 +5990,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6196,7 +6196,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6277,7 +6277,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ26">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AR26">
         <v>1.31</v>
@@ -6402,7 +6402,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6608,7 +6608,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6892,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ29">
         <v>1.67</v>
@@ -7226,7 +7226,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7638,7 +7638,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8050,7 +8050,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8256,7 +8256,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8462,7 +8462,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8668,7 +8668,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8746,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38">
         <v>1.43</v>
@@ -9080,7 +9080,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9492,7 +9492,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9698,7 +9698,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10188,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
         <v>0.8</v>
@@ -10522,7 +10522,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10728,7 +10728,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10934,7 +10934,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="Q49">
         <v>3.4</v>
@@ -11633,7 +11633,7 @@
         <v>0.2</v>
       </c>
       <c r="AQ52">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AR52">
         <v>1.29</v>
@@ -12248,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ55">
         <v>0</v>
@@ -13200,7 +13200,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13818,7 +13818,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14311,7 +14311,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AR65">
         <v>1.38</v>
@@ -15341,7 +15341,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ70">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AR70">
         <v>2.02</v>
@@ -16986,7 +16986,7 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ78">
         <v>0.4</v>
@@ -17195,7 +17195,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ79">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AR79">
         <v>1.62</v>
@@ -18919,6 +18919,212 @@
       </c>
       <c r="BP87">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7785268</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45836.54166666666</v>
+      </c>
+      <c r="F88">
+        <v>11</v>
+      </c>
+      <c r="G88" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s">
+        <v>85</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>2</v>
+      </c>
+      <c r="O88" t="s">
+        <v>147</v>
+      </c>
+      <c r="P88" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q88">
+        <v>2.83</v>
+      </c>
+      <c r="R88">
+        <v>2.43</v>
+      </c>
+      <c r="S88">
+        <v>3.05</v>
+      </c>
+      <c r="T88">
+        <v>1.2</v>
+      </c>
+      <c r="U88">
+        <v>3.68</v>
+      </c>
+      <c r="V88">
+        <v>2.12</v>
+      </c>
+      <c r="W88">
+        <v>1.64</v>
+      </c>
+      <c r="X88">
+        <v>4.5</v>
+      </c>
+      <c r="Y88">
+        <v>1.13</v>
+      </c>
+      <c r="Z88">
+        <v>1.85</v>
+      </c>
+      <c r="AA88">
+        <v>3.67</v>
+      </c>
+      <c r="AB88">
+        <v>3.26</v>
+      </c>
+      <c r="AC88">
+        <v>1.01</v>
+      </c>
+      <c r="AD88">
+        <v>17</v>
+      </c>
+      <c r="AE88">
+        <v>1.09</v>
+      </c>
+      <c r="AF88">
+        <v>5.25</v>
+      </c>
+      <c r="AG88">
+        <v>1.55</v>
+      </c>
+      <c r="AH88">
+        <v>2.29</v>
+      </c>
+      <c r="AI88">
+        <v>1.4</v>
+      </c>
+      <c r="AJ88">
+        <v>2.72</v>
+      </c>
+      <c r="AK88">
+        <v>1.5</v>
+      </c>
+      <c r="AL88">
+        <v>1.26</v>
+      </c>
+      <c r="AM88">
+        <v>1.56</v>
+      </c>
+      <c r="AN88">
+        <v>2</v>
+      </c>
+      <c r="AO88">
+        <v>2.5</v>
+      </c>
+      <c r="AP88">
+        <v>1.86</v>
+      </c>
+      <c r="AQ88">
+        <v>2.29</v>
+      </c>
+      <c r="AR88">
+        <v>2.33</v>
+      </c>
+      <c r="AS88">
+        <v>1.86</v>
+      </c>
+      <c r="AT88">
+        <v>4.19</v>
+      </c>
+      <c r="AU88">
+        <v>3</v>
+      </c>
+      <c r="AV88">
+        <v>5</v>
+      </c>
+      <c r="AW88">
+        <v>9</v>
+      </c>
+      <c r="AX88">
+        <v>6</v>
+      </c>
+      <c r="AY88">
+        <v>12</v>
+      </c>
+      <c r="AZ88">
+        <v>11</v>
+      </c>
+      <c r="BA88">
+        <v>9</v>
+      </c>
+      <c r="BB88">
+        <v>5</v>
+      </c>
+      <c r="BC88">
+        <v>14</v>
+      </c>
+      <c r="BD88">
+        <v>1.75</v>
+      </c>
+      <c r="BE88">
+        <v>6.75</v>
+      </c>
+      <c r="BF88">
+        <v>2.28</v>
+      </c>
+      <c r="BG88">
+        <v>1.2</v>
+      </c>
+      <c r="BH88">
+        <v>3.95</v>
+      </c>
+      <c r="BI88">
+        <v>1.35</v>
+      </c>
+      <c r="BJ88">
+        <v>2.9</v>
+      </c>
+      <c r="BK88">
+        <v>1.57</v>
+      </c>
+      <c r="BL88">
+        <v>2.23</v>
+      </c>
+      <c r="BM88">
+        <v>1.91</v>
+      </c>
+      <c r="BN88">
+        <v>1.78</v>
+      </c>
+      <c r="BO88">
+        <v>2.38</v>
+      </c>
+      <c r="BP88">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="207">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -996,7 +996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP88"/>
+  <dimension ref="A1:BP89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1951,7 +1951,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AQ15">
         <v>1.2</v>
@@ -4835,7 +4835,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ19">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
         <v>2.02</v>
@@ -5247,7 +5247,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ21">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR21">
         <v>1.94</v>
@@ -7510,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32">
         <v>0.8</v>
@@ -8749,7 +8749,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ38">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR38">
         <v>1.75</v>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR43">
         <v>1.63</v>
@@ -11630,7 +11630,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AQ52">
         <v>2.29</v>
@@ -12457,7 +12457,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ56">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -14720,7 +14720,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AQ67">
         <v>1.8</v>
@@ -16371,7 +16371,7 @@
         <v>2</v>
       </c>
       <c r="AQ75">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16780,7 +16780,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AQ77">
         <v>1.75</v>
@@ -19125,6 +19125,212 @@
       </c>
       <c r="BP88">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7785266</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45837.39583333334</v>
+      </c>
+      <c r="F89">
+        <v>11</v>
+      </c>
+      <c r="G89" t="s">
+        <v>83</v>
+      </c>
+      <c r="H89" t="s">
+        <v>84</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
+        <v>91</v>
+      </c>
+      <c r="P89" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q89">
+        <v>3.35</v>
+      </c>
+      <c r="R89">
+        <v>2.2</v>
+      </c>
+      <c r="S89">
+        <v>2.75</v>
+      </c>
+      <c r="T89">
+        <v>1.33</v>
+      </c>
+      <c r="U89">
+        <v>3</v>
+      </c>
+      <c r="V89">
+        <v>2.5</v>
+      </c>
+      <c r="W89">
+        <v>1.48</v>
+      </c>
+      <c r="X89">
+        <v>5.7</v>
+      </c>
+      <c r="Y89">
+        <v>1.08</v>
+      </c>
+      <c r="Z89">
+        <v>2.7</v>
+      </c>
+      <c r="AA89">
+        <v>3.34</v>
+      </c>
+      <c r="AB89">
+        <v>2.23</v>
+      </c>
+      <c r="AC89">
+        <v>1.05</v>
+      </c>
+      <c r="AD89">
+        <v>9.5</v>
+      </c>
+      <c r="AE89">
+        <v>1.25</v>
+      </c>
+      <c r="AF89">
+        <v>3.85</v>
+      </c>
+      <c r="AG89">
+        <v>1.81</v>
+      </c>
+      <c r="AH89">
+        <v>1.89</v>
+      </c>
+      <c r="AI89">
+        <v>1.6</v>
+      </c>
+      <c r="AJ89">
+        <v>2.15</v>
+      </c>
+      <c r="AK89">
+        <v>1.62</v>
+      </c>
+      <c r="AL89">
+        <v>1.25</v>
+      </c>
+      <c r="AM89">
+        <v>1.38</v>
+      </c>
+      <c r="AN89">
+        <v>0.2</v>
+      </c>
+      <c r="AO89">
+        <v>1.43</v>
+      </c>
+      <c r="AP89">
+        <v>0.33</v>
+      </c>
+      <c r="AQ89">
+        <v>1.38</v>
+      </c>
+      <c r="AR89">
+        <v>1.3</v>
+      </c>
+      <c r="AS89">
+        <v>1.18</v>
+      </c>
+      <c r="AT89">
+        <v>2.48</v>
+      </c>
+      <c r="AU89">
+        <v>4</v>
+      </c>
+      <c r="AV89">
+        <v>2</v>
+      </c>
+      <c r="AW89">
+        <v>4</v>
+      </c>
+      <c r="AX89">
+        <v>3</v>
+      </c>
+      <c r="AY89">
+        <v>8</v>
+      </c>
+      <c r="AZ89">
+        <v>5</v>
+      </c>
+      <c r="BA89">
+        <v>5</v>
+      </c>
+      <c r="BB89">
+        <v>4</v>
+      </c>
+      <c r="BC89">
+        <v>9</v>
+      </c>
+      <c r="BD89">
+        <v>2.1</v>
+      </c>
+      <c r="BE89">
+        <v>6.75</v>
+      </c>
+      <c r="BF89">
+        <v>1.86</v>
+      </c>
+      <c r="BG89">
+        <v>1.22</v>
+      </c>
+      <c r="BH89">
+        <v>3.8</v>
+      </c>
+      <c r="BI89">
+        <v>1.38</v>
+      </c>
+      <c r="BJ89">
+        <v>2.75</v>
+      </c>
+      <c r="BK89">
+        <v>1.61</v>
+      </c>
+      <c r="BL89">
+        <v>2.15</v>
+      </c>
+      <c r="BM89">
+        <v>1.97</v>
+      </c>
+      <c r="BN89">
+        <v>1.74</v>
+      </c>
+      <c r="BO89">
+        <v>2.43</v>
+      </c>
+      <c r="BP89">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="212">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,6 +460,15 @@
     <t>['70']</t>
   </si>
   <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['49', '71']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -478,9 +487,6 @@
     <t>['35']</t>
   </si>
   <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['45+1']</t>
   </si>
   <si>
@@ -635,6 +641,15 @@
   </si>
   <si>
     <t>['21', '26', '47']</t>
+  </si>
+  <si>
+    <t>['37', '9004']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['34', '41', '56']</t>
   </si>
 </sst>
 </file>
@@ -996,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP89"/>
+  <dimension ref="A1:BP93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1252,7 +1267,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1536,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
         <v>1.8</v>
@@ -1664,7 +1679,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1870,7 +1885,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2076,7 +2091,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2282,7 +2297,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2360,10 +2375,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ7">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2694,7 +2709,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -2772,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
         <v>1.75</v>
@@ -2978,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3312,7 +3327,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3393,7 +3408,7 @@
         <v>2</v>
       </c>
       <c r="AQ12">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3518,7 +3533,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3930,7 +3945,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4136,7 +4151,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4342,7 +4357,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4423,7 +4438,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ17">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4626,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18">
         <v>1.17</v>
@@ -4754,7 +4769,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4960,7 +4975,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5166,7 +5181,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5372,7 +5387,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5578,7 +5593,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5784,7 +5799,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5862,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>0</v>
@@ -5990,7 +6005,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6068,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ25">
         <v>0.6</v>
@@ -6196,7 +6211,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6402,7 +6417,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6483,7 +6498,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ27">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR27">
         <v>1.57</v>
@@ -6608,7 +6623,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6686,7 +6701,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ28">
         <v>1.75</v>
@@ -7098,10 +7113,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR30">
         <v>2.59</v>
@@ -7226,7 +7241,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7638,7 +7653,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7925,7 +7940,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR34">
         <v>2.49</v>
@@ -8050,7 +8065,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8256,7 +8271,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8337,7 +8352,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR36">
         <v>2</v>
@@ -8462,7 +8477,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8668,7 +8683,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8955,7 +8970,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ39">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR39">
         <v>1.22</v>
@@ -9080,7 +9095,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9367,7 +9382,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ41">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR41">
         <v>2.65</v>
@@ -9492,7 +9507,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9698,7 +9713,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -9982,7 +9997,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ44">
         <v>0</v>
@@ -10522,7 +10537,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10600,7 +10615,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ47">
         <v>1.67</v>
@@ -10728,7 +10743,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10809,7 +10824,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11140,7 +11155,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11427,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11552,7 +11567,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11758,7 +11773,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11964,7 +11979,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -12376,7 +12391,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12454,7 +12469,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -12582,7 +12597,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12788,7 +12803,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -12869,7 +12884,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR58">
         <v>1.94</v>
@@ -13072,10 +13087,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ59">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR59">
         <v>1.16</v>
@@ -13200,7 +13215,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13281,7 +13296,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR60">
         <v>2.1</v>
@@ -13406,7 +13421,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13484,7 +13499,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61">
         <v>0.8</v>
@@ -13690,7 +13705,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
         <v>1.67</v>
@@ -13818,7 +13833,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14105,7 +14120,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR64">
         <v>1.85</v>
@@ -14230,7 +14245,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14436,7 +14451,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14642,7 +14657,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14848,7 +14863,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15054,7 +15069,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15132,7 +15147,7 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
         <v>1.67</v>
@@ -15260,7 +15275,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15338,7 +15353,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>2.29</v>
@@ -15466,7 +15481,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15672,7 +15687,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15753,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="AQ72">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -15878,7 +15893,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16084,7 +16099,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16162,10 +16177,10 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AR74">
         <v>1.11</v>
@@ -16290,7 +16305,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16496,7 +16511,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16574,7 +16589,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AQ76">
         <v>0.6</v>
@@ -16702,7 +16717,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16908,7 +16923,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -16989,7 +17004,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ78">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR78">
         <v>2.33</v>
@@ -17114,7 +17129,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17192,7 +17207,7 @@
         <v>2.4</v>
       </c>
       <c r="AP79">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ79">
         <v>2.29</v>
@@ -17398,7 +17413,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
         <v>1.8</v>
@@ -17526,7 +17541,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17938,7 +17953,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18144,7 +18159,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18350,7 +18365,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18431,7 +18446,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ85">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -18968,7 +18983,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19267,22 +19282,22 @@
         <v>2.48</v>
       </c>
       <c r="AU89">
+        <v>5</v>
+      </c>
+      <c r="AV89">
         <v>4</v>
-      </c>
-      <c r="AV89">
-        <v>2</v>
       </c>
       <c r="AW89">
         <v>4</v>
       </c>
       <c r="AX89">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY89">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ89">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BA89">
         <v>5</v>
@@ -19331,6 +19346,830 @@
       </c>
       <c r="BP89">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7785262</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F90">
+        <v>11</v>
+      </c>
+      <c r="G90" t="s">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s">
+        <v>81</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>2</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>2</v>
+      </c>
+      <c r="N90">
+        <v>3</v>
+      </c>
+      <c r="O90" t="s">
+        <v>148</v>
+      </c>
+      <c r="P90" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q90">
+        <v>1.57</v>
+      </c>
+      <c r="R90">
+        <v>3</v>
+      </c>
+      <c r="S90">
+        <v>6.5</v>
+      </c>
+      <c r="T90">
+        <v>1.17</v>
+      </c>
+      <c r="U90">
+        <v>4.5</v>
+      </c>
+      <c r="V90">
+        <v>1.83</v>
+      </c>
+      <c r="W90">
+        <v>1.85</v>
+      </c>
+      <c r="X90">
+        <v>3.74</v>
+      </c>
+      <c r="Y90">
+        <v>1.19</v>
+      </c>
+      <c r="Z90">
+        <v>1.23</v>
+      </c>
+      <c r="AA90">
+        <v>5.7</v>
+      </c>
+      <c r="AB90">
+        <v>7.7</v>
+      </c>
+      <c r="AC90">
+        <v>1.01</v>
+      </c>
+      <c r="AD90">
+        <v>26</v>
+      </c>
+      <c r="AE90">
+        <v>1.08</v>
+      </c>
+      <c r="AF90">
+        <v>7.5</v>
+      </c>
+      <c r="AG90">
+        <v>1.3</v>
+      </c>
+      <c r="AH90">
+        <v>3.33</v>
+      </c>
+      <c r="AI90">
+        <v>1.6</v>
+      </c>
+      <c r="AJ90">
+        <v>2.15</v>
+      </c>
+      <c r="AK90">
+        <v>1.05</v>
+      </c>
+      <c r="AL90">
+        <v>1.11</v>
+      </c>
+      <c r="AM90">
+        <v>3.7</v>
+      </c>
+      <c r="AN90">
+        <v>2.4</v>
+      </c>
+      <c r="AO90">
+        <v>1.8</v>
+      </c>
+      <c r="AP90">
+        <v>2</v>
+      </c>
+      <c r="AQ90">
+        <v>2</v>
+      </c>
+      <c r="AR90">
+        <v>2.02</v>
+      </c>
+      <c r="AS90">
+        <v>1.66</v>
+      </c>
+      <c r="AT90">
+        <v>3.68</v>
+      </c>
+      <c r="AU90">
+        <v>7</v>
+      </c>
+      <c r="AV90">
+        <v>4</v>
+      </c>
+      <c r="AW90">
+        <v>23</v>
+      </c>
+      <c r="AX90">
+        <v>2</v>
+      </c>
+      <c r="AY90">
+        <v>30</v>
+      </c>
+      <c r="AZ90">
+        <v>6</v>
+      </c>
+      <c r="BA90">
+        <v>10</v>
+      </c>
+      <c r="BB90">
+        <v>2</v>
+      </c>
+      <c r="BC90">
+        <v>12</v>
+      </c>
+      <c r="BD90">
+        <v>1.23</v>
+      </c>
+      <c r="BE90">
+        <v>8.5</v>
+      </c>
+      <c r="BF90">
+        <v>4.4</v>
+      </c>
+      <c r="BG90">
+        <v>1.15</v>
+      </c>
+      <c r="BH90">
+        <v>4.6</v>
+      </c>
+      <c r="BI90">
+        <v>1.27</v>
+      </c>
+      <c r="BJ90">
+        <v>3.3</v>
+      </c>
+      <c r="BK90">
+        <v>1.46</v>
+      </c>
+      <c r="BL90">
+        <v>2.5</v>
+      </c>
+      <c r="BM90">
+        <v>1.73</v>
+      </c>
+      <c r="BN90">
+        <v>1.98</v>
+      </c>
+      <c r="BO90">
+        <v>2.08</v>
+      </c>
+      <c r="BP90">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7785264</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F91">
+        <v>11</v>
+      </c>
+      <c r="G91" t="s">
+        <v>77</v>
+      </c>
+      <c r="H91" t="s">
+        <v>73</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>2</v>
+      </c>
+      <c r="O91" t="s">
+        <v>149</v>
+      </c>
+      <c r="P91" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q91">
+        <v>2.45</v>
+      </c>
+      <c r="R91">
+        <v>2.15</v>
+      </c>
+      <c r="S91">
+        <v>4</v>
+      </c>
+      <c r="T91">
+        <v>1.35</v>
+      </c>
+      <c r="U91">
+        <v>2.95</v>
+      </c>
+      <c r="V91">
+        <v>2.62</v>
+      </c>
+      <c r="W91">
+        <v>1.42</v>
+      </c>
+      <c r="X91">
+        <v>6.65</v>
+      </c>
+      <c r="Y91">
+        <v>1.05</v>
+      </c>
+      <c r="Z91">
+        <v>1.86</v>
+      </c>
+      <c r="AA91">
+        <v>3.39</v>
+      </c>
+      <c r="AB91">
+        <v>3.47</v>
+      </c>
+      <c r="AC91">
+        <v>1.05</v>
+      </c>
+      <c r="AD91">
+        <v>9.5</v>
+      </c>
+      <c r="AE91">
+        <v>1.28</v>
+      </c>
+      <c r="AF91">
+        <v>3.65</v>
+      </c>
+      <c r="AG91">
+        <v>1.79</v>
+      </c>
+      <c r="AH91">
+        <v>1.91</v>
+      </c>
+      <c r="AI91">
+        <v>1.7</v>
+      </c>
+      <c r="AJ91">
+        <v>2</v>
+      </c>
+      <c r="AK91">
+        <v>1.25</v>
+      </c>
+      <c r="AL91">
+        <v>1.22</v>
+      </c>
+      <c r="AM91">
+        <v>1.85</v>
+      </c>
+      <c r="AN91">
+        <v>1.8</v>
+      </c>
+      <c r="AO91">
+        <v>0.8</v>
+      </c>
+      <c r="AP91">
+        <v>1.67</v>
+      </c>
+      <c r="AQ91">
+        <v>0.83</v>
+      </c>
+      <c r="AR91">
+        <v>1.53</v>
+      </c>
+      <c r="AS91">
+        <v>1.13</v>
+      </c>
+      <c r="AT91">
+        <v>2.66</v>
+      </c>
+      <c r="AU91">
+        <v>8</v>
+      </c>
+      <c r="AV91">
+        <v>4</v>
+      </c>
+      <c r="AW91">
+        <v>6</v>
+      </c>
+      <c r="AX91">
+        <v>9</v>
+      </c>
+      <c r="AY91">
+        <v>14</v>
+      </c>
+      <c r="AZ91">
+        <v>13</v>
+      </c>
+      <c r="BA91">
+        <v>10</v>
+      </c>
+      <c r="BB91">
+        <v>5</v>
+      </c>
+      <c r="BC91">
+        <v>15</v>
+      </c>
+      <c r="BD91">
+        <v>1.65</v>
+      </c>
+      <c r="BE91">
+        <v>7</v>
+      </c>
+      <c r="BF91">
+        <v>2.48</v>
+      </c>
+      <c r="BG91">
+        <v>1.19</v>
+      </c>
+      <c r="BH91">
+        <v>4.1</v>
+      </c>
+      <c r="BI91">
+        <v>1.34</v>
+      </c>
+      <c r="BJ91">
+        <v>2.9</v>
+      </c>
+      <c r="BK91">
+        <v>1.55</v>
+      </c>
+      <c r="BL91">
+        <v>2.25</v>
+      </c>
+      <c r="BM91">
+        <v>1.9</v>
+      </c>
+      <c r="BN91">
+        <v>1.79</v>
+      </c>
+      <c r="BO91">
+        <v>2.33</v>
+      </c>
+      <c r="BP91">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7785265</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F92">
+        <v>11</v>
+      </c>
+      <c r="G92" t="s">
+        <v>71</v>
+      </c>
+      <c r="H92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>91</v>
+      </c>
+      <c r="P92" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q92">
+        <v>3.1</v>
+      </c>
+      <c r="R92">
+        <v>1.95</v>
+      </c>
+      <c r="S92">
+        <v>3.55</v>
+      </c>
+      <c r="T92">
+        <v>1.48</v>
+      </c>
+      <c r="U92">
+        <v>2.45</v>
+      </c>
+      <c r="V92">
+        <v>3.2</v>
+      </c>
+      <c r="W92">
+        <v>1.3</v>
+      </c>
+      <c r="X92">
+        <v>9.1</v>
+      </c>
+      <c r="Y92">
+        <v>1</v>
+      </c>
+      <c r="Z92">
+        <v>2.25</v>
+      </c>
+      <c r="AA92">
+        <v>3.08</v>
+      </c>
+      <c r="AB92">
+        <v>2.85</v>
+      </c>
+      <c r="AC92">
+        <v>1.08</v>
+      </c>
+      <c r="AD92">
+        <v>7.5</v>
+      </c>
+      <c r="AE92">
+        <v>1.42</v>
+      </c>
+      <c r="AF92">
+        <v>2.8</v>
+      </c>
+      <c r="AG92">
+        <v>2.04</v>
+      </c>
+      <c r="AH92">
+        <v>1.69</v>
+      </c>
+      <c r="AI92">
+        <v>1.85</v>
+      </c>
+      <c r="AJ92">
+        <v>1.8</v>
+      </c>
+      <c r="AK92">
+        <v>1.38</v>
+      </c>
+      <c r="AL92">
+        <v>1.3</v>
+      </c>
+      <c r="AM92">
+        <v>1.53</v>
+      </c>
+      <c r="AN92">
+        <v>2.17</v>
+      </c>
+      <c r="AO92">
+        <v>2</v>
+      </c>
+      <c r="AP92">
+        <v>1.86</v>
+      </c>
+      <c r="AQ92">
+        <v>2.17</v>
+      </c>
+      <c r="AR92">
+        <v>1.11</v>
+      </c>
+      <c r="AS92">
+        <v>1.09</v>
+      </c>
+      <c r="AT92">
+        <v>2.2</v>
+      </c>
+      <c r="AU92">
+        <v>6</v>
+      </c>
+      <c r="AV92">
+        <v>5</v>
+      </c>
+      <c r="AW92">
+        <v>8</v>
+      </c>
+      <c r="AX92">
+        <v>3</v>
+      </c>
+      <c r="AY92">
+        <v>14</v>
+      </c>
+      <c r="AZ92">
+        <v>8</v>
+      </c>
+      <c r="BA92">
+        <v>8</v>
+      </c>
+      <c r="BB92">
+        <v>3</v>
+      </c>
+      <c r="BC92">
+        <v>11</v>
+      </c>
+      <c r="BD92">
+        <v>1.86</v>
+      </c>
+      <c r="BE92">
+        <v>6.4</v>
+      </c>
+      <c r="BF92">
+        <v>2.15</v>
+      </c>
+      <c r="BG92">
+        <v>1.33</v>
+      </c>
+      <c r="BH92">
+        <v>2.95</v>
+      </c>
+      <c r="BI92">
+        <v>1.56</v>
+      </c>
+      <c r="BJ92">
+        <v>2.23</v>
+      </c>
+      <c r="BK92">
+        <v>1.92</v>
+      </c>
+      <c r="BL92">
+        <v>1.78</v>
+      </c>
+      <c r="BM92">
+        <v>2.4</v>
+      </c>
+      <c r="BN92">
+        <v>1.49</v>
+      </c>
+      <c r="BO92">
+        <v>3.15</v>
+      </c>
+      <c r="BP92">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7785267</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F93">
+        <v>11</v>
+      </c>
+      <c r="G93" t="s">
+        <v>75</v>
+      </c>
+      <c r="H93" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>3</v>
+      </c>
+      <c r="N93">
+        <v>5</v>
+      </c>
+      <c r="O93" t="s">
+        <v>150</v>
+      </c>
+      <c r="P93" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q93">
+        <v>2.38</v>
+      </c>
+      <c r="R93">
+        <v>2.1</v>
+      </c>
+      <c r="S93">
+        <v>4.5</v>
+      </c>
+      <c r="T93">
+        <v>1.38</v>
+      </c>
+      <c r="U93">
+        <v>2.8</v>
+      </c>
+      <c r="V93">
+        <v>2.8</v>
+      </c>
+      <c r="W93">
+        <v>1.38</v>
+      </c>
+      <c r="X93">
+        <v>7.3</v>
+      </c>
+      <c r="Y93">
+        <v>1.03</v>
+      </c>
+      <c r="Z93">
+        <v>1.73</v>
+      </c>
+      <c r="AA93">
+        <v>3.4</v>
+      </c>
+      <c r="AB93">
+        <v>4</v>
+      </c>
+      <c r="AC93">
+        <v>1.06</v>
+      </c>
+      <c r="AD93">
+        <v>8.5</v>
+      </c>
+      <c r="AE93">
+        <v>1.33</v>
+      </c>
+      <c r="AF93">
+        <v>3.3</v>
+      </c>
+      <c r="AG93">
+        <v>1.92</v>
+      </c>
+      <c r="AH93">
+        <v>1.78</v>
+      </c>
+      <c r="AI93">
+        <v>1.83</v>
+      </c>
+      <c r="AJ93">
+        <v>1.85</v>
+      </c>
+      <c r="AK93">
+        <v>1.2</v>
+      </c>
+      <c r="AL93">
+        <v>1.22</v>
+      </c>
+      <c r="AM93">
+        <v>1.95</v>
+      </c>
+      <c r="AN93">
+        <v>0.8</v>
+      </c>
+      <c r="AO93">
+        <v>0.4</v>
+      </c>
+      <c r="AP93">
+        <v>0.67</v>
+      </c>
+      <c r="AQ93">
+        <v>0.83</v>
+      </c>
+      <c r="AR93">
+        <v>1.62</v>
+      </c>
+      <c r="AS93">
+        <v>0.97</v>
+      </c>
+      <c r="AT93">
+        <v>2.59</v>
+      </c>
+      <c r="AU93">
+        <v>5</v>
+      </c>
+      <c r="AV93">
+        <v>5</v>
+      </c>
+      <c r="AW93">
+        <v>8</v>
+      </c>
+      <c r="AX93">
+        <v>5</v>
+      </c>
+      <c r="AY93">
+        <v>13</v>
+      </c>
+      <c r="AZ93">
+        <v>10</v>
+      </c>
+      <c r="BA93">
+        <v>4</v>
+      </c>
+      <c r="BB93">
+        <v>0</v>
+      </c>
+      <c r="BC93">
+        <v>4</v>
+      </c>
+      <c r="BD93">
+        <v>1.6</v>
+      </c>
+      <c r="BE93">
+        <v>6.4</v>
+      </c>
+      <c r="BF93">
+        <v>2.65</v>
+      </c>
+      <c r="BG93">
+        <v>1.36</v>
+      </c>
+      <c r="BH93">
+        <v>2.8</v>
+      </c>
+      <c r="BI93">
+        <v>1.6</v>
+      </c>
+      <c r="BJ93">
+        <v>2.17</v>
+      </c>
+      <c r="BK93">
+        <v>1.98</v>
+      </c>
+      <c r="BL93">
+        <v>1.74</v>
+      </c>
+      <c r="BM93">
+        <v>2.5</v>
+      </c>
+      <c r="BN93">
+        <v>1.46</v>
+      </c>
+      <c r="BO93">
+        <v>3.3</v>
+      </c>
+      <c r="BP93">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="213">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -650,6 +650,9 @@
   </si>
   <si>
     <t>['34', '41', '56']</t>
+  </si>
+  <si>
+    <t>['39', '46']</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP93"/>
+  <dimension ref="A1:BP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3614,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4644,7 +4647,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR18">
         <v>0.92</v>
@@ -7734,7 +7737,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>1.87</v>
@@ -11236,7 +11239,7 @@
         <v>3</v>
       </c>
       <c r="AQ50">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -14944,7 +14947,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
         <v>1.1</v>
@@ -15974,7 +15977,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ73">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -20170,6 +20173,212 @@
       </c>
       <c r="BP93">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7785269</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45837.59375</v>
+      </c>
+      <c r="F94">
+        <v>11</v>
+      </c>
+      <c r="G94" t="s">
+        <v>70</v>
+      </c>
+      <c r="H94" t="s">
+        <v>72</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>2</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94" t="s">
+        <v>91</v>
+      </c>
+      <c r="P94" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q94">
+        <v>2.95</v>
+      </c>
+      <c r="R94">
+        <v>2.25</v>
+      </c>
+      <c r="S94">
+        <v>3</v>
+      </c>
+      <c r="T94">
+        <v>1.28</v>
+      </c>
+      <c r="U94">
+        <v>3.3</v>
+      </c>
+      <c r="V94">
+        <v>2.25</v>
+      </c>
+      <c r="W94">
+        <v>1.57</v>
+      </c>
+      <c r="X94">
+        <v>5.15</v>
+      </c>
+      <c r="Y94">
+        <v>1.1</v>
+      </c>
+      <c r="Z94">
+        <v>2.18</v>
+      </c>
+      <c r="AA94">
+        <v>3.28</v>
+      </c>
+      <c r="AB94">
+        <v>2.8</v>
+      </c>
+      <c r="AC94">
+        <v>1.04</v>
+      </c>
+      <c r="AD94">
+        <v>10</v>
+      </c>
+      <c r="AE94">
+        <v>1.2</v>
+      </c>
+      <c r="AF94">
+        <v>4.5</v>
+      </c>
+      <c r="AG94">
+        <v>1.57</v>
+      </c>
+      <c r="AH94">
+        <v>2.15</v>
+      </c>
+      <c r="AI94">
+        <v>1.45</v>
+      </c>
+      <c r="AJ94">
+        <v>2.5</v>
+      </c>
+      <c r="AK94">
+        <v>1.48</v>
+      </c>
+      <c r="AL94">
+        <v>1.22</v>
+      </c>
+      <c r="AM94">
+        <v>1.5</v>
+      </c>
+      <c r="AN94">
+        <v>0</v>
+      </c>
+      <c r="AO94">
+        <v>1.17</v>
+      </c>
+      <c r="AP94">
+        <v>0</v>
+      </c>
+      <c r="AQ94">
+        <v>1.43</v>
+      </c>
+      <c r="AR94">
+        <v>1.63</v>
+      </c>
+      <c r="AS94">
+        <v>1.18</v>
+      </c>
+      <c r="AT94">
+        <v>2.81</v>
+      </c>
+      <c r="AU94">
+        <v>3</v>
+      </c>
+      <c r="AV94">
+        <v>3</v>
+      </c>
+      <c r="AW94">
+        <v>2</v>
+      </c>
+      <c r="AX94">
+        <v>13</v>
+      </c>
+      <c r="AY94">
+        <v>5</v>
+      </c>
+      <c r="AZ94">
+        <v>16</v>
+      </c>
+      <c r="BA94">
+        <v>4</v>
+      </c>
+      <c r="BB94">
+        <v>3</v>
+      </c>
+      <c r="BC94">
+        <v>7</v>
+      </c>
+      <c r="BD94">
+        <v>1.79</v>
+      </c>
+      <c r="BE94">
+        <v>7</v>
+      </c>
+      <c r="BF94">
+        <v>2.18</v>
+      </c>
+      <c r="BG94">
+        <v>1.13</v>
+      </c>
+      <c r="BH94">
+        <v>5.1</v>
+      </c>
+      <c r="BI94">
+        <v>1.24</v>
+      </c>
+      <c r="BJ94">
+        <v>3.65</v>
+      </c>
+      <c r="BK94">
+        <v>1.41</v>
+      </c>
+      <c r="BL94">
+        <v>2.65</v>
+      </c>
+      <c r="BM94">
+        <v>1.65</v>
+      </c>
+      <c r="BN94">
+        <v>2.08</v>
+      </c>
+      <c r="BO94">
+        <v>1.98</v>
+      </c>
+      <c r="BP94">
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -467,6 +467,9 @@
   </si>
   <si>
     <t>['49', '71']</t>
+  </si>
+  <si>
+    <t>['89']</t>
   </si>
   <si>
     <t>['39', '49']</t>
@@ -1014,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP94"/>
+  <dimension ref="A1:BP95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1270,7 +1273,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1682,7 +1685,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1888,7 +1891,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2094,7 +2097,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2175,7 +2178,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ6">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2300,7 +2303,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2712,7 +2715,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3408,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ12">
         <v>2.17</v>
@@ -3536,7 +3539,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3948,7 +3951,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4154,7 +4157,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4360,7 +4363,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4772,7 +4775,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4978,7 +4981,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5056,7 +5059,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ20">
         <v>1.2</v>
@@ -5184,7 +5187,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5390,7 +5393,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5596,7 +5599,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5802,7 +5805,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6008,7 +6011,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6089,7 +6092,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ25">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>1.21</v>
@@ -6214,7 +6217,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6420,7 +6423,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6626,7 +6629,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7244,7 +7247,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7322,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ31">
         <v>0.8</v>
@@ -7656,7 +7659,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8068,7 +8071,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8274,7 +8277,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8480,7 +8483,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8686,7 +8689,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9098,7 +9101,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9510,7 +9513,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9591,7 +9594,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ42">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9716,7 +9719,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10412,7 +10415,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ46">
         <v>1.67</v>
@@ -10540,7 +10543,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10746,7 +10749,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11158,7 +11161,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11570,7 +11573,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11776,7 +11779,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11857,7 +11860,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ53">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>2.55</v>
@@ -11982,7 +11985,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -12394,7 +12397,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12600,7 +12603,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12806,7 +12809,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -12884,7 +12887,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -13218,7 +13221,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13424,7 +13427,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13836,7 +13839,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14248,7 +14251,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14454,7 +14457,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14660,7 +14663,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14866,7 +14869,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15072,7 +15075,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15278,7 +15281,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15484,7 +15487,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15562,7 +15565,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ71">
         <v>1.67</v>
@@ -15690,7 +15693,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15896,7 +15899,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16102,7 +16105,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16308,7 +16311,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16386,7 +16389,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ75">
         <v>1.38</v>
@@ -16514,7 +16517,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16595,7 +16598,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ76">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -16720,7 +16723,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16926,7 +16929,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17132,7 +17135,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17544,7 +17547,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17956,7 +17959,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18162,7 +18165,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18368,7 +18371,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18986,7 +18989,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19398,7 +19401,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19604,7 +19607,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19810,7 +19813,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20016,7 +20019,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20222,7 +20225,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20379,6 +20382,212 @@
       </c>
       <c r="BP94">
         <v>1.72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7785263</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
+      </c>
+      <c r="G95" t="s">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s">
+        <v>82</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>151</v>
+      </c>
+      <c r="P95" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q95">
+        <v>1.95</v>
+      </c>
+      <c r="R95">
+        <v>2.63</v>
+      </c>
+      <c r="S95">
+        <v>5</v>
+      </c>
+      <c r="T95">
+        <v>1.22</v>
+      </c>
+      <c r="U95">
+        <v>4</v>
+      </c>
+      <c r="V95">
+        <v>2.1</v>
+      </c>
+      <c r="W95">
+        <v>1.67</v>
+      </c>
+      <c r="X95">
+        <v>4.5</v>
+      </c>
+      <c r="Y95">
+        <v>1.18</v>
+      </c>
+      <c r="Z95">
+        <v>1.46</v>
+      </c>
+      <c r="AA95">
+        <v>4.2</v>
+      </c>
+      <c r="AB95">
+        <v>5</v>
+      </c>
+      <c r="AC95">
+        <v>1.01</v>
+      </c>
+      <c r="AD95">
+        <v>17</v>
+      </c>
+      <c r="AE95">
+        <v>1.13</v>
+      </c>
+      <c r="AF95">
+        <v>5.75</v>
+      </c>
+      <c r="AG95">
+        <v>1.41</v>
+      </c>
+      <c r="AH95">
+        <v>2.78</v>
+      </c>
+      <c r="AI95">
+        <v>1.53</v>
+      </c>
+      <c r="AJ95">
+        <v>2.38</v>
+      </c>
+      <c r="AK95">
+        <v>1.16</v>
+      </c>
+      <c r="AL95">
+        <v>1.19</v>
+      </c>
+      <c r="AM95">
+        <v>2.4</v>
+      </c>
+      <c r="AN95">
+        <v>2</v>
+      </c>
+      <c r="AO95">
+        <v>0.6</v>
+      </c>
+      <c r="AP95">
+        <v>2.13</v>
+      </c>
+      <c r="AQ95">
+        <v>0.5</v>
+      </c>
+      <c r="AR95">
+        <v>1.99</v>
+      </c>
+      <c r="AS95">
+        <v>1.68</v>
+      </c>
+      <c r="AT95">
+        <v>3.67</v>
+      </c>
+      <c r="AU95">
+        <v>10</v>
+      </c>
+      <c r="AV95">
+        <v>3</v>
+      </c>
+      <c r="AW95">
+        <v>14</v>
+      </c>
+      <c r="AX95">
+        <v>5</v>
+      </c>
+      <c r="AY95">
+        <v>24</v>
+      </c>
+      <c r="AZ95">
+        <v>8</v>
+      </c>
+      <c r="BA95">
+        <v>9</v>
+      </c>
+      <c r="BB95">
+        <v>3</v>
+      </c>
+      <c r="BC95">
+        <v>12</v>
+      </c>
+      <c r="BD95">
+        <v>1.5</v>
+      </c>
+      <c r="BE95">
+        <v>7</v>
+      </c>
+      <c r="BF95">
+        <v>2.8</v>
+      </c>
+      <c r="BG95">
+        <v>1.19</v>
+      </c>
+      <c r="BH95">
+        <v>4.1</v>
+      </c>
+      <c r="BI95">
+        <v>1.33</v>
+      </c>
+      <c r="BJ95">
+        <v>2.95</v>
+      </c>
+      <c r="BK95">
+        <v>1.54</v>
+      </c>
+      <c r="BL95">
+        <v>2.3</v>
+      </c>
+      <c r="BM95">
+        <v>1.85</v>
+      </c>
+      <c r="BN95">
+        <v>1.83</v>
+      </c>
+      <c r="BO95">
+        <v>2.32</v>
+      </c>
+      <c r="BP95">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="214">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -427,7 +427,7 @@
     <t>['4', '14', '22', '41']</t>
   </si>
   <si>
-    <t>['24', '4501', '72']</t>
+    <t>['24', '45+1', '72']</t>
   </si>
   <si>
     <t>['74']</t>
@@ -439,7 +439,7 @@
     <t>['23', '42']</t>
   </si>
   <si>
-    <t>['8', '58', '86']</t>
+    <t>['8', '58', '64', '86']</t>
   </si>
   <si>
     <t>['21', '33', '35', '84']</t>
@@ -451,7 +451,7 @@
     <t>['49']</t>
   </si>
   <si>
-    <t>['53', '59', '70', '82', '9002']</t>
+    <t>['53', '59', '70', '82', '90+2']</t>
   </si>
   <si>
     <t>['7', '60', '80']</t>
@@ -472,6 +472,12 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -487,9 +493,6 @@
     <t>['5', '64']</t>
   </si>
   <si>
-    <t>['35']</t>
-  </si>
-  <si>
     <t>['45+1']</t>
   </si>
   <si>
@@ -574,9 +577,6 @@
     <t>['59']</t>
   </si>
   <si>
-    <t>['38']</t>
-  </si>
-  <si>
     <t>['21']</t>
   </si>
   <si>
@@ -616,13 +616,13 @@
     <t>['67']</t>
   </si>
   <si>
-    <t>['9011']</t>
+    <t>['90+11']</t>
   </si>
   <si>
     <t>['30', '40']</t>
   </si>
   <si>
-    <t>['68', '9002']</t>
+    <t>['68', '90+2']</t>
   </si>
   <si>
     <t>['7', '50', '67', '86']</t>
@@ -637,7 +637,7 @@
     <t>['7', '80', '84']</t>
   </si>
   <si>
-    <t>['4503']</t>
+    <t>['45+3']</t>
   </si>
   <si>
     <t>['20']</t>
@@ -646,7 +646,7 @@
     <t>['21', '26', '47']</t>
   </si>
   <si>
-    <t>['37', '9004']</t>
+    <t>['37', '90+4']</t>
   </si>
   <si>
     <t>['9']</t>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP95"/>
+  <dimension ref="A1:BP97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1273,7 +1273,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1560,7 +1560,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1891,7 +1891,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
         <v>1.38</v>
@@ -2097,7 +2097,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2303,7 +2303,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2715,7 +2715,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -3539,7 +3539,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3951,7 +3951,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4032,7 +4032,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ15">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4157,7 +4157,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4363,7 +4363,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17">
         <v>0.83</v>
@@ -4775,7 +4775,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19">
         <v>1.38</v>
@@ -4981,7 +4981,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5062,7 +5062,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ20">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>1.82</v>
@@ -5187,7 +5187,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5393,7 +5393,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5599,7 +5599,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
         <v>1.32</v>
@@ -5805,7 +5805,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6011,7 +6011,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6217,7 +6217,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
         <v>2.29</v>
@@ -6423,7 +6423,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6629,7 +6629,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7247,7 +7247,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7659,7 +7659,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8071,7 +8071,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8152,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.51</v>
@@ -8277,7 +8277,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8355,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36">
         <v>2.17</v>
@@ -8483,7 +8483,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -8689,7 +8689,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8973,7 +8973,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
         <v>0.83</v>
@@ -9101,7 +9101,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9182,7 +9182,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ40">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
         <v>2.08</v>
@@ -9385,7 +9385,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ41">
         <v>2</v>
@@ -9513,7 +9513,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9719,7 +9719,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10543,7 +10543,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10749,7 +10749,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11161,7 +11161,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11573,7 +11573,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11779,7 +11779,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11857,7 +11857,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ53">
         <v>0.5</v>
@@ -11985,7 +11985,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -13221,7 +13221,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13839,7 +13839,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13917,7 +13917,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63">
         <v>1.67</v>
@@ -14538,7 +14538,7 @@
         <v>3</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.95</v>
@@ -14744,7 +14744,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ67">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.35</v>
@@ -17422,7 +17422,7 @@
         <v>2</v>
       </c>
       <c r="AQ80">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -17741,13 +17741,13 @@
         <v>1</v>
       </c>
       <c r="L82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82">
         <v>0</v>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O82" t="s">
         <v>141</v>
@@ -18449,7 +18449,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ85">
         <v>2.17</v>
@@ -18658,7 +18658,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ86">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -18861,7 +18861,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ87">
         <v>0.8</v>
@@ -18989,7 +18989,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -20588,6 +20588,418 @@
       </c>
       <c r="BP95">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7785270</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45843.375</v>
+      </c>
+      <c r="F96">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>73</v>
+      </c>
+      <c r="H96" t="s">
+        <v>80</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>2</v>
+      </c>
+      <c r="O96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P96" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q96">
+        <v>4.33</v>
+      </c>
+      <c r="R96">
+        <v>2.38</v>
+      </c>
+      <c r="S96">
+        <v>2.38</v>
+      </c>
+      <c r="T96">
+        <v>1.3</v>
+      </c>
+      <c r="U96">
+        <v>3.4</v>
+      </c>
+      <c r="V96">
+        <v>2.38</v>
+      </c>
+      <c r="W96">
+        <v>1.53</v>
+      </c>
+      <c r="X96">
+        <v>6</v>
+      </c>
+      <c r="Y96">
+        <v>1.13</v>
+      </c>
+      <c r="Z96">
+        <v>4.1</v>
+      </c>
+      <c r="AA96">
+        <v>3.73</v>
+      </c>
+      <c r="AB96">
+        <v>1.64</v>
+      </c>
+      <c r="AC96">
+        <v>1.03</v>
+      </c>
+      <c r="AD96">
+        <v>12</v>
+      </c>
+      <c r="AE96">
+        <v>1.21</v>
+      </c>
+      <c r="AF96">
+        <v>4.51</v>
+      </c>
+      <c r="AG96">
+        <v>1.57</v>
+      </c>
+      <c r="AH96">
+        <v>2.31</v>
+      </c>
+      <c r="AI96">
+        <v>1.62</v>
+      </c>
+      <c r="AJ96">
+        <v>2.2</v>
+      </c>
+      <c r="AK96">
+        <v>1.9</v>
+      </c>
+      <c r="AL96">
+        <v>1.25</v>
+      </c>
+      <c r="AM96">
+        <v>1.25</v>
+      </c>
+      <c r="AN96">
+        <v>1.4</v>
+      </c>
+      <c r="AO96">
+        <v>1.8</v>
+      </c>
+      <c r="AP96">
+        <v>1.33</v>
+      </c>
+      <c r="AQ96">
+        <v>1.67</v>
+      </c>
+      <c r="AR96">
+        <v>1.39</v>
+      </c>
+      <c r="AS96">
+        <v>1.79</v>
+      </c>
+      <c r="AT96">
+        <v>3.18</v>
+      </c>
+      <c r="AU96">
+        <v>5</v>
+      </c>
+      <c r="AV96">
+        <v>4</v>
+      </c>
+      <c r="AW96">
+        <v>4</v>
+      </c>
+      <c r="AX96">
+        <v>8</v>
+      </c>
+      <c r="AY96">
+        <v>9</v>
+      </c>
+      <c r="AZ96">
+        <v>12</v>
+      </c>
+      <c r="BA96">
+        <v>1</v>
+      </c>
+      <c r="BB96">
+        <v>8</v>
+      </c>
+      <c r="BC96">
+        <v>9</v>
+      </c>
+      <c r="BD96">
+        <v>2.65</v>
+      </c>
+      <c r="BE96">
+        <v>7</v>
+      </c>
+      <c r="BF96">
+        <v>1.56</v>
+      </c>
+      <c r="BG96">
+        <v>1.16</v>
+      </c>
+      <c r="BH96">
+        <v>4.6</v>
+      </c>
+      <c r="BI96">
+        <v>1.28</v>
+      </c>
+      <c r="BJ96">
+        <v>3.3</v>
+      </c>
+      <c r="BK96">
+        <v>1.47</v>
+      </c>
+      <c r="BL96">
+        <v>2.48</v>
+      </c>
+      <c r="BM96">
+        <v>1.73</v>
+      </c>
+      <c r="BN96">
+        <v>1.98</v>
+      </c>
+      <c r="BO96">
+        <v>2.08</v>
+      </c>
+      <c r="BP96">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7785276</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45843.45833333334</v>
+      </c>
+      <c r="F97">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>85</v>
+      </c>
+      <c r="H97" t="s">
+        <v>70</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>153</v>
+      </c>
+      <c r="P97" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q97">
+        <v>1.57</v>
+      </c>
+      <c r="R97">
+        <v>3.2</v>
+      </c>
+      <c r="S97">
+        <v>7.5</v>
+      </c>
+      <c r="T97">
+        <v>1.14</v>
+      </c>
+      <c r="U97">
+        <v>5.5</v>
+      </c>
+      <c r="V97">
+        <v>1.73</v>
+      </c>
+      <c r="W97">
+        <v>2</v>
+      </c>
+      <c r="X97">
+        <v>3.4</v>
+      </c>
+      <c r="Y97">
+        <v>1.3</v>
+      </c>
+      <c r="Z97">
+        <v>1.25</v>
+      </c>
+      <c r="AA97">
+        <v>5.3</v>
+      </c>
+      <c r="AB97">
+        <v>7.6</v>
+      </c>
+      <c r="AC97">
+        <v>1</v>
+      </c>
+      <c r="AD97">
+        <v>25</v>
+      </c>
+      <c r="AE97">
+        <v>1.04</v>
+      </c>
+      <c r="AF97">
+        <v>9.5</v>
+      </c>
+      <c r="AG97">
+        <v>1.28</v>
+      </c>
+      <c r="AH97">
+        <v>3.47</v>
+      </c>
+      <c r="AI97">
+        <v>1.57</v>
+      </c>
+      <c r="AJ97">
+        <v>2.25</v>
+      </c>
+      <c r="AK97">
+        <v>1.06</v>
+      </c>
+      <c r="AL97">
+        <v>1.07</v>
+      </c>
+      <c r="AM97">
+        <v>3.7</v>
+      </c>
+      <c r="AN97">
+        <v>2.43</v>
+      </c>
+      <c r="AO97">
+        <v>1.2</v>
+      </c>
+      <c r="AP97">
+        <v>2.5</v>
+      </c>
+      <c r="AQ97">
+        <v>1</v>
+      </c>
+      <c r="AR97">
+        <v>2.35</v>
+      </c>
+      <c r="AS97">
+        <v>1.53</v>
+      </c>
+      <c r="AT97">
+        <v>3.88</v>
+      </c>
+      <c r="AU97">
+        <v>6</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>14</v>
+      </c>
+      <c r="AX97">
+        <v>1</v>
+      </c>
+      <c r="AY97">
+        <v>20</v>
+      </c>
+      <c r="AZ97">
+        <v>3</v>
+      </c>
+      <c r="BA97">
+        <v>16</v>
+      </c>
+      <c r="BB97">
+        <v>2</v>
+      </c>
+      <c r="BC97">
+        <v>18</v>
+      </c>
+      <c r="BD97">
+        <v>1.26</v>
+      </c>
+      <c r="BE97">
+        <v>8.5</v>
+      </c>
+      <c r="BF97">
+        <v>3.95</v>
+      </c>
+      <c r="BG97">
+        <v>1.08</v>
+      </c>
+      <c r="BH97">
+        <v>6.25</v>
+      </c>
+      <c r="BI97">
+        <v>1.16</v>
+      </c>
+      <c r="BJ97">
+        <v>4.4</v>
+      </c>
+      <c r="BK97">
+        <v>1.28</v>
+      </c>
+      <c r="BL97">
+        <v>3.3</v>
+      </c>
+      <c r="BM97">
+        <v>1.47</v>
+      </c>
+      <c r="BN97">
+        <v>2.48</v>
+      </c>
+      <c r="BO97">
+        <v>1.7</v>
+      </c>
+      <c r="BP97">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="217">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -478,6 +478,12 @@
     <t>['38']</t>
   </si>
   <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -656,6 +662,9 @@
   </si>
   <si>
     <t>['39', '46']</t>
+  </si>
+  <si>
+    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP97"/>
+  <dimension ref="A1:BP99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1273,7 +1282,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1685,7 +1694,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1763,7 +1772,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4">
         <v>2.29</v>
@@ -1891,7 +1900,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2097,7 +2106,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2303,7 +2312,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2796,7 +2805,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3208,7 +3217,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ11">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3539,7 +3548,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3951,7 +3960,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4157,7 +4166,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4235,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ16">
         <v>0.8</v>
@@ -4363,7 +4372,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4775,7 +4784,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4981,7 +4990,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5187,7 +5196,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5393,7 +5402,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5471,7 +5480,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ22">
         <v>1.67</v>
@@ -5599,7 +5608,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5805,7 +5814,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6011,7 +6020,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6217,7 +6226,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6423,7 +6432,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6629,7 +6638,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6710,7 +6719,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ28">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -7247,7 +7256,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7534,7 +7543,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ32">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR32">
         <v>1.53</v>
@@ -7659,7 +7668,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7737,7 +7746,7 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33">
         <v>1.43</v>
@@ -8071,7 +8080,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8277,7 +8286,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8483,7 +8492,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8689,7 +8698,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9101,7 +9110,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9179,7 +9188,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ40">
         <v>1.67</v>
@@ -9513,7 +9522,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9719,7 +9728,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10543,7 +10552,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10749,7 +10758,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11033,10 +11042,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>1.56</v>
@@ -11161,7 +11170,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11573,7 +11582,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11779,7 +11788,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12066,7 +12075,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ54">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12397,7 +12406,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12603,7 +12612,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12809,7 +12818,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13221,7 +13230,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13299,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ60">
         <v>0.83</v>
@@ -13427,7 +13436,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13508,7 +13517,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ61">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR61">
         <v>1.27</v>
@@ -13839,7 +13848,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14251,7 +14260,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14329,7 +14338,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ65">
         <v>2.29</v>
@@ -14457,7 +14466,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14663,7 +14672,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14869,7 +14878,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15075,7 +15084,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15281,7 +15290,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15487,7 +15496,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15693,7 +15702,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15899,7 +15908,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16105,7 +16114,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16311,7 +16320,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16517,7 +16526,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16723,7 +16732,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16804,7 +16813,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ77">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AR77">
         <v>1.3</v>
@@ -16929,7 +16938,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17135,7 +17144,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17547,7 +17556,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17625,7 +17634,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AQ81">
         <v>1.67</v>
@@ -17959,7 +17968,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18037,7 +18046,7 @@
         <v>2</v>
       </c>
       <c r="AP83">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ83">
         <v>1.67</v>
@@ -18165,7 +18174,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18371,7 +18380,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18864,7 +18873,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ87">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR87">
         <v>2.49</v>
@@ -18989,7 +18998,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19401,7 +19410,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19607,7 +19616,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19813,7 +19822,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20019,7 +20028,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20225,7 +20234,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20637,7 +20646,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21000,6 +21009,418 @@
       </c>
       <c r="BP97">
         <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7785277</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45843.54166666666</v>
+      </c>
+      <c r="F98">
+        <v>12</v>
+      </c>
+      <c r="G98" t="s">
+        <v>72</v>
+      </c>
+      <c r="H98" t="s">
+        <v>71</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>154</v>
+      </c>
+      <c r="P98" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q98">
+        <v>2.75</v>
+      </c>
+      <c r="R98">
+        <v>2.1</v>
+      </c>
+      <c r="S98">
+        <v>4</v>
+      </c>
+      <c r="T98">
+        <v>1.4</v>
+      </c>
+      <c r="U98">
+        <v>2.75</v>
+      </c>
+      <c r="V98">
+        <v>3</v>
+      </c>
+      <c r="W98">
+        <v>1.36</v>
+      </c>
+      <c r="X98">
+        <v>8</v>
+      </c>
+      <c r="Y98">
+        <v>1.08</v>
+      </c>
+      <c r="Z98">
+        <v>2.16</v>
+      </c>
+      <c r="AA98">
+        <v>3.06</v>
+      </c>
+      <c r="AB98">
+        <v>3.03</v>
+      </c>
+      <c r="AC98">
+        <v>1.06</v>
+      </c>
+      <c r="AD98">
+        <v>8.5</v>
+      </c>
+      <c r="AE98">
+        <v>1.33</v>
+      </c>
+      <c r="AF98">
+        <v>3.25</v>
+      </c>
+      <c r="AG98">
+        <v>1.9</v>
+      </c>
+      <c r="AH98">
+        <v>1.8</v>
+      </c>
+      <c r="AI98">
+        <v>1.8</v>
+      </c>
+      <c r="AJ98">
+        <v>1.95</v>
+      </c>
+      <c r="AK98">
+        <v>1.3</v>
+      </c>
+      <c r="AL98">
+        <v>1.28</v>
+      </c>
+      <c r="AM98">
+        <v>1.67</v>
+      </c>
+      <c r="AN98">
+        <v>0.8</v>
+      </c>
+      <c r="AO98">
+        <v>0.8</v>
+      </c>
+      <c r="AP98">
+        <v>0.83</v>
+      </c>
+      <c r="AQ98">
+        <v>0.83</v>
+      </c>
+      <c r="AR98">
+        <v>2.13</v>
+      </c>
+      <c r="AS98">
+        <v>1.17</v>
+      </c>
+      <c r="AT98">
+        <v>3.3</v>
+      </c>
+      <c r="AU98">
+        <v>8</v>
+      </c>
+      <c r="AV98">
+        <v>9</v>
+      </c>
+      <c r="AW98">
+        <v>3</v>
+      </c>
+      <c r="AX98">
+        <v>6</v>
+      </c>
+      <c r="AY98">
+        <v>11</v>
+      </c>
+      <c r="AZ98">
+        <v>15</v>
+      </c>
+      <c r="BA98">
+        <v>5</v>
+      </c>
+      <c r="BB98">
+        <v>5</v>
+      </c>
+      <c r="BC98">
+        <v>10</v>
+      </c>
+      <c r="BD98">
+        <v>1.65</v>
+      </c>
+      <c r="BE98">
+        <v>6.75</v>
+      </c>
+      <c r="BF98">
+        <v>2.48</v>
+      </c>
+      <c r="BG98">
+        <v>1.21</v>
+      </c>
+      <c r="BH98">
+        <v>3.9</v>
+      </c>
+      <c r="BI98">
+        <v>1.38</v>
+      </c>
+      <c r="BJ98">
+        <v>2.8</v>
+      </c>
+      <c r="BK98">
+        <v>1.61</v>
+      </c>
+      <c r="BL98">
+        <v>2.15</v>
+      </c>
+      <c r="BM98">
+        <v>1.96</v>
+      </c>
+      <c r="BN98">
+        <v>1.74</v>
+      </c>
+      <c r="BO98">
+        <v>2.43</v>
+      </c>
+      <c r="BP98">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7785272</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45843.625</v>
+      </c>
+      <c r="F99">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>84</v>
+      </c>
+      <c r="H99" t="s">
+        <v>78</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>155</v>
+      </c>
+      <c r="P99" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q99">
+        <v>6.5</v>
+      </c>
+      <c r="R99">
+        <v>2.75</v>
+      </c>
+      <c r="S99">
+        <v>1.8</v>
+      </c>
+      <c r="T99">
+        <v>1.22</v>
+      </c>
+      <c r="U99">
+        <v>4</v>
+      </c>
+      <c r="V99">
+        <v>2</v>
+      </c>
+      <c r="W99">
+        <v>1.73</v>
+      </c>
+      <c r="X99">
+        <v>4.33</v>
+      </c>
+      <c r="Y99">
+        <v>1.2</v>
+      </c>
+      <c r="Z99">
+        <v>6.8</v>
+      </c>
+      <c r="AA99">
+        <v>5.1</v>
+      </c>
+      <c r="AB99">
+        <v>1.29</v>
+      </c>
+      <c r="AC99">
+        <v>1.02</v>
+      </c>
+      <c r="AD99">
+        <v>21</v>
+      </c>
+      <c r="AE99">
+        <v>1.11</v>
+      </c>
+      <c r="AF99">
+        <v>6.25</v>
+      </c>
+      <c r="AG99">
+        <v>1.38</v>
+      </c>
+      <c r="AH99">
+        <v>2.9</v>
+      </c>
+      <c r="AI99">
+        <v>1.67</v>
+      </c>
+      <c r="AJ99">
+        <v>2.1</v>
+      </c>
+      <c r="AK99">
+        <v>2.9</v>
+      </c>
+      <c r="AL99">
+        <v>1.11</v>
+      </c>
+      <c r="AM99">
+        <v>1.1</v>
+      </c>
+      <c r="AN99">
+        <v>1.2</v>
+      </c>
+      <c r="AO99">
+        <v>1.75</v>
+      </c>
+      <c r="AP99">
+        <v>1.17</v>
+      </c>
+      <c r="AQ99">
+        <v>1.6</v>
+      </c>
+      <c r="AR99">
+        <v>1.51</v>
+      </c>
+      <c r="AS99">
+        <v>1.47</v>
+      </c>
+      <c r="AT99">
+        <v>2.98</v>
+      </c>
+      <c r="AU99">
+        <v>3</v>
+      </c>
+      <c r="AV99">
+        <v>6</v>
+      </c>
+      <c r="AW99">
+        <v>6</v>
+      </c>
+      <c r="AX99">
+        <v>15</v>
+      </c>
+      <c r="AY99">
+        <v>9</v>
+      </c>
+      <c r="AZ99">
+        <v>21</v>
+      </c>
+      <c r="BA99">
+        <v>4</v>
+      </c>
+      <c r="BB99">
+        <v>7</v>
+      </c>
+      <c r="BC99">
+        <v>11</v>
+      </c>
+      <c r="BD99">
+        <v>3.65</v>
+      </c>
+      <c r="BE99">
+        <v>8</v>
+      </c>
+      <c r="BF99">
+        <v>1.3</v>
+      </c>
+      <c r="BG99">
+        <v>1.14</v>
+      </c>
+      <c r="BH99">
+        <v>4.8</v>
+      </c>
+      <c r="BI99">
+        <v>1.26</v>
+      </c>
+      <c r="BJ99">
+        <v>3.4</v>
+      </c>
+      <c r="BK99">
+        <v>1.44</v>
+      </c>
+      <c r="BL99">
+        <v>2.55</v>
+      </c>
+      <c r="BM99">
+        <v>1.7</v>
+      </c>
+      <c r="BN99">
+        <v>2.02</v>
+      </c>
+      <c r="BO99">
+        <v>2.05</v>
+      </c>
+      <c r="BP99">
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="193">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -424,177 +424,141 @@
     <t>['52', '68']</t>
   </si>
   <si>
-    <t>['4', '14', '22', '41']</t>
-  </si>
-  <si>
-    <t>['24', '45+1', '72']</t>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['45']</t>
+  </si>
+  <si>
+    <t>['90+7']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['39', '49']</t>
+  </si>
+  <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['2']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['5', '64']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
+    <t>['15', '25', '48', '79', '90+2']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['57', '74', '89']</t>
+  </si>
+  <si>
+    <t>['2', '65']</t>
+  </si>
+  <si>
+    <t>['77', '90+5']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['2', '4', '13', '37', '54']</t>
+  </si>
+  <si>
+    <t>['3', '28', '52']</t>
+  </si>
+  <si>
+    <t>['34', '44']</t>
+  </si>
+  <si>
+    <t>['8', '15']</t>
+  </si>
+  <si>
+    <t>['72', '90+4']</t>
+  </si>
+  <si>
+    <t>['19', '51', '85']</t>
+  </si>
+  <si>
+    <t>['9', '47', '55', '90+8']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['90+9']</t>
+  </si>
+  <si>
+    <t>['4', '36', '81', '90+6']</t>
+  </si>
+  <si>
+    <t>['62']</t>
+  </si>
+  <si>
+    <t>['55', '87']</t>
+  </si>
+  <si>
+    <t>['18', '37', '39']</t>
+  </si>
+  <si>
+    <t>['5', '90+2', '90+4']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['35', '45+2', '89', '90+7']</t>
+  </si>
+  <si>
+    <t>['59']</t>
+  </si>
+  <si>
+    <t>['21']</t>
+  </si>
+  <si>
+    <t>['6', '69']</t>
+  </si>
+  <si>
+    <t>['30', '90+5']</t>
+  </si>
+  <si>
+    <t>['26', '33', '88']</t>
   </si>
   <si>
     <t>['74']</t>
   </si>
   <si>
-    <t>['5', '40', '47']</t>
-  </si>
-  <si>
-    <t>['23', '42']</t>
-  </si>
-  <si>
-    <t>['8', '58', '64', '86']</t>
-  </si>
-  <si>
-    <t>['21', '33', '35', '84']</t>
-  </si>
-  <si>
-    <t>['30']</t>
-  </si>
-  <si>
-    <t>['49']</t>
-  </si>
-  <si>
-    <t>['53', '59', '70', '82', '90+2']</t>
-  </si>
-  <si>
-    <t>['7', '60', '80']</t>
-  </si>
-  <si>
-    <t>['70']</t>
-  </si>
-  <si>
-    <t>['34']</t>
-  </si>
-  <si>
-    <t>['46']</t>
-  </si>
-  <si>
-    <t>['49', '71']</t>
-  </si>
-  <si>
-    <t>['89']</t>
-  </si>
-  <si>
-    <t>['35']</t>
-  </si>
-  <si>
-    <t>['38']</t>
-  </si>
-  <si>
-    <t>['45']</t>
-  </si>
-  <si>
-    <t>['90+7']</t>
-  </si>
-  <si>
-    <t>['39', '49']</t>
-  </si>
-  <si>
-    <t>['63']</t>
-  </si>
-  <si>
-    <t>['2']</t>
-  </si>
-  <si>
-    <t>['43']</t>
-  </si>
-  <si>
-    <t>['5', '64']</t>
-  </si>
-  <si>
-    <t>['45+1']</t>
-  </si>
-  <si>
-    <t>['15', '25', '48', '79', '90+2']</t>
-  </si>
-  <si>
-    <t>['11']</t>
-  </si>
-  <si>
-    <t>['29']</t>
-  </si>
-  <si>
-    <t>['28']</t>
-  </si>
-  <si>
-    <t>['50']</t>
-  </si>
-  <si>
-    <t>['57', '74', '89']</t>
-  </si>
-  <si>
-    <t>['2', '65']</t>
-  </si>
-  <si>
-    <t>['77', '90+5']</t>
-  </si>
-  <si>
-    <t>['71']</t>
-  </si>
-  <si>
-    <t>['44']</t>
-  </si>
-  <si>
-    <t>['2', '4', '13', '37', '54']</t>
-  </si>
-  <si>
-    <t>['3', '28', '52']</t>
-  </si>
-  <si>
-    <t>['34', '44']</t>
-  </si>
-  <si>
-    <t>['8', '15']</t>
-  </si>
-  <si>
-    <t>['72', '90+4']</t>
-  </si>
-  <si>
-    <t>['19', '51', '85']</t>
-  </si>
-  <si>
-    <t>['9', '47', '55', '90+8']</t>
-  </si>
-  <si>
-    <t>['36']</t>
-  </si>
-  <si>
-    <t>['90+9']</t>
-  </si>
-  <si>
-    <t>['4', '36', '81', '90+6']</t>
-  </si>
-  <si>
-    <t>['62']</t>
-  </si>
-  <si>
-    <t>['55', '87']</t>
-  </si>
-  <si>
-    <t>['18', '37', '39']</t>
-  </si>
-  <si>
-    <t>['5', '90+2', '90+4']</t>
-  </si>
-  <si>
-    <t>['39']</t>
-  </si>
-  <si>
-    <t>['35', '45+2', '89', '90+7']</t>
-  </si>
-  <si>
-    <t>['59']</t>
-  </si>
-  <si>
-    <t>['21']</t>
-  </si>
-  <si>
-    <t>['6', '69']</t>
-  </si>
-  <si>
-    <t>['30', '90+5']</t>
-  </si>
-  <si>
-    <t>['26', '33', '88']</t>
-  </si>
-  <si>
     <t>['57']</t>
   </si>
   <si>
@@ -622,49 +586,13 @@
     <t>['67']</t>
   </si>
   <si>
-    <t>['90+11']</t>
-  </si>
-  <si>
-    <t>['30', '40']</t>
-  </si>
-  <si>
-    <t>['68', '90+2']</t>
-  </si>
-  <si>
-    <t>['7', '50', '67', '86']</t>
-  </si>
-  <si>
     <t>['83']</t>
   </si>
   <si>
-    <t>['3']</t>
-  </si>
-  <si>
-    <t>['7', '80', '84']</t>
-  </si>
-  <si>
-    <t>['45+3']</t>
-  </si>
-  <si>
-    <t>['20']</t>
-  </si>
-  <si>
-    <t>['21', '26', '47']</t>
-  </si>
-  <si>
-    <t>['37', '90+4']</t>
+    <t>['4']</t>
   </si>
   <si>
     <t>['9']</t>
-  </si>
-  <si>
-    <t>['34', '41', '56']</t>
-  </si>
-  <si>
-    <t>['39', '46']</t>
-  </si>
-  <si>
-    <t>['4']</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP99"/>
+  <dimension ref="A1:BP78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1282,7 +1210,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1363,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1566,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1694,7 +1622,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1772,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1900,7 +1828,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1978,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2106,7 +2034,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2184,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2312,7 +2240,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2390,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2596,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -2724,7 +2652,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -2802,10 +2730,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3008,10 +2936,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3214,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AQ11">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3342,7 +3270,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3420,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AQ12">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3548,7 +3476,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3629,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3835,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3960,7 +3888,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4038,10 +3966,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4166,7 +4094,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4244,10 +4172,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4372,7 +4300,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4450,10 +4378,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4656,10 +4584,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AQ18">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR18">
         <v>0.92</v>
@@ -4784,7 +4712,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4862,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AR19">
         <v>2.02</v>
@@ -4990,7 +4918,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5068,10 +4996,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR20">
         <v>1.82</v>
@@ -5196,7 +5124,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5274,10 +5202,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
         <v>1.94</v>
@@ -5402,7 +5330,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5480,10 +5408,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR22">
         <v>1.7</v>
@@ -5608,7 +5536,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5689,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR23">
         <v>1.32</v>
@@ -5814,7 +5742,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5892,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>0</v>
@@ -6020,7 +5948,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6098,10 +6026,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AR25">
         <v>1.21</v>
@@ -6226,7 +6154,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6304,10 +6232,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AQ26">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AR26">
         <v>1.31</v>
@@ -6432,7 +6360,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6510,7 +6438,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AQ27">
         <v>2</v>
@@ -6638,7 +6566,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6716,10 +6644,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -6922,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AQ29">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7128,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ30">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
       <c r="AR30">
         <v>2.59</v>
@@ -7256,7 +7184,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7334,10 +7262,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AQ31">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.79</v>
@@ -7540,10 +7468,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ32">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.53</v>
@@ -7668,7 +7596,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7746,10 +7674,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
+        <v>0.8</v>
+      </c>
+      <c r="AQ33">
         <v>1.17</v>
-      </c>
-      <c r="AQ33">
-        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>1.87</v>
@@ -7955,7 +7883,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR34">
         <v>2.49</v>
@@ -8080,7 +8008,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8161,7 +8089,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR35">
         <v>1.51</v>
@@ -8286,7 +8214,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8364,10 +8292,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ36">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AR36">
         <v>2</v>
@@ -8492,7 +8420,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8570,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -8698,7 +8626,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8776,10 +8704,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AQ38">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AR38">
         <v>1.75</v>
@@ -8982,10 +8910,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AQ39">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
       <c r="AR39">
         <v>1.22</v>
@@ -9110,7 +9038,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9188,10 +9116,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR40">
         <v>2.08</v>
@@ -9394,7 +9322,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ41">
         <v>2</v>
@@ -9522,7 +9450,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9600,10 +9528,10 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9728,7 +9656,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -9809,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AR43">
         <v>1.63</v>
@@ -10012,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>0</v>
@@ -10218,10 +10146,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AQ45">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR45">
         <v>2.27</v>
@@ -10424,10 +10352,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AQ46">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR46">
         <v>1.95</v>
@@ -10552,7 +10480,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10630,10 +10558,10 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR47">
         <v>1.44</v>
@@ -10758,7 +10686,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10836,10 +10764,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AQ48">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -10964,7 +10892,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="Q49">
         <v>3.4</v>
@@ -11042,10 +10970,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR49">
         <v>1.56</v>
@@ -11170,7 +11098,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11251,7 +11179,7 @@
         <v>3</v>
       </c>
       <c r="AQ50">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11457,7 +11385,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11582,7 +11510,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11660,10 +11588,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ52">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AR52">
         <v>1.29</v>
@@ -11788,7 +11716,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11866,10 +11794,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AR53">
         <v>2.55</v>
@@ -11994,7 +11922,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -12072,10 +12000,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12278,7 +12206,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AQ55">
         <v>0</v>
@@ -12406,7 +12334,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12484,10 +12412,10 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -12612,7 +12540,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12693,7 +12621,7 @@
         <v>0</v>
       </c>
       <c r="AQ57">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -12818,7 +12746,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -12896,7 +12824,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -13102,10 +13030,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AQ59">
-        <v>0.83</v>
+        <v>0.25</v>
       </c>
       <c r="AR59">
         <v>1.16</v>
@@ -13230,7 +13158,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13308,10 +13236,10 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AQ60">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR60">
         <v>2.1</v>
@@ -13436,7 +13364,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13514,10 +13442,10 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AQ61">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR61">
         <v>1.27</v>
@@ -13720,10 +13648,10 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ62">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR62">
         <v>2.13</v>
@@ -13848,7 +13776,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13926,10 +13854,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AQ63">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR63">
         <v>1.3</v>
@@ -14054,7 +13982,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="Q64">
         <v>2.6</v>
@@ -14135,7 +14063,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AR64">
         <v>1.85</v>
@@ -14260,7 +14188,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14338,10 +14266,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.17</v>
+        <v>0.8</v>
       </c>
       <c r="AQ65">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AR65">
         <v>1.38</v>
@@ -14466,7 +14394,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14547,7 +14475,7 @@
         <v>3</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
         <v>1.95</v>
@@ -14672,7 +14600,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14750,10 +14678,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR67">
         <v>1.35</v>
@@ -14878,7 +14806,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -14956,10 +14884,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="AQ68">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR68">
         <v>1.1</v>
@@ -15084,7 +15012,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15162,10 +15090,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AQ69">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AR69">
         <v>1.11</v>
@@ -15290,7 +15218,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15368,10 +15296,10 @@
         <v>2.25</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AR70">
         <v>2.02</v>
@@ -15496,7 +15424,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15574,10 +15502,10 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AQ71">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AR71">
         <v>1.99</v>
@@ -15702,7 +15630,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15783,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="AQ72">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -15908,7 +15836,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -15986,10 +15914,10 @@
         <v>1.4</v>
       </c>
       <c r="AP73">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16072,7 +16000,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>7785248</v>
+        <v>7785270</v>
       </c>
       <c r="C74" t="s">
         <v>68</v>
@@ -16081,25 +16009,25 @@
         <v>69</v>
       </c>
       <c r="E74" s="2">
-        <v>45809.39583333334</v>
+        <v>45843.375</v>
       </c>
       <c r="F74">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -16111,166 +16039,166 @@
         <v>2</v>
       </c>
       <c r="O74" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="Q74">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R74">
+        <v>2.38</v>
+      </c>
+      <c r="S74">
+        <v>2.38</v>
+      </c>
+      <c r="T74">
+        <v>1.3</v>
+      </c>
+      <c r="U74">
+        <v>3.4</v>
+      </c>
+      <c r="V74">
+        <v>2.38</v>
+      </c>
+      <c r="W74">
+        <v>1.53</v>
+      </c>
+      <c r="X74">
+        <v>6</v>
+      </c>
+      <c r="Y74">
+        <v>1.13</v>
+      </c>
+      <c r="Z74">
+        <v>4.1</v>
+      </c>
+      <c r="AA74">
+        <v>3.73</v>
+      </c>
+      <c r="AB74">
+        <v>1.64</v>
+      </c>
+      <c r="AC74">
+        <v>1.03</v>
+      </c>
+      <c r="AD74">
+        <v>12</v>
+      </c>
+      <c r="AE74">
+        <v>1.21</v>
+      </c>
+      <c r="AF74">
+        <v>4.51</v>
+      </c>
+      <c r="AG74">
+        <v>1.57</v>
+      </c>
+      <c r="AH74">
+        <v>2.31</v>
+      </c>
+      <c r="AI74">
+        <v>1.62</v>
+      </c>
+      <c r="AJ74">
         <v>2.2</v>
       </c>
-      <c r="S74">
-        <v>3.75</v>
-      </c>
-      <c r="T74">
-        <v>1.33</v>
-      </c>
-      <c r="U74">
-        <v>3</v>
-      </c>
-      <c r="V74">
-        <v>2.45</v>
-      </c>
-      <c r="W74">
-        <v>1.48</v>
-      </c>
-      <c r="X74">
-        <v>5.85</v>
-      </c>
-      <c r="Y74">
-        <v>1.07</v>
-      </c>
-      <c r="Z74">
-        <v>1.93</v>
-      </c>
-      <c r="AA74">
-        <v>3.45</v>
-      </c>
-      <c r="AB74">
-        <v>3.21</v>
-      </c>
-      <c r="AC74">
-        <v>1.04</v>
-      </c>
-      <c r="AD74">
-        <v>10</v>
-      </c>
-      <c r="AE74">
+      <c r="AK74">
+        <v>1.9</v>
+      </c>
+      <c r="AL74">
         <v>1.25</v>
       </c>
-      <c r="AF74">
-        <v>3.95</v>
-      </c>
-      <c r="AG74">
-        <v>1.72</v>
-      </c>
-      <c r="AH74">
-        <v>2</v>
-      </c>
-      <c r="AI74">
+      <c r="AM74">
+        <v>1.25</v>
+      </c>
+      <c r="AN74">
+        <v>1.75</v>
+      </c>
+      <c r="AO74">
+        <v>2.25</v>
+      </c>
+      <c r="AP74">
         <v>1.6</v>
       </c>
-      <c r="AJ74">
-        <v>2.15</v>
-      </c>
-      <c r="AK74">
-        <v>1.3</v>
-      </c>
-      <c r="AL74">
-        <v>1.22</v>
-      </c>
-      <c r="AM74">
-        <v>1.77</v>
-      </c>
-      <c r="AN74">
-        <v>2.4</v>
-      </c>
-      <c r="AO74">
-        <v>2</v>
-      </c>
-      <c r="AP74">
-        <v>1.86</v>
-      </c>
       <c r="AQ74">
         <v>2</v>
       </c>
       <c r="AR74">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AS74">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AT74">
-        <v>2.77</v>
+        <v>3.17</v>
       </c>
       <c r="AU74">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV74">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AW74">
         <v>4</v>
       </c>
       <c r="AX74">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY74">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ74">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA74">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BB74">
+        <v>8</v>
+      </c>
+      <c r="BC74">
         <v>9</v>
       </c>
-      <c r="BC74">
-        <v>15</v>
-      </c>
       <c r="BD74">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="BE74">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF74">
-        <v>2.45</v>
+        <v>1.56</v>
       </c>
       <c r="BG74">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="BH74">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="BI74">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="BJ74">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="BK74">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="BL74">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="BM74">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="BN74">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="BO74">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="BP74">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="75" spans="1:68">
@@ -16278,7 +16206,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>7785249</v>
+        <v>7785276</v>
       </c>
       <c r="C75" t="s">
         <v>68</v>
@@ -16287,196 +16215,196 @@
         <v>69</v>
       </c>
       <c r="E75" s="2">
-        <v>45809.5</v>
+        <v>45843.45833333334</v>
       </c>
       <c r="F75">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G75" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H75" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O75" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="Q75">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="R75">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="S75">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="T75">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="U75">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="V75">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="W75">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="X75">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y75">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
         <v>1.25</v>
       </c>
       <c r="AA75">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AB75">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC75">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD75">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF75">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="AG75">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH75">
-        <v>2.86</v>
+        <v>3.47</v>
       </c>
       <c r="AI75">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AJ75">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AK75">
         <v>1.06</v>
       </c>
       <c r="AL75">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AM75">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AN75">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AO75">
+        <v>1.5</v>
+      </c>
+      <c r="AP75">
+        <v>2.43</v>
+      </c>
+      <c r="AQ75">
+        <v>1.2</v>
+      </c>
+      <c r="AR75">
+        <v>2.49</v>
+      </c>
+      <c r="AS75">
         <v>1.67</v>
       </c>
-      <c r="AP75">
-        <v>2.13</v>
-      </c>
-      <c r="AQ75">
-        <v>1.38</v>
-      </c>
-      <c r="AR75">
-        <v>1.99</v>
-      </c>
-      <c r="AS75">
-        <v>1.18</v>
-      </c>
       <c r="AT75">
-        <v>3.17</v>
+        <v>4.16</v>
       </c>
       <c r="AU75">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV75">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW75">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AX75">
+        <v>1</v>
+      </c>
+      <c r="AY75">
+        <v>20</v>
+      </c>
+      <c r="AZ75">
         <v>3</v>
       </c>
-      <c r="AY75">
-        <v>11</v>
-      </c>
-      <c r="AZ75">
-        <v>8</v>
-      </c>
       <c r="BA75">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="BB75">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BC75">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BD75">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="BE75">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BF75">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BG75">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="BH75">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="BI75">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="BJ75">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BK75">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="BL75">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="BM75">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="BN75">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="BO75">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="BP75">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:68">
@@ -16484,7 +16412,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>7785250</v>
+        <v>7785277</v>
       </c>
       <c r="C76" t="s">
         <v>68</v>
@@ -16493,49 +16421,49 @@
         <v>69</v>
       </c>
       <c r="E76" s="2">
-        <v>45809.5</v>
+        <v>45843.54166666666</v>
       </c>
       <c r="F76">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G76" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H76" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76">
         <v>2</v>
       </c>
       <c r="L76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O76" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P76" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="Q76">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T76">
         <v>1.4</v>
@@ -16544,25 +16472,25 @@
         <v>2.75</v>
       </c>
       <c r="V76">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W76">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X76">
-        <v>6.65</v>
+        <v>8</v>
       </c>
       <c r="Y76">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z76">
-        <v>2.51</v>
+        <v>2.16</v>
       </c>
       <c r="AA76">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="AB76">
-        <v>2.49</v>
+        <v>3.03</v>
       </c>
       <c r="AC76">
         <v>1.06</v>
@@ -16571,118 +16499,118 @@
         <v>8.5</v>
       </c>
       <c r="AE76">
+        <v>1.33</v>
+      </c>
+      <c r="AF76">
+        <v>3.25</v>
+      </c>
+      <c r="AG76">
+        <v>1.9</v>
+      </c>
+      <c r="AH76">
+        <v>1.8</v>
+      </c>
+      <c r="AI76">
+        <v>1.8</v>
+      </c>
+      <c r="AJ76">
+        <v>1.95</v>
+      </c>
+      <c r="AK76">
         <v>1.3</v>
       </c>
-      <c r="AF76">
-        <v>3.4</v>
-      </c>
-      <c r="AG76">
-        <v>1.87</v>
-      </c>
-      <c r="AH76">
-        <v>1.83</v>
-      </c>
-      <c r="AI76">
+      <c r="AL76">
+        <v>1.28</v>
+      </c>
+      <c r="AM76">
         <v>1.67</v>
       </c>
-      <c r="AJ76">
-        <v>2.05</v>
-      </c>
-      <c r="AK76">
-        <v>1.48</v>
-      </c>
-      <c r="AL76">
-        <v>1.25</v>
-      </c>
-      <c r="AM76">
-        <v>1.48</v>
-      </c>
       <c r="AN76">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AR76">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="AS76">
-        <v>1.68</v>
+        <v>1.17</v>
       </c>
       <c r="AT76">
-        <v>3.21</v>
+        <v>3.36</v>
       </c>
       <c r="AU76">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV76">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX76">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY76">
         <v>11</v>
       </c>
       <c r="AZ76">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA76">
         <v>5</v>
       </c>
       <c r="BB76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC76">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD76">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="BE76">
         <v>6.75</v>
       </c>
       <c r="BF76">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="BG76">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BH76">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI76">
         <v>1.38</v>
       </c>
       <c r="BJ76">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="BK76">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BL76">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="BM76">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="BN76">
         <v>1.74</v>
       </c>
       <c r="BO76">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="BP76">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="77" spans="1:68">
@@ -16690,7 +16618,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>7785251</v>
+        <v>7785272</v>
       </c>
       <c r="C77" t="s">
         <v>68</v>
@@ -16699,13 +16627,13 @@
         <v>69</v>
       </c>
       <c r="E77" s="2">
-        <v>45809.5</v>
+        <v>45843.625</v>
       </c>
       <c r="F77">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s">
         <v>78</v>
@@ -16720,28 +16648,28 @@
         <v>1</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O77" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="Q77">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="R77">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="S77">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="T77">
         <v>1.22</v>
@@ -16762,13 +16690,13 @@
         <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>9.699999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AA77">
         <v>5.1</v>
       </c>
       <c r="AB77">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC77">
         <v>1.02</v>
@@ -16777,10 +16705,10 @@
         <v>21</v>
       </c>
       <c r="AE77">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AG77">
         <v>1.38</v>
@@ -16789,106 +16717,106 @@
         <v>2.9</v>
       </c>
       <c r="AI77">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AJ77">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AK77">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AL77">
         <v>1.11</v>
       </c>
       <c r="AM77">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AN77">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="AO77">
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>0.33</v>
+        <v>0.8</v>
       </c>
       <c r="AQ77">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AR77">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS77">
         <v>1.47</v>
       </c>
       <c r="AT77">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="AU77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV77">
+        <v>6</v>
+      </c>
+      <c r="AW77">
+        <v>6</v>
+      </c>
+      <c r="AX77">
+        <v>15</v>
+      </c>
+      <c r="AY77">
+        <v>9</v>
+      </c>
+      <c r="AZ77">
+        <v>21</v>
+      </c>
+      <c r="BA77">
+        <v>4</v>
+      </c>
+      <c r="BB77">
         <v>7</v>
       </c>
-      <c r="AW77">
-        <v>7</v>
-      </c>
-      <c r="AX77">
-        <v>6</v>
-      </c>
-      <c r="AY77">
-        <v>12</v>
-      </c>
-      <c r="AZ77">
-        <v>13</v>
-      </c>
-      <c r="BA77">
-        <v>3</v>
-      </c>
-      <c r="BB77">
-        <v>9</v>
-      </c>
       <c r="BC77">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD77">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="BE77">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BF77">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BG77">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BH77">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BI77">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="BJ77">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="BK77">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="BL77">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="BM77">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="BN77">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="BO77">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="BP77">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="78" spans="1:68">
@@ -16896,7 +16824,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>7785252</v>
+        <v>7785275</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -16905,16 +16833,16 @@
         <v>69</v>
       </c>
       <c r="E78" s="2">
-        <v>45809.5</v>
+        <v>45843.70833333334</v>
       </c>
       <c r="F78">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G78" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H78" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -16929,25 +16857,25 @@
         <v>1</v>
       </c>
       <c r="M78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O78" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="Q78">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R78">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="T78">
         <v>1.33</v>
@@ -16956,4471 +16884,145 @@
         <v>3.25</v>
       </c>
       <c r="V78">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X78">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y78">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z78">
+        <v>2.25</v>
+      </c>
+      <c r="AA78">
+        <v>3.25</v>
+      </c>
+      <c r="AB78">
+        <v>2.72</v>
+      </c>
+      <c r="AC78">
+        <v>1.05</v>
+      </c>
+      <c r="AD78">
+        <v>9.5</v>
+      </c>
+      <c r="AE78">
+        <v>1.25</v>
+      </c>
+      <c r="AF78">
+        <v>3.75</v>
+      </c>
+      <c r="AG78">
+        <v>1.78</v>
+      </c>
+      <c r="AH78">
+        <v>1.92</v>
+      </c>
+      <c r="AI78">
+        <v>1.67</v>
+      </c>
+      <c r="AJ78">
+        <v>2.1</v>
+      </c>
+      <c r="AK78">
+        <v>1.38</v>
+      </c>
+      <c r="AL78">
+        <v>1.25</v>
+      </c>
+      <c r="AM78">
+        <v>1.6</v>
+      </c>
+      <c r="AN78">
+        <v>1.8</v>
+      </c>
+      <c r="AO78">
+        <v>1.4</v>
+      </c>
+      <c r="AP78">
+        <v>2</v>
+      </c>
+      <c r="AQ78">
+        <v>1.17</v>
+      </c>
+      <c r="AR78">
+        <v>1.54</v>
+      </c>
+      <c r="AS78">
+        <v>1.51</v>
+      </c>
+      <c r="AT78">
+        <v>3.05</v>
+      </c>
+      <c r="AU78">
+        <v>3</v>
+      </c>
+      <c r="AV78">
+        <v>0</v>
+      </c>
+      <c r="AW78">
+        <v>2</v>
+      </c>
+      <c r="AX78">
+        <v>0</v>
+      </c>
+      <c r="AY78">
+        <v>5</v>
+      </c>
+      <c r="AZ78">
+        <v>0</v>
+      </c>
+      <c r="BA78">
+        <v>2</v>
+      </c>
+      <c r="BB78">
+        <v>2</v>
+      </c>
+      <c r="BC78">
+        <v>4</v>
+      </c>
+      <c r="BD78">
+        <v>1.81</v>
+      </c>
+      <c r="BE78">
+        <v>6.75</v>
+      </c>
+      <c r="BF78">
+        <v>2.17</v>
+      </c>
+      <c r="BG78">
+        <v>1.3</v>
+      </c>
+      <c r="BH78">
+        <v>3.05</v>
+      </c>
+      <c r="BI78">
+        <v>1.52</v>
+      </c>
+      <c r="BJ78">
+        <v>2.32</v>
+      </c>
+      <c r="BK78">
+        <v>1.85</v>
+      </c>
+      <c r="BL78">
+        <v>1.83</v>
+      </c>
+      <c r="BM78">
+        <v>2.32</v>
+      </c>
+      <c r="BN78">
+        <v>1.53</v>
+      </c>
+      <c r="BO78">
+        <v>2.95</v>
+      </c>
+      <c r="BP78">
         <v>1.33</v>
-      </c>
-      <c r="AA78">
-        <v>4.4</v>
-      </c>
-      <c r="AB78">
-        <v>7.3</v>
-      </c>
-      <c r="AC78">
-        <v>1.04</v>
-      </c>
-      <c r="AD78">
-        <v>10</v>
-      </c>
-      <c r="AE78">
-        <v>1.22</v>
-      </c>
-      <c r="AF78">
-        <v>4.2</v>
-      </c>
-      <c r="AG78">
-        <v>1.77</v>
-      </c>
-      <c r="AH78">
-        <v>1.93</v>
-      </c>
-      <c r="AI78">
-        <v>2.05</v>
-      </c>
-      <c r="AJ78">
-        <v>1.7</v>
-      </c>
-      <c r="AK78">
-        <v>1.07</v>
-      </c>
-      <c r="AL78">
-        <v>1.13</v>
-      </c>
-      <c r="AM78">
-        <v>3</v>
-      </c>
-      <c r="AN78">
-        <v>2.2</v>
-      </c>
-      <c r="AO78">
-        <v>0.25</v>
-      </c>
-      <c r="AP78">
-        <v>1.86</v>
-      </c>
-      <c r="AQ78">
-        <v>0.83</v>
-      </c>
-      <c r="AR78">
-        <v>2.33</v>
-      </c>
-      <c r="AS78">
-        <v>0.97</v>
-      </c>
-      <c r="AT78">
-        <v>3.3</v>
-      </c>
-      <c r="AU78">
-        <v>2</v>
-      </c>
-      <c r="AV78">
-        <v>9</v>
-      </c>
-      <c r="AW78">
-        <v>2</v>
-      </c>
-      <c r="AX78">
-        <v>4</v>
-      </c>
-      <c r="AY78">
-        <v>4</v>
-      </c>
-      <c r="AZ78">
-        <v>13</v>
-      </c>
-      <c r="BA78">
-        <v>6</v>
-      </c>
-      <c r="BB78">
-        <v>4</v>
-      </c>
-      <c r="BC78">
-        <v>10</v>
-      </c>
-      <c r="BD78">
-        <v>1.27</v>
-      </c>
-      <c r="BE78">
-        <v>7.5</v>
-      </c>
-      <c r="BF78">
-        <v>4.1</v>
-      </c>
-      <c r="BG78">
-        <v>1.4</v>
-      </c>
-      <c r="BH78">
-        <v>2.65</v>
-      </c>
-      <c r="BI78">
-        <v>1.68</v>
-      </c>
-      <c r="BJ78">
-        <v>2.05</v>
-      </c>
-      <c r="BK78">
-        <v>2.07</v>
-      </c>
-      <c r="BL78">
-        <v>1.67</v>
-      </c>
-      <c r="BM78">
-        <v>2.65</v>
-      </c>
-      <c r="BN78">
-        <v>1.42</v>
-      </c>
-      <c r="BO78">
-        <v>3.55</v>
-      </c>
-      <c r="BP78">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="79" spans="1:68">
-      <c r="A79" s="1">
-        <v>78</v>
-      </c>
-      <c r="B79">
-        <v>7785253</v>
-      </c>
-      <c r="C79" t="s">
-        <v>68</v>
-      </c>
-      <c r="D79" t="s">
-        <v>69</v>
-      </c>
-      <c r="E79" s="2">
-        <v>45809.59375</v>
-      </c>
-      <c r="F79">
-        <v>9</v>
-      </c>
-      <c r="G79" t="s">
-        <v>75</v>
-      </c>
-      <c r="H79" t="s">
-        <v>85</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>1</v>
-      </c>
-      <c r="K79">
-        <v>1</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>1</v>
-      </c>
-      <c r="N79">
-        <v>1</v>
-      </c>
-      <c r="O79" t="s">
-        <v>91</v>
-      </c>
-      <c r="P79" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q79">
-        <v>2.62</v>
-      </c>
-      <c r="R79">
-        <v>2.3</v>
-      </c>
-      <c r="S79">
-        <v>3.25</v>
-      </c>
-      <c r="T79">
-        <v>1.25</v>
-      </c>
-      <c r="U79">
-        <v>3.55</v>
-      </c>
-      <c r="V79">
-        <v>2.15</v>
-      </c>
-      <c r="W79">
-        <v>1.62</v>
-      </c>
-      <c r="X79">
-        <v>4.5</v>
-      </c>
-      <c r="Y79">
-        <v>1.13</v>
-      </c>
-      <c r="Z79">
-        <v>1.97</v>
-      </c>
-      <c r="AA79">
-        <v>3.7</v>
-      </c>
-      <c r="AB79">
-        <v>2.92</v>
-      </c>
-      <c r="AC79">
-        <v>1.01</v>
-      </c>
-      <c r="AD79">
-        <v>13</v>
-      </c>
-      <c r="AE79">
-        <v>1.17</v>
-      </c>
-      <c r="AF79">
-        <v>5</v>
-      </c>
-      <c r="AG79">
-        <v>1.44</v>
-      </c>
-      <c r="AH79">
-        <v>2.67</v>
-      </c>
-      <c r="AI79">
-        <v>1.42</v>
-      </c>
-      <c r="AJ79">
-        <v>2.6</v>
-      </c>
-      <c r="AK79">
-        <v>1.38</v>
-      </c>
-      <c r="AL79">
-        <v>1.22</v>
-      </c>
-      <c r="AM79">
-        <v>1.67</v>
-      </c>
-      <c r="AN79">
-        <v>1</v>
-      </c>
-      <c r="AO79">
-        <v>2.4</v>
-      </c>
-      <c r="AP79">
-        <v>0.67</v>
-      </c>
-      <c r="AQ79">
-        <v>2.29</v>
-      </c>
-      <c r="AR79">
-        <v>1.62</v>
-      </c>
-      <c r="AS79">
-        <v>1.86</v>
-      </c>
-      <c r="AT79">
-        <v>3.48</v>
-      </c>
-      <c r="AU79">
-        <v>0</v>
-      </c>
-      <c r="AV79">
-        <v>4</v>
-      </c>
-      <c r="AW79">
-        <v>6</v>
-      </c>
-      <c r="AX79">
-        <v>6</v>
-      </c>
-      <c r="AY79">
-        <v>6</v>
-      </c>
-      <c r="AZ79">
-        <v>10</v>
-      </c>
-      <c r="BA79">
-        <v>7</v>
-      </c>
-      <c r="BB79">
-        <v>4</v>
-      </c>
-      <c r="BC79">
-        <v>11</v>
-      </c>
-      <c r="BD79">
-        <v>1.67</v>
-      </c>
-      <c r="BE79">
-        <v>6.5</v>
-      </c>
-      <c r="BF79">
-        <v>2.45</v>
-      </c>
-      <c r="BG79">
-        <v>1.24</v>
-      </c>
-      <c r="BH79">
-        <v>3.55</v>
-      </c>
-      <c r="BI79">
-        <v>1.42</v>
-      </c>
-      <c r="BJ79">
-        <v>2.65</v>
-      </c>
-      <c r="BK79">
-        <v>1.68</v>
-      </c>
-      <c r="BL79">
-        <v>2.05</v>
-      </c>
-      <c r="BM79">
-        <v>2.07</v>
-      </c>
-      <c r="BN79">
-        <v>1.67</v>
-      </c>
-      <c r="BO79">
-        <v>2.55</v>
-      </c>
-      <c r="BP79">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:68">
-      <c r="A80" s="1">
-        <v>79</v>
-      </c>
-      <c r="B80">
-        <v>7785254</v>
-      </c>
-      <c r="C80" t="s">
-        <v>68</v>
-      </c>
-      <c r="D80" t="s">
-        <v>69</v>
-      </c>
-      <c r="E80" s="2">
-        <v>45829.54166666666</v>
-      </c>
-      <c r="F80">
-        <v>10</v>
-      </c>
-      <c r="G80" t="s">
-        <v>78</v>
-      </c>
-      <c r="H80" t="s">
-        <v>80</v>
-      </c>
-      <c r="I80">
-        <v>2</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>2</v>
-      </c>
-      <c r="L80">
-        <v>3</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>3</v>
-      </c>
-      <c r="O80" t="s">
-        <v>139</v>
-      </c>
-      <c r="P80" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q80">
-        <v>1.95</v>
-      </c>
-      <c r="R80">
-        <v>2.63</v>
-      </c>
-      <c r="S80">
-        <v>5</v>
-      </c>
-      <c r="T80">
-        <v>1.22</v>
-      </c>
-      <c r="U80">
-        <v>4</v>
-      </c>
-      <c r="V80">
-        <v>2</v>
-      </c>
-      <c r="W80">
-        <v>1.73</v>
-      </c>
-      <c r="X80">
-        <v>4.33</v>
-      </c>
-      <c r="Y80">
-        <v>1.2</v>
-      </c>
-      <c r="Z80">
-        <v>1.44</v>
-      </c>
-      <c r="AA80">
-        <v>4.6</v>
-      </c>
-      <c r="AB80">
-        <v>4.8</v>
-      </c>
-      <c r="AC80">
-        <v>1.02</v>
-      </c>
-      <c r="AD80">
-        <v>21</v>
-      </c>
-      <c r="AE80">
-        <v>1.12</v>
-      </c>
-      <c r="AF80">
-        <v>5.75</v>
-      </c>
-      <c r="AG80">
-        <v>1.42</v>
-      </c>
-      <c r="AH80">
-        <v>2.74</v>
-      </c>
-      <c r="AI80">
-        <v>1.53</v>
-      </c>
-      <c r="AJ80">
-        <v>2.38</v>
-      </c>
-      <c r="AK80">
-        <v>1.15</v>
-      </c>
-      <c r="AL80">
-        <v>1.18</v>
-      </c>
-      <c r="AM80">
-        <v>2.5</v>
-      </c>
-      <c r="AN80">
-        <v>2.25</v>
-      </c>
-      <c r="AO80">
-        <v>2.25</v>
-      </c>
-      <c r="AP80">
-        <v>2</v>
-      </c>
-      <c r="AQ80">
-        <v>1.67</v>
-      </c>
-      <c r="AR80">
-        <v>2.02</v>
-      </c>
-      <c r="AS80">
-        <v>1.79</v>
-      </c>
-      <c r="AT80">
-        <v>3.81</v>
-      </c>
-      <c r="AU80">
-        <v>5</v>
-      </c>
-      <c r="AV80">
-        <v>0</v>
-      </c>
-      <c r="AW80">
-        <v>0</v>
-      </c>
-      <c r="AX80">
-        <v>0</v>
-      </c>
-      <c r="AY80">
-        <v>5</v>
-      </c>
-      <c r="AZ80">
-        <v>0</v>
-      </c>
-      <c r="BA80">
-        <v>9</v>
-      </c>
-      <c r="BB80">
-        <v>2</v>
-      </c>
-      <c r="BC80">
-        <v>11</v>
-      </c>
-      <c r="BD80">
-        <v>1.44</v>
-      </c>
-      <c r="BE80">
-        <v>7</v>
-      </c>
-      <c r="BF80">
-        <v>3.05</v>
-      </c>
-      <c r="BG80">
-        <v>1.17</v>
-      </c>
-      <c r="BH80">
-        <v>4.3</v>
-      </c>
-      <c r="BI80">
-        <v>1.3</v>
-      </c>
-      <c r="BJ80">
-        <v>3.05</v>
-      </c>
-      <c r="BK80">
-        <v>1.5</v>
-      </c>
-      <c r="BL80">
-        <v>2.35</v>
-      </c>
-      <c r="BM80">
-        <v>1.82</v>
-      </c>
-      <c r="BN80">
-        <v>1.86</v>
-      </c>
-      <c r="BO80">
-        <v>2.23</v>
-      </c>
-      <c r="BP80">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="81" spans="1:68">
-      <c r="A81" s="1">
-        <v>80</v>
-      </c>
-      <c r="B81">
-        <v>7785261</v>
-      </c>
-      <c r="C81" t="s">
-        <v>68</v>
-      </c>
-      <c r="D81" t="s">
-        <v>69</v>
-      </c>
-      <c r="E81" s="2">
-        <v>45830.39583333334</v>
-      </c>
-      <c r="F81">
-        <v>10</v>
-      </c>
-      <c r="G81" t="s">
-        <v>72</v>
-      </c>
-      <c r="H81" t="s">
-        <v>75</v>
-      </c>
-      <c r="I81">
-        <v>2</v>
-      </c>
-      <c r="J81">
-        <v>1</v>
-      </c>
-      <c r="K81">
-        <v>3</v>
-      </c>
-      <c r="L81">
-        <v>2</v>
-      </c>
-      <c r="M81">
-        <v>3</v>
-      </c>
-      <c r="N81">
-        <v>5</v>
-      </c>
-      <c r="O81" t="s">
-        <v>140</v>
-      </c>
-      <c r="P81" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q81">
-        <v>3</v>
-      </c>
-      <c r="R81">
-        <v>2.3</v>
-      </c>
-      <c r="S81">
-        <v>3.25</v>
-      </c>
-      <c r="T81">
-        <v>1.33</v>
-      </c>
-      <c r="U81">
-        <v>3.25</v>
-      </c>
-      <c r="V81">
-        <v>2.5</v>
-      </c>
-      <c r="W81">
-        <v>1.5</v>
-      </c>
-      <c r="X81">
-        <v>6</v>
-      </c>
-      <c r="Y81">
-        <v>1.13</v>
-      </c>
-      <c r="Z81">
-        <v>2.37</v>
-      </c>
-      <c r="AA81">
-        <v>3.29</v>
-      </c>
-      <c r="AB81">
-        <v>2.54</v>
-      </c>
-      <c r="AC81">
-        <v>1.04</v>
-      </c>
-      <c r="AD81">
-        <v>10</v>
-      </c>
-      <c r="AE81">
-        <v>1.22</v>
-      </c>
-      <c r="AF81">
-        <v>4</v>
-      </c>
-      <c r="AG81">
-        <v>1.59</v>
-      </c>
-      <c r="AH81">
-        <v>2.2</v>
-      </c>
-      <c r="AI81">
-        <v>1.62</v>
-      </c>
-      <c r="AJ81">
-        <v>2.2</v>
-      </c>
-      <c r="AK81">
-        <v>1.44</v>
-      </c>
-      <c r="AL81">
-        <v>1.28</v>
-      </c>
-      <c r="AM81">
-        <v>1.53</v>
-      </c>
-      <c r="AN81">
-        <v>1</v>
-      </c>
-      <c r="AO81">
-        <v>1.4</v>
-      </c>
-      <c r="AP81">
-        <v>0.83</v>
-      </c>
-      <c r="AQ81">
-        <v>1.67</v>
-      </c>
-      <c r="AR81">
-        <v>2.19</v>
-      </c>
-      <c r="AS81">
-        <v>1.51</v>
-      </c>
-      <c r="AT81">
-        <v>3.7</v>
-      </c>
-      <c r="AU81">
-        <v>8</v>
-      </c>
-      <c r="AV81">
-        <v>7</v>
-      </c>
-      <c r="AW81">
-        <v>7</v>
-      </c>
-      <c r="AX81">
-        <v>11</v>
-      </c>
-      <c r="AY81">
-        <v>15</v>
-      </c>
-      <c r="AZ81">
-        <v>18</v>
-      </c>
-      <c r="BA81">
-        <v>5</v>
-      </c>
-      <c r="BB81">
-        <v>7</v>
-      </c>
-      <c r="BC81">
-        <v>12</v>
-      </c>
-      <c r="BD81">
-        <v>1.96</v>
-      </c>
-      <c r="BE81">
-        <v>6.75</v>
-      </c>
-      <c r="BF81">
-        <v>1.98</v>
-      </c>
-      <c r="BG81">
-        <v>1.22</v>
-      </c>
-      <c r="BH81">
-        <v>3.8</v>
-      </c>
-      <c r="BI81">
-        <v>1.38</v>
-      </c>
-      <c r="BJ81">
-        <v>2.7</v>
-      </c>
-      <c r="BK81">
-        <v>1.65</v>
-      </c>
-      <c r="BL81">
-        <v>2.1</v>
-      </c>
-      <c r="BM81">
-        <v>1.98</v>
-      </c>
-      <c r="BN81">
-        <v>1.72</v>
-      </c>
-      <c r="BO81">
-        <v>2.48</v>
-      </c>
-      <c r="BP81">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="82" spans="1:68">
-      <c r="A82" s="1">
-        <v>81</v>
-      </c>
-      <c r="B82">
-        <v>7785258</v>
-      </c>
-      <c r="C82" t="s">
-        <v>68</v>
-      </c>
-      <c r="D82" t="s">
-        <v>69</v>
-      </c>
-      <c r="E82" s="2">
-        <v>45830.5</v>
-      </c>
-      <c r="F82">
-        <v>10</v>
-      </c>
-      <c r="G82" t="s">
-        <v>82</v>
-      </c>
-      <c r="H82" t="s">
-        <v>83</v>
-      </c>
-      <c r="I82">
-        <v>1</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>1</v>
-      </c>
-      <c r="L82">
-        <v>4</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>4</v>
-      </c>
-      <c r="O82" t="s">
-        <v>141</v>
-      </c>
-      <c r="P82" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q82">
-        <v>1.8</v>
-      </c>
-      <c r="R82">
-        <v>2.63</v>
-      </c>
-      <c r="S82">
-        <v>7</v>
-      </c>
-      <c r="T82">
-        <v>1.25</v>
-      </c>
-      <c r="U82">
-        <v>3.75</v>
-      </c>
-      <c r="V82">
-        <v>2.25</v>
-      </c>
-      <c r="W82">
-        <v>1.57</v>
-      </c>
-      <c r="X82">
-        <v>5.5</v>
-      </c>
-      <c r="Y82">
-        <v>1.14</v>
-      </c>
-      <c r="Z82">
-        <v>1.34</v>
-      </c>
-      <c r="AA82">
-        <v>4.5</v>
-      </c>
-      <c r="AB82">
-        <v>6.5</v>
-      </c>
-      <c r="AC82">
-        <v>1.01</v>
-      </c>
-      <c r="AD82">
-        <v>17</v>
-      </c>
-      <c r="AE82">
-        <v>1.17</v>
-      </c>
-      <c r="AF82">
-        <v>5</v>
-      </c>
-      <c r="AG82">
-        <v>1.5</v>
-      </c>
-      <c r="AH82">
-        <v>2.48</v>
-      </c>
-      <c r="AI82">
-        <v>1.8</v>
-      </c>
-      <c r="AJ82">
-        <v>1.95</v>
-      </c>
-      <c r="AK82">
-        <v>1.1</v>
-      </c>
-      <c r="AL82">
-        <v>1.16</v>
-      </c>
-      <c r="AM82">
-        <v>2.9</v>
-      </c>
-      <c r="AN82">
-        <v>3</v>
-      </c>
-      <c r="AO82">
-        <v>0</v>
-      </c>
-      <c r="AP82">
-        <v>3</v>
-      </c>
-      <c r="AQ82">
-        <v>0</v>
-      </c>
-      <c r="AR82">
-        <v>2.07</v>
-      </c>
-      <c r="AS82">
-        <v>0.95</v>
-      </c>
-      <c r="AT82">
-        <v>3.02</v>
-      </c>
-      <c r="AU82">
-        <v>11</v>
-      </c>
-      <c r="AV82">
-        <v>8</v>
-      </c>
-      <c r="AW82">
-        <v>2</v>
-      </c>
-      <c r="AX82">
-        <v>11</v>
-      </c>
-      <c r="AY82">
-        <v>13</v>
-      </c>
-      <c r="AZ82">
-        <v>19</v>
-      </c>
-      <c r="BA82">
-        <v>3</v>
-      </c>
-      <c r="BB82">
-        <v>8</v>
-      </c>
-      <c r="BC82">
-        <v>11</v>
-      </c>
-      <c r="BD82">
-        <v>1.29</v>
-      </c>
-      <c r="BE82">
-        <v>8</v>
-      </c>
-      <c r="BF82">
-        <v>3.9</v>
-      </c>
-      <c r="BG82">
-        <v>1.2</v>
-      </c>
-      <c r="BH82">
-        <v>4</v>
-      </c>
-      <c r="BI82">
-        <v>1.34</v>
-      </c>
-      <c r="BJ82">
-        <v>2.9</v>
-      </c>
-      <c r="BK82">
-        <v>1.57</v>
-      </c>
-      <c r="BL82">
-        <v>2.23</v>
-      </c>
-      <c r="BM82">
-        <v>1.9</v>
-      </c>
-      <c r="BN82">
-        <v>1.79</v>
-      </c>
-      <c r="BO82">
-        <v>2.32</v>
-      </c>
-      <c r="BP82">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="83" spans="1:68">
-      <c r="A83" s="1">
-        <v>82</v>
-      </c>
-      <c r="B83">
-        <v>7785257</v>
-      </c>
-      <c r="C83" t="s">
-        <v>68</v>
-      </c>
-      <c r="D83" t="s">
-        <v>69</v>
-      </c>
-      <c r="E83" s="2">
-        <v>45830.5</v>
-      </c>
-      <c r="F83">
-        <v>10</v>
-      </c>
-      <c r="G83" t="s">
-        <v>84</v>
-      </c>
-      <c r="H83" t="s">
-        <v>79</v>
-      </c>
-      <c r="I83">
-        <v>3</v>
-      </c>
-      <c r="J83">
-        <v>1</v>
-      </c>
-      <c r="K83">
-        <v>4</v>
-      </c>
-      <c r="L83">
-        <v>4</v>
-      </c>
-      <c r="M83">
-        <v>1</v>
-      </c>
-      <c r="N83">
-        <v>5</v>
-      </c>
-      <c r="O83" t="s">
-        <v>142</v>
-      </c>
-      <c r="P83" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q83">
-        <v>4.75</v>
-      </c>
-      <c r="R83">
-        <v>2.4</v>
-      </c>
-      <c r="S83">
-        <v>2.2</v>
-      </c>
-      <c r="T83">
-        <v>1.3</v>
-      </c>
-      <c r="U83">
-        <v>3.4</v>
-      </c>
-      <c r="V83">
-        <v>2.38</v>
-      </c>
-      <c r="W83">
-        <v>1.53</v>
-      </c>
-      <c r="X83">
-        <v>6</v>
-      </c>
-      <c r="Y83">
-        <v>1.13</v>
-      </c>
-      <c r="Z83">
-        <v>4.2</v>
-      </c>
-      <c r="AA83">
-        <v>3.78</v>
-      </c>
-      <c r="AB83">
-        <v>1.62</v>
-      </c>
-      <c r="AC83">
-        <v>1.04</v>
-      </c>
-      <c r="AD83">
-        <v>10</v>
-      </c>
-      <c r="AE83">
-        <v>1.2</v>
-      </c>
-      <c r="AF83">
-        <v>4.33</v>
-      </c>
-      <c r="AG83">
-        <v>1.56</v>
-      </c>
-      <c r="AH83">
-        <v>2.27</v>
-      </c>
-      <c r="AI83">
-        <v>1.67</v>
-      </c>
-      <c r="AJ83">
-        <v>2.1</v>
-      </c>
-      <c r="AK83">
-        <v>2.05</v>
-      </c>
-      <c r="AL83">
-        <v>1.23</v>
-      </c>
-      <c r="AM83">
-        <v>1.21</v>
-      </c>
-      <c r="AN83">
-        <v>0.75</v>
-      </c>
-      <c r="AO83">
-        <v>2</v>
-      </c>
-      <c r="AP83">
-        <v>1.17</v>
-      </c>
-      <c r="AQ83">
-        <v>1.67</v>
-      </c>
-      <c r="AR83">
-        <v>1.44</v>
-      </c>
-      <c r="AS83">
-        <v>1.21</v>
-      </c>
-      <c r="AT83">
-        <v>2.65</v>
-      </c>
-      <c r="AU83">
-        <v>9</v>
-      </c>
-      <c r="AV83">
-        <v>6</v>
-      </c>
-      <c r="AW83">
-        <v>4</v>
-      </c>
-      <c r="AX83">
-        <v>7</v>
-      </c>
-      <c r="AY83">
-        <v>13</v>
-      </c>
-      <c r="AZ83">
-        <v>13</v>
-      </c>
-      <c r="BA83">
-        <v>3</v>
-      </c>
-      <c r="BB83">
-        <v>9</v>
-      </c>
-      <c r="BC83">
-        <v>12</v>
-      </c>
-      <c r="BD83">
-        <v>3.15</v>
-      </c>
-      <c r="BE83">
-        <v>7</v>
-      </c>
-      <c r="BF83">
-        <v>1.42</v>
-      </c>
-      <c r="BG83">
-        <v>1.22</v>
-      </c>
-      <c r="BH83">
-        <v>3.8</v>
-      </c>
-      <c r="BI83">
-        <v>1.38</v>
-      </c>
-      <c r="BJ83">
-        <v>2.8</v>
-      </c>
-      <c r="BK83">
-        <v>1.61</v>
-      </c>
-      <c r="BL83">
-        <v>2.15</v>
-      </c>
-      <c r="BM83">
-        <v>1.97</v>
-      </c>
-      <c r="BN83">
-        <v>1.74</v>
-      </c>
-      <c r="BO83">
-        <v>2.43</v>
-      </c>
-      <c r="BP83">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="84" spans="1:68">
-      <c r="A84" s="1">
-        <v>83</v>
-      </c>
-      <c r="B84">
-        <v>7785259</v>
-      </c>
-      <c r="C84" t="s">
-        <v>68</v>
-      </c>
-      <c r="D84" t="s">
-        <v>69</v>
-      </c>
-      <c r="E84" s="2">
-        <v>45830.5</v>
-      </c>
-      <c r="F84">
-        <v>10</v>
-      </c>
-      <c r="G84" t="s">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s">
-        <v>77</v>
-      </c>
-      <c r="I84">
-        <v>1</v>
-      </c>
-      <c r="J84">
-        <v>1</v>
-      </c>
-      <c r="K84">
-        <v>2</v>
-      </c>
-      <c r="L84">
-        <v>1</v>
-      </c>
-      <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84">
-        <v>2</v>
-      </c>
-      <c r="O84" t="s">
-        <v>143</v>
-      </c>
-      <c r="P84" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q84">
-        <v>2.1</v>
-      </c>
-      <c r="R84">
-        <v>2.4</v>
-      </c>
-      <c r="S84">
-        <v>5</v>
-      </c>
-      <c r="T84">
-        <v>1.29</v>
-      </c>
-      <c r="U84">
-        <v>3.5</v>
-      </c>
-      <c r="V84">
-        <v>2.38</v>
-      </c>
-      <c r="W84">
-        <v>1.53</v>
-      </c>
-      <c r="X84">
-        <v>5.5</v>
-      </c>
-      <c r="Y84">
-        <v>1.14</v>
-      </c>
-      <c r="Z84">
-        <v>1.56</v>
-      </c>
-      <c r="AA84">
-        <v>3.9</v>
-      </c>
-      <c r="AB84">
-        <v>4.5</v>
-      </c>
-      <c r="AC84">
-        <v>1.03</v>
-      </c>
-      <c r="AD84">
-        <v>11</v>
-      </c>
-      <c r="AE84">
-        <v>1.2</v>
-      </c>
-      <c r="AF84">
-        <v>4.33</v>
-      </c>
-      <c r="AG84">
-        <v>1.58</v>
-      </c>
-      <c r="AH84">
-        <v>2.22</v>
-      </c>
-      <c r="AI84">
-        <v>1.67</v>
-      </c>
-      <c r="AJ84">
-        <v>2.1</v>
-      </c>
-      <c r="AK84">
-        <v>1.18</v>
-      </c>
-      <c r="AL84">
-        <v>1.22</v>
-      </c>
-      <c r="AM84">
-        <v>2.25</v>
-      </c>
-      <c r="AN84">
-        <v>1</v>
-      </c>
-      <c r="AO84">
-        <v>0.75</v>
-      </c>
-      <c r="AP84">
-        <v>1</v>
-      </c>
-      <c r="AQ84">
-        <v>0.8</v>
-      </c>
-      <c r="AR84">
-        <v>1.74</v>
-      </c>
-      <c r="AS84">
-        <v>1.09</v>
-      </c>
-      <c r="AT84">
-        <v>2.83</v>
-      </c>
-      <c r="AU84">
-        <v>5</v>
-      </c>
-      <c r="AV84">
-        <v>3</v>
-      </c>
-      <c r="AW84">
-        <v>3</v>
-      </c>
-      <c r="AX84">
-        <v>7</v>
-      </c>
-      <c r="AY84">
-        <v>8</v>
-      </c>
-      <c r="AZ84">
-        <v>10</v>
-      </c>
-      <c r="BA84">
-        <v>3</v>
-      </c>
-      <c r="BB84">
-        <v>2</v>
-      </c>
-      <c r="BC84">
-        <v>5</v>
-      </c>
-      <c r="BD84">
-        <v>1.49</v>
-      </c>
-      <c r="BE84">
-        <v>7</v>
-      </c>
-      <c r="BF84">
-        <v>2.9</v>
-      </c>
-      <c r="BG84">
-        <v>1.22</v>
-      </c>
-      <c r="BH84">
-        <v>3.7</v>
-      </c>
-      <c r="BI84">
-        <v>1.38</v>
-      </c>
-      <c r="BJ84">
-        <v>2.7</v>
-      </c>
-      <c r="BK84">
-        <v>1.64</v>
-      </c>
-      <c r="BL84">
-        <v>2.1</v>
-      </c>
-      <c r="BM84">
-        <v>2</v>
-      </c>
-      <c r="BN84">
-        <v>1.71</v>
-      </c>
-      <c r="BO84">
-        <v>2.5</v>
-      </c>
-      <c r="BP84">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="85" spans="1:68">
-      <c r="A85" s="1">
-        <v>84</v>
-      </c>
-      <c r="B85">
-        <v>7785255</v>
-      </c>
-      <c r="C85" t="s">
-        <v>68</v>
-      </c>
-      <c r="D85" t="s">
-        <v>69</v>
-      </c>
-      <c r="E85" s="2">
-        <v>45830.5</v>
-      </c>
-      <c r="F85">
-        <v>10</v>
-      </c>
-      <c r="G85" t="s">
-        <v>73</v>
-      </c>
-      <c r="H85" t="s">
-        <v>76</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>2</v>
-      </c>
-      <c r="K85">
-        <v>2</v>
-      </c>
-      <c r="L85">
-        <v>1</v>
-      </c>
-      <c r="M85">
-        <v>3</v>
-      </c>
-      <c r="N85">
-        <v>4</v>
-      </c>
-      <c r="O85" t="s">
-        <v>144</v>
-      </c>
-      <c r="P85" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q85">
-        <v>3.75</v>
-      </c>
-      <c r="R85">
-        <v>2.25</v>
-      </c>
-      <c r="S85">
-        <v>2.75</v>
-      </c>
-      <c r="T85">
-        <v>1.36</v>
-      </c>
-      <c r="U85">
-        <v>3</v>
-      </c>
-      <c r="V85">
-        <v>2.63</v>
-      </c>
-      <c r="W85">
-        <v>1.44</v>
-      </c>
-      <c r="X85">
-        <v>7</v>
-      </c>
-      <c r="Y85">
-        <v>1.1</v>
-      </c>
-      <c r="Z85">
-        <v>3.16</v>
-      </c>
-      <c r="AA85">
-        <v>3.25</v>
-      </c>
-      <c r="AB85">
-        <v>2.02</v>
-      </c>
-      <c r="AC85">
-        <v>1.05</v>
-      </c>
-      <c r="AD85">
-        <v>9.5</v>
-      </c>
-      <c r="AE85">
-        <v>1.28</v>
-      </c>
-      <c r="AF85">
-        <v>3.65</v>
-      </c>
-      <c r="AG85">
-        <v>1.79</v>
-      </c>
-      <c r="AH85">
-        <v>1.91</v>
-      </c>
-      <c r="AI85">
-        <v>1.7</v>
-      </c>
-      <c r="AJ85">
-        <v>2.05</v>
-      </c>
-      <c r="AK85">
-        <v>1.71</v>
-      </c>
-      <c r="AL85">
-        <v>1.28</v>
-      </c>
-      <c r="AM85">
-        <v>1.32</v>
-      </c>
-      <c r="AN85">
-        <v>1.75</v>
-      </c>
-      <c r="AO85">
-        <v>1.75</v>
-      </c>
-      <c r="AP85">
-        <v>1.33</v>
-      </c>
-      <c r="AQ85">
-        <v>2.17</v>
-      </c>
-      <c r="AR85">
-        <v>1.38</v>
-      </c>
-      <c r="AS85">
-        <v>1.15</v>
-      </c>
-      <c r="AT85">
-        <v>2.53</v>
-      </c>
-      <c r="AU85">
-        <v>5</v>
-      </c>
-      <c r="AV85">
-        <v>5</v>
-      </c>
-      <c r="AW85">
-        <v>6</v>
-      </c>
-      <c r="AX85">
-        <v>0</v>
-      </c>
-      <c r="AY85">
-        <v>11</v>
-      </c>
-      <c r="AZ85">
-        <v>5</v>
-      </c>
-      <c r="BA85">
-        <v>6</v>
-      </c>
-      <c r="BB85">
-        <v>2</v>
-      </c>
-      <c r="BC85">
-        <v>8</v>
-      </c>
-      <c r="BD85">
-        <v>2.4</v>
-      </c>
-      <c r="BE85">
-        <v>6.75</v>
-      </c>
-      <c r="BF85">
-        <v>1.68</v>
-      </c>
-      <c r="BG85">
-        <v>1.23</v>
-      </c>
-      <c r="BH85">
-        <v>3.65</v>
-      </c>
-      <c r="BI85">
-        <v>1.41</v>
-      </c>
-      <c r="BJ85">
-        <v>2.65</v>
-      </c>
-      <c r="BK85">
-        <v>1.67</v>
-      </c>
-      <c r="BL85">
-        <v>2.07</v>
-      </c>
-      <c r="BM85">
-        <v>2.02</v>
-      </c>
-      <c r="BN85">
-        <v>1.7</v>
-      </c>
-      <c r="BO85">
-        <v>2.55</v>
-      </c>
-      <c r="BP85">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="86" spans="1:68">
-      <c r="A86" s="1">
-        <v>85</v>
-      </c>
-      <c r="B86">
-        <v>7785256</v>
-      </c>
-      <c r="C86" t="s">
-        <v>68</v>
-      </c>
-      <c r="D86" t="s">
-        <v>69</v>
-      </c>
-      <c r="E86" s="2">
-        <v>45830.5</v>
-      </c>
-      <c r="F86">
-        <v>10</v>
-      </c>
-      <c r="G86" t="s">
-        <v>74</v>
-      </c>
-      <c r="H86" t="s">
-        <v>70</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>5</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>5</v>
-      </c>
-      <c r="O86" t="s">
-        <v>145</v>
-      </c>
-      <c r="P86" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q86">
-        <v>2.75</v>
-      </c>
-      <c r="R86">
-        <v>2.2</v>
-      </c>
-      <c r="S86">
-        <v>3.75</v>
-      </c>
-      <c r="T86">
-        <v>1.36</v>
-      </c>
-      <c r="U86">
-        <v>3</v>
-      </c>
-      <c r="V86">
-        <v>2.63</v>
-      </c>
-      <c r="W86">
-        <v>1.44</v>
-      </c>
-      <c r="X86">
-        <v>7</v>
-      </c>
-      <c r="Y86">
-        <v>1.1</v>
-      </c>
-      <c r="Z86">
-        <v>2.08</v>
-      </c>
-      <c r="AA86">
-        <v>3.39</v>
-      </c>
-      <c r="AB86">
-        <v>2.9</v>
-      </c>
-      <c r="AC86">
-        <v>1.05</v>
-      </c>
-      <c r="AD86">
-        <v>9.5</v>
-      </c>
-      <c r="AE86">
-        <v>1.28</v>
-      </c>
-      <c r="AF86">
-        <v>3.55</v>
-      </c>
-      <c r="AG86">
-        <v>1.86</v>
-      </c>
-      <c r="AH86">
-        <v>1.84</v>
-      </c>
-      <c r="AI86">
-        <v>1.7</v>
-      </c>
-      <c r="AJ86">
-        <v>2.05</v>
-      </c>
-      <c r="AK86">
-        <v>1.35</v>
-      </c>
-      <c r="AL86">
-        <v>1.29</v>
-      </c>
-      <c r="AM86">
-        <v>1.65</v>
-      </c>
-      <c r="AN86">
-        <v>0.75</v>
-      </c>
-      <c r="AO86">
-        <v>1.5</v>
-      </c>
-      <c r="AP86">
-        <v>1.2</v>
-      </c>
-      <c r="AQ86">
-        <v>1</v>
-      </c>
-      <c r="AR86">
-        <v>1.15</v>
-      </c>
-      <c r="AS86">
-        <v>1.67</v>
-      </c>
-      <c r="AT86">
-        <v>2.82</v>
-      </c>
-      <c r="AU86">
-        <v>6</v>
-      </c>
-      <c r="AV86">
-        <v>2</v>
-      </c>
-      <c r="AW86">
-        <v>8</v>
-      </c>
-      <c r="AX86">
-        <v>8</v>
-      </c>
-      <c r="AY86">
-        <v>14</v>
-      </c>
-      <c r="AZ86">
-        <v>10</v>
-      </c>
-      <c r="BA86">
-        <v>6</v>
-      </c>
-      <c r="BB86">
-        <v>2</v>
-      </c>
-      <c r="BC86">
-        <v>8</v>
-      </c>
-      <c r="BD86">
-        <v>1.7</v>
-      </c>
-      <c r="BE86">
-        <v>6.75</v>
-      </c>
-      <c r="BF86">
-        <v>2.4</v>
-      </c>
-      <c r="BG86">
-        <v>1.24</v>
-      </c>
-      <c r="BH86">
-        <v>3.55</v>
-      </c>
-      <c r="BI86">
-        <v>1.43</v>
-      </c>
-      <c r="BJ86">
-        <v>2.6</v>
-      </c>
-      <c r="BK86">
-        <v>1.7</v>
-      </c>
-      <c r="BL86">
-        <v>2.02</v>
-      </c>
-      <c r="BM86">
-        <v>2.08</v>
-      </c>
-      <c r="BN86">
-        <v>1.65</v>
-      </c>
-      <c r="BO86">
-        <v>2.65</v>
-      </c>
-      <c r="BP86">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="87" spans="1:68">
-      <c r="A87" s="1">
-        <v>86</v>
-      </c>
-      <c r="B87">
-        <v>7785260</v>
-      </c>
-      <c r="C87" t="s">
-        <v>68</v>
-      </c>
-      <c r="D87" t="s">
-        <v>69</v>
-      </c>
-      <c r="E87" s="2">
-        <v>45830.59375</v>
-      </c>
-      <c r="F87">
-        <v>10</v>
-      </c>
-      <c r="G87" t="s">
-        <v>85</v>
-      </c>
-      <c r="H87" t="s">
-        <v>71</v>
-      </c>
-      <c r="I87">
-        <v>1</v>
-      </c>
-      <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>1</v>
-      </c>
-      <c r="L87">
-        <v>3</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>3</v>
-      </c>
-      <c r="O87" t="s">
-        <v>146</v>
-      </c>
-      <c r="P87" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q87">
-        <v>2.1</v>
-      </c>
-      <c r="R87">
-        <v>2.5</v>
-      </c>
-      <c r="S87">
-        <v>5</v>
-      </c>
-      <c r="T87">
-        <v>1.29</v>
-      </c>
-      <c r="U87">
-        <v>3.5</v>
-      </c>
-      <c r="V87">
-        <v>2.25</v>
-      </c>
-      <c r="W87">
-        <v>1.57</v>
-      </c>
-      <c r="X87">
-        <v>5.5</v>
-      </c>
-      <c r="Y87">
-        <v>1.14</v>
-      </c>
-      <c r="Z87">
-        <v>1.52</v>
-      </c>
-      <c r="AA87">
-        <v>3.95</v>
-      </c>
-      <c r="AB87">
-        <v>4.8</v>
-      </c>
-      <c r="AC87">
-        <v>1.03</v>
-      </c>
-      <c r="AD87">
-        <v>11</v>
-      </c>
-      <c r="AE87">
-        <v>1.2</v>
-      </c>
-      <c r="AF87">
-        <v>4.5</v>
-      </c>
-      <c r="AG87">
-        <v>1.55</v>
-      </c>
-      <c r="AH87">
-        <v>2.29</v>
-      </c>
-      <c r="AI87">
-        <v>1.67</v>
-      </c>
-      <c r="AJ87">
-        <v>2.1</v>
-      </c>
-      <c r="AK87">
-        <v>1.18</v>
-      </c>
-      <c r="AL87">
-        <v>1.21</v>
-      </c>
-      <c r="AM87">
-        <v>2.25</v>
-      </c>
-      <c r="AN87">
-        <v>2.33</v>
-      </c>
-      <c r="AO87">
-        <v>1</v>
-      </c>
-      <c r="AP87">
-        <v>2.5</v>
-      </c>
-      <c r="AQ87">
-        <v>0.83</v>
-      </c>
-      <c r="AR87">
-        <v>2.49</v>
-      </c>
-      <c r="AS87">
-        <v>1.17</v>
-      </c>
-      <c r="AT87">
-        <v>3.66</v>
-      </c>
-      <c r="AU87">
-        <v>5</v>
-      </c>
-      <c r="AV87">
-        <v>2</v>
-      </c>
-      <c r="AW87">
-        <v>9</v>
-      </c>
-      <c r="AX87">
-        <v>9</v>
-      </c>
-      <c r="AY87">
-        <v>14</v>
-      </c>
-      <c r="AZ87">
-        <v>11</v>
-      </c>
-      <c r="BA87">
-        <v>6</v>
-      </c>
-      <c r="BB87">
-        <v>6</v>
-      </c>
-      <c r="BC87">
-        <v>12</v>
-      </c>
-      <c r="BD87">
-        <v>1.46</v>
-      </c>
-      <c r="BE87">
-        <v>7</v>
-      </c>
-      <c r="BF87">
-        <v>3</v>
-      </c>
-      <c r="BG87">
-        <v>1.18</v>
-      </c>
-      <c r="BH87">
-        <v>4.1</v>
-      </c>
-      <c r="BI87">
-        <v>1.32</v>
-      </c>
-      <c r="BJ87">
-        <v>3.05</v>
-      </c>
-      <c r="BK87">
-        <v>1.53</v>
-      </c>
-      <c r="BL87">
-        <v>2.3</v>
-      </c>
-      <c r="BM87">
-        <v>1.83</v>
-      </c>
-      <c r="BN87">
-        <v>1.85</v>
-      </c>
-      <c r="BO87">
-        <v>2.25</v>
-      </c>
-      <c r="BP87">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="88" spans="1:68">
-      <c r="A88" s="1">
-        <v>87</v>
-      </c>
-      <c r="B88">
-        <v>7785268</v>
-      </c>
-      <c r="C88" t="s">
-        <v>68</v>
-      </c>
-      <c r="D88" t="s">
-        <v>69</v>
-      </c>
-      <c r="E88" s="2">
-        <v>45836.54166666666</v>
-      </c>
-      <c r="F88">
-        <v>11</v>
-      </c>
-      <c r="G88" t="s">
-        <v>79</v>
-      </c>
-      <c r="H88" t="s">
-        <v>85</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <v>1</v>
-      </c>
-      <c r="K88">
-        <v>1</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88">
-        <v>1</v>
-      </c>
-      <c r="N88">
-        <v>2</v>
-      </c>
-      <c r="O88" t="s">
-        <v>147</v>
-      </c>
-      <c r="P88" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q88">
-        <v>2.83</v>
-      </c>
-      <c r="R88">
-        <v>2.43</v>
-      </c>
-      <c r="S88">
-        <v>3.05</v>
-      </c>
-      <c r="T88">
-        <v>1.2</v>
-      </c>
-      <c r="U88">
-        <v>3.68</v>
-      </c>
-      <c r="V88">
-        <v>2.12</v>
-      </c>
-      <c r="W88">
-        <v>1.64</v>
-      </c>
-      <c r="X88">
-        <v>4.5</v>
-      </c>
-      <c r="Y88">
-        <v>1.13</v>
-      </c>
-      <c r="Z88">
-        <v>1.85</v>
-      </c>
-      <c r="AA88">
-        <v>3.67</v>
-      </c>
-      <c r="AB88">
-        <v>3.26</v>
-      </c>
-      <c r="AC88">
-        <v>1.01</v>
-      </c>
-      <c r="AD88">
-        <v>17</v>
-      </c>
-      <c r="AE88">
-        <v>1.09</v>
-      </c>
-      <c r="AF88">
-        <v>5.25</v>
-      </c>
-      <c r="AG88">
-        <v>1.55</v>
-      </c>
-      <c r="AH88">
-        <v>2.29</v>
-      </c>
-      <c r="AI88">
-        <v>1.4</v>
-      </c>
-      <c r="AJ88">
-        <v>2.72</v>
-      </c>
-      <c r="AK88">
-        <v>1.5</v>
-      </c>
-      <c r="AL88">
-        <v>1.26</v>
-      </c>
-      <c r="AM88">
-        <v>1.56</v>
-      </c>
-      <c r="AN88">
-        <v>2</v>
-      </c>
-      <c r="AO88">
-        <v>2.5</v>
-      </c>
-      <c r="AP88">
-        <v>1.86</v>
-      </c>
-      <c r="AQ88">
-        <v>2.29</v>
-      </c>
-      <c r="AR88">
-        <v>2.33</v>
-      </c>
-      <c r="AS88">
-        <v>1.86</v>
-      </c>
-      <c r="AT88">
-        <v>4.19</v>
-      </c>
-      <c r="AU88">
-        <v>3</v>
-      </c>
-      <c r="AV88">
-        <v>5</v>
-      </c>
-      <c r="AW88">
-        <v>9</v>
-      </c>
-      <c r="AX88">
-        <v>6</v>
-      </c>
-      <c r="AY88">
-        <v>12</v>
-      </c>
-      <c r="AZ88">
-        <v>11</v>
-      </c>
-      <c r="BA88">
-        <v>9</v>
-      </c>
-      <c r="BB88">
-        <v>5</v>
-      </c>
-      <c r="BC88">
-        <v>14</v>
-      </c>
-      <c r="BD88">
-        <v>1.75</v>
-      </c>
-      <c r="BE88">
-        <v>6.75</v>
-      </c>
-      <c r="BF88">
-        <v>2.28</v>
-      </c>
-      <c r="BG88">
-        <v>1.2</v>
-      </c>
-      <c r="BH88">
-        <v>3.95</v>
-      </c>
-      <c r="BI88">
-        <v>1.35</v>
-      </c>
-      <c r="BJ88">
-        <v>2.9</v>
-      </c>
-      <c r="BK88">
-        <v>1.57</v>
-      </c>
-      <c r="BL88">
-        <v>2.23</v>
-      </c>
-      <c r="BM88">
-        <v>1.91</v>
-      </c>
-      <c r="BN88">
-        <v>1.78</v>
-      </c>
-      <c r="BO88">
-        <v>2.38</v>
-      </c>
-      <c r="BP88">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:68">
-      <c r="A89" s="1">
-        <v>88</v>
-      </c>
-      <c r="B89">
-        <v>7785266</v>
-      </c>
-      <c r="C89" t="s">
-        <v>68</v>
-      </c>
-      <c r="D89" t="s">
-        <v>69</v>
-      </c>
-      <c r="E89" s="2">
-        <v>45837.39583333334</v>
-      </c>
-      <c r="F89">
-        <v>11</v>
-      </c>
-      <c r="G89" t="s">
-        <v>83</v>
-      </c>
-      <c r="H89" t="s">
-        <v>84</v>
-      </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89" t="s">
-        <v>91</v>
-      </c>
-      <c r="P89" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q89">
-        <v>3.35</v>
-      </c>
-      <c r="R89">
-        <v>2.2</v>
-      </c>
-      <c r="S89">
-        <v>2.75</v>
-      </c>
-      <c r="T89">
-        <v>1.33</v>
-      </c>
-      <c r="U89">
-        <v>3</v>
-      </c>
-      <c r="V89">
-        <v>2.5</v>
-      </c>
-      <c r="W89">
-        <v>1.48</v>
-      </c>
-      <c r="X89">
-        <v>5.7</v>
-      </c>
-      <c r="Y89">
-        <v>1.08</v>
-      </c>
-      <c r="Z89">
-        <v>2.7</v>
-      </c>
-      <c r="AA89">
-        <v>3.34</v>
-      </c>
-      <c r="AB89">
-        <v>2.23</v>
-      </c>
-      <c r="AC89">
-        <v>1.05</v>
-      </c>
-      <c r="AD89">
-        <v>9.5</v>
-      </c>
-      <c r="AE89">
-        <v>1.25</v>
-      </c>
-      <c r="AF89">
-        <v>3.85</v>
-      </c>
-      <c r="AG89">
-        <v>1.81</v>
-      </c>
-      <c r="AH89">
-        <v>1.89</v>
-      </c>
-      <c r="AI89">
-        <v>1.6</v>
-      </c>
-      <c r="AJ89">
-        <v>2.15</v>
-      </c>
-      <c r="AK89">
-        <v>1.62</v>
-      </c>
-      <c r="AL89">
-        <v>1.25</v>
-      </c>
-      <c r="AM89">
-        <v>1.38</v>
-      </c>
-      <c r="AN89">
-        <v>0.2</v>
-      </c>
-      <c r="AO89">
-        <v>1.43</v>
-      </c>
-      <c r="AP89">
-        <v>0.33</v>
-      </c>
-      <c r="AQ89">
-        <v>1.38</v>
-      </c>
-      <c r="AR89">
-        <v>1.3</v>
-      </c>
-      <c r="AS89">
-        <v>1.18</v>
-      </c>
-      <c r="AT89">
-        <v>2.48</v>
-      </c>
-      <c r="AU89">
-        <v>5</v>
-      </c>
-      <c r="AV89">
-        <v>4</v>
-      </c>
-      <c r="AW89">
-        <v>4</v>
-      </c>
-      <c r="AX89">
-        <v>8</v>
-      </c>
-      <c r="AY89">
-        <v>9</v>
-      </c>
-      <c r="AZ89">
-        <v>12</v>
-      </c>
-      <c r="BA89">
-        <v>5</v>
-      </c>
-      <c r="BB89">
-        <v>4</v>
-      </c>
-      <c r="BC89">
-        <v>9</v>
-      </c>
-      <c r="BD89">
-        <v>2.1</v>
-      </c>
-      <c r="BE89">
-        <v>6.75</v>
-      </c>
-      <c r="BF89">
-        <v>1.86</v>
-      </c>
-      <c r="BG89">
-        <v>1.22</v>
-      </c>
-      <c r="BH89">
-        <v>3.8</v>
-      </c>
-      <c r="BI89">
-        <v>1.38</v>
-      </c>
-      <c r="BJ89">
-        <v>2.75</v>
-      </c>
-      <c r="BK89">
-        <v>1.61</v>
-      </c>
-      <c r="BL89">
-        <v>2.15</v>
-      </c>
-      <c r="BM89">
-        <v>1.97</v>
-      </c>
-      <c r="BN89">
-        <v>1.74</v>
-      </c>
-      <c r="BO89">
-        <v>2.43</v>
-      </c>
-      <c r="BP89">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="90" spans="1:68">
-      <c r="A90" s="1">
-        <v>89</v>
-      </c>
-      <c r="B90">
-        <v>7785262</v>
-      </c>
-      <c r="C90" t="s">
-        <v>68</v>
-      </c>
-      <c r="D90" t="s">
-        <v>69</v>
-      </c>
-      <c r="E90" s="2">
-        <v>45837.5</v>
-      </c>
-      <c r="F90">
-        <v>11</v>
-      </c>
-      <c r="G90" t="s">
-        <v>78</v>
-      </c>
-      <c r="H90" t="s">
-        <v>81</v>
-      </c>
-      <c r="I90">
-        <v>1</v>
-      </c>
-      <c r="J90">
-        <v>1</v>
-      </c>
-      <c r="K90">
-        <v>2</v>
-      </c>
-      <c r="L90">
-        <v>1</v>
-      </c>
-      <c r="M90">
-        <v>2</v>
-      </c>
-      <c r="N90">
-        <v>3</v>
-      </c>
-      <c r="O90" t="s">
-        <v>148</v>
-      </c>
-      <c r="P90" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q90">
-        <v>1.57</v>
-      </c>
-      <c r="R90">
-        <v>3</v>
-      </c>
-      <c r="S90">
-        <v>6.5</v>
-      </c>
-      <c r="T90">
-        <v>1.17</v>
-      </c>
-      <c r="U90">
-        <v>4.5</v>
-      </c>
-      <c r="V90">
-        <v>1.83</v>
-      </c>
-      <c r="W90">
-        <v>1.85</v>
-      </c>
-      <c r="X90">
-        <v>3.74</v>
-      </c>
-      <c r="Y90">
-        <v>1.19</v>
-      </c>
-      <c r="Z90">
-        <v>1.23</v>
-      </c>
-      <c r="AA90">
-        <v>5.7</v>
-      </c>
-      <c r="AB90">
-        <v>7.7</v>
-      </c>
-      <c r="AC90">
-        <v>1.01</v>
-      </c>
-      <c r="AD90">
-        <v>26</v>
-      </c>
-      <c r="AE90">
-        <v>1.08</v>
-      </c>
-      <c r="AF90">
-        <v>7.5</v>
-      </c>
-      <c r="AG90">
-        <v>1.3</v>
-      </c>
-      <c r="AH90">
-        <v>3.33</v>
-      </c>
-      <c r="AI90">
-        <v>1.6</v>
-      </c>
-      <c r="AJ90">
-        <v>2.15</v>
-      </c>
-      <c r="AK90">
-        <v>1.05</v>
-      </c>
-      <c r="AL90">
-        <v>1.11</v>
-      </c>
-      <c r="AM90">
-        <v>3.7</v>
-      </c>
-      <c r="AN90">
-        <v>2.4</v>
-      </c>
-      <c r="AO90">
-        <v>1.8</v>
-      </c>
-      <c r="AP90">
-        <v>2</v>
-      </c>
-      <c r="AQ90">
-        <v>2</v>
-      </c>
-      <c r="AR90">
-        <v>2.02</v>
-      </c>
-      <c r="AS90">
-        <v>1.66</v>
-      </c>
-      <c r="AT90">
-        <v>3.68</v>
-      </c>
-      <c r="AU90">
-        <v>7</v>
-      </c>
-      <c r="AV90">
-        <v>4</v>
-      </c>
-      <c r="AW90">
-        <v>23</v>
-      </c>
-      <c r="AX90">
-        <v>2</v>
-      </c>
-      <c r="AY90">
-        <v>30</v>
-      </c>
-      <c r="AZ90">
-        <v>6</v>
-      </c>
-      <c r="BA90">
-        <v>10</v>
-      </c>
-      <c r="BB90">
-        <v>2</v>
-      </c>
-      <c r="BC90">
-        <v>12</v>
-      </c>
-      <c r="BD90">
-        <v>1.23</v>
-      </c>
-      <c r="BE90">
-        <v>8.5</v>
-      </c>
-      <c r="BF90">
-        <v>4.4</v>
-      </c>
-      <c r="BG90">
-        <v>1.15</v>
-      </c>
-      <c r="BH90">
-        <v>4.6</v>
-      </c>
-      <c r="BI90">
-        <v>1.27</v>
-      </c>
-      <c r="BJ90">
-        <v>3.3</v>
-      </c>
-      <c r="BK90">
-        <v>1.46</v>
-      </c>
-      <c r="BL90">
-        <v>2.5</v>
-      </c>
-      <c r="BM90">
-        <v>1.73</v>
-      </c>
-      <c r="BN90">
-        <v>1.98</v>
-      </c>
-      <c r="BO90">
-        <v>2.08</v>
-      </c>
-      <c r="BP90">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="91" spans="1:68">
-      <c r="A91" s="1">
-        <v>90</v>
-      </c>
-      <c r="B91">
-        <v>7785264</v>
-      </c>
-      <c r="C91" t="s">
-        <v>68</v>
-      </c>
-      <c r="D91" t="s">
-        <v>69</v>
-      </c>
-      <c r="E91" s="2">
-        <v>45837.5</v>
-      </c>
-      <c r="F91">
-        <v>11</v>
-      </c>
-      <c r="G91" t="s">
-        <v>77</v>
-      </c>
-      <c r="H91" t="s">
-        <v>73</v>
-      </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <v>1</v>
-      </c>
-      <c r="K91">
-        <v>1</v>
-      </c>
-      <c r="L91">
-        <v>1</v>
-      </c>
-      <c r="M91">
-        <v>1</v>
-      </c>
-      <c r="N91">
-        <v>2</v>
-      </c>
-      <c r="O91" t="s">
-        <v>149</v>
-      </c>
-      <c r="P91" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q91">
-        <v>2.45</v>
-      </c>
-      <c r="R91">
-        <v>2.15</v>
-      </c>
-      <c r="S91">
-        <v>4</v>
-      </c>
-      <c r="T91">
-        <v>1.35</v>
-      </c>
-      <c r="U91">
-        <v>2.95</v>
-      </c>
-      <c r="V91">
-        <v>2.62</v>
-      </c>
-      <c r="W91">
-        <v>1.42</v>
-      </c>
-      <c r="X91">
-        <v>6.65</v>
-      </c>
-      <c r="Y91">
-        <v>1.05</v>
-      </c>
-      <c r="Z91">
-        <v>1.86</v>
-      </c>
-      <c r="AA91">
-        <v>3.39</v>
-      </c>
-      <c r="AB91">
-        <v>3.47</v>
-      </c>
-      <c r="AC91">
-        <v>1.05</v>
-      </c>
-      <c r="AD91">
-        <v>9.5</v>
-      </c>
-      <c r="AE91">
-        <v>1.28</v>
-      </c>
-      <c r="AF91">
-        <v>3.65</v>
-      </c>
-      <c r="AG91">
-        <v>1.79</v>
-      </c>
-      <c r="AH91">
-        <v>1.91</v>
-      </c>
-      <c r="AI91">
-        <v>1.7</v>
-      </c>
-      <c r="AJ91">
-        <v>2</v>
-      </c>
-      <c r="AK91">
-        <v>1.25</v>
-      </c>
-      <c r="AL91">
-        <v>1.22</v>
-      </c>
-      <c r="AM91">
-        <v>1.85</v>
-      </c>
-      <c r="AN91">
-        <v>1.8</v>
-      </c>
-      <c r="AO91">
-        <v>0.8</v>
-      </c>
-      <c r="AP91">
-        <v>1.67</v>
-      </c>
-      <c r="AQ91">
-        <v>0.83</v>
-      </c>
-      <c r="AR91">
-        <v>1.53</v>
-      </c>
-      <c r="AS91">
-        <v>1.13</v>
-      </c>
-      <c r="AT91">
-        <v>2.66</v>
-      </c>
-      <c r="AU91">
-        <v>8</v>
-      </c>
-      <c r="AV91">
-        <v>4</v>
-      </c>
-      <c r="AW91">
-        <v>6</v>
-      </c>
-      <c r="AX91">
-        <v>9</v>
-      </c>
-      <c r="AY91">
-        <v>14</v>
-      </c>
-      <c r="AZ91">
-        <v>13</v>
-      </c>
-      <c r="BA91">
-        <v>10</v>
-      </c>
-      <c r="BB91">
-        <v>5</v>
-      </c>
-      <c r="BC91">
-        <v>15</v>
-      </c>
-      <c r="BD91">
-        <v>1.65</v>
-      </c>
-      <c r="BE91">
-        <v>7</v>
-      </c>
-      <c r="BF91">
-        <v>2.48</v>
-      </c>
-      <c r="BG91">
-        <v>1.19</v>
-      </c>
-      <c r="BH91">
-        <v>4.1</v>
-      </c>
-      <c r="BI91">
-        <v>1.34</v>
-      </c>
-      <c r="BJ91">
-        <v>2.9</v>
-      </c>
-      <c r="BK91">
-        <v>1.55</v>
-      </c>
-      <c r="BL91">
-        <v>2.25</v>
-      </c>
-      <c r="BM91">
-        <v>1.9</v>
-      </c>
-      <c r="BN91">
-        <v>1.79</v>
-      </c>
-      <c r="BO91">
-        <v>2.33</v>
-      </c>
-      <c r="BP91">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="92" spans="1:68">
-      <c r="A92" s="1">
-        <v>91</v>
-      </c>
-      <c r="B92">
-        <v>7785265</v>
-      </c>
-      <c r="C92" t="s">
-        <v>68</v>
-      </c>
-      <c r="D92" t="s">
-        <v>69</v>
-      </c>
-      <c r="E92" s="2">
-        <v>45837.5</v>
-      </c>
-      <c r="F92">
-        <v>11</v>
-      </c>
-      <c r="G92" t="s">
-        <v>71</v>
-      </c>
-      <c r="H92" t="s">
-        <v>76</v>
-      </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
-      <c r="J92">
-        <v>1</v>
-      </c>
-      <c r="K92">
-        <v>1</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92">
-        <v>1</v>
-      </c>
-      <c r="O92" t="s">
-        <v>91</v>
-      </c>
-      <c r="P92" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q92">
-        <v>3.1</v>
-      </c>
-      <c r="R92">
-        <v>1.95</v>
-      </c>
-      <c r="S92">
-        <v>3.55</v>
-      </c>
-      <c r="T92">
-        <v>1.48</v>
-      </c>
-      <c r="U92">
-        <v>2.45</v>
-      </c>
-      <c r="V92">
-        <v>3.2</v>
-      </c>
-      <c r="W92">
-        <v>1.3</v>
-      </c>
-      <c r="X92">
-        <v>9.1</v>
-      </c>
-      <c r="Y92">
-        <v>1</v>
-      </c>
-      <c r="Z92">
-        <v>2.25</v>
-      </c>
-      <c r="AA92">
-        <v>3.08</v>
-      </c>
-      <c r="AB92">
-        <v>2.85</v>
-      </c>
-      <c r="AC92">
-        <v>1.08</v>
-      </c>
-      <c r="AD92">
-        <v>7.5</v>
-      </c>
-      <c r="AE92">
-        <v>1.42</v>
-      </c>
-      <c r="AF92">
-        <v>2.8</v>
-      </c>
-      <c r="AG92">
-        <v>2.04</v>
-      </c>
-      <c r="AH92">
-        <v>1.69</v>
-      </c>
-      <c r="AI92">
-        <v>1.85</v>
-      </c>
-      <c r="AJ92">
-        <v>1.8</v>
-      </c>
-      <c r="AK92">
-        <v>1.38</v>
-      </c>
-      <c r="AL92">
-        <v>1.3</v>
-      </c>
-      <c r="AM92">
-        <v>1.53</v>
-      </c>
-      <c r="AN92">
-        <v>2.17</v>
-      </c>
-      <c r="AO92">
-        <v>2</v>
-      </c>
-      <c r="AP92">
-        <v>1.86</v>
-      </c>
-      <c r="AQ92">
-        <v>2.17</v>
-      </c>
-      <c r="AR92">
-        <v>1.11</v>
-      </c>
-      <c r="AS92">
-        <v>1.09</v>
-      </c>
-      <c r="AT92">
-        <v>2.2</v>
-      </c>
-      <c r="AU92">
-        <v>6</v>
-      </c>
-      <c r="AV92">
-        <v>5</v>
-      </c>
-      <c r="AW92">
-        <v>8</v>
-      </c>
-      <c r="AX92">
-        <v>3</v>
-      </c>
-      <c r="AY92">
-        <v>14</v>
-      </c>
-      <c r="AZ92">
-        <v>8</v>
-      </c>
-      <c r="BA92">
-        <v>8</v>
-      </c>
-      <c r="BB92">
-        <v>3</v>
-      </c>
-      <c r="BC92">
-        <v>11</v>
-      </c>
-      <c r="BD92">
-        <v>1.86</v>
-      </c>
-      <c r="BE92">
-        <v>6.4</v>
-      </c>
-      <c r="BF92">
-        <v>2.15</v>
-      </c>
-      <c r="BG92">
-        <v>1.33</v>
-      </c>
-      <c r="BH92">
-        <v>2.95</v>
-      </c>
-      <c r="BI92">
-        <v>1.56</v>
-      </c>
-      <c r="BJ92">
-        <v>2.23</v>
-      </c>
-      <c r="BK92">
-        <v>1.92</v>
-      </c>
-      <c r="BL92">
-        <v>1.78</v>
-      </c>
-      <c r="BM92">
-        <v>2.4</v>
-      </c>
-      <c r="BN92">
-        <v>1.49</v>
-      </c>
-      <c r="BO92">
-        <v>3.15</v>
-      </c>
-      <c r="BP92">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:68">
-      <c r="A93" s="1">
-        <v>92</v>
-      </c>
-      <c r="B93">
-        <v>7785267</v>
-      </c>
-      <c r="C93" t="s">
-        <v>68</v>
-      </c>
-      <c r="D93" t="s">
-        <v>69</v>
-      </c>
-      <c r="E93" s="2">
-        <v>45837.5</v>
-      </c>
-      <c r="F93">
-        <v>11</v>
-      </c>
-      <c r="G93" t="s">
-        <v>75</v>
-      </c>
-      <c r="H93" t="s">
-        <v>74</v>
-      </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <v>2</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
-      </c>
-      <c r="L93">
-        <v>2</v>
-      </c>
-      <c r="M93">
-        <v>3</v>
-      </c>
-      <c r="N93">
-        <v>5</v>
-      </c>
-      <c r="O93" t="s">
-        <v>150</v>
-      </c>
-      <c r="P93" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q93">
-        <v>2.38</v>
-      </c>
-      <c r="R93">
-        <v>2.1</v>
-      </c>
-      <c r="S93">
-        <v>4.5</v>
-      </c>
-      <c r="T93">
-        <v>1.38</v>
-      </c>
-      <c r="U93">
-        <v>2.8</v>
-      </c>
-      <c r="V93">
-        <v>2.8</v>
-      </c>
-      <c r="W93">
-        <v>1.38</v>
-      </c>
-      <c r="X93">
-        <v>7.3</v>
-      </c>
-      <c r="Y93">
-        <v>1.03</v>
-      </c>
-      <c r="Z93">
-        <v>1.73</v>
-      </c>
-      <c r="AA93">
-        <v>3.4</v>
-      </c>
-      <c r="AB93">
-        <v>4</v>
-      </c>
-      <c r="AC93">
-        <v>1.06</v>
-      </c>
-      <c r="AD93">
-        <v>8.5</v>
-      </c>
-      <c r="AE93">
-        <v>1.33</v>
-      </c>
-      <c r="AF93">
-        <v>3.3</v>
-      </c>
-      <c r="AG93">
-        <v>1.92</v>
-      </c>
-      <c r="AH93">
-        <v>1.78</v>
-      </c>
-      <c r="AI93">
-        <v>1.83</v>
-      </c>
-      <c r="AJ93">
-        <v>1.85</v>
-      </c>
-      <c r="AK93">
-        <v>1.2</v>
-      </c>
-      <c r="AL93">
-        <v>1.22</v>
-      </c>
-      <c r="AM93">
-        <v>1.95</v>
-      </c>
-      <c r="AN93">
-        <v>0.8</v>
-      </c>
-      <c r="AO93">
-        <v>0.4</v>
-      </c>
-      <c r="AP93">
-        <v>0.67</v>
-      </c>
-      <c r="AQ93">
-        <v>0.83</v>
-      </c>
-      <c r="AR93">
-        <v>1.62</v>
-      </c>
-      <c r="AS93">
-        <v>0.97</v>
-      </c>
-      <c r="AT93">
-        <v>2.59</v>
-      </c>
-      <c r="AU93">
-        <v>5</v>
-      </c>
-      <c r="AV93">
-        <v>5</v>
-      </c>
-      <c r="AW93">
-        <v>8</v>
-      </c>
-      <c r="AX93">
-        <v>5</v>
-      </c>
-      <c r="AY93">
-        <v>13</v>
-      </c>
-      <c r="AZ93">
-        <v>10</v>
-      </c>
-      <c r="BA93">
-        <v>4</v>
-      </c>
-      <c r="BB93">
-        <v>0</v>
-      </c>
-      <c r="BC93">
-        <v>4</v>
-      </c>
-      <c r="BD93">
-        <v>1.6</v>
-      </c>
-      <c r="BE93">
-        <v>6.4</v>
-      </c>
-      <c r="BF93">
-        <v>2.65</v>
-      </c>
-      <c r="BG93">
-        <v>1.36</v>
-      </c>
-      <c r="BH93">
-        <v>2.8</v>
-      </c>
-      <c r="BI93">
-        <v>1.6</v>
-      </c>
-      <c r="BJ93">
-        <v>2.17</v>
-      </c>
-      <c r="BK93">
-        <v>1.98</v>
-      </c>
-      <c r="BL93">
-        <v>1.74</v>
-      </c>
-      <c r="BM93">
-        <v>2.5</v>
-      </c>
-      <c r="BN93">
-        <v>1.46</v>
-      </c>
-      <c r="BO93">
-        <v>3.3</v>
-      </c>
-      <c r="BP93">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="94" spans="1:68">
-      <c r="A94" s="1">
-        <v>93</v>
-      </c>
-      <c r="B94">
-        <v>7785269</v>
-      </c>
-      <c r="C94" t="s">
-        <v>68</v>
-      </c>
-      <c r="D94" t="s">
-        <v>69</v>
-      </c>
-      <c r="E94" s="2">
-        <v>45837.59375</v>
-      </c>
-      <c r="F94">
-        <v>11</v>
-      </c>
-      <c r="G94" t="s">
-        <v>70</v>
-      </c>
-      <c r="H94" t="s">
-        <v>72</v>
-      </c>
-      <c r="I94">
-        <v>0</v>
-      </c>
-      <c r="J94">
-        <v>1</v>
-      </c>
-      <c r="K94">
-        <v>1</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>2</v>
-      </c>
-      <c r="N94">
-        <v>2</v>
-      </c>
-      <c r="O94" t="s">
-        <v>91</v>
-      </c>
-      <c r="P94" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q94">
-        <v>2.95</v>
-      </c>
-      <c r="R94">
-        <v>2.25</v>
-      </c>
-      <c r="S94">
-        <v>3</v>
-      </c>
-      <c r="T94">
-        <v>1.28</v>
-      </c>
-      <c r="U94">
-        <v>3.3</v>
-      </c>
-      <c r="V94">
-        <v>2.25</v>
-      </c>
-      <c r="W94">
-        <v>1.57</v>
-      </c>
-      <c r="X94">
-        <v>5.15</v>
-      </c>
-      <c r="Y94">
-        <v>1.1</v>
-      </c>
-      <c r="Z94">
-        <v>2.18</v>
-      </c>
-      <c r="AA94">
-        <v>3.28</v>
-      </c>
-      <c r="AB94">
-        <v>2.8</v>
-      </c>
-      <c r="AC94">
-        <v>1.04</v>
-      </c>
-      <c r="AD94">
-        <v>10</v>
-      </c>
-      <c r="AE94">
-        <v>1.2</v>
-      </c>
-      <c r="AF94">
-        <v>4.5</v>
-      </c>
-      <c r="AG94">
-        <v>1.57</v>
-      </c>
-      <c r="AH94">
-        <v>2.15</v>
-      </c>
-      <c r="AI94">
-        <v>1.45</v>
-      </c>
-      <c r="AJ94">
-        <v>2.5</v>
-      </c>
-      <c r="AK94">
-        <v>1.48</v>
-      </c>
-      <c r="AL94">
-        <v>1.22</v>
-      </c>
-      <c r="AM94">
-        <v>1.5</v>
-      </c>
-      <c r="AN94">
-        <v>0</v>
-      </c>
-      <c r="AO94">
-        <v>1.17</v>
-      </c>
-      <c r="AP94">
-        <v>0</v>
-      </c>
-      <c r="AQ94">
-        <v>1.43</v>
-      </c>
-      <c r="AR94">
-        <v>1.63</v>
-      </c>
-      <c r="AS94">
-        <v>1.18</v>
-      </c>
-      <c r="AT94">
-        <v>2.81</v>
-      </c>
-      <c r="AU94">
-        <v>3</v>
-      </c>
-      <c r="AV94">
-        <v>3</v>
-      </c>
-      <c r="AW94">
-        <v>2</v>
-      </c>
-      <c r="AX94">
-        <v>13</v>
-      </c>
-      <c r="AY94">
-        <v>5</v>
-      </c>
-      <c r="AZ94">
-        <v>16</v>
-      </c>
-      <c r="BA94">
-        <v>4</v>
-      </c>
-      <c r="BB94">
-        <v>3</v>
-      </c>
-      <c r="BC94">
-        <v>7</v>
-      </c>
-      <c r="BD94">
-        <v>1.79</v>
-      </c>
-      <c r="BE94">
-        <v>7</v>
-      </c>
-      <c r="BF94">
-        <v>2.18</v>
-      </c>
-      <c r="BG94">
-        <v>1.13</v>
-      </c>
-      <c r="BH94">
-        <v>5.1</v>
-      </c>
-      <c r="BI94">
-        <v>1.24</v>
-      </c>
-      <c r="BJ94">
-        <v>3.65</v>
-      </c>
-      <c r="BK94">
-        <v>1.41</v>
-      </c>
-      <c r="BL94">
-        <v>2.65</v>
-      </c>
-      <c r="BM94">
-        <v>1.65</v>
-      </c>
-      <c r="BN94">
-        <v>2.08</v>
-      </c>
-      <c r="BO94">
-        <v>1.98</v>
-      </c>
-      <c r="BP94">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="95" spans="1:68">
-      <c r="A95" s="1">
-        <v>94</v>
-      </c>
-      <c r="B95">
-        <v>7785263</v>
-      </c>
-      <c r="C95" t="s">
-        <v>68</v>
-      </c>
-      <c r="D95" t="s">
-        <v>69</v>
-      </c>
-      <c r="E95" s="2">
-        <v>45838.58333333334</v>
-      </c>
-      <c r="F95">
-        <v>11</v>
-      </c>
-      <c r="G95" t="s">
-        <v>80</v>
-      </c>
-      <c r="H95" t="s">
-        <v>82</v>
-      </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <v>0</v>
-      </c>
-      <c r="L95">
-        <v>1</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>1</v>
-      </c>
-      <c r="O95" t="s">
-        <v>151</v>
-      </c>
-      <c r="P95" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q95">
-        <v>1.95</v>
-      </c>
-      <c r="R95">
-        <v>2.63</v>
-      </c>
-      <c r="S95">
-        <v>5</v>
-      </c>
-      <c r="T95">
-        <v>1.22</v>
-      </c>
-      <c r="U95">
-        <v>4</v>
-      </c>
-      <c r="V95">
-        <v>2.1</v>
-      </c>
-      <c r="W95">
-        <v>1.67</v>
-      </c>
-      <c r="X95">
-        <v>4.5</v>
-      </c>
-      <c r="Y95">
-        <v>1.18</v>
-      </c>
-      <c r="Z95">
-        <v>1.46</v>
-      </c>
-      <c r="AA95">
-        <v>4.2</v>
-      </c>
-      <c r="AB95">
-        <v>5</v>
-      </c>
-      <c r="AC95">
-        <v>1.01</v>
-      </c>
-      <c r="AD95">
-        <v>17</v>
-      </c>
-      <c r="AE95">
-        <v>1.13</v>
-      </c>
-      <c r="AF95">
-        <v>5.75</v>
-      </c>
-      <c r="AG95">
-        <v>1.41</v>
-      </c>
-      <c r="AH95">
-        <v>2.78</v>
-      </c>
-      <c r="AI95">
-        <v>1.53</v>
-      </c>
-      <c r="AJ95">
-        <v>2.38</v>
-      </c>
-      <c r="AK95">
-        <v>1.16</v>
-      </c>
-      <c r="AL95">
-        <v>1.19</v>
-      </c>
-      <c r="AM95">
-        <v>2.4</v>
-      </c>
-      <c r="AN95">
-        <v>2</v>
-      </c>
-      <c r="AO95">
-        <v>0.6</v>
-      </c>
-      <c r="AP95">
-        <v>2.13</v>
-      </c>
-      <c r="AQ95">
-        <v>0.5</v>
-      </c>
-      <c r="AR95">
-        <v>1.99</v>
-      </c>
-      <c r="AS95">
-        <v>1.68</v>
-      </c>
-      <c r="AT95">
-        <v>3.67</v>
-      </c>
-      <c r="AU95">
-        <v>10</v>
-      </c>
-      <c r="AV95">
-        <v>3</v>
-      </c>
-      <c r="AW95">
-        <v>14</v>
-      </c>
-      <c r="AX95">
-        <v>5</v>
-      </c>
-      <c r="AY95">
-        <v>24</v>
-      </c>
-      <c r="AZ95">
-        <v>8</v>
-      </c>
-      <c r="BA95">
-        <v>9</v>
-      </c>
-      <c r="BB95">
-        <v>3</v>
-      </c>
-      <c r="BC95">
-        <v>12</v>
-      </c>
-      <c r="BD95">
-        <v>1.5</v>
-      </c>
-      <c r="BE95">
-        <v>7</v>
-      </c>
-      <c r="BF95">
-        <v>2.8</v>
-      </c>
-      <c r="BG95">
-        <v>1.19</v>
-      </c>
-      <c r="BH95">
-        <v>4.1</v>
-      </c>
-      <c r="BI95">
-        <v>1.33</v>
-      </c>
-      <c r="BJ95">
-        <v>2.95</v>
-      </c>
-      <c r="BK95">
-        <v>1.54</v>
-      </c>
-      <c r="BL95">
-        <v>2.3</v>
-      </c>
-      <c r="BM95">
-        <v>1.85</v>
-      </c>
-      <c r="BN95">
-        <v>1.83</v>
-      </c>
-      <c r="BO95">
-        <v>2.32</v>
-      </c>
-      <c r="BP95">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="96" spans="1:68">
-      <c r="A96" s="1">
-        <v>95</v>
-      </c>
-      <c r="B96">
-        <v>7785270</v>
-      </c>
-      <c r="C96" t="s">
-        <v>68</v>
-      </c>
-      <c r="D96" t="s">
-        <v>69</v>
-      </c>
-      <c r="E96" s="2">
-        <v>45843.375</v>
-      </c>
-      <c r="F96">
-        <v>12</v>
-      </c>
-      <c r="G96" t="s">
-        <v>73</v>
-      </c>
-      <c r="H96" t="s">
-        <v>80</v>
-      </c>
-      <c r="I96">
-        <v>1</v>
-      </c>
-      <c r="J96">
-        <v>0</v>
-      </c>
-      <c r="K96">
-        <v>1</v>
-      </c>
-      <c r="L96">
-        <v>1</v>
-      </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96">
-        <v>2</v>
-      </c>
-      <c r="O96" t="s">
-        <v>152</v>
-      </c>
-      <c r="P96" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q96">
-        <v>4.33</v>
-      </c>
-      <c r="R96">
-        <v>2.38</v>
-      </c>
-      <c r="S96">
-        <v>2.38</v>
-      </c>
-      <c r="T96">
-        <v>1.3</v>
-      </c>
-      <c r="U96">
-        <v>3.4</v>
-      </c>
-      <c r="V96">
-        <v>2.38</v>
-      </c>
-      <c r="W96">
-        <v>1.53</v>
-      </c>
-      <c r="X96">
-        <v>6</v>
-      </c>
-      <c r="Y96">
-        <v>1.13</v>
-      </c>
-      <c r="Z96">
-        <v>4.1</v>
-      </c>
-      <c r="AA96">
-        <v>3.73</v>
-      </c>
-      <c r="AB96">
-        <v>1.64</v>
-      </c>
-      <c r="AC96">
-        <v>1.03</v>
-      </c>
-      <c r="AD96">
-        <v>12</v>
-      </c>
-      <c r="AE96">
-        <v>1.21</v>
-      </c>
-      <c r="AF96">
-        <v>4.51</v>
-      </c>
-      <c r="AG96">
-        <v>1.57</v>
-      </c>
-      <c r="AH96">
-        <v>2.31</v>
-      </c>
-      <c r="AI96">
-        <v>1.62</v>
-      </c>
-      <c r="AJ96">
-        <v>2.2</v>
-      </c>
-      <c r="AK96">
-        <v>1.9</v>
-      </c>
-      <c r="AL96">
-        <v>1.25</v>
-      </c>
-      <c r="AM96">
-        <v>1.25</v>
-      </c>
-      <c r="AN96">
-        <v>1.4</v>
-      </c>
-      <c r="AO96">
-        <v>1.8</v>
-      </c>
-      <c r="AP96">
-        <v>1.33</v>
-      </c>
-      <c r="AQ96">
-        <v>1.67</v>
-      </c>
-      <c r="AR96">
-        <v>1.39</v>
-      </c>
-      <c r="AS96">
-        <v>1.79</v>
-      </c>
-      <c r="AT96">
-        <v>3.18</v>
-      </c>
-      <c r="AU96">
-        <v>5</v>
-      </c>
-      <c r="AV96">
-        <v>4</v>
-      </c>
-      <c r="AW96">
-        <v>4</v>
-      </c>
-      <c r="AX96">
-        <v>8</v>
-      </c>
-      <c r="AY96">
-        <v>9</v>
-      </c>
-      <c r="AZ96">
-        <v>12</v>
-      </c>
-      <c r="BA96">
-        <v>1</v>
-      </c>
-      <c r="BB96">
-        <v>8</v>
-      </c>
-      <c r="BC96">
-        <v>9</v>
-      </c>
-      <c r="BD96">
-        <v>2.65</v>
-      </c>
-      <c r="BE96">
-        <v>7</v>
-      </c>
-      <c r="BF96">
-        <v>1.56</v>
-      </c>
-      <c r="BG96">
-        <v>1.16</v>
-      </c>
-      <c r="BH96">
-        <v>4.6</v>
-      </c>
-      <c r="BI96">
-        <v>1.28</v>
-      </c>
-      <c r="BJ96">
-        <v>3.3</v>
-      </c>
-      <c r="BK96">
-        <v>1.47</v>
-      </c>
-      <c r="BL96">
-        <v>2.48</v>
-      </c>
-      <c r="BM96">
-        <v>1.73</v>
-      </c>
-      <c r="BN96">
-        <v>1.98</v>
-      </c>
-      <c r="BO96">
-        <v>2.08</v>
-      </c>
-      <c r="BP96">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="97" spans="1:68">
-      <c r="A97" s="1">
-        <v>96</v>
-      </c>
-      <c r="B97">
-        <v>7785276</v>
-      </c>
-      <c r="C97" t="s">
-        <v>68</v>
-      </c>
-      <c r="D97" t="s">
-        <v>69</v>
-      </c>
-      <c r="E97" s="2">
-        <v>45843.45833333334</v>
-      </c>
-      <c r="F97">
-        <v>12</v>
-      </c>
-      <c r="G97" t="s">
-        <v>85</v>
-      </c>
-      <c r="H97" t="s">
-        <v>70</v>
-      </c>
-      <c r="I97">
-        <v>1</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>1</v>
-      </c>
-      <c r="L97">
-        <v>1</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>1</v>
-      </c>
-      <c r="O97" t="s">
-        <v>153</v>
-      </c>
-      <c r="P97" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q97">
-        <v>1.57</v>
-      </c>
-      <c r="R97">
-        <v>3.2</v>
-      </c>
-      <c r="S97">
-        <v>7.5</v>
-      </c>
-      <c r="T97">
-        <v>1.14</v>
-      </c>
-      <c r="U97">
-        <v>5.5</v>
-      </c>
-      <c r="V97">
-        <v>1.73</v>
-      </c>
-      <c r="W97">
-        <v>2</v>
-      </c>
-      <c r="X97">
-        <v>3.4</v>
-      </c>
-      <c r="Y97">
-        <v>1.3</v>
-      </c>
-      <c r="Z97">
-        <v>1.25</v>
-      </c>
-      <c r="AA97">
-        <v>5.3</v>
-      </c>
-      <c r="AB97">
-        <v>7.6</v>
-      </c>
-      <c r="AC97">
-        <v>1</v>
-      </c>
-      <c r="AD97">
-        <v>25</v>
-      </c>
-      <c r="AE97">
-        <v>1.04</v>
-      </c>
-      <c r="AF97">
-        <v>9.5</v>
-      </c>
-      <c r="AG97">
-        <v>1.28</v>
-      </c>
-      <c r="AH97">
-        <v>3.47</v>
-      </c>
-      <c r="AI97">
-        <v>1.57</v>
-      </c>
-      <c r="AJ97">
-        <v>2.25</v>
-      </c>
-      <c r="AK97">
-        <v>1.06</v>
-      </c>
-      <c r="AL97">
-        <v>1.07</v>
-      </c>
-      <c r="AM97">
-        <v>3.7</v>
-      </c>
-      <c r="AN97">
-        <v>2.43</v>
-      </c>
-      <c r="AO97">
-        <v>1.2</v>
-      </c>
-      <c r="AP97">
-        <v>2.5</v>
-      </c>
-      <c r="AQ97">
-        <v>1</v>
-      </c>
-      <c r="AR97">
-        <v>2.35</v>
-      </c>
-      <c r="AS97">
-        <v>1.53</v>
-      </c>
-      <c r="AT97">
-        <v>3.88</v>
-      </c>
-      <c r="AU97">
-        <v>6</v>
-      </c>
-      <c r="AV97">
-        <v>2</v>
-      </c>
-      <c r="AW97">
-        <v>14</v>
-      </c>
-      <c r="AX97">
-        <v>1</v>
-      </c>
-      <c r="AY97">
-        <v>20</v>
-      </c>
-      <c r="AZ97">
-        <v>3</v>
-      </c>
-      <c r="BA97">
-        <v>16</v>
-      </c>
-      <c r="BB97">
-        <v>2</v>
-      </c>
-      <c r="BC97">
-        <v>18</v>
-      </c>
-      <c r="BD97">
-        <v>1.26</v>
-      </c>
-      <c r="BE97">
-        <v>8.5</v>
-      </c>
-      <c r="BF97">
-        <v>3.95</v>
-      </c>
-      <c r="BG97">
-        <v>1.08</v>
-      </c>
-      <c r="BH97">
-        <v>6.25</v>
-      </c>
-      <c r="BI97">
-        <v>1.16</v>
-      </c>
-      <c r="BJ97">
-        <v>4.4</v>
-      </c>
-      <c r="BK97">
-        <v>1.28</v>
-      </c>
-      <c r="BL97">
-        <v>3.3</v>
-      </c>
-      <c r="BM97">
-        <v>1.47</v>
-      </c>
-      <c r="BN97">
-        <v>2.48</v>
-      </c>
-      <c r="BO97">
-        <v>1.7</v>
-      </c>
-      <c r="BP97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:68">
-      <c r="A98" s="1">
-        <v>97</v>
-      </c>
-      <c r="B98">
-        <v>7785277</v>
-      </c>
-      <c r="C98" t="s">
-        <v>68</v>
-      </c>
-      <c r="D98" t="s">
-        <v>69</v>
-      </c>
-      <c r="E98" s="2">
-        <v>45843.54166666666</v>
-      </c>
-      <c r="F98">
-        <v>12</v>
-      </c>
-      <c r="G98" t="s">
-        <v>72</v>
-      </c>
-      <c r="H98" t="s">
-        <v>71</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98">
-        <v>1</v>
-      </c>
-      <c r="K98">
-        <v>2</v>
-      </c>
-      <c r="L98">
-        <v>1</v>
-      </c>
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98">
-        <v>2</v>
-      </c>
-      <c r="O98" t="s">
-        <v>154</v>
-      </c>
-      <c r="P98" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q98">
-        <v>2.75</v>
-      </c>
-      <c r="R98">
-        <v>2.1</v>
-      </c>
-      <c r="S98">
-        <v>4</v>
-      </c>
-      <c r="T98">
-        <v>1.4</v>
-      </c>
-      <c r="U98">
-        <v>2.75</v>
-      </c>
-      <c r="V98">
-        <v>3</v>
-      </c>
-      <c r="W98">
-        <v>1.36</v>
-      </c>
-      <c r="X98">
-        <v>8</v>
-      </c>
-      <c r="Y98">
-        <v>1.08</v>
-      </c>
-      <c r="Z98">
-        <v>2.16</v>
-      </c>
-      <c r="AA98">
-        <v>3.06</v>
-      </c>
-      <c r="AB98">
-        <v>3.03</v>
-      </c>
-      <c r="AC98">
-        <v>1.06</v>
-      </c>
-      <c r="AD98">
-        <v>8.5</v>
-      </c>
-      <c r="AE98">
-        <v>1.33</v>
-      </c>
-      <c r="AF98">
-        <v>3.25</v>
-      </c>
-      <c r="AG98">
-        <v>1.9</v>
-      </c>
-      <c r="AH98">
-        <v>1.8</v>
-      </c>
-      <c r="AI98">
-        <v>1.8</v>
-      </c>
-      <c r="AJ98">
-        <v>1.95</v>
-      </c>
-      <c r="AK98">
-        <v>1.3</v>
-      </c>
-      <c r="AL98">
-        <v>1.28</v>
-      </c>
-      <c r="AM98">
-        <v>1.67</v>
-      </c>
-      <c r="AN98">
-        <v>0.8</v>
-      </c>
-      <c r="AO98">
-        <v>0.8</v>
-      </c>
-      <c r="AP98">
-        <v>0.83</v>
-      </c>
-      <c r="AQ98">
-        <v>0.83</v>
-      </c>
-      <c r="AR98">
-        <v>2.13</v>
-      </c>
-      <c r="AS98">
-        <v>1.17</v>
-      </c>
-      <c r="AT98">
-        <v>3.3</v>
-      </c>
-      <c r="AU98">
-        <v>8</v>
-      </c>
-      <c r="AV98">
-        <v>9</v>
-      </c>
-      <c r="AW98">
-        <v>3</v>
-      </c>
-      <c r="AX98">
-        <v>6</v>
-      </c>
-      <c r="AY98">
-        <v>11</v>
-      </c>
-      <c r="AZ98">
-        <v>15</v>
-      </c>
-      <c r="BA98">
-        <v>5</v>
-      </c>
-      <c r="BB98">
-        <v>5</v>
-      </c>
-      <c r="BC98">
-        <v>10</v>
-      </c>
-      <c r="BD98">
-        <v>1.65</v>
-      </c>
-      <c r="BE98">
-        <v>6.75</v>
-      </c>
-      <c r="BF98">
-        <v>2.48</v>
-      </c>
-      <c r="BG98">
-        <v>1.21</v>
-      </c>
-      <c r="BH98">
-        <v>3.9</v>
-      </c>
-      <c r="BI98">
-        <v>1.38</v>
-      </c>
-      <c r="BJ98">
-        <v>2.8</v>
-      </c>
-      <c r="BK98">
-        <v>1.61</v>
-      </c>
-      <c r="BL98">
-        <v>2.15</v>
-      </c>
-      <c r="BM98">
-        <v>1.96</v>
-      </c>
-      <c r="BN98">
-        <v>1.74</v>
-      </c>
-      <c r="BO98">
-        <v>2.43</v>
-      </c>
-      <c r="BP98">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="99" spans="1:68">
-      <c r="A99" s="1">
-        <v>98</v>
-      </c>
-      <c r="B99">
-        <v>7785272</v>
-      </c>
-      <c r="C99" t="s">
-        <v>68</v>
-      </c>
-      <c r="D99" t="s">
-        <v>69</v>
-      </c>
-      <c r="E99" s="2">
-        <v>45843.625</v>
-      </c>
-      <c r="F99">
-        <v>12</v>
-      </c>
-      <c r="G99" t="s">
-        <v>84</v>
-      </c>
-      <c r="H99" t="s">
-        <v>78</v>
-      </c>
-      <c r="I99">
-        <v>0</v>
-      </c>
-      <c r="J99">
-        <v>1</v>
-      </c>
-      <c r="K99">
-        <v>1</v>
-      </c>
-      <c r="L99">
-        <v>1</v>
-      </c>
-      <c r="M99">
-        <v>1</v>
-      </c>
-      <c r="N99">
-        <v>2</v>
-      </c>
-      <c r="O99" t="s">
-        <v>155</v>
-      </c>
-      <c r="P99" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q99">
-        <v>6.5</v>
-      </c>
-      <c r="R99">
-        <v>2.75</v>
-      </c>
-      <c r="S99">
-        <v>1.8</v>
-      </c>
-      <c r="T99">
-        <v>1.22</v>
-      </c>
-      <c r="U99">
-        <v>4</v>
-      </c>
-      <c r="V99">
-        <v>2</v>
-      </c>
-      <c r="W99">
-        <v>1.73</v>
-      </c>
-      <c r="X99">
-        <v>4.33</v>
-      </c>
-      <c r="Y99">
-        <v>1.2</v>
-      </c>
-      <c r="Z99">
-        <v>6.8</v>
-      </c>
-      <c r="AA99">
-        <v>5.1</v>
-      </c>
-      <c r="AB99">
-        <v>1.29</v>
-      </c>
-      <c r="AC99">
-        <v>1.02</v>
-      </c>
-      <c r="AD99">
-        <v>21</v>
-      </c>
-      <c r="AE99">
-        <v>1.11</v>
-      </c>
-      <c r="AF99">
-        <v>6.25</v>
-      </c>
-      <c r="AG99">
-        <v>1.38</v>
-      </c>
-      <c r="AH99">
-        <v>2.9</v>
-      </c>
-      <c r="AI99">
-        <v>1.67</v>
-      </c>
-      <c r="AJ99">
-        <v>2.1</v>
-      </c>
-      <c r="AK99">
-        <v>2.9</v>
-      </c>
-      <c r="AL99">
-        <v>1.11</v>
-      </c>
-      <c r="AM99">
-        <v>1.1</v>
-      </c>
-      <c r="AN99">
-        <v>1.2</v>
-      </c>
-      <c r="AO99">
-        <v>1.75</v>
-      </c>
-      <c r="AP99">
-        <v>1.17</v>
-      </c>
-      <c r="AQ99">
-        <v>1.6</v>
-      </c>
-      <c r="AR99">
-        <v>1.51</v>
-      </c>
-      <c r="AS99">
-        <v>1.47</v>
-      </c>
-      <c r="AT99">
-        <v>2.98</v>
-      </c>
-      <c r="AU99">
-        <v>3</v>
-      </c>
-      <c r="AV99">
-        <v>6</v>
-      </c>
-      <c r="AW99">
-        <v>6</v>
-      </c>
-      <c r="AX99">
-        <v>15</v>
-      </c>
-      <c r="AY99">
-        <v>9</v>
-      </c>
-      <c r="AZ99">
-        <v>21</v>
-      </c>
-      <c r="BA99">
-        <v>4</v>
-      </c>
-      <c r="BB99">
-        <v>7</v>
-      </c>
-      <c r="BC99">
-        <v>11</v>
-      </c>
-      <c r="BD99">
-        <v>3.65</v>
-      </c>
-      <c r="BE99">
-        <v>8</v>
-      </c>
-      <c r="BF99">
-        <v>1.3</v>
-      </c>
-      <c r="BG99">
-        <v>1.14</v>
-      </c>
-      <c r="BH99">
-        <v>4.8</v>
-      </c>
-      <c r="BI99">
-        <v>1.26</v>
-      </c>
-      <c r="BJ99">
-        <v>3.4</v>
-      </c>
-      <c r="BK99">
-        <v>1.44</v>
-      </c>
-      <c r="BL99">
-        <v>2.55</v>
-      </c>
-      <c r="BM99">
-        <v>1.7</v>
-      </c>
-      <c r="BN99">
-        <v>2.02</v>
-      </c>
-      <c r="BO99">
-        <v>2.05</v>
-      </c>
-      <c r="BP99">
-        <v>1.68</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="218">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -424,6 +424,54 @@
     <t>['52', '68']</t>
   </si>
   <si>
+    <t>['4', '14', '22', '41']</t>
+  </si>
+  <si>
+    <t>['24', '45+1', '72']</t>
+  </si>
+  <si>
+    <t>['74']</t>
+  </si>
+  <si>
+    <t>['5', '40', '47']</t>
+  </si>
+  <si>
+    <t>['23', '42']</t>
+  </si>
+  <si>
+    <t>['8', '58', '64', '86']</t>
+  </si>
+  <si>
+    <t>['21', '33', '35', '84']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['49']</t>
+  </si>
+  <si>
+    <t>['53', '59', '70', '82', '90+2']</t>
+  </si>
+  <si>
+    <t>['7', '60', '80']</t>
+  </si>
+  <si>
+    <t>['70']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['49', '71']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
@@ -454,9 +502,6 @@
     <t>['5', '64']</t>
   </si>
   <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['45+1']</t>
   </si>
   <si>
@@ -532,9 +577,6 @@
     <t>['5', '90+2', '90+4']</t>
   </si>
   <si>
-    <t>['70']</t>
-  </si>
-  <si>
     <t>['39']</t>
   </si>
   <si>
@@ -556,9 +598,6 @@
     <t>['26', '33', '88']</t>
   </si>
   <si>
-    <t>['74']</t>
-  </si>
-  <si>
     <t>['57']</t>
   </si>
   <si>
@@ -586,13 +625,49 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['90+11']</t>
+  </si>
+  <si>
+    <t>['30', '40']</t>
+  </si>
+  <si>
+    <t>['68', '90+2']</t>
+  </si>
+  <si>
+    <t>['7', '50', '67', '86']</t>
+  </si>
+  <si>
     <t>['83']</t>
   </si>
   <si>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['7', '80', '84']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['20']</t>
+  </si>
+  <si>
+    <t>['21', '26', '47']</t>
+  </si>
+  <si>
+    <t>['37', '90+4']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['34', '41', '56']</t>
+  </si>
+  <si>
+    <t>['39', '46']</t>
+  </si>
+  <si>
     <t>['4']</t>
-  </si>
-  <si>
-    <t>['9']</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP78"/>
+  <dimension ref="A1:BP100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1210,7 +1285,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1291,7 +1366,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1494,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AQ3">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1622,7 +1697,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1700,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ4">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1828,7 +1903,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1906,10 +1981,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ5">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2034,7 +2109,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2112,10 +2187,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ6">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2240,7 +2315,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2318,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ7">
         <v>2</v>
@@ -2652,7 +2727,7 @@
         <v>91</v>
       </c>
       <c r="P9" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="Q9">
         <v>6.5</v>
@@ -2730,10 +2805,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2936,10 +3011,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3142,10 +3217,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3270,7 +3345,7 @@
         <v>95</v>
       </c>
       <c r="P12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q12">
         <v>2.2</v>
@@ -3348,10 +3423,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AQ12">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3476,7 +3551,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3557,7 +3632,7 @@
         <v>1</v>
       </c>
       <c r="AQ13">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3763,7 +3838,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3888,7 +3963,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -3966,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ15">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4094,7 +4169,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4172,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="AP16">
+        <v>1.17</v>
+      </c>
+      <c r="AQ16">
         <v>0.8</v>
-      </c>
-      <c r="AQ16">
-        <v>0.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4300,7 +4375,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4378,10 +4453,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17">
-        <v>0.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4584,10 +4659,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AQ18">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR18">
         <v>0.92</v>
@@ -4712,7 +4787,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4790,10 +4865,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ19">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AR19">
         <v>2.02</v>
@@ -4918,7 +4993,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -4996,10 +5071,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AQ20">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR20">
         <v>1.82</v>
@@ -5124,7 +5199,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5205,7 +5280,7 @@
         <v>2</v>
       </c>
       <c r="AQ21">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AR21">
         <v>1.94</v>
@@ -5330,7 +5405,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5408,10 +5483,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR22">
         <v>1.7</v>
@@ -5536,7 +5611,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5617,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR23">
         <v>1.32</v>
@@ -5742,7 +5817,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5820,7 +5895,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>0</v>
@@ -5948,7 +6023,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6026,10 +6101,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AQ25">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AR25">
         <v>1.21</v>
@@ -6154,7 +6229,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6232,10 +6307,10 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AR26">
         <v>1.31</v>
@@ -6360,7 +6435,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6438,7 +6513,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27">
         <v>2</v>
@@ -6566,7 +6641,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6644,10 +6719,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -6850,10 +6925,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ29">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7056,10 +7131,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>0.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR30">
         <v>2.59</v>
@@ -7184,7 +7259,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7262,10 +7337,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AQ31">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR31">
         <v>1.79</v>
@@ -7468,10 +7543,10 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR32">
         <v>1.53</v>
@@ -7596,7 +7671,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7674,10 +7749,10 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR33">
         <v>1.87</v>
@@ -7883,7 +7958,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR34">
         <v>2.49</v>
@@ -8008,7 +8083,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8089,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>1.51</v>
@@ -8214,7 +8289,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8292,10 +8367,10 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AR36">
         <v>2</v>
@@ -8420,7 +8495,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8498,7 +8573,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -8626,7 +8701,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8704,10 +8779,10 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ38">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AR38">
         <v>1.75</v>
@@ -8910,10 +8985,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>0.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR39">
         <v>1.22</v>
@@ -9038,7 +9113,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9116,10 +9191,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ40">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR40">
         <v>2.08</v>
@@ -9322,7 +9397,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ41">
         <v>2</v>
@@ -9450,7 +9525,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9531,7 +9606,7 @@
         <v>2</v>
       </c>
       <c r="AQ42">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9656,7 +9731,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -9737,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AR43">
         <v>1.63</v>
@@ -9940,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ44">
         <v>0</v>
@@ -10146,10 +10221,10 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR45">
         <v>2.27</v>
@@ -10352,10 +10427,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AQ46">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR46">
         <v>1.95</v>
@@ -10480,7 +10555,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10558,10 +10633,10 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR47">
         <v>1.44</v>
@@ -10686,7 +10761,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10764,10 +10839,10 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ48">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -10892,7 +10967,7 @@
         <v>91</v>
       </c>
       <c r="P49" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="Q49">
         <v>3.4</v>
@@ -10970,10 +11045,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR49">
         <v>1.56</v>
@@ -11098,7 +11173,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11179,7 +11254,7 @@
         <v>3</v>
       </c>
       <c r="AQ50">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11385,7 +11460,7 @@
         <v>1</v>
       </c>
       <c r="AQ51">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11510,7 +11585,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11588,10 +11663,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ52">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AR52">
         <v>1.29</v>
@@ -11716,7 +11791,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11794,10 +11869,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ53">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>2.55</v>
@@ -11922,7 +11997,7 @@
         <v>126</v>
       </c>
       <c r="P54" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="Q54">
         <v>4.75</v>
@@ -12003,7 +12078,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12206,7 +12281,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ55">
         <v>0</v>
@@ -12334,7 +12409,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12412,10 +12487,10 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -12540,7 +12615,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12621,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="AQ57">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -12746,7 +12821,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -12824,7 +12899,7 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AQ58">
         <v>2</v>
@@ -13030,10 +13105,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AQ59">
-        <v>0.25</v>
+        <v>0.83</v>
       </c>
       <c r="AR59">
         <v>1.16</v>
@@ -13158,7 +13233,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13236,10 +13311,10 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR60">
         <v>2.1</v>
@@ -13364,7 +13439,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13442,10 +13517,10 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ61">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AR61">
         <v>1.27</v>
@@ -13648,10 +13723,10 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ62">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR62">
         <v>2.13</v>
@@ -13776,7 +13851,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13854,10 +13929,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ63">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR63">
         <v>1.3</v>
@@ -13982,7 +14057,7 @@
         <v>91</v>
       </c>
       <c r="P64" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="Q64">
         <v>2.6</v>
@@ -14063,7 +14138,7 @@
         <v>1</v>
       </c>
       <c r="AQ64">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AR64">
         <v>1.85</v>
@@ -14188,7 +14263,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14266,10 +14341,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AQ65">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AR65">
         <v>1.38</v>
@@ -14394,7 +14469,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14475,7 +14550,7 @@
         <v>3</v>
       </c>
       <c r="AQ66">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AR66">
         <v>1.95</v>
@@ -14600,7 +14675,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14678,10 +14753,10 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AQ67">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR67">
         <v>1.35</v>
@@ -14806,7 +14881,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -14884,10 +14959,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AQ68">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR68">
         <v>1.1</v>
@@ -15012,7 +15087,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15090,10 +15165,10 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="AQ69">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR69">
         <v>1.11</v>
@@ -15218,7 +15293,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15296,10 +15371,10 @@
         <v>2.25</v>
       </c>
       <c r="AP70">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AR70">
         <v>2.02</v>
@@ -15424,7 +15499,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15502,10 +15577,10 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AQ71">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR71">
         <v>1.99</v>
@@ -15630,7 +15705,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15711,7 +15786,7 @@
         <v>0</v>
       </c>
       <c r="AQ72">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -15836,7 +15911,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -15917,7 +15992,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16000,7 +16075,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>7785270</v>
+        <v>7785248</v>
       </c>
       <c r="C74" t="s">
         <v>68</v>
@@ -16009,25 +16084,25 @@
         <v>69</v>
       </c>
       <c r="E74" s="2">
-        <v>45843.375</v>
+        <v>45809.39583333334</v>
       </c>
       <c r="F74">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -16039,166 +16114,166 @@
         <v>2</v>
       </c>
       <c r="O74" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="Q74">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="T74">
+        <v>1.33</v>
+      </c>
+      <c r="U74">
+        <v>3</v>
+      </c>
+      <c r="V74">
+        <v>2.45</v>
+      </c>
+      <c r="W74">
+        <v>1.48</v>
+      </c>
+      <c r="X74">
+        <v>5.85</v>
+      </c>
+      <c r="Y74">
+        <v>1.07</v>
+      </c>
+      <c r="Z74">
+        <v>1.93</v>
+      </c>
+      <c r="AA74">
+        <v>3.45</v>
+      </c>
+      <c r="AB74">
+        <v>3.21</v>
+      </c>
+      <c r="AC74">
+        <v>1.04</v>
+      </c>
+      <c r="AD74">
+        <v>10</v>
+      </c>
+      <c r="AE74">
+        <v>1.25</v>
+      </c>
+      <c r="AF74">
+        <v>3.95</v>
+      </c>
+      <c r="AG74">
+        <v>1.72</v>
+      </c>
+      <c r="AH74">
+        <v>2</v>
+      </c>
+      <c r="AI74">
+        <v>1.6</v>
+      </c>
+      <c r="AJ74">
+        <v>2.15</v>
+      </c>
+      <c r="AK74">
         <v>1.3</v>
       </c>
-      <c r="U74">
-        <v>3.4</v>
-      </c>
-      <c r="V74">
-        <v>2.38</v>
-      </c>
-      <c r="W74">
-        <v>1.53</v>
-      </c>
-      <c r="X74">
-        <v>6</v>
-      </c>
-      <c r="Y74">
-        <v>1.13</v>
-      </c>
-      <c r="Z74">
-        <v>4.1</v>
-      </c>
-      <c r="AA74">
-        <v>3.73</v>
-      </c>
-      <c r="AB74">
-        <v>1.64</v>
-      </c>
-      <c r="AC74">
-        <v>1.03</v>
-      </c>
-      <c r="AD74">
-        <v>12</v>
-      </c>
-      <c r="AE74">
-        <v>1.21</v>
-      </c>
-      <c r="AF74">
-        <v>4.51</v>
-      </c>
-      <c r="AG74">
-        <v>1.57</v>
-      </c>
-      <c r="AH74">
-        <v>2.31</v>
-      </c>
-      <c r="AI74">
-        <v>1.62</v>
-      </c>
-      <c r="AJ74">
-        <v>2.2</v>
-      </c>
-      <c r="AK74">
-        <v>1.9</v>
-      </c>
       <c r="AL74">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM74">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AN74">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AO74">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AQ74">
         <v>2</v>
       </c>
       <c r="AR74">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="AS74">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT74">
-        <v>3.17</v>
+        <v>2.77</v>
       </c>
       <c r="AU74">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV74">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW74">
         <v>4</v>
       </c>
       <c r="AX74">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY74">
+        <v>13</v>
+      </c>
+      <c r="AZ74">
+        <v>13</v>
+      </c>
+      <c r="BA74">
+        <v>6</v>
+      </c>
+      <c r="BB74">
         <v>9</v>
       </c>
-      <c r="AZ74">
-        <v>12</v>
-      </c>
-      <c r="BA74">
-        <v>1</v>
-      </c>
-      <c r="BB74">
-        <v>8</v>
-      </c>
       <c r="BC74">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BD74">
-        <v>2.65</v>
+        <v>1.65</v>
       </c>
       <c r="BE74">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF74">
-        <v>1.56</v>
+        <v>2.45</v>
       </c>
       <c r="BG74">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="BH74">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI74">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="BJ74">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="BK74">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="BL74">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="BM74">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="BN74">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="BO74">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="BP74">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="75" spans="1:68">
@@ -16206,7 +16281,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>7785276</v>
+        <v>7785249</v>
       </c>
       <c r="C75" t="s">
         <v>68</v>
@@ -16215,196 +16290,196 @@
         <v>69</v>
       </c>
       <c r="E75" s="2">
-        <v>45843.45833333334</v>
+        <v>45809.5</v>
       </c>
       <c r="F75">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G75" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O75" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="Q75">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R75">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="S75">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="T75">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="U75">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="V75">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="W75">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="X75">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z75">
         <v>1.25</v>
       </c>
       <c r="AA75">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AB75">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC75">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AD75">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AE75">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AG75">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AH75">
-        <v>3.47</v>
+        <v>2.86</v>
       </c>
       <c r="AI75">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AJ75">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AK75">
         <v>1.06</v>
       </c>
       <c r="AL75">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AM75">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AN75">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AO75">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AQ75">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AR75">
-        <v>2.49</v>
+        <v>1.99</v>
       </c>
       <c r="AS75">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AT75">
-        <v>4.16</v>
+        <v>3.17</v>
       </c>
       <c r="AU75">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AV75">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AW75">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AX75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY75">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ75">
+        <v>8</v>
+      </c>
+      <c r="BA75">
         <v>3</v>
       </c>
-      <c r="BA75">
-        <v>16</v>
-      </c>
       <c r="BB75">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BC75">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BD75">
+        <v>1.21</v>
+      </c>
+      <c r="BE75">
+        <v>9</v>
+      </c>
+      <c r="BF75">
+        <v>4.6</v>
+      </c>
+      <c r="BG75">
+        <v>1.14</v>
+      </c>
+      <c r="BH75">
+        <v>4.8</v>
+      </c>
+      <c r="BI75">
         <v>1.26</v>
       </c>
-      <c r="BE75">
-        <v>8.5</v>
-      </c>
-      <c r="BF75">
-        <v>3.95</v>
-      </c>
-      <c r="BG75">
-        <v>1.08</v>
-      </c>
-      <c r="BH75">
-        <v>6.25</v>
-      </c>
-      <c r="BI75">
-        <v>1.16</v>
-      </c>
       <c r="BJ75">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BK75">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="BL75">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="BM75">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="BN75">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="BO75">
+        <v>2.02</v>
+      </c>
+      <c r="BP75">
         <v>1.7</v>
-      </c>
-      <c r="BP75">
-        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:68">
@@ -16412,7 +16487,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>7785277</v>
+        <v>7785250</v>
       </c>
       <c r="C76" t="s">
         <v>68</v>
@@ -16421,49 +16496,49 @@
         <v>69</v>
       </c>
       <c r="E76" s="2">
-        <v>45843.54166666666</v>
+        <v>45809.5</v>
       </c>
       <c r="F76">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G76" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H76" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76">
         <v>2</v>
       </c>
       <c r="L76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="Q76">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T76">
         <v>1.4</v>
@@ -16472,25 +16547,25 @@
         <v>2.75</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W76">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X76">
-        <v>8</v>
+        <v>6.65</v>
       </c>
       <c r="Y76">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z76">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="AA76">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="AB76">
-        <v>3.03</v>
+        <v>2.49</v>
       </c>
       <c r="AC76">
         <v>1.06</v>
@@ -16499,118 +16574,118 @@
         <v>8.5</v>
       </c>
       <c r="AE76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF76">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AG76">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH76">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AI76">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ76">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AK76">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL76">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AM76">
+        <v>1.48</v>
+      </c>
+      <c r="AN76">
+        <v>1.5</v>
+      </c>
+      <c r="AO76">
+        <v>0.75</v>
+      </c>
+      <c r="AP76">
         <v>1.67</v>
       </c>
-      <c r="AN76">
-        <v>1</v>
-      </c>
-      <c r="AO76">
-        <v>1</v>
-      </c>
-      <c r="AP76">
-        <v>1</v>
-      </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AR76">
-        <v>2.19</v>
+        <v>1.53</v>
       </c>
       <c r="AS76">
-        <v>1.17</v>
+        <v>1.68</v>
       </c>
       <c r="AT76">
-        <v>3.36</v>
+        <v>3.21</v>
       </c>
       <c r="AU76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV76">
+        <v>4</v>
+      </c>
+      <c r="AW76">
+        <v>4</v>
+      </c>
+      <c r="AX76">
         <v>9</v>
-      </c>
-      <c r="AW76">
-        <v>3</v>
-      </c>
-      <c r="AX76">
-        <v>6</v>
       </c>
       <c r="AY76">
         <v>11</v>
       </c>
       <c r="AZ76">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA76">
         <v>5</v>
       </c>
       <c r="BB76">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC76">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD76">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="BE76">
         <v>6.75</v>
       </c>
       <c r="BF76">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="BG76">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BH76">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI76">
         <v>1.38</v>
       </c>
       <c r="BJ76">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="BK76">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="BL76">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="BM76">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="BN76">
         <v>1.74</v>
       </c>
       <c r="BO76">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="BP76">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="77" spans="1:68">
@@ -16618,7 +16693,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>7785272</v>
+        <v>7785251</v>
       </c>
       <c r="C77" t="s">
         <v>68</v>
@@ -16627,13 +16702,13 @@
         <v>69</v>
       </c>
       <c r="E77" s="2">
-        <v>45843.625</v>
+        <v>45809.5</v>
       </c>
       <c r="F77">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s">
         <v>78</v>
@@ -16648,28 +16723,28 @@
         <v>1</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O77" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="Q77">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="R77">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S77">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="T77">
         <v>1.22</v>
@@ -16690,13 +16765,13 @@
         <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>6.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA77">
         <v>5.1</v>
       </c>
       <c r="AB77">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC77">
         <v>1.02</v>
@@ -16705,10 +16780,10 @@
         <v>21</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF77">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AG77">
         <v>1.38</v>
@@ -16717,106 +16792,106 @@
         <v>2.9</v>
       </c>
       <c r="AI77">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AJ77">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AK77">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AL77">
         <v>1.11</v>
       </c>
       <c r="AM77">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AN77">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AO77">
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="AQ77">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AR77">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS77">
         <v>1.47</v>
       </c>
       <c r="AT77">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="AU77">
+        <v>5</v>
+      </c>
+      <c r="AV77">
+        <v>7</v>
+      </c>
+      <c r="AW77">
+        <v>7</v>
+      </c>
+      <c r="AX77">
+        <v>6</v>
+      </c>
+      <c r="AY77">
+        <v>12</v>
+      </c>
+      <c r="AZ77">
+        <v>13</v>
+      </c>
+      <c r="BA77">
         <v>3</v>
       </c>
-      <c r="AV77">
-        <v>6</v>
-      </c>
-      <c r="AW77">
-        <v>6</v>
-      </c>
-      <c r="AX77">
-        <v>15</v>
-      </c>
-      <c r="AY77">
+      <c r="BB77">
         <v>9</v>
       </c>
-      <c r="AZ77">
-        <v>21</v>
-      </c>
-      <c r="BA77">
-        <v>4</v>
-      </c>
-      <c r="BB77">
-        <v>7</v>
-      </c>
       <c r="BC77">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD77">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="BE77">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF77">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BG77">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BH77">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="BI77">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BJ77">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="BK77">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="BL77">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="BM77">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="BN77">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="BO77">
-        <v>2.05</v>
+        <v>2.33</v>
       </c>
       <c r="BP77">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="78" spans="1:68">
@@ -16824,7 +16899,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>7785275</v>
+        <v>7785252</v>
       </c>
       <c r="C78" t="s">
         <v>68</v>
@@ -16833,16 +16908,16 @@
         <v>69</v>
       </c>
       <c r="E78" s="2">
-        <v>45843.70833333334</v>
+        <v>45809.5</v>
       </c>
       <c r="F78">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -16857,25 +16932,25 @@
         <v>1</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>91</v>
+        <v>207</v>
       </c>
       <c r="Q78">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="R78">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="T78">
         <v>1.33</v>
@@ -16884,144 +16959,4676 @@
         <v>3.25</v>
       </c>
       <c r="V78">
+        <v>2.5</v>
+      </c>
+      <c r="W78">
+        <v>1.5</v>
+      </c>
+      <c r="X78">
+        <v>6.5</v>
+      </c>
+      <c r="Y78">
+        <v>1.11</v>
+      </c>
+      <c r="Z78">
+        <v>1.33</v>
+      </c>
+      <c r="AA78">
+        <v>4.4</v>
+      </c>
+      <c r="AB78">
+        <v>7.3</v>
+      </c>
+      <c r="AC78">
+        <v>1.04</v>
+      </c>
+      <c r="AD78">
+        <v>10</v>
+      </c>
+      <c r="AE78">
+        <v>1.22</v>
+      </c>
+      <c r="AF78">
+        <v>4.2</v>
+      </c>
+      <c r="AG78">
+        <v>1.77</v>
+      </c>
+      <c r="AH78">
+        <v>1.93</v>
+      </c>
+      <c r="AI78">
+        <v>2.05</v>
+      </c>
+      <c r="AJ78">
+        <v>1.7</v>
+      </c>
+      <c r="AK78">
+        <v>1.07</v>
+      </c>
+      <c r="AL78">
+        <v>1.13</v>
+      </c>
+      <c r="AM78">
+        <v>3</v>
+      </c>
+      <c r="AN78">
+        <v>2.2</v>
+      </c>
+      <c r="AO78">
+        <v>0.25</v>
+      </c>
+      <c r="AP78">
+        <v>1.86</v>
+      </c>
+      <c r="AQ78">
+        <v>0.83</v>
+      </c>
+      <c r="AR78">
+        <v>2.33</v>
+      </c>
+      <c r="AS78">
+        <v>0.97</v>
+      </c>
+      <c r="AT78">
+        <v>3.3</v>
+      </c>
+      <c r="AU78">
+        <v>2</v>
+      </c>
+      <c r="AV78">
+        <v>9</v>
+      </c>
+      <c r="AW78">
+        <v>2</v>
+      </c>
+      <c r="AX78">
+        <v>4</v>
+      </c>
+      <c r="AY78">
+        <v>4</v>
+      </c>
+      <c r="AZ78">
+        <v>13</v>
+      </c>
+      <c r="BA78">
+        <v>6</v>
+      </c>
+      <c r="BB78">
+        <v>4</v>
+      </c>
+      <c r="BC78">
+        <v>10</v>
+      </c>
+      <c r="BD78">
+        <v>1.27</v>
+      </c>
+      <c r="BE78">
+        <v>7.5</v>
+      </c>
+      <c r="BF78">
+        <v>4.1</v>
+      </c>
+      <c r="BG78">
+        <v>1.4</v>
+      </c>
+      <c r="BH78">
+        <v>2.65</v>
+      </c>
+      <c r="BI78">
+        <v>1.68</v>
+      </c>
+      <c r="BJ78">
+        <v>2.05</v>
+      </c>
+      <c r="BK78">
+        <v>2.07</v>
+      </c>
+      <c r="BL78">
+        <v>1.67</v>
+      </c>
+      <c r="BM78">
+        <v>2.65</v>
+      </c>
+      <c r="BN78">
+        <v>1.42</v>
+      </c>
+      <c r="BO78">
+        <v>3.55</v>
+      </c>
+      <c r="BP78">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:68">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>7785253</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45809.59375</v>
+      </c>
+      <c r="F79">
+        <v>9</v>
+      </c>
+      <c r="G79" t="s">
+        <v>75</v>
+      </c>
+      <c r="H79" t="s">
+        <v>85</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="s">
+        <v>91</v>
+      </c>
+      <c r="P79" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q79">
+        <v>2.62</v>
+      </c>
+      <c r="R79">
+        <v>2.3</v>
+      </c>
+      <c r="S79">
+        <v>3.25</v>
+      </c>
+      <c r="T79">
+        <v>1.25</v>
+      </c>
+      <c r="U79">
+        <v>3.55</v>
+      </c>
+      <c r="V79">
+        <v>2.15</v>
+      </c>
+      <c r="W79">
+        <v>1.62</v>
+      </c>
+      <c r="X79">
+        <v>4.5</v>
+      </c>
+      <c r="Y79">
+        <v>1.13</v>
+      </c>
+      <c r="Z79">
+        <v>1.97</v>
+      </c>
+      <c r="AA79">
+        <v>3.7</v>
+      </c>
+      <c r="AB79">
+        <v>2.92</v>
+      </c>
+      <c r="AC79">
+        <v>1.01</v>
+      </c>
+      <c r="AD79">
+        <v>13</v>
+      </c>
+      <c r="AE79">
+        <v>1.17</v>
+      </c>
+      <c r="AF79">
+        <v>5</v>
+      </c>
+      <c r="AG79">
+        <v>1.44</v>
+      </c>
+      <c r="AH79">
+        <v>2.67</v>
+      </c>
+      <c r="AI79">
+        <v>1.42</v>
+      </c>
+      <c r="AJ79">
+        <v>2.6</v>
+      </c>
+      <c r="AK79">
+        <v>1.38</v>
+      </c>
+      <c r="AL79">
+        <v>1.22</v>
+      </c>
+      <c r="AM79">
+        <v>1.67</v>
+      </c>
+      <c r="AN79">
+        <v>1</v>
+      </c>
+      <c r="AO79">
+        <v>2.4</v>
+      </c>
+      <c r="AP79">
+        <v>0.67</v>
+      </c>
+      <c r="AQ79">
+        <v>2.29</v>
+      </c>
+      <c r="AR79">
+        <v>1.62</v>
+      </c>
+      <c r="AS79">
+        <v>1.86</v>
+      </c>
+      <c r="AT79">
+        <v>3.48</v>
+      </c>
+      <c r="AU79">
+        <v>0</v>
+      </c>
+      <c r="AV79">
+        <v>4</v>
+      </c>
+      <c r="AW79">
+        <v>6</v>
+      </c>
+      <c r="AX79">
+        <v>6</v>
+      </c>
+      <c r="AY79">
+        <v>6</v>
+      </c>
+      <c r="AZ79">
+        <v>10</v>
+      </c>
+      <c r="BA79">
+        <v>7</v>
+      </c>
+      <c r="BB79">
+        <v>4</v>
+      </c>
+      <c r="BC79">
+        <v>11</v>
+      </c>
+      <c r="BD79">
+        <v>1.67</v>
+      </c>
+      <c r="BE79">
+        <v>6.5</v>
+      </c>
+      <c r="BF79">
+        <v>2.45</v>
+      </c>
+      <c r="BG79">
+        <v>1.24</v>
+      </c>
+      <c r="BH79">
+        <v>3.55</v>
+      </c>
+      <c r="BI79">
+        <v>1.42</v>
+      </c>
+      <c r="BJ79">
+        <v>2.65</v>
+      </c>
+      <c r="BK79">
+        <v>1.68</v>
+      </c>
+      <c r="BL79">
+        <v>2.05</v>
+      </c>
+      <c r="BM79">
+        <v>2.07</v>
+      </c>
+      <c r="BN79">
+        <v>1.67</v>
+      </c>
+      <c r="BO79">
+        <v>2.55</v>
+      </c>
+      <c r="BP79">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:68">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>7785254</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45829.54166666666</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>3</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>3</v>
+      </c>
+      <c r="O80" t="s">
+        <v>139</v>
+      </c>
+      <c r="P80" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q80">
+        <v>1.95</v>
+      </c>
+      <c r="R80">
         <v>2.63</v>
       </c>
-      <c r="W78">
+      <c r="S80">
+        <v>5</v>
+      </c>
+      <c r="T80">
+        <v>1.22</v>
+      </c>
+      <c r="U80">
+        <v>4</v>
+      </c>
+      <c r="V80">
+        <v>2</v>
+      </c>
+      <c r="W80">
+        <v>1.73</v>
+      </c>
+      <c r="X80">
+        <v>4.33</v>
+      </c>
+      <c r="Y80">
+        <v>1.2</v>
+      </c>
+      <c r="Z80">
         <v>1.44</v>
       </c>
-      <c r="X78">
+      <c r="AA80">
+        <v>4.6</v>
+      </c>
+      <c r="AB80">
+        <v>4.8</v>
+      </c>
+      <c r="AC80">
+        <v>1.02</v>
+      </c>
+      <c r="AD80">
+        <v>21</v>
+      </c>
+      <c r="AE80">
+        <v>1.12</v>
+      </c>
+      <c r="AF80">
+        <v>5.75</v>
+      </c>
+      <c r="AG80">
+        <v>1.42</v>
+      </c>
+      <c r="AH80">
+        <v>2.74</v>
+      </c>
+      <c r="AI80">
+        <v>1.53</v>
+      </c>
+      <c r="AJ80">
+        <v>2.38</v>
+      </c>
+      <c r="AK80">
+        <v>1.15</v>
+      </c>
+      <c r="AL80">
+        <v>1.18</v>
+      </c>
+      <c r="AM80">
+        <v>2.5</v>
+      </c>
+      <c r="AN80">
+        <v>2.25</v>
+      </c>
+      <c r="AO80">
+        <v>2.25</v>
+      </c>
+      <c r="AP80">
+        <v>2</v>
+      </c>
+      <c r="AQ80">
+        <v>1.67</v>
+      </c>
+      <c r="AR80">
+        <v>2.02</v>
+      </c>
+      <c r="AS80">
+        <v>1.79</v>
+      </c>
+      <c r="AT80">
+        <v>3.81</v>
+      </c>
+      <c r="AU80">
+        <v>5</v>
+      </c>
+      <c r="AV80">
+        <v>0</v>
+      </c>
+      <c r="AW80">
+        <v>0</v>
+      </c>
+      <c r="AX80">
+        <v>0</v>
+      </c>
+      <c r="AY80">
+        <v>5</v>
+      </c>
+      <c r="AZ80">
+        <v>0</v>
+      </c>
+      <c r="BA80">
+        <v>9</v>
+      </c>
+      <c r="BB80">
+        <v>2</v>
+      </c>
+      <c r="BC80">
+        <v>11</v>
+      </c>
+      <c r="BD80">
+        <v>1.44</v>
+      </c>
+      <c r="BE80">
         <v>7</v>
       </c>
-      <c r="Y78">
+      <c r="BF80">
+        <v>3.05</v>
+      </c>
+      <c r="BG80">
+        <v>1.17</v>
+      </c>
+      <c r="BH80">
+        <v>4.3</v>
+      </c>
+      <c r="BI80">
+        <v>1.3</v>
+      </c>
+      <c r="BJ80">
+        <v>3.05</v>
+      </c>
+      <c r="BK80">
+        <v>1.5</v>
+      </c>
+      <c r="BL80">
+        <v>2.35</v>
+      </c>
+      <c r="BM80">
+        <v>1.82</v>
+      </c>
+      <c r="BN80">
+        <v>1.86</v>
+      </c>
+      <c r="BO80">
+        <v>2.23</v>
+      </c>
+      <c r="BP80">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:68">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>7785261</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45830.39583333334</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81" t="s">
+        <v>72</v>
+      </c>
+      <c r="H81" t="s">
+        <v>75</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>3</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>3</v>
+      </c>
+      <c r="N81">
+        <v>5</v>
+      </c>
+      <c r="O81" t="s">
+        <v>140</v>
+      </c>
+      <c r="P81" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q81">
+        <v>3</v>
+      </c>
+      <c r="R81">
+        <v>2.3</v>
+      </c>
+      <c r="S81">
+        <v>3.25</v>
+      </c>
+      <c r="T81">
+        <v>1.33</v>
+      </c>
+      <c r="U81">
+        <v>3.25</v>
+      </c>
+      <c r="V81">
+        <v>2.5</v>
+      </c>
+      <c r="W81">
+        <v>1.5</v>
+      </c>
+      <c r="X81">
+        <v>6</v>
+      </c>
+      <c r="Y81">
+        <v>1.13</v>
+      </c>
+      <c r="Z81">
+        <v>2.37</v>
+      </c>
+      <c r="AA81">
+        <v>3.29</v>
+      </c>
+      <c r="AB81">
+        <v>2.54</v>
+      </c>
+      <c r="AC81">
+        <v>1.04</v>
+      </c>
+      <c r="AD81">
+        <v>10</v>
+      </c>
+      <c r="AE81">
+        <v>1.22</v>
+      </c>
+      <c r="AF81">
+        <v>4</v>
+      </c>
+      <c r="AG81">
+        <v>1.59</v>
+      </c>
+      <c r="AH81">
+        <v>2.2</v>
+      </c>
+      <c r="AI81">
+        <v>1.62</v>
+      </c>
+      <c r="AJ81">
+        <v>2.2</v>
+      </c>
+      <c r="AK81">
+        <v>1.44</v>
+      </c>
+      <c r="AL81">
+        <v>1.28</v>
+      </c>
+      <c r="AM81">
+        <v>1.53</v>
+      </c>
+      <c r="AN81">
+        <v>1</v>
+      </c>
+      <c r="AO81">
+        <v>1.4</v>
+      </c>
+      <c r="AP81">
+        <v>0.83</v>
+      </c>
+      <c r="AQ81">
+        <v>1.43</v>
+      </c>
+      <c r="AR81">
+        <v>2.19</v>
+      </c>
+      <c r="AS81">
+        <v>1.51</v>
+      </c>
+      <c r="AT81">
+        <v>3.7</v>
+      </c>
+      <c r="AU81">
+        <v>8</v>
+      </c>
+      <c r="AV81">
+        <v>7</v>
+      </c>
+      <c r="AW81">
+        <v>7</v>
+      </c>
+      <c r="AX81">
+        <v>11</v>
+      </c>
+      <c r="AY81">
+        <v>15</v>
+      </c>
+      <c r="AZ81">
+        <v>18</v>
+      </c>
+      <c r="BA81">
+        <v>5</v>
+      </c>
+      <c r="BB81">
+        <v>7</v>
+      </c>
+      <c r="BC81">
+        <v>12</v>
+      </c>
+      <c r="BD81">
+        <v>1.96</v>
+      </c>
+      <c r="BE81">
+        <v>6.75</v>
+      </c>
+      <c r="BF81">
+        <v>1.98</v>
+      </c>
+      <c r="BG81">
+        <v>1.22</v>
+      </c>
+      <c r="BH81">
+        <v>3.8</v>
+      </c>
+      <c r="BI81">
+        <v>1.38</v>
+      </c>
+      <c r="BJ81">
+        <v>2.7</v>
+      </c>
+      <c r="BK81">
+        <v>1.65</v>
+      </c>
+      <c r="BL81">
+        <v>2.1</v>
+      </c>
+      <c r="BM81">
+        <v>1.98</v>
+      </c>
+      <c r="BN81">
+        <v>1.72</v>
+      </c>
+      <c r="BO81">
+        <v>2.48</v>
+      </c>
+      <c r="BP81">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:68">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>7785258</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F82">
+        <v>10</v>
+      </c>
+      <c r="G82" t="s">
+        <v>82</v>
+      </c>
+      <c r="H82" t="s">
+        <v>83</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>4</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>4</v>
+      </c>
+      <c r="O82" t="s">
+        <v>141</v>
+      </c>
+      <c r="P82" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q82">
+        <v>1.8</v>
+      </c>
+      <c r="R82">
+        <v>2.63</v>
+      </c>
+      <c r="S82">
+        <v>7</v>
+      </c>
+      <c r="T82">
+        <v>1.25</v>
+      </c>
+      <c r="U82">
+        <v>3.75</v>
+      </c>
+      <c r="V82">
+        <v>2.25</v>
+      </c>
+      <c r="W82">
+        <v>1.57</v>
+      </c>
+      <c r="X82">
+        <v>5.5</v>
+      </c>
+      <c r="Y82">
+        <v>1.14</v>
+      </c>
+      <c r="Z82">
+        <v>1.34</v>
+      </c>
+      <c r="AA82">
+        <v>4.5</v>
+      </c>
+      <c r="AB82">
+        <v>6.5</v>
+      </c>
+      <c r="AC82">
+        <v>1.01</v>
+      </c>
+      <c r="AD82">
+        <v>17</v>
+      </c>
+      <c r="AE82">
+        <v>1.17</v>
+      </c>
+      <c r="AF82">
+        <v>5</v>
+      </c>
+      <c r="AG82">
+        <v>1.5</v>
+      </c>
+      <c r="AH82">
+        <v>2.48</v>
+      </c>
+      <c r="AI82">
+        <v>1.8</v>
+      </c>
+      <c r="AJ82">
+        <v>1.95</v>
+      </c>
+      <c r="AK82">
         <v>1.1</v>
       </c>
-      <c r="Z78">
+      <c r="AL82">
+        <v>1.16</v>
+      </c>
+      <c r="AM82">
+        <v>2.9</v>
+      </c>
+      <c r="AN82">
+        <v>3</v>
+      </c>
+      <c r="AO82">
+        <v>0</v>
+      </c>
+      <c r="AP82">
+        <v>3</v>
+      </c>
+      <c r="AQ82">
+        <v>0</v>
+      </c>
+      <c r="AR82">
+        <v>2.07</v>
+      </c>
+      <c r="AS82">
+        <v>0.95</v>
+      </c>
+      <c r="AT82">
+        <v>3.02</v>
+      </c>
+      <c r="AU82">
+        <v>11</v>
+      </c>
+      <c r="AV82">
+        <v>8</v>
+      </c>
+      <c r="AW82">
+        <v>2</v>
+      </c>
+      <c r="AX82">
+        <v>11</v>
+      </c>
+      <c r="AY82">
+        <v>13</v>
+      </c>
+      <c r="AZ82">
+        <v>19</v>
+      </c>
+      <c r="BA82">
+        <v>3</v>
+      </c>
+      <c r="BB82">
+        <v>8</v>
+      </c>
+      <c r="BC82">
+        <v>11</v>
+      </c>
+      <c r="BD82">
+        <v>1.29</v>
+      </c>
+      <c r="BE82">
+        <v>8</v>
+      </c>
+      <c r="BF82">
+        <v>3.9</v>
+      </c>
+      <c r="BG82">
+        <v>1.2</v>
+      </c>
+      <c r="BH82">
+        <v>4</v>
+      </c>
+      <c r="BI82">
+        <v>1.34</v>
+      </c>
+      <c r="BJ82">
+        <v>2.9</v>
+      </c>
+      <c r="BK82">
+        <v>1.57</v>
+      </c>
+      <c r="BL82">
+        <v>2.23</v>
+      </c>
+      <c r="BM82">
+        <v>1.9</v>
+      </c>
+      <c r="BN82">
+        <v>1.79</v>
+      </c>
+      <c r="BO82">
+        <v>2.32</v>
+      </c>
+      <c r="BP82">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="83" spans="1:68">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>7785257</v>
+      </c>
+      <c r="C83" t="s">
+        <v>68</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83" t="s">
+        <v>84</v>
+      </c>
+      <c r="H83" t="s">
+        <v>79</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="K83">
+        <v>4</v>
+      </c>
+      <c r="L83">
+        <v>4</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>5</v>
+      </c>
+      <c r="O83" t="s">
+        <v>142</v>
+      </c>
+      <c r="P83" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q83">
+        <v>4.75</v>
+      </c>
+      <c r="R83">
+        <v>2.4</v>
+      </c>
+      <c r="S83">
+        <v>2.2</v>
+      </c>
+      <c r="T83">
+        <v>1.3</v>
+      </c>
+      <c r="U83">
+        <v>3.4</v>
+      </c>
+      <c r="V83">
+        <v>2.38</v>
+      </c>
+      <c r="W83">
+        <v>1.53</v>
+      </c>
+      <c r="X83">
+        <v>6</v>
+      </c>
+      <c r="Y83">
+        <v>1.13</v>
+      </c>
+      <c r="Z83">
+        <v>4.2</v>
+      </c>
+      <c r="AA83">
+        <v>3.78</v>
+      </c>
+      <c r="AB83">
+        <v>1.62</v>
+      </c>
+      <c r="AC83">
+        <v>1.04</v>
+      </c>
+      <c r="AD83">
+        <v>10</v>
+      </c>
+      <c r="AE83">
+        <v>1.2</v>
+      </c>
+      <c r="AF83">
+        <v>4.33</v>
+      </c>
+      <c r="AG83">
+        <v>1.56</v>
+      </c>
+      <c r="AH83">
+        <v>2.27</v>
+      </c>
+      <c r="AI83">
+        <v>1.67</v>
+      </c>
+      <c r="AJ83">
+        <v>2.1</v>
+      </c>
+      <c r="AK83">
+        <v>2.05</v>
+      </c>
+      <c r="AL83">
+        <v>1.23</v>
+      </c>
+      <c r="AM83">
+        <v>1.21</v>
+      </c>
+      <c r="AN83">
+        <v>0.75</v>
+      </c>
+      <c r="AO83">
+        <v>2</v>
+      </c>
+      <c r="AP83">
+        <v>1.17</v>
+      </c>
+      <c r="AQ83">
+        <v>1.67</v>
+      </c>
+      <c r="AR83">
+        <v>1.44</v>
+      </c>
+      <c r="AS83">
+        <v>1.21</v>
+      </c>
+      <c r="AT83">
+        <v>2.65</v>
+      </c>
+      <c r="AU83">
+        <v>9</v>
+      </c>
+      <c r="AV83">
+        <v>6</v>
+      </c>
+      <c r="AW83">
+        <v>4</v>
+      </c>
+      <c r="AX83">
+        <v>7</v>
+      </c>
+      <c r="AY83">
+        <v>13</v>
+      </c>
+      <c r="AZ83">
+        <v>13</v>
+      </c>
+      <c r="BA83">
+        <v>3</v>
+      </c>
+      <c r="BB83">
+        <v>9</v>
+      </c>
+      <c r="BC83">
+        <v>12</v>
+      </c>
+      <c r="BD83">
+        <v>3.15</v>
+      </c>
+      <c r="BE83">
+        <v>7</v>
+      </c>
+      <c r="BF83">
+        <v>1.42</v>
+      </c>
+      <c r="BG83">
+        <v>1.22</v>
+      </c>
+      <c r="BH83">
+        <v>3.8</v>
+      </c>
+      <c r="BI83">
+        <v>1.38</v>
+      </c>
+      <c r="BJ83">
+        <v>2.8</v>
+      </c>
+      <c r="BK83">
+        <v>1.61</v>
+      </c>
+      <c r="BL83">
+        <v>2.15</v>
+      </c>
+      <c r="BM83">
+        <v>1.97</v>
+      </c>
+      <c r="BN83">
+        <v>1.74</v>
+      </c>
+      <c r="BO83">
+        <v>2.43</v>
+      </c>
+      <c r="BP83">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:68">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>7785259</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84" t="s">
+        <v>81</v>
+      </c>
+      <c r="H84" t="s">
+        <v>77</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="K84">
+        <v>2</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>2</v>
+      </c>
+      <c r="O84" t="s">
+        <v>143</v>
+      </c>
+      <c r="P84" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q84">
+        <v>2.1</v>
+      </c>
+      <c r="R84">
+        <v>2.4</v>
+      </c>
+      <c r="S84">
+        <v>5</v>
+      </c>
+      <c r="T84">
+        <v>1.29</v>
+      </c>
+      <c r="U84">
+        <v>3.5</v>
+      </c>
+      <c r="V84">
+        <v>2.38</v>
+      </c>
+      <c r="W84">
+        <v>1.53</v>
+      </c>
+      <c r="X84">
+        <v>5.5</v>
+      </c>
+      <c r="Y84">
+        <v>1.14</v>
+      </c>
+      <c r="Z84">
+        <v>1.56</v>
+      </c>
+      <c r="AA84">
+        <v>3.9</v>
+      </c>
+      <c r="AB84">
+        <v>4.5</v>
+      </c>
+      <c r="AC84">
+        <v>1.03</v>
+      </c>
+      <c r="AD84">
+        <v>11</v>
+      </c>
+      <c r="AE84">
+        <v>1.2</v>
+      </c>
+      <c r="AF84">
+        <v>4.33</v>
+      </c>
+      <c r="AG84">
+        <v>1.58</v>
+      </c>
+      <c r="AH84">
+        <v>2.22</v>
+      </c>
+      <c r="AI84">
+        <v>1.67</v>
+      </c>
+      <c r="AJ84">
+        <v>2.1</v>
+      </c>
+      <c r="AK84">
+        <v>1.18</v>
+      </c>
+      <c r="AL84">
+        <v>1.22</v>
+      </c>
+      <c r="AM84">
         <v>2.25</v>
       </c>
-      <c r="AA78">
+      <c r="AN84">
+        <v>1</v>
+      </c>
+      <c r="AO84">
+        <v>0.75</v>
+      </c>
+      <c r="AP84">
+        <v>1</v>
+      </c>
+      <c r="AQ84">
+        <v>0.8</v>
+      </c>
+      <c r="AR84">
+        <v>1.74</v>
+      </c>
+      <c r="AS84">
+        <v>1.09</v>
+      </c>
+      <c r="AT84">
+        <v>2.83</v>
+      </c>
+      <c r="AU84">
+        <v>5</v>
+      </c>
+      <c r="AV84">
+        <v>3</v>
+      </c>
+      <c r="AW84">
+        <v>3</v>
+      </c>
+      <c r="AX84">
+        <v>7</v>
+      </c>
+      <c r="AY84">
+        <v>8</v>
+      </c>
+      <c r="AZ84">
+        <v>10</v>
+      </c>
+      <c r="BA84">
+        <v>3</v>
+      </c>
+      <c r="BB84">
+        <v>2</v>
+      </c>
+      <c r="BC84">
+        <v>5</v>
+      </c>
+      <c r="BD84">
+        <v>1.49</v>
+      </c>
+      <c r="BE84">
+        <v>7</v>
+      </c>
+      <c r="BF84">
+        <v>2.9</v>
+      </c>
+      <c r="BG84">
+        <v>1.22</v>
+      </c>
+      <c r="BH84">
+        <v>3.7</v>
+      </c>
+      <c r="BI84">
+        <v>1.38</v>
+      </c>
+      <c r="BJ84">
+        <v>2.7</v>
+      </c>
+      <c r="BK84">
+        <v>1.64</v>
+      </c>
+      <c r="BL84">
+        <v>2.1</v>
+      </c>
+      <c r="BM84">
+        <v>2</v>
+      </c>
+      <c r="BN84">
+        <v>1.71</v>
+      </c>
+      <c r="BO84">
+        <v>2.5</v>
+      </c>
+      <c r="BP84">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:68">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7785255</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F85">
+        <v>10</v>
+      </c>
+      <c r="G85" t="s">
+        <v>73</v>
+      </c>
+      <c r="H85" t="s">
+        <v>76</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>3</v>
+      </c>
+      <c r="N85">
+        <v>4</v>
+      </c>
+      <c r="O85" t="s">
+        <v>144</v>
+      </c>
+      <c r="P85" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q85">
+        <v>3.75</v>
+      </c>
+      <c r="R85">
+        <v>2.25</v>
+      </c>
+      <c r="S85">
+        <v>2.75</v>
+      </c>
+      <c r="T85">
+        <v>1.36</v>
+      </c>
+      <c r="U85">
+        <v>3</v>
+      </c>
+      <c r="V85">
+        <v>2.63</v>
+      </c>
+      <c r="W85">
+        <v>1.44</v>
+      </c>
+      <c r="X85">
+        <v>7</v>
+      </c>
+      <c r="Y85">
+        <v>1.1</v>
+      </c>
+      <c r="Z85">
+        <v>3.16</v>
+      </c>
+      <c r="AA85">
         <v>3.25</v>
       </c>
-      <c r="AB78">
+      <c r="AB85">
+        <v>2.02</v>
+      </c>
+      <c r="AC85">
+        <v>1.05</v>
+      </c>
+      <c r="AD85">
+        <v>9.5</v>
+      </c>
+      <c r="AE85">
+        <v>1.28</v>
+      </c>
+      <c r="AF85">
+        <v>3.65</v>
+      </c>
+      <c r="AG85">
+        <v>1.79</v>
+      </c>
+      <c r="AH85">
+        <v>1.91</v>
+      </c>
+      <c r="AI85">
+        <v>1.7</v>
+      </c>
+      <c r="AJ85">
+        <v>2.05</v>
+      </c>
+      <c r="AK85">
+        <v>1.71</v>
+      </c>
+      <c r="AL85">
+        <v>1.28</v>
+      </c>
+      <c r="AM85">
+        <v>1.32</v>
+      </c>
+      <c r="AN85">
+        <v>1.75</v>
+      </c>
+      <c r="AO85">
+        <v>1.75</v>
+      </c>
+      <c r="AP85">
+        <v>1.33</v>
+      </c>
+      <c r="AQ85">
+        <v>2.17</v>
+      </c>
+      <c r="AR85">
+        <v>1.38</v>
+      </c>
+      <c r="AS85">
+        <v>1.15</v>
+      </c>
+      <c r="AT85">
+        <v>2.53</v>
+      </c>
+      <c r="AU85">
+        <v>5</v>
+      </c>
+      <c r="AV85">
+        <v>5</v>
+      </c>
+      <c r="AW85">
+        <v>6</v>
+      </c>
+      <c r="AX85">
+        <v>0</v>
+      </c>
+      <c r="AY85">
+        <v>11</v>
+      </c>
+      <c r="AZ85">
+        <v>5</v>
+      </c>
+      <c r="BA85">
+        <v>6</v>
+      </c>
+      <c r="BB85">
+        <v>2</v>
+      </c>
+      <c r="BC85">
+        <v>8</v>
+      </c>
+      <c r="BD85">
+        <v>2.4</v>
+      </c>
+      <c r="BE85">
+        <v>6.75</v>
+      </c>
+      <c r="BF85">
+        <v>1.68</v>
+      </c>
+      <c r="BG85">
+        <v>1.23</v>
+      </c>
+      <c r="BH85">
+        <v>3.65</v>
+      </c>
+      <c r="BI85">
+        <v>1.41</v>
+      </c>
+      <c r="BJ85">
+        <v>2.65</v>
+      </c>
+      <c r="BK85">
+        <v>1.67</v>
+      </c>
+      <c r="BL85">
+        <v>2.07</v>
+      </c>
+      <c r="BM85">
+        <v>2.02</v>
+      </c>
+      <c r="BN85">
+        <v>1.7</v>
+      </c>
+      <c r="BO85">
+        <v>2.55</v>
+      </c>
+      <c r="BP85">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:68">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>7785256</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="2">
+        <v>45830.5</v>
+      </c>
+      <c r="F86">
+        <v>10</v>
+      </c>
+      <c r="G86" t="s">
+        <v>74</v>
+      </c>
+      <c r="H86" t="s">
+        <v>70</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>5</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>5</v>
+      </c>
+      <c r="O86" t="s">
+        <v>145</v>
+      </c>
+      <c r="P86" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q86">
+        <v>2.75</v>
+      </c>
+      <c r="R86">
+        <v>2.2</v>
+      </c>
+      <c r="S86">
+        <v>3.75</v>
+      </c>
+      <c r="T86">
+        <v>1.36</v>
+      </c>
+      <c r="U86">
+        <v>3</v>
+      </c>
+      <c r="V86">
+        <v>2.63</v>
+      </c>
+      <c r="W86">
+        <v>1.44</v>
+      </c>
+      <c r="X86">
+        <v>7</v>
+      </c>
+      <c r="Y86">
+        <v>1.1</v>
+      </c>
+      <c r="Z86">
+        <v>2.08</v>
+      </c>
+      <c r="AA86">
+        <v>3.39</v>
+      </c>
+      <c r="AB86">
+        <v>2.9</v>
+      </c>
+      <c r="AC86">
+        <v>1.05</v>
+      </c>
+      <c r="AD86">
+        <v>9.5</v>
+      </c>
+      <c r="AE86">
+        <v>1.28</v>
+      </c>
+      <c r="AF86">
+        <v>3.55</v>
+      </c>
+      <c r="AG86">
+        <v>1.86</v>
+      </c>
+      <c r="AH86">
+        <v>1.84</v>
+      </c>
+      <c r="AI86">
+        <v>1.7</v>
+      </c>
+      <c r="AJ86">
+        <v>2.05</v>
+      </c>
+      <c r="AK86">
+        <v>1.35</v>
+      </c>
+      <c r="AL86">
+        <v>1.29</v>
+      </c>
+      <c r="AM86">
+        <v>1.65</v>
+      </c>
+      <c r="AN86">
+        <v>0.75</v>
+      </c>
+      <c r="AO86">
+        <v>1.5</v>
+      </c>
+      <c r="AP86">
+        <v>1.2</v>
+      </c>
+      <c r="AQ86">
+        <v>1</v>
+      </c>
+      <c r="AR86">
+        <v>1.15</v>
+      </c>
+      <c r="AS86">
+        <v>1.67</v>
+      </c>
+      <c r="AT86">
+        <v>2.82</v>
+      </c>
+      <c r="AU86">
+        <v>6</v>
+      </c>
+      <c r="AV86">
+        <v>2</v>
+      </c>
+      <c r="AW86">
+        <v>8</v>
+      </c>
+      <c r="AX86">
+        <v>8</v>
+      </c>
+      <c r="AY86">
+        <v>14</v>
+      </c>
+      <c r="AZ86">
+        <v>10</v>
+      </c>
+      <c r="BA86">
+        <v>6</v>
+      </c>
+      <c r="BB86">
+        <v>2</v>
+      </c>
+      <c r="BC86">
+        <v>8</v>
+      </c>
+      <c r="BD86">
+        <v>1.7</v>
+      </c>
+      <c r="BE86">
+        <v>6.75</v>
+      </c>
+      <c r="BF86">
+        <v>2.4</v>
+      </c>
+      <c r="BG86">
+        <v>1.24</v>
+      </c>
+      <c r="BH86">
+        <v>3.55</v>
+      </c>
+      <c r="BI86">
+        <v>1.43</v>
+      </c>
+      <c r="BJ86">
+        <v>2.6</v>
+      </c>
+      <c r="BK86">
+        <v>1.7</v>
+      </c>
+      <c r="BL86">
+        <v>2.02</v>
+      </c>
+      <c r="BM86">
+        <v>2.08</v>
+      </c>
+      <c r="BN86">
+        <v>1.65</v>
+      </c>
+      <c r="BO86">
+        <v>2.65</v>
+      </c>
+      <c r="BP86">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:68">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>7785260</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="2">
+        <v>45830.59375</v>
+      </c>
+      <c r="F87">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>85</v>
+      </c>
+      <c r="H87" t="s">
+        <v>71</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>3</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" t="s">
+        <v>146</v>
+      </c>
+      <c r="P87" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q87">
+        <v>2.1</v>
+      </c>
+      <c r="R87">
+        <v>2.5</v>
+      </c>
+      <c r="S87">
+        <v>5</v>
+      </c>
+      <c r="T87">
+        <v>1.29</v>
+      </c>
+      <c r="U87">
+        <v>3.5</v>
+      </c>
+      <c r="V87">
+        <v>2.25</v>
+      </c>
+      <c r="W87">
+        <v>1.57</v>
+      </c>
+      <c r="X87">
+        <v>5.5</v>
+      </c>
+      <c r="Y87">
+        <v>1.14</v>
+      </c>
+      <c r="Z87">
+        <v>1.52</v>
+      </c>
+      <c r="AA87">
+        <v>3.95</v>
+      </c>
+      <c r="AB87">
+        <v>4.8</v>
+      </c>
+      <c r="AC87">
+        <v>1.03</v>
+      </c>
+      <c r="AD87">
+        <v>11</v>
+      </c>
+      <c r="AE87">
+        <v>1.2</v>
+      </c>
+      <c r="AF87">
+        <v>4.5</v>
+      </c>
+      <c r="AG87">
+        <v>1.55</v>
+      </c>
+      <c r="AH87">
+        <v>2.29</v>
+      </c>
+      <c r="AI87">
+        <v>1.67</v>
+      </c>
+      <c r="AJ87">
+        <v>2.1</v>
+      </c>
+      <c r="AK87">
+        <v>1.18</v>
+      </c>
+      <c r="AL87">
+        <v>1.21</v>
+      </c>
+      <c r="AM87">
+        <v>2.25</v>
+      </c>
+      <c r="AN87">
+        <v>2.33</v>
+      </c>
+      <c r="AO87">
+        <v>1</v>
+      </c>
+      <c r="AP87">
+        <v>2.5</v>
+      </c>
+      <c r="AQ87">
+        <v>0.83</v>
+      </c>
+      <c r="AR87">
+        <v>2.49</v>
+      </c>
+      <c r="AS87">
+        <v>1.17</v>
+      </c>
+      <c r="AT87">
+        <v>3.66</v>
+      </c>
+      <c r="AU87">
+        <v>5</v>
+      </c>
+      <c r="AV87">
+        <v>2</v>
+      </c>
+      <c r="AW87">
+        <v>9</v>
+      </c>
+      <c r="AX87">
+        <v>9</v>
+      </c>
+      <c r="AY87">
+        <v>14</v>
+      </c>
+      <c r="AZ87">
+        <v>11</v>
+      </c>
+      <c r="BA87">
+        <v>6</v>
+      </c>
+      <c r="BB87">
+        <v>6</v>
+      </c>
+      <c r="BC87">
+        <v>12</v>
+      </c>
+      <c r="BD87">
+        <v>1.46</v>
+      </c>
+      <c r="BE87">
+        <v>7</v>
+      </c>
+      <c r="BF87">
+        <v>3</v>
+      </c>
+      <c r="BG87">
+        <v>1.18</v>
+      </c>
+      <c r="BH87">
+        <v>4.1</v>
+      </c>
+      <c r="BI87">
+        <v>1.32</v>
+      </c>
+      <c r="BJ87">
+        <v>3.05</v>
+      </c>
+      <c r="BK87">
+        <v>1.53</v>
+      </c>
+      <c r="BL87">
+        <v>2.3</v>
+      </c>
+      <c r="BM87">
+        <v>1.83</v>
+      </c>
+      <c r="BN87">
+        <v>1.85</v>
+      </c>
+      <c r="BO87">
+        <v>2.25</v>
+      </c>
+      <c r="BP87">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:68">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>7785268</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="2">
+        <v>45836.54166666666</v>
+      </c>
+      <c r="F88">
+        <v>11</v>
+      </c>
+      <c r="G88" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" t="s">
+        <v>85</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>2</v>
+      </c>
+      <c r="O88" t="s">
+        <v>147</v>
+      </c>
+      <c r="P88" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q88">
+        <v>2.83</v>
+      </c>
+      <c r="R88">
+        <v>2.43</v>
+      </c>
+      <c r="S88">
+        <v>3.05</v>
+      </c>
+      <c r="T88">
+        <v>1.2</v>
+      </c>
+      <c r="U88">
+        <v>3.68</v>
+      </c>
+      <c r="V88">
+        <v>2.12</v>
+      </c>
+      <c r="W88">
+        <v>1.64</v>
+      </c>
+      <c r="X88">
+        <v>4.5</v>
+      </c>
+      <c r="Y88">
+        <v>1.13</v>
+      </c>
+      <c r="Z88">
+        <v>1.85</v>
+      </c>
+      <c r="AA88">
+        <v>3.67</v>
+      </c>
+      <c r="AB88">
+        <v>3.26</v>
+      </c>
+      <c r="AC88">
+        <v>1.01</v>
+      </c>
+      <c r="AD88">
+        <v>17</v>
+      </c>
+      <c r="AE88">
+        <v>1.09</v>
+      </c>
+      <c r="AF88">
+        <v>5.25</v>
+      </c>
+      <c r="AG88">
+        <v>1.55</v>
+      </c>
+      <c r="AH88">
+        <v>2.29</v>
+      </c>
+      <c r="AI88">
+        <v>1.4</v>
+      </c>
+      <c r="AJ88">
         <v>2.72</v>
       </c>
-      <c r="AC78">
+      <c r="AK88">
+        <v>1.5</v>
+      </c>
+      <c r="AL88">
+        <v>1.26</v>
+      </c>
+      <c r="AM88">
+        <v>1.56</v>
+      </c>
+      <c r="AN88">
+        <v>2</v>
+      </c>
+      <c r="AO88">
+        <v>2.5</v>
+      </c>
+      <c r="AP88">
+        <v>1.86</v>
+      </c>
+      <c r="AQ88">
+        <v>2.29</v>
+      </c>
+      <c r="AR88">
+        <v>2.33</v>
+      </c>
+      <c r="AS88">
+        <v>1.86</v>
+      </c>
+      <c r="AT88">
+        <v>4.19</v>
+      </c>
+      <c r="AU88">
+        <v>3</v>
+      </c>
+      <c r="AV88">
+        <v>5</v>
+      </c>
+      <c r="AW88">
+        <v>9</v>
+      </c>
+      <c r="AX88">
+        <v>6</v>
+      </c>
+      <c r="AY88">
+        <v>12</v>
+      </c>
+      <c r="AZ88">
+        <v>11</v>
+      </c>
+      <c r="BA88">
+        <v>9</v>
+      </c>
+      <c r="BB88">
+        <v>5</v>
+      </c>
+      <c r="BC88">
+        <v>14</v>
+      </c>
+      <c r="BD88">
+        <v>1.75</v>
+      </c>
+      <c r="BE88">
+        <v>6.75</v>
+      </c>
+      <c r="BF88">
+        <v>2.28</v>
+      </c>
+      <c r="BG88">
+        <v>1.2</v>
+      </c>
+      <c r="BH88">
+        <v>3.95</v>
+      </c>
+      <c r="BI88">
+        <v>1.35</v>
+      </c>
+      <c r="BJ88">
+        <v>2.9</v>
+      </c>
+      <c r="BK88">
+        <v>1.57</v>
+      </c>
+      <c r="BL88">
+        <v>2.23</v>
+      </c>
+      <c r="BM88">
+        <v>1.91</v>
+      </c>
+      <c r="BN88">
+        <v>1.78</v>
+      </c>
+      <c r="BO88">
+        <v>2.38</v>
+      </c>
+      <c r="BP88">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:68">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>7785266</v>
+      </c>
+      <c r="C89" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45837.39583333334</v>
+      </c>
+      <c r="F89">
+        <v>11</v>
+      </c>
+      <c r="G89" t="s">
+        <v>83</v>
+      </c>
+      <c r="H89" t="s">
+        <v>84</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
+        <v>91</v>
+      </c>
+      <c r="P89" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q89">
+        <v>3.35</v>
+      </c>
+      <c r="R89">
+        <v>2.2</v>
+      </c>
+      <c r="S89">
+        <v>2.75</v>
+      </c>
+      <c r="T89">
+        <v>1.33</v>
+      </c>
+      <c r="U89">
+        <v>3</v>
+      </c>
+      <c r="V89">
+        <v>2.5</v>
+      </c>
+      <c r="W89">
+        <v>1.48</v>
+      </c>
+      <c r="X89">
+        <v>5.7</v>
+      </c>
+      <c r="Y89">
+        <v>1.08</v>
+      </c>
+      <c r="Z89">
+        <v>2.7</v>
+      </c>
+      <c r="AA89">
+        <v>3.34</v>
+      </c>
+      <c r="AB89">
+        <v>2.23</v>
+      </c>
+      <c r="AC89">
         <v>1.05</v>
       </c>
-      <c r="AD78">
+      <c r="AD89">
         <v>9.5</v>
       </c>
-      <c r="AE78">
+      <c r="AE89">
         <v>1.25</v>
       </c>
-      <c r="AF78">
+      <c r="AF89">
+        <v>3.85</v>
+      </c>
+      <c r="AG89">
+        <v>1.81</v>
+      </c>
+      <c r="AH89">
+        <v>1.89</v>
+      </c>
+      <c r="AI89">
+        <v>1.6</v>
+      </c>
+      <c r="AJ89">
+        <v>2.15</v>
+      </c>
+      <c r="AK89">
+        <v>1.62</v>
+      </c>
+      <c r="AL89">
+        <v>1.25</v>
+      </c>
+      <c r="AM89">
+        <v>1.38</v>
+      </c>
+      <c r="AN89">
+        <v>0.2</v>
+      </c>
+      <c r="AO89">
+        <v>1.43</v>
+      </c>
+      <c r="AP89">
+        <v>0.33</v>
+      </c>
+      <c r="AQ89">
+        <v>1.38</v>
+      </c>
+      <c r="AR89">
+        <v>1.3</v>
+      </c>
+      <c r="AS89">
+        <v>1.18</v>
+      </c>
+      <c r="AT89">
+        <v>2.48</v>
+      </c>
+      <c r="AU89">
+        <v>5</v>
+      </c>
+      <c r="AV89">
+        <v>4</v>
+      </c>
+      <c r="AW89">
+        <v>4</v>
+      </c>
+      <c r="AX89">
+        <v>8</v>
+      </c>
+      <c r="AY89">
+        <v>9</v>
+      </c>
+      <c r="AZ89">
+        <v>12</v>
+      </c>
+      <c r="BA89">
+        <v>5</v>
+      </c>
+      <c r="BB89">
+        <v>4</v>
+      </c>
+      <c r="BC89">
+        <v>9</v>
+      </c>
+      <c r="BD89">
+        <v>2.1</v>
+      </c>
+      <c r="BE89">
+        <v>6.75</v>
+      </c>
+      <c r="BF89">
+        <v>1.86</v>
+      </c>
+      <c r="BG89">
+        <v>1.22</v>
+      </c>
+      <c r="BH89">
+        <v>3.8</v>
+      </c>
+      <c r="BI89">
+        <v>1.38</v>
+      </c>
+      <c r="BJ89">
+        <v>2.75</v>
+      </c>
+      <c r="BK89">
+        <v>1.61</v>
+      </c>
+      <c r="BL89">
+        <v>2.15</v>
+      </c>
+      <c r="BM89">
+        <v>1.97</v>
+      </c>
+      <c r="BN89">
+        <v>1.74</v>
+      </c>
+      <c r="BO89">
+        <v>2.43</v>
+      </c>
+      <c r="BP89">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:68">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>7785262</v>
+      </c>
+      <c r="C90" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F90">
+        <v>11</v>
+      </c>
+      <c r="G90" t="s">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s">
+        <v>81</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>2</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>2</v>
+      </c>
+      <c r="N90">
+        <v>3</v>
+      </c>
+      <c r="O90" t="s">
+        <v>148</v>
+      </c>
+      <c r="P90" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q90">
+        <v>1.57</v>
+      </c>
+      <c r="R90">
+        <v>3</v>
+      </c>
+      <c r="S90">
+        <v>6.5</v>
+      </c>
+      <c r="T90">
+        <v>1.17</v>
+      </c>
+      <c r="U90">
+        <v>4.5</v>
+      </c>
+      <c r="V90">
+        <v>1.83</v>
+      </c>
+      <c r="W90">
+        <v>1.85</v>
+      </c>
+      <c r="X90">
+        <v>3.74</v>
+      </c>
+      <c r="Y90">
+        <v>1.19</v>
+      </c>
+      <c r="Z90">
+        <v>1.23</v>
+      </c>
+      <c r="AA90">
+        <v>5.7</v>
+      </c>
+      <c r="AB90">
+        <v>7.7</v>
+      </c>
+      <c r="AC90">
+        <v>1.01</v>
+      </c>
+      <c r="AD90">
+        <v>26</v>
+      </c>
+      <c r="AE90">
+        <v>1.08</v>
+      </c>
+      <c r="AF90">
+        <v>7.5</v>
+      </c>
+      <c r="AG90">
+        <v>1.3</v>
+      </c>
+      <c r="AH90">
+        <v>3.33</v>
+      </c>
+      <c r="AI90">
+        <v>1.6</v>
+      </c>
+      <c r="AJ90">
+        <v>2.15</v>
+      </c>
+      <c r="AK90">
+        <v>1.05</v>
+      </c>
+      <c r="AL90">
+        <v>1.11</v>
+      </c>
+      <c r="AM90">
+        <v>3.7</v>
+      </c>
+      <c r="AN90">
+        <v>2.4</v>
+      </c>
+      <c r="AO90">
+        <v>1.8</v>
+      </c>
+      <c r="AP90">
+        <v>2</v>
+      </c>
+      <c r="AQ90">
+        <v>2</v>
+      </c>
+      <c r="AR90">
+        <v>2.02</v>
+      </c>
+      <c r="AS90">
+        <v>1.66</v>
+      </c>
+      <c r="AT90">
+        <v>3.68</v>
+      </c>
+      <c r="AU90">
+        <v>7</v>
+      </c>
+      <c r="AV90">
+        <v>4</v>
+      </c>
+      <c r="AW90">
+        <v>23</v>
+      </c>
+      <c r="AX90">
+        <v>2</v>
+      </c>
+      <c r="AY90">
+        <v>30</v>
+      </c>
+      <c r="AZ90">
+        <v>6</v>
+      </c>
+      <c r="BA90">
+        <v>10</v>
+      </c>
+      <c r="BB90">
+        <v>2</v>
+      </c>
+      <c r="BC90">
+        <v>12</v>
+      </c>
+      <c r="BD90">
+        <v>1.23</v>
+      </c>
+      <c r="BE90">
+        <v>8.5</v>
+      </c>
+      <c r="BF90">
+        <v>4.4</v>
+      </c>
+      <c r="BG90">
+        <v>1.15</v>
+      </c>
+      <c r="BH90">
+        <v>4.6</v>
+      </c>
+      <c r="BI90">
+        <v>1.27</v>
+      </c>
+      <c r="BJ90">
+        <v>3.3</v>
+      </c>
+      <c r="BK90">
+        <v>1.46</v>
+      </c>
+      <c r="BL90">
+        <v>2.5</v>
+      </c>
+      <c r="BM90">
+        <v>1.73</v>
+      </c>
+      <c r="BN90">
+        <v>1.98</v>
+      </c>
+      <c r="BO90">
+        <v>2.08</v>
+      </c>
+      <c r="BP90">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:68">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>7785264</v>
+      </c>
+      <c r="C91" t="s">
+        <v>68</v>
+      </c>
+      <c r="D91" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F91">
+        <v>11</v>
+      </c>
+      <c r="G91" t="s">
+        <v>77</v>
+      </c>
+      <c r="H91" t="s">
+        <v>73</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>2</v>
+      </c>
+      <c r="O91" t="s">
+        <v>149</v>
+      </c>
+      <c r="P91" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q91">
+        <v>2.45</v>
+      </c>
+      <c r="R91">
+        <v>2.15</v>
+      </c>
+      <c r="S91">
+        <v>4</v>
+      </c>
+      <c r="T91">
+        <v>1.35</v>
+      </c>
+      <c r="U91">
+        <v>2.95</v>
+      </c>
+      <c r="V91">
+        <v>2.62</v>
+      </c>
+      <c r="W91">
+        <v>1.42</v>
+      </c>
+      <c r="X91">
+        <v>6.65</v>
+      </c>
+      <c r="Y91">
+        <v>1.05</v>
+      </c>
+      <c r="Z91">
+        <v>1.86</v>
+      </c>
+      <c r="AA91">
+        <v>3.39</v>
+      </c>
+      <c r="AB91">
+        <v>3.47</v>
+      </c>
+      <c r="AC91">
+        <v>1.05</v>
+      </c>
+      <c r="AD91">
+        <v>9.5</v>
+      </c>
+      <c r="AE91">
+        <v>1.28</v>
+      </c>
+      <c r="AF91">
+        <v>3.65</v>
+      </c>
+      <c r="AG91">
+        <v>1.79</v>
+      </c>
+      <c r="AH91">
+        <v>1.91</v>
+      </c>
+      <c r="AI91">
+        <v>1.7</v>
+      </c>
+      <c r="AJ91">
+        <v>2</v>
+      </c>
+      <c r="AK91">
+        <v>1.25</v>
+      </c>
+      <c r="AL91">
+        <v>1.22</v>
+      </c>
+      <c r="AM91">
+        <v>1.85</v>
+      </c>
+      <c r="AN91">
+        <v>1.8</v>
+      </c>
+      <c r="AO91">
+        <v>0.8</v>
+      </c>
+      <c r="AP91">
+        <v>1.67</v>
+      </c>
+      <c r="AQ91">
+        <v>0.83</v>
+      </c>
+      <c r="AR91">
+        <v>1.53</v>
+      </c>
+      <c r="AS91">
+        <v>1.13</v>
+      </c>
+      <c r="AT91">
+        <v>2.66</v>
+      </c>
+      <c r="AU91">
+        <v>8</v>
+      </c>
+      <c r="AV91">
+        <v>4</v>
+      </c>
+      <c r="AW91">
+        <v>6</v>
+      </c>
+      <c r="AX91">
+        <v>9</v>
+      </c>
+      <c r="AY91">
+        <v>14</v>
+      </c>
+      <c r="AZ91">
+        <v>13</v>
+      </c>
+      <c r="BA91">
+        <v>10</v>
+      </c>
+      <c r="BB91">
+        <v>5</v>
+      </c>
+      <c r="BC91">
+        <v>15</v>
+      </c>
+      <c r="BD91">
+        <v>1.65</v>
+      </c>
+      <c r="BE91">
+        <v>7</v>
+      </c>
+      <c r="BF91">
+        <v>2.48</v>
+      </c>
+      <c r="BG91">
+        <v>1.19</v>
+      </c>
+      <c r="BH91">
+        <v>4.1</v>
+      </c>
+      <c r="BI91">
+        <v>1.34</v>
+      </c>
+      <c r="BJ91">
+        <v>2.9</v>
+      </c>
+      <c r="BK91">
+        <v>1.55</v>
+      </c>
+      <c r="BL91">
+        <v>2.25</v>
+      </c>
+      <c r="BM91">
+        <v>1.9</v>
+      </c>
+      <c r="BN91">
+        <v>1.79</v>
+      </c>
+      <c r="BO91">
+        <v>2.33</v>
+      </c>
+      <c r="BP91">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="92" spans="1:68">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>7785265</v>
+      </c>
+      <c r="C92" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F92">
+        <v>11</v>
+      </c>
+      <c r="G92" t="s">
+        <v>71</v>
+      </c>
+      <c r="H92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>91</v>
+      </c>
+      <c r="P92" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q92">
+        <v>3.1</v>
+      </c>
+      <c r="R92">
+        <v>1.95</v>
+      </c>
+      <c r="S92">
+        <v>3.55</v>
+      </c>
+      <c r="T92">
+        <v>1.48</v>
+      </c>
+      <c r="U92">
+        <v>2.45</v>
+      </c>
+      <c r="V92">
+        <v>3.2</v>
+      </c>
+      <c r="W92">
+        <v>1.3</v>
+      </c>
+      <c r="X92">
+        <v>9.1</v>
+      </c>
+      <c r="Y92">
+        <v>1</v>
+      </c>
+      <c r="Z92">
+        <v>2.25</v>
+      </c>
+      <c r="AA92">
+        <v>3.08</v>
+      </c>
+      <c r="AB92">
+        <v>2.85</v>
+      </c>
+      <c r="AC92">
+        <v>1.08</v>
+      </c>
+      <c r="AD92">
+        <v>7.5</v>
+      </c>
+      <c r="AE92">
+        <v>1.42</v>
+      </c>
+      <c r="AF92">
+        <v>2.8</v>
+      </c>
+      <c r="AG92">
+        <v>2.04</v>
+      </c>
+      <c r="AH92">
+        <v>1.69</v>
+      </c>
+      <c r="AI92">
+        <v>1.85</v>
+      </c>
+      <c r="AJ92">
+        <v>1.8</v>
+      </c>
+      <c r="AK92">
+        <v>1.38</v>
+      </c>
+      <c r="AL92">
+        <v>1.3</v>
+      </c>
+      <c r="AM92">
+        <v>1.53</v>
+      </c>
+      <c r="AN92">
+        <v>2.17</v>
+      </c>
+      <c r="AO92">
+        <v>2</v>
+      </c>
+      <c r="AP92">
+        <v>1.86</v>
+      </c>
+      <c r="AQ92">
+        <v>2.17</v>
+      </c>
+      <c r="AR92">
+        <v>1.11</v>
+      </c>
+      <c r="AS92">
+        <v>1.09</v>
+      </c>
+      <c r="AT92">
+        <v>2.2</v>
+      </c>
+      <c r="AU92">
+        <v>6</v>
+      </c>
+      <c r="AV92">
+        <v>5</v>
+      </c>
+      <c r="AW92">
+        <v>8</v>
+      </c>
+      <c r="AX92">
+        <v>3</v>
+      </c>
+      <c r="AY92">
+        <v>14</v>
+      </c>
+      <c r="AZ92">
+        <v>8</v>
+      </c>
+      <c r="BA92">
+        <v>8</v>
+      </c>
+      <c r="BB92">
+        <v>3</v>
+      </c>
+      <c r="BC92">
+        <v>11</v>
+      </c>
+      <c r="BD92">
+        <v>1.86</v>
+      </c>
+      <c r="BE92">
+        <v>6.4</v>
+      </c>
+      <c r="BF92">
+        <v>2.15</v>
+      </c>
+      <c r="BG92">
+        <v>1.33</v>
+      </c>
+      <c r="BH92">
+        <v>2.95</v>
+      </c>
+      <c r="BI92">
+        <v>1.56</v>
+      </c>
+      <c r="BJ92">
+        <v>2.23</v>
+      </c>
+      <c r="BK92">
+        <v>1.92</v>
+      </c>
+      <c r="BL92">
+        <v>1.78</v>
+      </c>
+      <c r="BM92">
+        <v>2.4</v>
+      </c>
+      <c r="BN92">
+        <v>1.49</v>
+      </c>
+      <c r="BO92">
+        <v>3.15</v>
+      </c>
+      <c r="BP92">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:68">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>7785267</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="2">
+        <v>45837.5</v>
+      </c>
+      <c r="F93">
+        <v>11</v>
+      </c>
+      <c r="G93" t="s">
+        <v>75</v>
+      </c>
+      <c r="H93" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>3</v>
+      </c>
+      <c r="N93">
+        <v>5</v>
+      </c>
+      <c r="O93" t="s">
+        <v>150</v>
+      </c>
+      <c r="P93" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q93">
+        <v>2.38</v>
+      </c>
+      <c r="R93">
+        <v>2.1</v>
+      </c>
+      <c r="S93">
+        <v>4.5</v>
+      </c>
+      <c r="T93">
+        <v>1.38</v>
+      </c>
+      <c r="U93">
+        <v>2.8</v>
+      </c>
+      <c r="V93">
+        <v>2.8</v>
+      </c>
+      <c r="W93">
+        <v>1.38</v>
+      </c>
+      <c r="X93">
+        <v>7.3</v>
+      </c>
+      <c r="Y93">
+        <v>1.03</v>
+      </c>
+      <c r="Z93">
+        <v>1.73</v>
+      </c>
+      <c r="AA93">
+        <v>3.4</v>
+      </c>
+      <c r="AB93">
+        <v>4</v>
+      </c>
+      <c r="AC93">
+        <v>1.06</v>
+      </c>
+      <c r="AD93">
+        <v>8.5</v>
+      </c>
+      <c r="AE93">
+        <v>1.33</v>
+      </c>
+      <c r="AF93">
+        <v>3.3</v>
+      </c>
+      <c r="AG93">
+        <v>1.92</v>
+      </c>
+      <c r="AH93">
+        <v>1.78</v>
+      </c>
+      <c r="AI93">
+        <v>1.83</v>
+      </c>
+      <c r="AJ93">
+        <v>1.85</v>
+      </c>
+      <c r="AK93">
+        <v>1.2</v>
+      </c>
+      <c r="AL93">
+        <v>1.22</v>
+      </c>
+      <c r="AM93">
+        <v>1.95</v>
+      </c>
+      <c r="AN93">
+        <v>0.8</v>
+      </c>
+      <c r="AO93">
+        <v>0.4</v>
+      </c>
+      <c r="AP93">
+        <v>0.67</v>
+      </c>
+      <c r="AQ93">
+        <v>0.83</v>
+      </c>
+      <c r="AR93">
+        <v>1.62</v>
+      </c>
+      <c r="AS93">
+        <v>0.97</v>
+      </c>
+      <c r="AT93">
+        <v>2.59</v>
+      </c>
+      <c r="AU93">
+        <v>5</v>
+      </c>
+      <c r="AV93">
+        <v>5</v>
+      </c>
+      <c r="AW93">
+        <v>8</v>
+      </c>
+      <c r="AX93">
+        <v>5</v>
+      </c>
+      <c r="AY93">
+        <v>13</v>
+      </c>
+      <c r="AZ93">
+        <v>10</v>
+      </c>
+      <c r="BA93">
+        <v>4</v>
+      </c>
+      <c r="BB93">
+        <v>0</v>
+      </c>
+      <c r="BC93">
+        <v>4</v>
+      </c>
+      <c r="BD93">
+        <v>1.6</v>
+      </c>
+      <c r="BE93">
+        <v>6.4</v>
+      </c>
+      <c r="BF93">
+        <v>2.65</v>
+      </c>
+      <c r="BG93">
+        <v>1.36</v>
+      </c>
+      <c r="BH93">
+        <v>2.8</v>
+      </c>
+      <c r="BI93">
+        <v>1.6</v>
+      </c>
+      <c r="BJ93">
+        <v>2.17</v>
+      </c>
+      <c r="BK93">
+        <v>1.98</v>
+      </c>
+      <c r="BL93">
+        <v>1.74</v>
+      </c>
+      <c r="BM93">
+        <v>2.5</v>
+      </c>
+      <c r="BN93">
+        <v>1.46</v>
+      </c>
+      <c r="BO93">
+        <v>3.3</v>
+      </c>
+      <c r="BP93">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:68">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>7785269</v>
+      </c>
+      <c r="C94" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45837.59375</v>
+      </c>
+      <c r="F94">
+        <v>11</v>
+      </c>
+      <c r="G94" t="s">
+        <v>70</v>
+      </c>
+      <c r="H94" t="s">
+        <v>72</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>2</v>
+      </c>
+      <c r="N94">
+        <v>2</v>
+      </c>
+      <c r="O94" t="s">
+        <v>91</v>
+      </c>
+      <c r="P94" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q94">
+        <v>2.95</v>
+      </c>
+      <c r="R94">
+        <v>2.25</v>
+      </c>
+      <c r="S94">
+        <v>3</v>
+      </c>
+      <c r="T94">
+        <v>1.28</v>
+      </c>
+      <c r="U94">
+        <v>3.3</v>
+      </c>
+      <c r="V94">
+        <v>2.25</v>
+      </c>
+      <c r="W94">
+        <v>1.57</v>
+      </c>
+      <c r="X94">
+        <v>5.15</v>
+      </c>
+      <c r="Y94">
+        <v>1.1</v>
+      </c>
+      <c r="Z94">
+        <v>2.18</v>
+      </c>
+      <c r="AA94">
+        <v>3.28</v>
+      </c>
+      <c r="AB94">
+        <v>2.8</v>
+      </c>
+      <c r="AC94">
+        <v>1.04</v>
+      </c>
+      <c r="AD94">
+        <v>10</v>
+      </c>
+      <c r="AE94">
+        <v>1.2</v>
+      </c>
+      <c r="AF94">
+        <v>4.5</v>
+      </c>
+      <c r="AG94">
+        <v>1.57</v>
+      </c>
+      <c r="AH94">
+        <v>2.15</v>
+      </c>
+      <c r="AI94">
+        <v>1.45</v>
+      </c>
+      <c r="AJ94">
+        <v>2.5</v>
+      </c>
+      <c r="AK94">
+        <v>1.48</v>
+      </c>
+      <c r="AL94">
+        <v>1.22</v>
+      </c>
+      <c r="AM94">
+        <v>1.5</v>
+      </c>
+      <c r="AN94">
+        <v>0</v>
+      </c>
+      <c r="AO94">
+        <v>1.17</v>
+      </c>
+      <c r="AP94">
+        <v>0</v>
+      </c>
+      <c r="AQ94">
+        <v>1.43</v>
+      </c>
+      <c r="AR94">
+        <v>1.63</v>
+      </c>
+      <c r="AS94">
+        <v>1.18</v>
+      </c>
+      <c r="AT94">
+        <v>2.81</v>
+      </c>
+      <c r="AU94">
+        <v>3</v>
+      </c>
+      <c r="AV94">
+        <v>3</v>
+      </c>
+      <c r="AW94">
+        <v>2</v>
+      </c>
+      <c r="AX94">
+        <v>13</v>
+      </c>
+      <c r="AY94">
+        <v>5</v>
+      </c>
+      <c r="AZ94">
+        <v>16</v>
+      </c>
+      <c r="BA94">
+        <v>4</v>
+      </c>
+      <c r="BB94">
+        <v>3</v>
+      </c>
+      <c r="BC94">
+        <v>7</v>
+      </c>
+      <c r="BD94">
+        <v>1.79</v>
+      </c>
+      <c r="BE94">
+        <v>7</v>
+      </c>
+      <c r="BF94">
+        <v>2.18</v>
+      </c>
+      <c r="BG94">
+        <v>1.13</v>
+      </c>
+      <c r="BH94">
+        <v>5.1</v>
+      </c>
+      <c r="BI94">
+        <v>1.24</v>
+      </c>
+      <c r="BJ94">
+        <v>3.65</v>
+      </c>
+      <c r="BK94">
+        <v>1.41</v>
+      </c>
+      <c r="BL94">
+        <v>2.65</v>
+      </c>
+      <c r="BM94">
+        <v>1.65</v>
+      </c>
+      <c r="BN94">
+        <v>2.08</v>
+      </c>
+      <c r="BO94">
+        <v>1.98</v>
+      </c>
+      <c r="BP94">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:68">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>7785263</v>
+      </c>
+      <c r="C95" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
+      </c>
+      <c r="G95" t="s">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s">
+        <v>82</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="s">
+        <v>151</v>
+      </c>
+      <c r="P95" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q95">
+        <v>1.95</v>
+      </c>
+      <c r="R95">
+        <v>2.63</v>
+      </c>
+      <c r="S95">
+        <v>5</v>
+      </c>
+      <c r="T95">
+        <v>1.22</v>
+      </c>
+      <c r="U95">
+        <v>4</v>
+      </c>
+      <c r="V95">
+        <v>2.1</v>
+      </c>
+      <c r="W95">
+        <v>1.67</v>
+      </c>
+      <c r="X95">
+        <v>4.5</v>
+      </c>
+      <c r="Y95">
+        <v>1.18</v>
+      </c>
+      <c r="Z95">
+        <v>1.46</v>
+      </c>
+      <c r="AA95">
+        <v>4.2</v>
+      </c>
+      <c r="AB95">
+        <v>5</v>
+      </c>
+      <c r="AC95">
+        <v>1.01</v>
+      </c>
+      <c r="AD95">
+        <v>17</v>
+      </c>
+      <c r="AE95">
+        <v>1.13</v>
+      </c>
+      <c r="AF95">
+        <v>5.75</v>
+      </c>
+      <c r="AG95">
+        <v>1.41</v>
+      </c>
+      <c r="AH95">
+        <v>2.78</v>
+      </c>
+      <c r="AI95">
+        <v>1.53</v>
+      </c>
+      <c r="AJ95">
+        <v>2.38</v>
+      </c>
+      <c r="AK95">
+        <v>1.16</v>
+      </c>
+      <c r="AL95">
+        <v>1.19</v>
+      </c>
+      <c r="AM95">
+        <v>2.4</v>
+      </c>
+      <c r="AN95">
+        <v>2</v>
+      </c>
+      <c r="AO95">
+        <v>0.6</v>
+      </c>
+      <c r="AP95">
+        <v>2.13</v>
+      </c>
+      <c r="AQ95">
+        <v>0.5</v>
+      </c>
+      <c r="AR95">
+        <v>1.99</v>
+      </c>
+      <c r="AS95">
+        <v>1.68</v>
+      </c>
+      <c r="AT95">
+        <v>3.67</v>
+      </c>
+      <c r="AU95">
+        <v>10</v>
+      </c>
+      <c r="AV95">
+        <v>3</v>
+      </c>
+      <c r="AW95">
+        <v>14</v>
+      </c>
+      <c r="AX95">
+        <v>5</v>
+      </c>
+      <c r="AY95">
+        <v>24</v>
+      </c>
+      <c r="AZ95">
+        <v>8</v>
+      </c>
+      <c r="BA95">
+        <v>9</v>
+      </c>
+      <c r="BB95">
+        <v>3</v>
+      </c>
+      <c r="BC95">
+        <v>12</v>
+      </c>
+      <c r="BD95">
+        <v>1.5</v>
+      </c>
+      <c r="BE95">
+        <v>7</v>
+      </c>
+      <c r="BF95">
+        <v>2.8</v>
+      </c>
+      <c r="BG95">
+        <v>1.19</v>
+      </c>
+      <c r="BH95">
+        <v>4.1</v>
+      </c>
+      <c r="BI95">
+        <v>1.33</v>
+      </c>
+      <c r="BJ95">
+        <v>2.95</v>
+      </c>
+      <c r="BK95">
+        <v>1.54</v>
+      </c>
+      <c r="BL95">
+        <v>2.3</v>
+      </c>
+      <c r="BM95">
+        <v>1.85</v>
+      </c>
+      <c r="BN95">
+        <v>1.83</v>
+      </c>
+      <c r="BO95">
+        <v>2.32</v>
+      </c>
+      <c r="BP95">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="96" spans="1:68">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>7785270</v>
+      </c>
+      <c r="C96" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="2">
+        <v>45843.375</v>
+      </c>
+      <c r="F96">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>73</v>
+      </c>
+      <c r="H96" t="s">
+        <v>80</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>2</v>
+      </c>
+      <c r="O96" t="s">
+        <v>152</v>
+      </c>
+      <c r="P96" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q96">
+        <v>4.33</v>
+      </c>
+      <c r="R96">
+        <v>2.38</v>
+      </c>
+      <c r="S96">
+        <v>2.38</v>
+      </c>
+      <c r="T96">
+        <v>1.3</v>
+      </c>
+      <c r="U96">
+        <v>3.4</v>
+      </c>
+      <c r="V96">
+        <v>2.38</v>
+      </c>
+      <c r="W96">
+        <v>1.53</v>
+      </c>
+      <c r="X96">
+        <v>6</v>
+      </c>
+      <c r="Y96">
+        <v>1.13</v>
+      </c>
+      <c r="Z96">
+        <v>4.1</v>
+      </c>
+      <c r="AA96">
+        <v>3.73</v>
+      </c>
+      <c r="AB96">
+        <v>1.64</v>
+      </c>
+      <c r="AC96">
+        <v>1.03</v>
+      </c>
+      <c r="AD96">
+        <v>12</v>
+      </c>
+      <c r="AE96">
+        <v>1.21</v>
+      </c>
+      <c r="AF96">
+        <v>4.51</v>
+      </c>
+      <c r="AG96">
+        <v>1.57</v>
+      </c>
+      <c r="AH96">
+        <v>2.31</v>
+      </c>
+      <c r="AI96">
+        <v>1.62</v>
+      </c>
+      <c r="AJ96">
+        <v>2.2</v>
+      </c>
+      <c r="AK96">
+        <v>1.9</v>
+      </c>
+      <c r="AL96">
+        <v>1.25</v>
+      </c>
+      <c r="AM96">
+        <v>1.25</v>
+      </c>
+      <c r="AN96">
+        <v>1.4</v>
+      </c>
+      <c r="AO96">
+        <v>1.8</v>
+      </c>
+      <c r="AP96">
+        <v>1.33</v>
+      </c>
+      <c r="AQ96">
+        <v>1.67</v>
+      </c>
+      <c r="AR96">
+        <v>1.39</v>
+      </c>
+      <c r="AS96">
+        <v>1.79</v>
+      </c>
+      <c r="AT96">
+        <v>3.18</v>
+      </c>
+      <c r="AU96">
+        <v>5</v>
+      </c>
+      <c r="AV96">
+        <v>4</v>
+      </c>
+      <c r="AW96">
+        <v>4</v>
+      </c>
+      <c r="AX96">
+        <v>8</v>
+      </c>
+      <c r="AY96">
+        <v>9</v>
+      </c>
+      <c r="AZ96">
+        <v>12</v>
+      </c>
+      <c r="BA96">
+        <v>1</v>
+      </c>
+      <c r="BB96">
+        <v>8</v>
+      </c>
+      <c r="BC96">
+        <v>9</v>
+      </c>
+      <c r="BD96">
+        <v>2.65</v>
+      </c>
+      <c r="BE96">
+        <v>7</v>
+      </c>
+      <c r="BF96">
+        <v>1.56</v>
+      </c>
+      <c r="BG96">
+        <v>1.16</v>
+      </c>
+      <c r="BH96">
+        <v>4.6</v>
+      </c>
+      <c r="BI96">
+        <v>1.28</v>
+      </c>
+      <c r="BJ96">
+        <v>3.3</v>
+      </c>
+      <c r="BK96">
+        <v>1.47</v>
+      </c>
+      <c r="BL96">
+        <v>2.48</v>
+      </c>
+      <c r="BM96">
+        <v>1.73</v>
+      </c>
+      <c r="BN96">
+        <v>1.98</v>
+      </c>
+      <c r="BO96">
+        <v>2.08</v>
+      </c>
+      <c r="BP96">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="97" spans="1:68">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>7785276</v>
+      </c>
+      <c r="C97" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="2">
+        <v>45843.45833333334</v>
+      </c>
+      <c r="F97">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>85</v>
+      </c>
+      <c r="H97" t="s">
+        <v>70</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>153</v>
+      </c>
+      <c r="P97" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q97">
+        <v>1.57</v>
+      </c>
+      <c r="R97">
+        <v>3.2</v>
+      </c>
+      <c r="S97">
+        <v>7.5</v>
+      </c>
+      <c r="T97">
+        <v>1.14</v>
+      </c>
+      <c r="U97">
+        <v>5.5</v>
+      </c>
+      <c r="V97">
+        <v>1.73</v>
+      </c>
+      <c r="W97">
+        <v>2</v>
+      </c>
+      <c r="X97">
+        <v>3.4</v>
+      </c>
+      <c r="Y97">
+        <v>1.3</v>
+      </c>
+      <c r="Z97">
+        <v>1.25</v>
+      </c>
+      <c r="AA97">
+        <v>5.3</v>
+      </c>
+      <c r="AB97">
+        <v>7.6</v>
+      </c>
+      <c r="AC97">
+        <v>1</v>
+      </c>
+      <c r="AD97">
+        <v>25</v>
+      </c>
+      <c r="AE97">
+        <v>1.04</v>
+      </c>
+      <c r="AF97">
+        <v>9.5</v>
+      </c>
+      <c r="AG97">
+        <v>1.28</v>
+      </c>
+      <c r="AH97">
+        <v>3.47</v>
+      </c>
+      <c r="AI97">
+        <v>1.57</v>
+      </c>
+      <c r="AJ97">
+        <v>2.25</v>
+      </c>
+      <c r="AK97">
+        <v>1.06</v>
+      </c>
+      <c r="AL97">
+        <v>1.07</v>
+      </c>
+      <c r="AM97">
+        <v>3.7</v>
+      </c>
+      <c r="AN97">
+        <v>2.43</v>
+      </c>
+      <c r="AO97">
+        <v>1.2</v>
+      </c>
+      <c r="AP97">
+        <v>2.5</v>
+      </c>
+      <c r="AQ97">
+        <v>1</v>
+      </c>
+      <c r="AR97">
+        <v>2.35</v>
+      </c>
+      <c r="AS97">
+        <v>1.53</v>
+      </c>
+      <c r="AT97">
+        <v>3.88</v>
+      </c>
+      <c r="AU97">
+        <v>6</v>
+      </c>
+      <c r="AV97">
+        <v>2</v>
+      </c>
+      <c r="AW97">
+        <v>14</v>
+      </c>
+      <c r="AX97">
+        <v>1</v>
+      </c>
+      <c r="AY97">
+        <v>20</v>
+      </c>
+      <c r="AZ97">
+        <v>3</v>
+      </c>
+      <c r="BA97">
+        <v>16</v>
+      </c>
+      <c r="BB97">
+        <v>2</v>
+      </c>
+      <c r="BC97">
+        <v>18</v>
+      </c>
+      <c r="BD97">
+        <v>1.26</v>
+      </c>
+      <c r="BE97">
+        <v>8.5</v>
+      </c>
+      <c r="BF97">
+        <v>3.95</v>
+      </c>
+      <c r="BG97">
+        <v>1.08</v>
+      </c>
+      <c r="BH97">
+        <v>6.25</v>
+      </c>
+      <c r="BI97">
+        <v>1.16</v>
+      </c>
+      <c r="BJ97">
+        <v>4.4</v>
+      </c>
+      <c r="BK97">
+        <v>1.28</v>
+      </c>
+      <c r="BL97">
+        <v>3.3</v>
+      </c>
+      <c r="BM97">
+        <v>1.47</v>
+      </c>
+      <c r="BN97">
+        <v>2.48</v>
+      </c>
+      <c r="BO97">
+        <v>1.7</v>
+      </c>
+      <c r="BP97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:68">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>7785277</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="2">
+        <v>45843.54166666666</v>
+      </c>
+      <c r="F98">
+        <v>12</v>
+      </c>
+      <c r="G98" t="s">
+        <v>72</v>
+      </c>
+      <c r="H98" t="s">
+        <v>71</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>2</v>
+      </c>
+      <c r="O98" t="s">
+        <v>154</v>
+      </c>
+      <c r="P98" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q98">
+        <v>2.75</v>
+      </c>
+      <c r="R98">
+        <v>2.1</v>
+      </c>
+      <c r="S98">
+        <v>4</v>
+      </c>
+      <c r="T98">
+        <v>1.4</v>
+      </c>
+      <c r="U98">
+        <v>2.75</v>
+      </c>
+      <c r="V98">
+        <v>3</v>
+      </c>
+      <c r="W98">
+        <v>1.36</v>
+      </c>
+      <c r="X98">
+        <v>8</v>
+      </c>
+      <c r="Y98">
+        <v>1.08</v>
+      </c>
+      <c r="Z98">
+        <v>2.16</v>
+      </c>
+      <c r="AA98">
+        <v>3.06</v>
+      </c>
+      <c r="AB98">
+        <v>3.03</v>
+      </c>
+      <c r="AC98">
+        <v>1.06</v>
+      </c>
+      <c r="AD98">
+        <v>8.5</v>
+      </c>
+      <c r="AE98">
+        <v>1.33</v>
+      </c>
+      <c r="AF98">
+        <v>3.25</v>
+      </c>
+      <c r="AG98">
+        <v>1.9</v>
+      </c>
+      <c r="AH98">
+        <v>1.8</v>
+      </c>
+      <c r="AI98">
+        <v>1.8</v>
+      </c>
+      <c r="AJ98">
+        <v>1.95</v>
+      </c>
+      <c r="AK98">
+        <v>1.3</v>
+      </c>
+      <c r="AL98">
+        <v>1.28</v>
+      </c>
+      <c r="AM98">
+        <v>1.67</v>
+      </c>
+      <c r="AN98">
+        <v>0.8</v>
+      </c>
+      <c r="AO98">
+        <v>0.8</v>
+      </c>
+      <c r="AP98">
+        <v>0.83</v>
+      </c>
+      <c r="AQ98">
+        <v>0.83</v>
+      </c>
+      <c r="AR98">
+        <v>2.13</v>
+      </c>
+      <c r="AS98">
+        <v>1.17</v>
+      </c>
+      <c r="AT98">
+        <v>3.3</v>
+      </c>
+      <c r="AU98">
+        <v>8</v>
+      </c>
+      <c r="AV98">
+        <v>9</v>
+      </c>
+      <c r="AW98">
+        <v>3</v>
+      </c>
+      <c r="AX98">
+        <v>6</v>
+      </c>
+      <c r="AY98">
+        <v>11</v>
+      </c>
+      <c r="AZ98">
+        <v>15</v>
+      </c>
+      <c r="BA98">
+        <v>5</v>
+      </c>
+      <c r="BB98">
+        <v>5</v>
+      </c>
+      <c r="BC98">
+        <v>10</v>
+      </c>
+      <c r="BD98">
+        <v>1.65</v>
+      </c>
+      <c r="BE98">
+        <v>6.75</v>
+      </c>
+      <c r="BF98">
+        <v>2.48</v>
+      </c>
+      <c r="BG98">
+        <v>1.21</v>
+      </c>
+      <c r="BH98">
+        <v>3.9</v>
+      </c>
+      <c r="BI98">
+        <v>1.38</v>
+      </c>
+      <c r="BJ98">
+        <v>2.8</v>
+      </c>
+      <c r="BK98">
+        <v>1.61</v>
+      </c>
+      <c r="BL98">
+        <v>2.15</v>
+      </c>
+      <c r="BM98">
+        <v>1.96</v>
+      </c>
+      <c r="BN98">
+        <v>1.74</v>
+      </c>
+      <c r="BO98">
+        <v>2.43</v>
+      </c>
+      <c r="BP98">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="99" spans="1:68">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7785272</v>
+      </c>
+      <c r="C99" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45843.625</v>
+      </c>
+      <c r="F99">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>84</v>
+      </c>
+      <c r="H99" t="s">
+        <v>78</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" t="s">
+        <v>155</v>
+      </c>
+      <c r="P99" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q99">
+        <v>6.5</v>
+      </c>
+      <c r="R99">
+        <v>2.75</v>
+      </c>
+      <c r="S99">
+        <v>1.8</v>
+      </c>
+      <c r="T99">
+        <v>1.22</v>
+      </c>
+      <c r="U99">
+        <v>4</v>
+      </c>
+      <c r="V99">
+        <v>2</v>
+      </c>
+      <c r="W99">
+        <v>1.73</v>
+      </c>
+      <c r="X99">
+        <v>4.33</v>
+      </c>
+      <c r="Y99">
+        <v>1.2</v>
+      </c>
+      <c r="Z99">
+        <v>6.8</v>
+      </c>
+      <c r="AA99">
+        <v>5.1</v>
+      </c>
+      <c r="AB99">
+        <v>1.29</v>
+      </c>
+      <c r="AC99">
+        <v>1.02</v>
+      </c>
+      <c r="AD99">
+        <v>21</v>
+      </c>
+      <c r="AE99">
+        <v>1.11</v>
+      </c>
+      <c r="AF99">
+        <v>6.25</v>
+      </c>
+      <c r="AG99">
+        <v>1.38</v>
+      </c>
+      <c r="AH99">
+        <v>2.9</v>
+      </c>
+      <c r="AI99">
+        <v>1.67</v>
+      </c>
+      <c r="AJ99">
+        <v>2.1</v>
+      </c>
+      <c r="AK99">
+        <v>2.9</v>
+      </c>
+      <c r="AL99">
+        <v>1.11</v>
+      </c>
+      <c r="AM99">
+        <v>1.1</v>
+      </c>
+      <c r="AN99">
+        <v>1.2</v>
+      </c>
+      <c r="AO99">
+        <v>1.75</v>
+      </c>
+      <c r="AP99">
+        <v>1.17</v>
+      </c>
+      <c r="AQ99">
+        <v>1.6</v>
+      </c>
+      <c r="AR99">
+        <v>1.51</v>
+      </c>
+      <c r="AS99">
+        <v>1.47</v>
+      </c>
+      <c r="AT99">
+        <v>2.98</v>
+      </c>
+      <c r="AU99">
+        <v>3</v>
+      </c>
+      <c r="AV99">
+        <v>6</v>
+      </c>
+      <c r="AW99">
+        <v>6</v>
+      </c>
+      <c r="AX99">
+        <v>15</v>
+      </c>
+      <c r="AY99">
+        <v>9</v>
+      </c>
+      <c r="AZ99">
+        <v>21</v>
+      </c>
+      <c r="BA99">
+        <v>4</v>
+      </c>
+      <c r="BB99">
+        <v>7</v>
+      </c>
+      <c r="BC99">
+        <v>11</v>
+      </c>
+      <c r="BD99">
+        <v>3.65</v>
+      </c>
+      <c r="BE99">
+        <v>8</v>
+      </c>
+      <c r="BF99">
+        <v>1.3</v>
+      </c>
+      <c r="BG99">
+        <v>1.14</v>
+      </c>
+      <c r="BH99">
+        <v>4.8</v>
+      </c>
+      <c r="BI99">
+        <v>1.26</v>
+      </c>
+      <c r="BJ99">
+        <v>3.4</v>
+      </c>
+      <c r="BK99">
+        <v>1.44</v>
+      </c>
+      <c r="BL99">
+        <v>2.55</v>
+      </c>
+      <c r="BM99">
+        <v>1.7</v>
+      </c>
+      <c r="BN99">
+        <v>2.02</v>
+      </c>
+      <c r="BO99">
+        <v>2.05</v>
+      </c>
+      <c r="BP99">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:68">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>7785275</v>
+      </c>
+      <c r="C100" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45843.70833333334</v>
+      </c>
+      <c r="F100">
+        <v>12</v>
+      </c>
+      <c r="G100" t="s">
+        <v>76</v>
+      </c>
+      <c r="H100" t="s">
+        <v>75</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>156</v>
+      </c>
+      <c r="P100" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q100">
+        <v>2.88</v>
+      </c>
+      <c r="R100">
+        <v>2.25</v>
+      </c>
+      <c r="S100">
+        <v>3.5</v>
+      </c>
+      <c r="T100">
+        <v>1.33</v>
+      </c>
+      <c r="U100">
+        <v>3.25</v>
+      </c>
+      <c r="V100">
+        <v>2.63</v>
+      </c>
+      <c r="W100">
+        <v>1.44</v>
+      </c>
+      <c r="X100">
+        <v>7</v>
+      </c>
+      <c r="Y100">
+        <v>1.1</v>
+      </c>
+      <c r="Z100">
+        <v>2.25</v>
+      </c>
+      <c r="AA100">
+        <v>3.25</v>
+      </c>
+      <c r="AB100">
+        <v>2.72</v>
+      </c>
+      <c r="AC100">
+        <v>1.05</v>
+      </c>
+      <c r="AD100">
+        <v>9.5</v>
+      </c>
+      <c r="AE100">
+        <v>1.25</v>
+      </c>
+      <c r="AF100">
         <v>3.75</v>
       </c>
-      <c r="AG78">
+      <c r="AG100">
         <v>1.78</v>
       </c>
-      <c r="AH78">
+      <c r="AH100">
         <v>1.92</v>
       </c>
-      <c r="AI78">
+      <c r="AI100">
         <v>1.67</v>
       </c>
-      <c r="AJ78">
+      <c r="AJ100">
         <v>2.1</v>
       </c>
-      <c r="AK78">
+      <c r="AK100">
         <v>1.38</v>
       </c>
-      <c r="AL78">
+      <c r="AL100">
         <v>1.25</v>
       </c>
-      <c r="AM78">
+      <c r="AM100">
         <v>1.6</v>
       </c>
-      <c r="AN78">
+      <c r="AN100">
         <v>1.8</v>
       </c>
-      <c r="AO78">
-        <v>1.4</v>
-      </c>
-      <c r="AP78">
-        <v>2</v>
-      </c>
-      <c r="AQ78">
-        <v>1.17</v>
-      </c>
-      <c r="AR78">
+      <c r="AO100">
+        <v>1.67</v>
+      </c>
+      <c r="AP100">
+        <v>2</v>
+      </c>
+      <c r="AQ100">
+        <v>1.43</v>
+      </c>
+      <c r="AR100">
         <v>1.54</v>
       </c>
-      <c r="AS78">
-        <v>1.51</v>
-      </c>
-      <c r="AT78">
+      <c r="AS100">
+        <v>1.59</v>
+      </c>
+      <c r="AT100">
+        <v>3.13</v>
+      </c>
+      <c r="AU100">
+        <v>3</v>
+      </c>
+      <c r="AV100">
+        <v>0</v>
+      </c>
+      <c r="AW100">
+        <v>2</v>
+      </c>
+      <c r="AX100">
+        <v>0</v>
+      </c>
+      <c r="AY100">
+        <v>5</v>
+      </c>
+      <c r="AZ100">
+        <v>0</v>
+      </c>
+      <c r="BA100">
+        <v>2</v>
+      </c>
+      <c r="BB100">
+        <v>2</v>
+      </c>
+      <c r="BC100">
+        <v>4</v>
+      </c>
+      <c r="BD100">
+        <v>1.81</v>
+      </c>
+      <c r="BE100">
+        <v>6.75</v>
+      </c>
+      <c r="BF100">
+        <v>2.17</v>
+      </c>
+      <c r="BG100">
+        <v>1.3</v>
+      </c>
+      <c r="BH100">
         <v>3.05</v>
       </c>
-      <c r="AU78">
-        <v>3</v>
-      </c>
-      <c r="AV78">
-        <v>0</v>
-      </c>
-      <c r="AW78">
-        <v>2</v>
-      </c>
-      <c r="AX78">
-        <v>0</v>
-      </c>
-      <c r="AY78">
-        <v>5</v>
-      </c>
-      <c r="AZ78">
-        <v>0</v>
-      </c>
-      <c r="BA78">
-        <v>2</v>
-      </c>
-      <c r="BB78">
-        <v>2</v>
-      </c>
-      <c r="BC78">
-        <v>4</v>
-      </c>
-      <c r="BD78">
-        <v>1.81</v>
-      </c>
-      <c r="BE78">
-        <v>6.75</v>
-      </c>
-      <c r="BF78">
-        <v>2.17</v>
-      </c>
-      <c r="BG78">
-        <v>1.3</v>
-      </c>
-      <c r="BH78">
-        <v>3.05</v>
-      </c>
-      <c r="BI78">
+      <c r="BI100">
         <v>1.52</v>
       </c>
-      <c r="BJ78">
+      <c r="BJ100">
         <v>2.32</v>
       </c>
-      <c r="BK78">
+      <c r="BK100">
         <v>1.85</v>
       </c>
-      <c r="BL78">
+      <c r="BL100">
         <v>1.83</v>
       </c>
-      <c r="BM78">
+      <c r="BM100">
         <v>2.32</v>
       </c>
-      <c r="BN78">
+      <c r="BN100">
         <v>1.53</v>
       </c>
-      <c r="BO78">
+      <c r="BO100">
         <v>2.95</v>
       </c>
-      <c r="BP78">
+      <c r="BP100">
         <v>1.33</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="222">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -487,6 +487,12 @@
     <t>['80']</t>
   </si>
   <si>
+    <t>['27', '39']</t>
+  </si>
+  <si>
+    <t>['46', '75', '85']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -668,6 +674,12 @@
   </si>
   <si>
     <t>['4']</t>
+  </si>
+  <si>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['53']</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP100"/>
+  <dimension ref="A1:BP103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1285,7 +1297,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1366,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1697,7 +1709,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1903,7 +1915,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2109,7 +2121,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2187,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ6">
         <v>0.5</v>
@@ -2315,7 +2327,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -3551,7 +3563,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3629,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13">
         <v>1.43</v>
@@ -3963,7 +3975,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4169,7 +4181,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4250,7 +4262,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ16">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4375,7 +4387,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4787,7 +4799,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4993,7 +5005,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5199,7 +5211,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5405,7 +5417,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5486,7 +5498,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ22">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR22">
         <v>1.7</v>
@@ -5611,7 +5623,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5817,7 +5829,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6023,7 +6035,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6229,7 +6241,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6435,7 +6447,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6513,7 +6525,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27">
         <v>2</v>
@@ -6641,7 +6653,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7259,7 +7271,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7340,7 +7352,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ31">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR31">
         <v>1.79</v>
@@ -7671,7 +7683,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8083,7 +8095,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8161,7 +8173,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8289,7 +8301,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8495,7 +8507,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8701,7 +8713,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9113,7 +9125,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9525,7 +9537,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9731,7 +9743,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10224,7 +10236,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ45">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR45">
         <v>2.27</v>
@@ -10430,7 +10442,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ46">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR46">
         <v>1.95</v>
@@ -10555,7 +10567,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10761,7 +10773,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10839,7 +10851,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ48">
         <v>2.17</v>
@@ -11173,7 +11185,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11457,7 +11469,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ51">
         <v>0.83</v>
@@ -11585,7 +11597,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11791,7 +11803,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12409,7 +12421,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12615,7 +12627,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12696,7 +12708,7 @@
         <v>0</v>
       </c>
       <c r="AQ57">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -12821,7 +12833,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13233,7 +13245,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13439,7 +13451,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13726,7 +13738,7 @@
         <v>2</v>
       </c>
       <c r="AQ62">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR62">
         <v>2.13</v>
@@ -13851,7 +13863,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14135,7 +14147,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ64">
         <v>2.17</v>
@@ -14263,7 +14275,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14469,7 +14481,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14675,7 +14687,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14881,7 +14893,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -14959,7 +14971,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ68">
         <v>1.43</v>
@@ -15087,7 +15099,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15168,7 +15180,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ69">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR69">
         <v>1.11</v>
@@ -15293,7 +15305,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15499,7 +15511,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15705,7 +15717,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15911,7 +15923,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16117,7 +16129,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16323,7 +16335,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16529,7 +16541,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16735,7 +16747,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16941,7 +16953,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17147,7 +17159,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17559,7 +17571,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17971,7 +17983,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18052,7 +18064,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ83">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18177,7 +18189,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18255,10 +18267,10 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ84">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AR84">
         <v>1.74</v>
@@ -18383,7 +18395,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18667,7 +18679,7 @@
         <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AQ86">
         <v>1</v>
@@ -19001,7 +19013,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19413,7 +19425,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19619,7 +19631,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19825,7 +19837,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20031,7 +20043,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20237,7 +20249,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20649,7 +20661,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21061,7 +21073,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21267,7 +21279,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21630,6 +21642,624 @@
       </c>
       <c r="BP100">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="101" spans="1:68">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>7785273</v>
+      </c>
+      <c r="C101" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" t="s">
+        <v>69</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45844.39583333334</v>
+      </c>
+      <c r="F101">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>82</v>
+      </c>
+      <c r="H101" t="s">
+        <v>79</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>2</v>
+      </c>
+      <c r="O101" t="s">
+        <v>157</v>
+      </c>
+      <c r="P101" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q101">
+        <v>3.1</v>
+      </c>
+      <c r="R101">
+        <v>2.2</v>
+      </c>
+      <c r="S101">
+        <v>2.95</v>
+      </c>
+      <c r="T101">
+        <v>1.3</v>
+      </c>
+      <c r="U101">
+        <v>3.2</v>
+      </c>
+      <c r="V101">
+        <v>2.4</v>
+      </c>
+      <c r="W101">
+        <v>1.5</v>
+      </c>
+      <c r="X101">
+        <v>5.45</v>
+      </c>
+      <c r="Y101">
+        <v>1.08</v>
+      </c>
+      <c r="Z101">
+        <v>2.5</v>
+      </c>
+      <c r="AA101">
+        <v>3.37</v>
+      </c>
+      <c r="AB101">
+        <v>2.36</v>
+      </c>
+      <c r="AC101">
+        <v>1.04</v>
+      </c>
+      <c r="AD101">
+        <v>10</v>
+      </c>
+      <c r="AE101">
+        <v>1.22</v>
+      </c>
+      <c r="AF101">
+        <v>4.2</v>
+      </c>
+      <c r="AG101">
+        <v>1.61</v>
+      </c>
+      <c r="AH101">
+        <v>2.1</v>
+      </c>
+      <c r="AI101">
+        <v>1.5</v>
+      </c>
+      <c r="AJ101">
+        <v>2.35</v>
+      </c>
+      <c r="AK101">
+        <v>1.5</v>
+      </c>
+      <c r="AL101">
+        <v>1.25</v>
+      </c>
+      <c r="AM101">
+        <v>1.48</v>
+      </c>
+      <c r="AN101">
+        <v>3</v>
+      </c>
+      <c r="AO101">
+        <v>1.67</v>
+      </c>
+      <c r="AP101">
+        <v>3</v>
+      </c>
+      <c r="AQ101">
+        <v>1.43</v>
+      </c>
+      <c r="AR101">
+        <v>2.06</v>
+      </c>
+      <c r="AS101">
+        <v>1.31</v>
+      </c>
+      <c r="AT101">
+        <v>3.37</v>
+      </c>
+      <c r="AU101">
+        <v>8</v>
+      </c>
+      <c r="AV101">
+        <v>3</v>
+      </c>
+      <c r="AW101">
+        <v>6</v>
+      </c>
+      <c r="AX101">
+        <v>9</v>
+      </c>
+      <c r="AY101">
+        <v>14</v>
+      </c>
+      <c r="AZ101">
+        <v>12</v>
+      </c>
+      <c r="BA101">
+        <v>2</v>
+      </c>
+      <c r="BB101">
+        <v>3</v>
+      </c>
+      <c r="BC101">
+        <v>5</v>
+      </c>
+      <c r="BD101">
+        <v>2.17</v>
+      </c>
+      <c r="BE101">
+        <v>6.75</v>
+      </c>
+      <c r="BF101">
+        <v>1.81</v>
+      </c>
+      <c r="BG101">
+        <v>1.24</v>
+      </c>
+      <c r="BH101">
+        <v>3.55</v>
+      </c>
+      <c r="BI101">
+        <v>1.43</v>
+      </c>
+      <c r="BJ101">
+        <v>2.55</v>
+      </c>
+      <c r="BK101">
+        <v>1.7</v>
+      </c>
+      <c r="BL101">
+        <v>2</v>
+      </c>
+      <c r="BM101">
+        <v>2.08</v>
+      </c>
+      <c r="BN101">
+        <v>1.65</v>
+      </c>
+      <c r="BO101">
+        <v>2.65</v>
+      </c>
+      <c r="BP101">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="102" spans="1:68">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>7785274</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="2">
+        <v>45844.39583333334</v>
+      </c>
+      <c r="F102">
+        <v>12</v>
+      </c>
+      <c r="G102" t="s">
+        <v>81</v>
+      </c>
+      <c r="H102" t="s">
+        <v>83</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>3</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>4</v>
+      </c>
+      <c r="O102" t="s">
+        <v>158</v>
+      </c>
+      <c r="P102" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q102">
+        <v>1.73</v>
+      </c>
+      <c r="R102">
+        <v>2.75</v>
+      </c>
+      <c r="S102">
+        <v>7</v>
+      </c>
+      <c r="T102">
+        <v>1.22</v>
+      </c>
+      <c r="U102">
+        <v>4</v>
+      </c>
+      <c r="V102">
+        <v>2</v>
+      </c>
+      <c r="W102">
+        <v>1.73</v>
+      </c>
+      <c r="X102">
+        <v>4.33</v>
+      </c>
+      <c r="Y102">
+        <v>1.2</v>
+      </c>
+      <c r="Z102">
+        <v>1.27</v>
+      </c>
+      <c r="AA102">
+        <v>4.9</v>
+      </c>
+      <c r="AB102">
+        <v>7.7</v>
+      </c>
+      <c r="AC102">
+        <v>1.01</v>
+      </c>
+      <c r="AD102">
+        <v>16.5</v>
+      </c>
+      <c r="AE102">
+        <v>1.12</v>
+      </c>
+      <c r="AF102">
+        <v>6.24</v>
+      </c>
+      <c r="AG102">
+        <v>1.42</v>
+      </c>
+      <c r="AH102">
+        <v>2.65</v>
+      </c>
+      <c r="AI102">
+        <v>1.75</v>
+      </c>
+      <c r="AJ102">
+        <v>2</v>
+      </c>
+      <c r="AK102">
+        <v>1.07</v>
+      </c>
+      <c r="AL102">
+        <v>1.11</v>
+      </c>
+      <c r="AM102">
+        <v>3.2</v>
+      </c>
+      <c r="AN102">
+        <v>1</v>
+      </c>
+      <c r="AO102">
+        <v>0</v>
+      </c>
+      <c r="AP102">
+        <v>1.33</v>
+      </c>
+      <c r="AQ102">
+        <v>0</v>
+      </c>
+      <c r="AR102">
+        <v>1.65</v>
+      </c>
+      <c r="AS102">
+        <v>1.17</v>
+      </c>
+      <c r="AT102">
+        <v>2.82</v>
+      </c>
+      <c r="AU102">
+        <v>9</v>
+      </c>
+      <c r="AV102">
+        <v>5</v>
+      </c>
+      <c r="AW102">
+        <v>8</v>
+      </c>
+      <c r="AX102">
+        <v>8</v>
+      </c>
+      <c r="AY102">
+        <v>17</v>
+      </c>
+      <c r="AZ102">
+        <v>13</v>
+      </c>
+      <c r="BA102">
+        <v>19</v>
+      </c>
+      <c r="BB102">
+        <v>1</v>
+      </c>
+      <c r="BC102">
+        <v>20</v>
+      </c>
+      <c r="BD102">
+        <v>1.26</v>
+      </c>
+      <c r="BE102">
+        <v>8</v>
+      </c>
+      <c r="BF102">
+        <v>4.1</v>
+      </c>
+      <c r="BG102">
+        <v>1.19</v>
+      </c>
+      <c r="BH102">
+        <v>4.1</v>
+      </c>
+      <c r="BI102">
+        <v>1.32</v>
+      </c>
+      <c r="BJ102">
+        <v>3.05</v>
+      </c>
+      <c r="BK102">
+        <v>1.53</v>
+      </c>
+      <c r="BL102">
+        <v>2.3</v>
+      </c>
+      <c r="BM102">
+        <v>1.84</v>
+      </c>
+      <c r="BN102">
+        <v>1.84</v>
+      </c>
+      <c r="BO102">
+        <v>2.28</v>
+      </c>
+      <c r="BP102">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:68">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>7785271</v>
+      </c>
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45844.39583333334</v>
+      </c>
+      <c r="F103">
+        <v>12</v>
+      </c>
+      <c r="G103" t="s">
+        <v>74</v>
+      </c>
+      <c r="H103" t="s">
+        <v>77</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>1</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>2</v>
+      </c>
+      <c r="O103" t="s">
+        <v>124</v>
+      </c>
+      <c r="P103" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q103">
+        <v>2.38</v>
+      </c>
+      <c r="R103">
+        <v>2.2</v>
+      </c>
+      <c r="S103">
+        <v>5</v>
+      </c>
+      <c r="T103">
+        <v>1.44</v>
+      </c>
+      <c r="U103">
+        <v>2.63</v>
+      </c>
+      <c r="V103">
+        <v>3</v>
+      </c>
+      <c r="W103">
+        <v>1.36</v>
+      </c>
+      <c r="X103">
+        <v>9</v>
+      </c>
+      <c r="Y103">
+        <v>1.07</v>
+      </c>
+      <c r="Z103">
+        <v>1.74</v>
+      </c>
+      <c r="AA103">
+        <v>3.27</v>
+      </c>
+      <c r="AB103">
+        <v>4.2</v>
+      </c>
+      <c r="AC103">
+        <v>1.01</v>
+      </c>
+      <c r="AD103">
+        <v>8.6</v>
+      </c>
+      <c r="AE103">
+        <v>1.35</v>
+      </c>
+      <c r="AF103">
+        <v>3.21</v>
+      </c>
+      <c r="AG103">
+        <v>1.96</v>
+      </c>
+      <c r="AH103">
+        <v>1.74</v>
+      </c>
+      <c r="AI103">
+        <v>1.95</v>
+      </c>
+      <c r="AJ103">
+        <v>1.8</v>
+      </c>
+      <c r="AK103">
+        <v>1.2</v>
+      </c>
+      <c r="AL103">
+        <v>1.25</v>
+      </c>
+      <c r="AM103">
+        <v>1.95</v>
+      </c>
+      <c r="AN103">
+        <v>1.2</v>
+      </c>
+      <c r="AO103">
+        <v>0.8</v>
+      </c>
+      <c r="AP103">
+        <v>1.17</v>
+      </c>
+      <c r="AQ103">
+        <v>0.83</v>
+      </c>
+      <c r="AR103">
+        <v>1.27</v>
+      </c>
+      <c r="AS103">
+        <v>1.1</v>
+      </c>
+      <c r="AT103">
+        <v>2.37</v>
+      </c>
+      <c r="AU103">
+        <v>5</v>
+      </c>
+      <c r="AV103">
+        <v>5</v>
+      </c>
+      <c r="AW103">
+        <v>10</v>
+      </c>
+      <c r="AX103">
+        <v>2</v>
+      </c>
+      <c r="AY103">
+        <v>15</v>
+      </c>
+      <c r="AZ103">
+        <v>7</v>
+      </c>
+      <c r="BA103">
+        <v>7</v>
+      </c>
+      <c r="BB103">
+        <v>2</v>
+      </c>
+      <c r="BC103">
+        <v>9</v>
+      </c>
+      <c r="BD103">
+        <v>1.48</v>
+      </c>
+      <c r="BE103">
+        <v>7</v>
+      </c>
+      <c r="BF103">
+        <v>2.9</v>
+      </c>
+      <c r="BG103">
+        <v>1.28</v>
+      </c>
+      <c r="BH103">
+        <v>3.2</v>
+      </c>
+      <c r="BI103">
+        <v>1.49</v>
+      </c>
+      <c r="BJ103">
+        <v>2.4</v>
+      </c>
+      <c r="BK103">
+        <v>1.79</v>
+      </c>
+      <c r="BL103">
+        <v>1.9</v>
+      </c>
+      <c r="BM103">
+        <v>2.23</v>
+      </c>
+      <c r="BN103">
+        <v>1.56</v>
+      </c>
+      <c r="BO103">
+        <v>2.9</v>
+      </c>
+      <c r="BP103">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -491,6 +491,9 @@
   </si>
   <si>
     <t>['46', '75', '85']</t>
+  </si>
+  <si>
+    <t>['59', '68']</t>
   </si>
   <si>
     <t>['39', '49']</t>
@@ -1041,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP103"/>
+  <dimension ref="A1:BP104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1297,7 +1300,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1709,7 +1712,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1915,7 +1918,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2121,7 +2124,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2202,7 +2205,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ6">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2327,7 +2330,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -3023,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ10">
         <v>0.83</v>
@@ -3563,7 +3566,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3975,7 +3978,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4181,7 +4184,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4387,7 +4390,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4799,7 +4802,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5005,7 +5008,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5211,7 +5214,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5417,7 +5420,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5623,7 +5626,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5829,7 +5832,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6035,7 +6038,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6116,7 +6119,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ25">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR25">
         <v>1.21</v>
@@ -6241,7 +6244,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6447,7 +6450,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6653,7 +6656,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7143,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30">
         <v>0.83</v>
@@ -7271,7 +7274,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7683,7 +7686,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8095,7 +8098,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8301,7 +8304,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8507,7 +8510,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8713,7 +8716,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9125,7 +9128,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9537,7 +9540,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9618,7 +9621,7 @@
         <v>2</v>
       </c>
       <c r="AQ42">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR42">
         <v>1.9</v>
@@ -9743,7 +9746,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10567,7 +10570,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10773,7 +10776,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11185,7 +11188,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11597,7 +11600,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11803,7 +11806,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11884,7 +11887,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR53">
         <v>2.55</v>
@@ -12421,7 +12424,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12627,7 +12630,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12833,7 +12836,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13245,7 +13248,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13451,7 +13454,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13735,7 +13738,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ62">
         <v>1.43</v>
@@ -13863,7 +13866,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14275,7 +14278,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14481,7 +14484,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14687,7 +14690,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14893,7 +14896,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15099,7 +15102,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15305,7 +15308,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15383,7 +15386,7 @@
         <v>2.25</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ70">
         <v>2.29</v>
@@ -15511,7 +15514,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15717,7 +15720,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15923,7 +15926,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16129,7 +16132,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16335,7 +16338,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16541,7 +16544,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16622,7 +16625,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ76">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR76">
         <v>1.53</v>
@@ -16747,7 +16750,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16953,7 +16956,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17159,7 +17162,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17443,7 +17446,7 @@
         <v>2.25</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ80">
         <v>1.67</v>
@@ -17571,7 +17574,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17983,7 +17986,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18189,7 +18192,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18395,7 +18398,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19013,7 +19016,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19425,7 +19428,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19503,7 +19506,7 @@
         <v>1.8</v>
       </c>
       <c r="AP90">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ90">
         <v>2</v>
@@ -19631,7 +19634,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19837,7 +19840,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20043,7 +20046,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20249,7 +20252,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20536,7 +20539,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ95">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR95">
         <v>1.99</v>
@@ -20661,7 +20664,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21073,7 +21076,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21279,7 +21282,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21897,7 +21900,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22103,7 +22106,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22260,6 +22263,212 @@
       </c>
       <c r="BP103">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:68">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>7785278</v>
+      </c>
+      <c r="C104" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="2">
+        <v>45850.45833333334</v>
+      </c>
+      <c r="F104">
+        <v>13</v>
+      </c>
+      <c r="G104" t="s">
+        <v>78</v>
+      </c>
+      <c r="H104" t="s">
+        <v>82</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>2</v>
+      </c>
+      <c r="O104" t="s">
+        <v>159</v>
+      </c>
+      <c r="P104" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q104">
+        <v>1.62</v>
+      </c>
+      <c r="R104">
+        <v>3.1</v>
+      </c>
+      <c r="S104">
+        <v>8</v>
+      </c>
+      <c r="T104">
+        <v>1.18</v>
+      </c>
+      <c r="U104">
+        <v>4.5</v>
+      </c>
+      <c r="V104">
+        <v>1.83</v>
+      </c>
+      <c r="W104">
+        <v>1.83</v>
+      </c>
+      <c r="X104">
+        <v>3.75</v>
+      </c>
+      <c r="Y104">
+        <v>1.25</v>
+      </c>
+      <c r="Z104">
+        <v>1.26</v>
+      </c>
+      <c r="AA104">
+        <v>5.1</v>
+      </c>
+      <c r="AB104">
+        <v>7.8</v>
+      </c>
+      <c r="AC104">
+        <v>1.01</v>
+      </c>
+      <c r="AD104">
+        <v>29</v>
+      </c>
+      <c r="AE104">
+        <v>1.08</v>
+      </c>
+      <c r="AF104">
+        <v>7.5</v>
+      </c>
+      <c r="AG104">
+        <v>1.3</v>
+      </c>
+      <c r="AH104">
+        <v>3.33</v>
+      </c>
+      <c r="AI104">
+        <v>1.67</v>
+      </c>
+      <c r="AJ104">
+        <v>2.1</v>
+      </c>
+      <c r="AK104">
+        <v>1.05</v>
+      </c>
+      <c r="AL104">
+        <v>1.11</v>
+      </c>
+      <c r="AM104">
+        <v>3.75</v>
+      </c>
+      <c r="AN104">
+        <v>2</v>
+      </c>
+      <c r="AO104">
+        <v>0.5</v>
+      </c>
+      <c r="AP104">
+        <v>2.14</v>
+      </c>
+      <c r="AQ104">
+        <v>0.43</v>
+      </c>
+      <c r="AR104">
+        <v>2.38</v>
+      </c>
+      <c r="AS104">
+        <v>1.53</v>
+      </c>
+      <c r="AT104">
+        <v>3.91</v>
+      </c>
+      <c r="AU104">
+        <v>6</v>
+      </c>
+      <c r="AV104">
+        <v>2</v>
+      </c>
+      <c r="AW104">
+        <v>9</v>
+      </c>
+      <c r="AX104">
+        <v>1</v>
+      </c>
+      <c r="AY104">
+        <v>15</v>
+      </c>
+      <c r="AZ104">
+        <v>3</v>
+      </c>
+      <c r="BA104">
+        <v>4</v>
+      </c>
+      <c r="BB104">
+        <v>1</v>
+      </c>
+      <c r="BC104">
+        <v>5</v>
+      </c>
+      <c r="BD104">
+        <v>1.14</v>
+      </c>
+      <c r="BE104">
+        <v>12</v>
+      </c>
+      <c r="BF104">
+        <v>6.5</v>
+      </c>
+      <c r="BG104">
+        <v>1.2</v>
+      </c>
+      <c r="BH104">
+        <v>3.9</v>
+      </c>
+      <c r="BI104">
+        <v>1.38</v>
+      </c>
+      <c r="BJ104">
+        <v>2.8</v>
+      </c>
+      <c r="BK104">
+        <v>1.64</v>
+      </c>
+      <c r="BL104">
+        <v>2.18</v>
+      </c>
+      <c r="BM104">
+        <v>2.01</v>
+      </c>
+      <c r="BN104">
+        <v>1.75</v>
+      </c>
+      <c r="BO104">
+        <v>2.5</v>
+      </c>
+      <c r="BP104">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -496,6 +496,9 @@
     <t>['59', '68']</t>
   </si>
   <si>
+    <t>['81', '85', '88', '90+9']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -683,6 +686,9 @@
   </si>
   <si>
     <t>['53']</t>
+  </si>
+  <si>
+    <t>['4', '63']</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP104"/>
+  <dimension ref="A1:BP105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1300,7 +1306,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1584,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ3">
         <v>1.67</v>
@@ -1712,7 +1718,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1918,7 +1924,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2124,7 +2130,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2330,7 +2336,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -3566,7 +3572,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3853,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="AQ14">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3978,7 +3984,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4184,7 +4190,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4390,7 +4396,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4674,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
         <v>1.43</v>
@@ -4802,7 +4808,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5008,7 +5014,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5214,7 +5220,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5420,7 +5426,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5626,7 +5632,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5832,7 +5838,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6038,7 +6044,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6116,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>0.43</v>
@@ -6244,7 +6250,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6450,7 +6456,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6656,7 +6662,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6943,7 +6949,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ29">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR29">
         <v>1.99</v>
@@ -7274,7 +7280,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7686,7 +7692,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8098,7 +8104,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8304,7 +8310,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8510,7 +8516,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8716,7 +8722,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9128,7 +9134,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9540,7 +9546,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9746,7 +9752,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10570,7 +10576,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10651,7 +10657,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ47">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR47">
         <v>1.44</v>
@@ -10776,7 +10782,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11188,7 +11194,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11600,7 +11606,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11806,7 +11812,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12424,7 +12430,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12630,7 +12636,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12836,7 +12842,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13120,7 +13126,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ59">
         <v>0.83</v>
@@ -13248,7 +13254,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13454,7 +13460,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13866,7 +13872,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13947,7 +13953,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ63">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.3</v>
@@ -14278,7 +14284,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14484,7 +14490,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14690,7 +14696,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14896,7 +14902,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15102,7 +15108,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15180,7 +15186,7 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ69">
         <v>1.43</v>
@@ -15308,7 +15314,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15514,7 +15520,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15595,7 +15601,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ71">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR71">
         <v>1.99</v>
@@ -15720,7 +15726,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15926,7 +15932,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16132,7 +16138,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16210,7 +16216,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16338,7 +16344,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16544,7 +16550,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16750,7 +16756,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16956,7 +16962,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17162,7 +17168,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17574,7 +17580,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17655,7 +17661,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ81">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR81">
         <v>2.19</v>
@@ -17986,7 +17992,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18192,7 +18198,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18398,7 +18404,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19016,7 +19022,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19428,7 +19434,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19634,7 +19640,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19840,7 +19846,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -19918,7 +19924,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ92">
         <v>2.17</v>
@@ -20046,7 +20052,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20252,7 +20258,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20664,7 +20670,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21076,7 +21082,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21282,7 +21288,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21569,7 +21575,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR100">
         <v>1.54</v>
@@ -21900,7 +21906,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22106,7 +22112,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22405,31 +22411,31 @@
         <v>3.91</v>
       </c>
       <c r="AU104">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV104">
         <v>2</v>
       </c>
       <c r="AW104">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AX104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY104">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AZ104">
+        <v>4</v>
+      </c>
+      <c r="BA104">
         <v>3</v>
       </c>
-      <c r="BA104">
+      <c r="BB104">
+        <v>1</v>
+      </c>
+      <c r="BC104">
         <v>4</v>
-      </c>
-      <c r="BB104">
-        <v>1</v>
-      </c>
-      <c r="BC104">
-        <v>5</v>
       </c>
       <c r="BD104">
         <v>1.14</v>
@@ -22469,6 +22475,212 @@
       </c>
       <c r="BP104">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="105" spans="1:68">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>7785281</v>
+      </c>
+      <c r="C105" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45850.54166666666</v>
+      </c>
+      <c r="F105">
+        <v>13</v>
+      </c>
+      <c r="G105" t="s">
+        <v>71</v>
+      </c>
+      <c r="H105" t="s">
+        <v>75</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
+        <v>1</v>
+      </c>
+      <c r="L105">
+        <v>4</v>
+      </c>
+      <c r="M105">
+        <v>2</v>
+      </c>
+      <c r="N105">
+        <v>6</v>
+      </c>
+      <c r="O105" t="s">
+        <v>160</v>
+      </c>
+      <c r="P105" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q105">
+        <v>3.1</v>
+      </c>
+      <c r="R105">
+        <v>2.2</v>
+      </c>
+      <c r="S105">
+        <v>3.4</v>
+      </c>
+      <c r="T105">
+        <v>1.4</v>
+      </c>
+      <c r="U105">
+        <v>2.75</v>
+      </c>
+      <c r="V105">
+        <v>2.75</v>
+      </c>
+      <c r="W105">
+        <v>1.4</v>
+      </c>
+      <c r="X105">
+        <v>8</v>
+      </c>
+      <c r="Y105">
+        <v>1.08</v>
+      </c>
+      <c r="Z105">
+        <v>2.62</v>
+      </c>
+      <c r="AA105">
+        <v>3.1</v>
+      </c>
+      <c r="AB105">
+        <v>2.41</v>
+      </c>
+      <c r="AC105">
+        <v>1.06</v>
+      </c>
+      <c r="AD105">
+        <v>8.5</v>
+      </c>
+      <c r="AE105">
+        <v>1.33</v>
+      </c>
+      <c r="AF105">
+        <v>3.3</v>
+      </c>
+      <c r="AG105">
+        <v>1.89</v>
+      </c>
+      <c r="AH105">
+        <v>1.81</v>
+      </c>
+      <c r="AI105">
+        <v>1.75</v>
+      </c>
+      <c r="AJ105">
+        <v>2</v>
+      </c>
+      <c r="AK105">
+        <v>1.44</v>
+      </c>
+      <c r="AL105">
+        <v>1.25</v>
+      </c>
+      <c r="AM105">
+        <v>1.5</v>
+      </c>
+      <c r="AN105">
+        <v>1.86</v>
+      </c>
+      <c r="AO105">
+        <v>1.43</v>
+      </c>
+      <c r="AP105">
+        <v>2</v>
+      </c>
+      <c r="AQ105">
+        <v>1.25</v>
+      </c>
+      <c r="AR105">
+        <v>1.24</v>
+      </c>
+      <c r="AS105">
+        <v>1.36</v>
+      </c>
+      <c r="AT105">
+        <v>2.6</v>
+      </c>
+      <c r="AU105">
+        <v>8</v>
+      </c>
+      <c r="AV105">
+        <v>8</v>
+      </c>
+      <c r="AW105">
+        <v>7</v>
+      </c>
+      <c r="AX105">
+        <v>4</v>
+      </c>
+      <c r="AY105">
+        <v>15</v>
+      </c>
+      <c r="AZ105">
+        <v>12</v>
+      </c>
+      <c r="BA105">
+        <v>7</v>
+      </c>
+      <c r="BB105">
+        <v>4</v>
+      </c>
+      <c r="BC105">
+        <v>11</v>
+      </c>
+      <c r="BD105">
+        <v>1.91</v>
+      </c>
+      <c r="BE105">
+        <v>8</v>
+      </c>
+      <c r="BF105">
+        <v>2.2</v>
+      </c>
+      <c r="BG105">
+        <v>1.22</v>
+      </c>
+      <c r="BH105">
+        <v>3.7</v>
+      </c>
+      <c r="BI105">
+        <v>1.42</v>
+      </c>
+      <c r="BJ105">
+        <v>2.67</v>
+      </c>
+      <c r="BK105">
+        <v>1.69</v>
+      </c>
+      <c r="BL105">
+        <v>2.09</v>
+      </c>
+      <c r="BM105">
+        <v>2.09</v>
+      </c>
+      <c r="BN105">
+        <v>1.69</v>
+      </c>
+      <c r="BO105">
+        <v>2.62</v>
+      </c>
+      <c r="BP105">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -497,6 +497,9 @@
   </si>
   <si>
     <t>['81', '85', '88', '90+9']</t>
+  </si>
+  <si>
+    <t>['76']</t>
   </si>
   <si>
     <t>['39', '49']</t>
@@ -1050,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP105"/>
+  <dimension ref="A1:BP106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1306,7 +1309,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1718,7 +1721,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1924,7 +1927,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2130,7 +2133,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2336,7 +2339,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2826,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ9">
         <v>1.6</v>
@@ -3572,7 +3575,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3653,7 +3656,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ13">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3984,7 +3987,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4190,7 +4193,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4396,7 +4399,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4683,7 +4686,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
         <v>0.92</v>
@@ -4808,7 +4811,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5014,7 +5017,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5220,7 +5223,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5426,7 +5429,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5632,7 +5635,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5838,7 +5841,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -5916,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ24">
         <v>0</v>
@@ -6044,7 +6047,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6250,7 +6253,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6456,7 +6459,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6662,7 +6665,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7280,7 +7283,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7692,7 +7695,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7773,7 +7776,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ33">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR33">
         <v>1.87</v>
@@ -8104,7 +8107,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8310,7 +8313,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8516,7 +8519,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8722,7 +8725,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9134,7 +9137,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9546,7 +9549,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9752,7 +9755,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10576,7 +10579,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10654,7 +10657,7 @@
         <v>0.5</v>
       </c>
       <c r="AP47">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ47">
         <v>1.25</v>
@@ -10782,7 +10785,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11194,7 +11197,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11275,7 +11278,7 @@
         <v>3</v>
       </c>
       <c r="AQ50">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR50">
         <v>2.16</v>
@@ -11606,7 +11609,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11812,7 +11815,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12430,7 +12433,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12636,7 +12639,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12842,7 +12845,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13254,7 +13257,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13460,7 +13463,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13538,7 +13541,7 @@
         <v>1.33</v>
       </c>
       <c r="AP61">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ61">
         <v>0.83</v>
@@ -13872,7 +13875,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14284,7 +14287,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14490,7 +14493,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14696,7 +14699,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14902,7 +14905,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -14983,7 +14986,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ68">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR68">
         <v>1.1</v>
@@ -15108,7 +15111,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15314,7 +15317,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15520,7 +15523,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15726,7 +15729,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15932,7 +15935,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16013,7 +16016,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR73">
         <v>1.54</v>
@@ -16138,7 +16141,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16344,7 +16347,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16550,7 +16553,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16628,7 +16631,7 @@
         <v>0.75</v>
       </c>
       <c r="AP76">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ76">
         <v>0.43</v>
@@ -16756,7 +16759,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16962,7 +16965,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17168,7 +17171,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17580,7 +17583,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17992,7 +17995,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18198,7 +18201,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18404,7 +18407,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19022,7 +19025,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19434,7 +19437,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19640,7 +19643,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19718,7 +19721,7 @@
         <v>0.8</v>
       </c>
       <c r="AP91">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91">
         <v>0.83</v>
@@ -19846,7 +19849,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20052,7 +20055,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20258,7 +20261,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20339,7 +20342,7 @@
         <v>0</v>
       </c>
       <c r="AQ94">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR94">
         <v>1.63</v>
@@ -20670,7 +20673,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21082,7 +21085,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21288,7 +21291,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21906,7 +21909,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22112,7 +22115,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22524,7 +22527,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22681,6 +22684,212 @@
       </c>
       <c r="BP105">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="106" spans="1:68">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7785280</v>
+      </c>
+      <c r="C106" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" t="s">
+        <v>69</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45851.39583333334</v>
+      </c>
+      <c r="F106">
+        <v>13</v>
+      </c>
+      <c r="G106" t="s">
+        <v>77</v>
+      </c>
+      <c r="H106" t="s">
+        <v>72</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>161</v>
+      </c>
+      <c r="P106" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q106">
+        <v>3</v>
+      </c>
+      <c r="R106">
+        <v>2.3</v>
+      </c>
+      <c r="S106">
+        <v>3.25</v>
+      </c>
+      <c r="T106">
+        <v>1.33</v>
+      </c>
+      <c r="U106">
+        <v>3.25</v>
+      </c>
+      <c r="V106">
+        <v>2.5</v>
+      </c>
+      <c r="W106">
+        <v>1.5</v>
+      </c>
+      <c r="X106">
+        <v>6.5</v>
+      </c>
+      <c r="Y106">
+        <v>1.11</v>
+      </c>
+      <c r="Z106">
+        <v>2.3</v>
+      </c>
+      <c r="AA106">
+        <v>3.13</v>
+      </c>
+      <c r="AB106">
+        <v>2.74</v>
+      </c>
+      <c r="AC106">
+        <v>1.05</v>
+      </c>
+      <c r="AD106">
+        <v>9.5</v>
+      </c>
+      <c r="AE106">
+        <v>1.25</v>
+      </c>
+      <c r="AF106">
+        <v>3.8</v>
+      </c>
+      <c r="AG106">
+        <v>1.84</v>
+      </c>
+      <c r="AH106">
+        <v>1.86</v>
+      </c>
+      <c r="AI106">
+        <v>1.62</v>
+      </c>
+      <c r="AJ106">
+        <v>2.2</v>
+      </c>
+      <c r="AK106">
+        <v>1.42</v>
+      </c>
+      <c r="AL106">
+        <v>1.29</v>
+      </c>
+      <c r="AM106">
+        <v>1.55</v>
+      </c>
+      <c r="AN106">
+        <v>1.67</v>
+      </c>
+      <c r="AO106">
+        <v>1.43</v>
+      </c>
+      <c r="AP106">
+        <v>1.86</v>
+      </c>
+      <c r="AQ106">
+        <v>1.25</v>
+      </c>
+      <c r="AR106">
+        <v>1.58</v>
+      </c>
+      <c r="AS106">
+        <v>1.26</v>
+      </c>
+      <c r="AT106">
+        <v>2.84</v>
+      </c>
+      <c r="AU106">
+        <v>7</v>
+      </c>
+      <c r="AV106">
+        <v>3</v>
+      </c>
+      <c r="AW106">
+        <v>9</v>
+      </c>
+      <c r="AX106">
+        <v>8</v>
+      </c>
+      <c r="AY106">
+        <v>16</v>
+      </c>
+      <c r="AZ106">
+        <v>11</v>
+      </c>
+      <c r="BA106">
+        <v>6</v>
+      </c>
+      <c r="BB106">
+        <v>2</v>
+      </c>
+      <c r="BC106">
+        <v>8</v>
+      </c>
+      <c r="BD106">
+        <v>2</v>
+      </c>
+      <c r="BE106">
+        <v>8</v>
+      </c>
+      <c r="BF106">
+        <v>2</v>
+      </c>
+      <c r="BG106">
+        <v>1.17</v>
+      </c>
+      <c r="BH106">
+        <v>4.15</v>
+      </c>
+      <c r="BI106">
+        <v>1.34</v>
+      </c>
+      <c r="BJ106">
+        <v>3.02</v>
+      </c>
+      <c r="BK106">
+        <v>1.58</v>
+      </c>
+      <c r="BL106">
+        <v>2.28</v>
+      </c>
+      <c r="BM106">
+        <v>1.95</v>
+      </c>
+      <c r="BN106">
+        <v>1.77</v>
+      </c>
+      <c r="BO106">
+        <v>2.38</v>
+      </c>
+      <c r="BP106">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="232">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -502,6 +502,15 @@
     <t>['76']</t>
   </si>
   <si>
+    <t>['15', '45+8']</t>
+  </si>
+  <si>
+    <t>['42', '68']</t>
+  </si>
+  <si>
+    <t>['18', '28', '77']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -692,6 +701,15 @@
   </si>
   <si>
     <t>['4', '63']</t>
+  </si>
+  <si>
+    <t>['43', '86']</t>
+  </si>
+  <si>
+    <t>['9', '14', '90+6']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP106"/>
+  <dimension ref="A1:BP111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1309,7 +1327,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1721,7 +1739,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1802,7 +1820,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ4">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -1927,7 +1945,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2133,7 +2151,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2339,7 +2357,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2420,7 +2438,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ7">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3038,7 +3056,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ10">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3241,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
         <v>0.83</v>
@@ -3447,10 +3465,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ12">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3575,7 +3593,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3987,7 +4005,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4065,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ15">
         <v>1</v>
@@ -4193,7 +4211,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4271,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ16">
         <v>0.83</v>
@@ -4399,7 +4417,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4480,7 +4498,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ17">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4811,7 +4829,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5017,7 +5035,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5095,7 +5113,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5223,7 +5241,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5429,7 +5447,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5635,7 +5653,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5841,7 +5859,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6047,7 +6065,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6253,7 +6271,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6334,7 +6352,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR26">
         <v>1.31</v>
@@ -6459,7 +6477,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6540,7 +6558,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ27">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR27">
         <v>1.57</v>
@@ -6665,7 +6683,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6949,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ29">
         <v>1.25</v>
@@ -7158,7 +7176,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ30">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR30">
         <v>2.59</v>
@@ -7283,7 +7301,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7361,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ31">
         <v>0.83</v>
@@ -7567,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ32">
         <v>0.83</v>
@@ -7695,7 +7713,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -7773,7 +7791,7 @@
         <v>0.5</v>
       </c>
       <c r="AP33">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ33">
         <v>1.25</v>
@@ -7982,7 +8000,7 @@
         <v>3</v>
       </c>
       <c r="AQ34">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR34">
         <v>2.49</v>
@@ -8107,7 +8125,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8313,7 +8331,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8394,7 +8412,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ36">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR36">
         <v>2</v>
@@ -8519,7 +8537,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8725,7 +8743,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8803,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
         <v>1.38</v>
@@ -9012,7 +9030,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR39">
         <v>1.22</v>
@@ -9137,7 +9155,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9424,7 +9442,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ41">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR41">
         <v>2.65</v>
@@ -9549,7 +9567,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9755,7 +9773,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10245,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="AP45">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>0.83</v>
@@ -10451,7 +10469,7 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ46">
         <v>1.43</v>
@@ -10579,7 +10597,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10785,7 +10803,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10866,7 +10884,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ48">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR48">
         <v>1.22</v>
@@ -11069,7 +11087,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49">
         <v>0.83</v>
@@ -11197,7 +11215,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11484,7 +11502,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ51">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR51">
         <v>1.64</v>
@@ -11609,7 +11627,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11687,10 +11705,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ52">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR52">
         <v>1.29</v>
@@ -11815,7 +11833,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12305,7 +12323,7 @@
         <v>0</v>
       </c>
       <c r="AP55">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ55">
         <v>0</v>
@@ -12433,7 +12451,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12639,7 +12657,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12845,7 +12863,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -12923,10 +12941,10 @@
         <v>2.33</v>
       </c>
       <c r="AP58">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ58">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR58">
         <v>1.94</v>
@@ -13132,7 +13150,7 @@
         <v>2</v>
       </c>
       <c r="AQ59">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR59">
         <v>1.16</v>
@@ -13257,7 +13275,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13338,7 +13356,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ60">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR60">
         <v>2.1</v>
@@ -13463,7 +13481,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13875,7 +13893,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14162,7 +14180,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ64">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR64">
         <v>1.85</v>
@@ -14287,7 +14305,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14365,10 +14383,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ65">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR65">
         <v>1.38</v>
@@ -14493,7 +14511,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14699,7 +14717,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14777,7 +14795,7 @@
         <v>2</v>
       </c>
       <c r="AP67">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ67">
         <v>1.67</v>
@@ -14905,7 +14923,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15111,7 +15129,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15317,7 +15335,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15398,7 +15416,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ70">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR70">
         <v>2.02</v>
@@ -15523,7 +15541,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15601,7 +15619,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ71">
         <v>1.25</v>
@@ -15729,7 +15747,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15810,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="AQ72">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -15935,7 +15953,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16141,7 +16159,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16222,7 +16240,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR74">
         <v>1.11</v>
@@ -16347,7 +16365,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16425,7 +16443,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ75">
         <v>1.38</v>
@@ -16553,7 +16571,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16759,7 +16777,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16837,7 +16855,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ77">
         <v>1.6</v>
@@ -16965,7 +16983,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17043,10 +17061,10 @@
         <v>0.25</v>
       </c>
       <c r="AP78">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ78">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR78">
         <v>2.33</v>
@@ -17171,7 +17189,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17252,7 +17270,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ79">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR79">
         <v>1.62</v>
@@ -17583,7 +17601,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17995,7 +18013,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18073,7 +18091,7 @@
         <v>2</v>
       </c>
       <c r="AP83">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ83">
         <v>1.43</v>
@@ -18201,7 +18219,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18407,7 +18425,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18488,7 +18506,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ85">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19025,7 +19043,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19103,10 +19121,10 @@
         <v>2.5</v>
       </c>
       <c r="AP88">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR88">
         <v>2.33</v>
@@ -19309,7 +19327,7 @@
         <v>1.43</v>
       </c>
       <c r="AP89">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AQ89">
         <v>1.38</v>
@@ -19437,7 +19455,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19518,7 +19536,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ90">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AR90">
         <v>2.02</v>
@@ -19643,7 +19661,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19724,7 +19742,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -19849,7 +19867,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -19930,7 +19948,7 @@
         <v>2</v>
       </c>
       <c r="AQ92">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AR92">
         <v>1.11</v>
@@ -20055,7 +20073,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20136,7 +20154,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ93">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR93">
         <v>1.62</v>
@@ -20261,7 +20279,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20545,7 +20563,7 @@
         <v>0.6</v>
       </c>
       <c r="AP95">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ95">
         <v>0.43</v>
@@ -20673,7 +20691,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21085,7 +21103,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21291,7 +21309,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21369,7 +21387,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ99">
         <v>1.6</v>
@@ -21909,7 +21927,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22115,7 +22133,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22527,7 +22545,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22890,6 +22908,1036 @@
       </c>
       <c r="BP106">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="107" spans="1:68">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>7785282</v>
+      </c>
+      <c r="C107" t="s">
+        <v>68</v>
+      </c>
+      <c r="D107" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F107">
+        <v>13</v>
+      </c>
+      <c r="G107" t="s">
+        <v>83</v>
+      </c>
+      <c r="H107" t="s">
+        <v>74</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>2</v>
+      </c>
+      <c r="N107">
+        <v>2</v>
+      </c>
+      <c r="O107" t="s">
+        <v>91</v>
+      </c>
+      <c r="P107" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q107">
+        <v>4.33</v>
+      </c>
+      <c r="R107">
+        <v>2.2</v>
+      </c>
+      <c r="S107">
+        <v>2.5</v>
+      </c>
+      <c r="T107">
+        <v>1.36</v>
+      </c>
+      <c r="U107">
+        <v>3</v>
+      </c>
+      <c r="V107">
+        <v>2.75</v>
+      </c>
+      <c r="W107">
+        <v>1.4</v>
+      </c>
+      <c r="X107">
+        <v>7</v>
+      </c>
+      <c r="Y107">
+        <v>1.1</v>
+      </c>
+      <c r="Z107">
+        <v>3.5</v>
+      </c>
+      <c r="AA107">
+        <v>3.35</v>
+      </c>
+      <c r="AB107">
+        <v>1.87</v>
+      </c>
+      <c r="AC107">
+        <v>1.05</v>
+      </c>
+      <c r="AD107">
+        <v>9</v>
+      </c>
+      <c r="AE107">
+        <v>1.3</v>
+      </c>
+      <c r="AF107">
+        <v>3.45</v>
+      </c>
+      <c r="AG107">
+        <v>1.82</v>
+      </c>
+      <c r="AH107">
+        <v>1.88</v>
+      </c>
+      <c r="AI107">
+        <v>1.8</v>
+      </c>
+      <c r="AJ107">
+        <v>1.95</v>
+      </c>
+      <c r="AK107">
+        <v>1.78</v>
+      </c>
+      <c r="AL107">
+        <v>1.29</v>
+      </c>
+      <c r="AM107">
+        <v>1.27</v>
+      </c>
+      <c r="AN107">
+        <v>0.33</v>
+      </c>
+      <c r="AO107">
+        <v>0.83</v>
+      </c>
+      <c r="AP107">
+        <v>0.29</v>
+      </c>
+      <c r="AQ107">
+        <v>1.14</v>
+      </c>
+      <c r="AR107">
+        <v>1.3</v>
+      </c>
+      <c r="AS107">
+        <v>1</v>
+      </c>
+      <c r="AT107">
+        <v>2.3</v>
+      </c>
+      <c r="AU107">
+        <v>3</v>
+      </c>
+      <c r="AV107">
+        <v>5</v>
+      </c>
+      <c r="AW107">
+        <v>6</v>
+      </c>
+      <c r="AX107">
+        <v>14</v>
+      </c>
+      <c r="AY107">
+        <v>9</v>
+      </c>
+      <c r="AZ107">
+        <v>19</v>
+      </c>
+      <c r="BA107">
+        <v>3</v>
+      </c>
+      <c r="BB107">
+        <v>11</v>
+      </c>
+      <c r="BC107">
+        <v>14</v>
+      </c>
+      <c r="BD107">
+        <v>2.6</v>
+      </c>
+      <c r="BE107">
+        <v>8.5</v>
+      </c>
+      <c r="BF107">
+        <v>1.62</v>
+      </c>
+      <c r="BG107">
+        <v>1.22</v>
+      </c>
+      <c r="BH107">
+        <v>3.65</v>
+      </c>
+      <c r="BI107">
+        <v>1.42</v>
+      </c>
+      <c r="BJ107">
+        <v>2.65</v>
+      </c>
+      <c r="BK107">
+        <v>1.7</v>
+      </c>
+      <c r="BL107">
+        <v>2.05</v>
+      </c>
+      <c r="BM107">
+        <v>2.11</v>
+      </c>
+      <c r="BN107">
+        <v>1.68</v>
+      </c>
+      <c r="BO107">
+        <v>2.65</v>
+      </c>
+      <c r="BP107">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="108" spans="1:68">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>7785283</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
+      </c>
+      <c r="D108" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F108">
+        <v>13</v>
+      </c>
+      <c r="G108" t="s">
+        <v>84</v>
+      </c>
+      <c r="H108" t="s">
+        <v>81</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108" t="s">
+        <v>91</v>
+      </c>
+      <c r="P108" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q108">
+        <v>3.1</v>
+      </c>
+      <c r="R108">
+        <v>2.4</v>
+      </c>
+      <c r="S108">
+        <v>2.88</v>
+      </c>
+      <c r="T108">
+        <v>1.25</v>
+      </c>
+      <c r="U108">
+        <v>3.75</v>
+      </c>
+      <c r="V108">
+        <v>2.25</v>
+      </c>
+      <c r="W108">
+        <v>1.57</v>
+      </c>
+      <c r="X108">
+        <v>5.5</v>
+      </c>
+      <c r="Y108">
+        <v>1.14</v>
+      </c>
+      <c r="Z108">
+        <v>2.68</v>
+      </c>
+      <c r="AA108">
+        <v>3.18</v>
+      </c>
+      <c r="AB108">
+        <v>2.32</v>
+      </c>
+      <c r="AC108">
+        <v>1.04</v>
+      </c>
+      <c r="AD108">
+        <v>10</v>
+      </c>
+      <c r="AE108">
+        <v>1.18</v>
+      </c>
+      <c r="AF108">
+        <v>4.75</v>
+      </c>
+      <c r="AG108">
+        <v>1.67</v>
+      </c>
+      <c r="AH108">
+        <v>2</v>
+      </c>
+      <c r="AI108">
+        <v>1.5</v>
+      </c>
+      <c r="AJ108">
+        <v>2.5</v>
+      </c>
+      <c r="AK108">
+        <v>1.55</v>
+      </c>
+      <c r="AL108">
+        <v>1.27</v>
+      </c>
+      <c r="AM108">
+        <v>1.44</v>
+      </c>
+      <c r="AN108">
+        <v>1.17</v>
+      </c>
+      <c r="AO108">
+        <v>2</v>
+      </c>
+      <c r="AP108">
+        <v>1.14</v>
+      </c>
+      <c r="AQ108">
+        <v>1.86</v>
+      </c>
+      <c r="AR108">
+        <v>1.44</v>
+      </c>
+      <c r="AS108">
+        <v>1.49</v>
+      </c>
+      <c r="AT108">
+        <v>2.93</v>
+      </c>
+      <c r="AU108">
+        <v>3</v>
+      </c>
+      <c r="AV108">
+        <v>9</v>
+      </c>
+      <c r="AW108">
+        <v>5</v>
+      </c>
+      <c r="AX108">
+        <v>20</v>
+      </c>
+      <c r="AY108">
+        <v>8</v>
+      </c>
+      <c r="AZ108">
+        <v>29</v>
+      </c>
+      <c r="BA108">
+        <v>4</v>
+      </c>
+      <c r="BB108">
+        <v>12</v>
+      </c>
+      <c r="BC108">
+        <v>16</v>
+      </c>
+      <c r="BD108">
+        <v>2.15</v>
+      </c>
+      <c r="BE108">
+        <v>6.75</v>
+      </c>
+      <c r="BF108">
+        <v>1.84</v>
+      </c>
+      <c r="BG108">
+        <v>1.18</v>
+      </c>
+      <c r="BH108">
+        <v>4.3</v>
+      </c>
+      <c r="BI108">
+        <v>1.3</v>
+      </c>
+      <c r="BJ108">
+        <v>3.05</v>
+      </c>
+      <c r="BK108">
+        <v>1.52</v>
+      </c>
+      <c r="BL108">
+        <v>2.33</v>
+      </c>
+      <c r="BM108">
+        <v>1.91</v>
+      </c>
+      <c r="BN108">
+        <v>1.8</v>
+      </c>
+      <c r="BO108">
+        <v>2.23</v>
+      </c>
+      <c r="BP108">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="109" spans="1:68">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>7785284</v>
+      </c>
+      <c r="C109" t="s">
+        <v>68</v>
+      </c>
+      <c r="D109" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F109">
+        <v>13</v>
+      </c>
+      <c r="G109" t="s">
+        <v>79</v>
+      </c>
+      <c r="H109" t="s">
+        <v>73</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>2</v>
+      </c>
+      <c r="L109">
+        <v>2</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
+      <c r="O109" t="s">
+        <v>162</v>
+      </c>
+      <c r="P109" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q109">
+        <v>1.95</v>
+      </c>
+      <c r="R109">
+        <v>2.5</v>
+      </c>
+      <c r="S109">
+        <v>6.5</v>
+      </c>
+      <c r="T109">
+        <v>1.3</v>
+      </c>
+      <c r="U109">
+        <v>3.4</v>
+      </c>
+      <c r="V109">
+        <v>2.5</v>
+      </c>
+      <c r="W109">
+        <v>1.5</v>
+      </c>
+      <c r="X109">
+        <v>6</v>
+      </c>
+      <c r="Y109">
+        <v>1.13</v>
+      </c>
+      <c r="Z109">
+        <v>1.42</v>
+      </c>
+      <c r="AA109">
+        <v>4.1</v>
+      </c>
+      <c r="AB109">
+        <v>5.8</v>
+      </c>
+      <c r="AC109">
+        <v>1.04</v>
+      </c>
+      <c r="AD109">
+        <v>10</v>
+      </c>
+      <c r="AE109">
+        <v>1.22</v>
+      </c>
+      <c r="AF109">
+        <v>4.2</v>
+      </c>
+      <c r="AG109">
+        <v>1.63</v>
+      </c>
+      <c r="AH109">
+        <v>2.13</v>
+      </c>
+      <c r="AI109">
+        <v>1.91</v>
+      </c>
+      <c r="AJ109">
+        <v>1.91</v>
+      </c>
+      <c r="AK109">
+        <v>1.13</v>
+      </c>
+      <c r="AL109">
+        <v>1.21</v>
+      </c>
+      <c r="AM109">
+        <v>2.5</v>
+      </c>
+      <c r="AN109">
+        <v>1.86</v>
+      </c>
+      <c r="AO109">
+        <v>0.83</v>
+      </c>
+      <c r="AP109">
+        <v>2</v>
+      </c>
+      <c r="AQ109">
+        <v>0.71</v>
+      </c>
+      <c r="AR109">
+        <v>2.17</v>
+      </c>
+      <c r="AS109">
+        <v>1.18</v>
+      </c>
+      <c r="AT109">
+        <v>3.35</v>
+      </c>
+      <c r="AU109">
+        <v>7</v>
+      </c>
+      <c r="AV109">
+        <v>0</v>
+      </c>
+      <c r="AW109">
+        <v>7</v>
+      </c>
+      <c r="AX109">
+        <v>13</v>
+      </c>
+      <c r="AY109">
+        <v>14</v>
+      </c>
+      <c r="AZ109">
+        <v>13</v>
+      </c>
+      <c r="BA109">
+        <v>9</v>
+      </c>
+      <c r="BB109">
+        <v>6</v>
+      </c>
+      <c r="BC109">
+        <v>15</v>
+      </c>
+      <c r="BD109">
+        <v>1.22</v>
+      </c>
+      <c r="BE109">
+        <v>9</v>
+      </c>
+      <c r="BF109">
+        <v>4.6</v>
+      </c>
+      <c r="BG109">
+        <v>1.17</v>
+      </c>
+      <c r="BH109">
+        <v>4.35</v>
+      </c>
+      <c r="BI109">
+        <v>1.3</v>
+      </c>
+      <c r="BJ109">
+        <v>3.15</v>
+      </c>
+      <c r="BK109">
+        <v>1.5</v>
+      </c>
+      <c r="BL109">
+        <v>2.4</v>
+      </c>
+      <c r="BM109">
+        <v>1.85</v>
+      </c>
+      <c r="BN109">
+        <v>1.85</v>
+      </c>
+      <c r="BO109">
+        <v>2.15</v>
+      </c>
+      <c r="BP109">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:68">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>7785285</v>
+      </c>
+      <c r="C110" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45851.5</v>
+      </c>
+      <c r="F110">
+        <v>13</v>
+      </c>
+      <c r="G110" t="s">
+        <v>70</v>
+      </c>
+      <c r="H110" t="s">
+        <v>76</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>2</v>
+      </c>
+      <c r="K110">
+        <v>3</v>
+      </c>
+      <c r="L110">
+        <v>2</v>
+      </c>
+      <c r="M110">
+        <v>3</v>
+      </c>
+      <c r="N110">
+        <v>5</v>
+      </c>
+      <c r="O110" t="s">
+        <v>163</v>
+      </c>
+      <c r="P110" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q110">
+        <v>4</v>
+      </c>
+      <c r="R110">
+        <v>2.3</v>
+      </c>
+      <c r="S110">
+        <v>2.5</v>
+      </c>
+      <c r="T110">
+        <v>1.33</v>
+      </c>
+      <c r="U110">
+        <v>3.25</v>
+      </c>
+      <c r="V110">
+        <v>2.5</v>
+      </c>
+      <c r="W110">
+        <v>1.5</v>
+      </c>
+      <c r="X110">
+        <v>6.5</v>
+      </c>
+      <c r="Y110">
+        <v>1.11</v>
+      </c>
+      <c r="Z110">
+        <v>3.38</v>
+      </c>
+      <c r="AA110">
+        <v>3.27</v>
+      </c>
+      <c r="AB110">
+        <v>1.93</v>
+      </c>
+      <c r="AC110">
+        <v>1.05</v>
+      </c>
+      <c r="AD110">
+        <v>9.5</v>
+      </c>
+      <c r="AE110">
+        <v>1.25</v>
+      </c>
+      <c r="AF110">
+        <v>3.85</v>
+      </c>
+      <c r="AG110">
+        <v>1.54</v>
+      </c>
+      <c r="AH110">
+        <v>2.3</v>
+      </c>
+      <c r="AI110">
+        <v>1.62</v>
+      </c>
+      <c r="AJ110">
+        <v>2.2</v>
+      </c>
+      <c r="AK110">
+        <v>1.77</v>
+      </c>
+      <c r="AL110">
+        <v>1.28</v>
+      </c>
+      <c r="AM110">
+        <v>1.29</v>
+      </c>
+      <c r="AN110">
+        <v>0</v>
+      </c>
+      <c r="AO110">
+        <v>2.17</v>
+      </c>
+      <c r="AP110">
+        <v>0</v>
+      </c>
+      <c r="AQ110">
+        <v>2.29</v>
+      </c>
+      <c r="AR110">
+        <v>1.45</v>
+      </c>
+      <c r="AS110">
+        <v>1.09</v>
+      </c>
+      <c r="AT110">
+        <v>2.54</v>
+      </c>
+      <c r="AU110">
+        <v>4</v>
+      </c>
+      <c r="AV110">
+        <v>9</v>
+      </c>
+      <c r="AW110">
+        <v>6</v>
+      </c>
+      <c r="AX110">
+        <v>11</v>
+      </c>
+      <c r="AY110">
+        <v>10</v>
+      </c>
+      <c r="AZ110">
+        <v>20</v>
+      </c>
+      <c r="BA110">
+        <v>4</v>
+      </c>
+      <c r="BB110">
+        <v>4</v>
+      </c>
+      <c r="BC110">
+        <v>8</v>
+      </c>
+      <c r="BD110">
+        <v>1.92</v>
+      </c>
+      <c r="BE110">
+        <v>6.75</v>
+      </c>
+      <c r="BF110">
+        <v>2.05</v>
+      </c>
+      <c r="BG110">
+        <v>1.16</v>
+      </c>
+      <c r="BH110">
+        <v>4.4</v>
+      </c>
+      <c r="BI110">
+        <v>1.29</v>
+      </c>
+      <c r="BJ110">
+        <v>3.2</v>
+      </c>
+      <c r="BK110">
+        <v>1.49</v>
+      </c>
+      <c r="BL110">
+        <v>2.4</v>
+      </c>
+      <c r="BM110">
+        <v>1.85</v>
+      </c>
+      <c r="BN110">
+        <v>1.85</v>
+      </c>
+      <c r="BO110">
+        <v>2.15</v>
+      </c>
+      <c r="BP110">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:68">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>7785279</v>
+      </c>
+      <c r="C111" t="s">
+        <v>68</v>
+      </c>
+      <c r="D111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45851.59375</v>
+      </c>
+      <c r="F111">
+        <v>13</v>
+      </c>
+      <c r="G111" t="s">
+        <v>80</v>
+      </c>
+      <c r="H111" t="s">
+        <v>85</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111">
+        <v>3</v>
+      </c>
+      <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111" t="s">
+        <v>164</v>
+      </c>
+      <c r="P111" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q111">
+        <v>2.75</v>
+      </c>
+      <c r="R111">
+        <v>2.5</v>
+      </c>
+      <c r="S111">
+        <v>3.1</v>
+      </c>
+      <c r="T111">
+        <v>1.25</v>
+      </c>
+      <c r="U111">
+        <v>3.75</v>
+      </c>
+      <c r="V111">
+        <v>2.1</v>
+      </c>
+      <c r="W111">
+        <v>1.67</v>
+      </c>
+      <c r="X111">
+        <v>4.5</v>
+      </c>
+      <c r="Y111">
+        <v>1.18</v>
+      </c>
+      <c r="Z111">
+        <v>2.4</v>
+      </c>
+      <c r="AA111">
+        <v>3.38</v>
+      </c>
+      <c r="AB111">
+        <v>2.46</v>
+      </c>
+      <c r="AC111">
+        <v>1.04</v>
+      </c>
+      <c r="AD111">
+        <v>10</v>
+      </c>
+      <c r="AE111">
+        <v>1.17</v>
+      </c>
+      <c r="AF111">
+        <v>5</v>
+      </c>
+      <c r="AG111">
+        <v>1.57</v>
+      </c>
+      <c r="AH111">
+        <v>2.15</v>
+      </c>
+      <c r="AI111">
+        <v>1.4</v>
+      </c>
+      <c r="AJ111">
+        <v>2.75</v>
+      </c>
+      <c r="AK111">
+        <v>1.47</v>
+      </c>
+      <c r="AL111">
+        <v>1.26</v>
+      </c>
+      <c r="AM111">
+        <v>1.55</v>
+      </c>
+      <c r="AN111">
+        <v>2.13</v>
+      </c>
+      <c r="AO111">
+        <v>2.29</v>
+      </c>
+      <c r="AP111">
+        <v>2.22</v>
+      </c>
+      <c r="AQ111">
+        <v>2</v>
+      </c>
+      <c r="AR111">
+        <v>2.11</v>
+      </c>
+      <c r="AS111">
+        <v>1.77</v>
+      </c>
+      <c r="AT111">
+        <v>3.88</v>
+      </c>
+      <c r="AU111">
+        <v>7</v>
+      </c>
+      <c r="AV111">
+        <v>5</v>
+      </c>
+      <c r="AW111">
+        <v>11</v>
+      </c>
+      <c r="AX111">
+        <v>7</v>
+      </c>
+      <c r="AY111">
+        <v>18</v>
+      </c>
+      <c r="AZ111">
+        <v>12</v>
+      </c>
+      <c r="BA111">
+        <v>5</v>
+      </c>
+      <c r="BB111">
+        <v>2</v>
+      </c>
+      <c r="BC111">
+        <v>7</v>
+      </c>
+      <c r="BD111">
+        <v>1.95</v>
+      </c>
+      <c r="BE111">
+        <v>6.75</v>
+      </c>
+      <c r="BF111">
+        <v>2.02</v>
+      </c>
+      <c r="BG111">
+        <v>1.19</v>
+      </c>
+      <c r="BH111">
+        <v>4.1</v>
+      </c>
+      <c r="BI111">
+        <v>1.33</v>
+      </c>
+      <c r="BJ111">
+        <v>2.95</v>
+      </c>
+      <c r="BK111">
+        <v>1.55</v>
+      </c>
+      <c r="BL111">
+        <v>2.25</v>
+      </c>
+      <c r="BM111">
+        <v>1.77</v>
+      </c>
+      <c r="BN111">
+        <v>1.95</v>
+      </c>
+      <c r="BO111">
+        <v>2.33</v>
+      </c>
+      <c r="BP111">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="233">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -711,6 +711,9 @@
   <si>
     <t>['90+2']</t>
   </si>
+  <si>
+    <t>['87']</t>
+  </si>
 </sst>
 </file>
 
@@ -1071,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1611,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ3">
         <v>1.67</v>
@@ -2850,7 +2853,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ9">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -4701,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ18">
         <v>1.25</v>
@@ -6143,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ25">
         <v>0.43</v>
@@ -6764,7 +6767,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ28">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -12120,7 +12123,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -13147,7 +13150,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ59">
         <v>1.14</v>
@@ -15207,7 +15210,7 @@
         <v>1.75</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ69">
         <v>1.43</v>
@@ -16237,7 +16240,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ74">
         <v>1.86</v>
@@ -16858,7 +16861,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ77">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR77">
         <v>1.3</v>
@@ -19945,7 +19948,7 @@
         <v>2</v>
       </c>
       <c r="AP92">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ92">
         <v>2.29</v>
@@ -21390,7 +21393,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ99">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AR99">
         <v>1.51</v>
@@ -22623,7 +22626,7 @@
         <v>1.43</v>
       </c>
       <c r="AP105">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ105">
         <v>1.25</v>
@@ -23938,6 +23941,212 @@
       </c>
       <c r="BP111">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7785210</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45854.54166666666</v>
+      </c>
+      <c r="F112">
+        <v>5</v>
+      </c>
+      <c r="G112" t="s">
+        <v>71</v>
+      </c>
+      <c r="H112" t="s">
+        <v>78</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>1</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>91</v>
+      </c>
+      <c r="P112" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q112">
+        <v>5</v>
+      </c>
+      <c r="R112">
+        <v>2.2</v>
+      </c>
+      <c r="S112">
+        <v>2.1</v>
+      </c>
+      <c r="T112">
+        <v>1.35</v>
+      </c>
+      <c r="U112">
+        <v>2.9</v>
+      </c>
+      <c r="V112">
+        <v>2.65</v>
+      </c>
+      <c r="W112">
+        <v>1.42</v>
+      </c>
+      <c r="X112">
+        <v>6.75</v>
+      </c>
+      <c r="Y112">
+        <v>1.09</v>
+      </c>
+      <c r="Z112">
+        <v>4.1</v>
+      </c>
+      <c r="AA112">
+        <v>3.79</v>
+      </c>
+      <c r="AB112">
+        <v>1.64</v>
+      </c>
+      <c r="AC112">
+        <v>1.02</v>
+      </c>
+      <c r="AD112">
+        <v>10</v>
+      </c>
+      <c r="AE112">
+        <v>1.22</v>
+      </c>
+      <c r="AF112">
+        <v>3.64</v>
+      </c>
+      <c r="AG112">
+        <v>1.8</v>
+      </c>
+      <c r="AH112">
+        <v>1.9</v>
+      </c>
+      <c r="AI112">
+        <v>1.88</v>
+      </c>
+      <c r="AJ112">
+        <v>1.8</v>
+      </c>
+      <c r="AK112">
+        <v>2.25</v>
+      </c>
+      <c r="AL112">
+        <v>1.23</v>
+      </c>
+      <c r="AM112">
+        <v>1.16</v>
+      </c>
+      <c r="AN112">
+        <v>2</v>
+      </c>
+      <c r="AO112">
+        <v>1.6</v>
+      </c>
+      <c r="AP112">
+        <v>1.78</v>
+      </c>
+      <c r="AQ112">
+        <v>1.83</v>
+      </c>
+      <c r="AR112">
+        <v>1.37</v>
+      </c>
+      <c r="AS112">
+        <v>1.7</v>
+      </c>
+      <c r="AT112">
+        <v>3.07</v>
+      </c>
+      <c r="AU112">
+        <v>3</v>
+      </c>
+      <c r="AV112">
+        <v>7</v>
+      </c>
+      <c r="AW112">
+        <v>5</v>
+      </c>
+      <c r="AX112">
+        <v>18</v>
+      </c>
+      <c r="AY112">
+        <v>8</v>
+      </c>
+      <c r="AZ112">
+        <v>25</v>
+      </c>
+      <c r="BA112">
+        <v>3</v>
+      </c>
+      <c r="BB112">
+        <v>8</v>
+      </c>
+      <c r="BC112">
+        <v>11</v>
+      </c>
+      <c r="BD112">
+        <v>2.65</v>
+      </c>
+      <c r="BE112">
+        <v>7</v>
+      </c>
+      <c r="BF112">
+        <v>1.56</v>
+      </c>
+      <c r="BG112">
+        <v>1.21</v>
+      </c>
+      <c r="BH112">
+        <v>3.9</v>
+      </c>
+      <c r="BI112">
+        <v>1.36</v>
+      </c>
+      <c r="BJ112">
+        <v>2.8</v>
+      </c>
+      <c r="BK112">
+        <v>1.58</v>
+      </c>
+      <c r="BL112">
+        <v>2.18</v>
+      </c>
+      <c r="BM112">
+        <v>1.94</v>
+      </c>
+      <c r="BN112">
+        <v>1.76</v>
+      </c>
+      <c r="BO112">
+        <v>2.4</v>
+      </c>
+      <c r="BP112">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -511,6 +511,9 @@
     <t>['18', '28', '77']</t>
   </si>
   <si>
+    <t>['20', '87']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -713,6 +716,9 @@
   </si>
   <si>
     <t>['87']</t>
+  </si>
+  <si>
+    <t>['5', '34']</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP112"/>
+  <dimension ref="A1:BP113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1330,7 +1336,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1411,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1742,7 +1748,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1948,7 +1954,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2154,7 +2160,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2360,7 +2366,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -3596,7 +3602,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3674,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ13">
         <v>1.25</v>
@@ -4008,7 +4014,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4214,7 +4220,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4420,7 +4426,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4832,7 +4838,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -5038,7 +5044,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5244,7 +5250,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5450,7 +5456,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5531,7 +5537,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ22">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR22">
         <v>1.7</v>
@@ -5656,7 +5662,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5862,7 +5868,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6068,7 +6074,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6274,7 +6280,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6480,7 +6486,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6686,7 +6692,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7304,7 +7310,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7716,7 +7722,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8128,7 +8134,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8206,7 +8212,7 @@
         <v>1.5</v>
       </c>
       <c r="AP35">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8334,7 +8340,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8540,7 +8546,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8746,7 +8752,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9158,7 +9164,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9570,7 +9576,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9776,7 +9782,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10475,7 +10481,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ46">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR46">
         <v>1.95</v>
@@ -10600,7 +10606,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10806,7 +10812,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11218,7 +11224,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11502,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ51">
         <v>0.71</v>
@@ -11630,7 +11636,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11836,7 +11842,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12454,7 +12460,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12660,7 +12666,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12866,7 +12872,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13278,7 +13284,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13484,7 +13490,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13771,7 +13777,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ62">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR62">
         <v>2.13</v>
@@ -13896,7 +13902,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14180,7 +14186,7 @@
         <v>1.33</v>
       </c>
       <c r="AP64">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ64">
         <v>2.29</v>
@@ -14308,7 +14314,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14514,7 +14520,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14720,7 +14726,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14926,7 +14932,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15132,7 +15138,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15213,7 +15219,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ69">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR69">
         <v>1.11</v>
@@ -15338,7 +15344,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15544,7 +15550,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15750,7 +15756,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15956,7 +15962,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16162,7 +16168,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16368,7 +16374,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16574,7 +16580,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16780,7 +16786,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16986,7 +16992,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17192,7 +17198,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17604,7 +17610,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -18016,7 +18022,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18097,7 +18103,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ83">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR83">
         <v>1.44</v>
@@ -18222,7 +18228,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18300,7 +18306,7 @@
         <v>0.75</v>
       </c>
       <c r="AP84">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ84">
         <v>0.83</v>
@@ -18428,7 +18434,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -19046,7 +19052,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19458,7 +19464,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19664,7 +19670,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19870,7 +19876,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20076,7 +20082,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20282,7 +20288,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20694,7 +20700,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -21106,7 +21112,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21312,7 +21318,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21805,7 +21811,7 @@
         <v>3</v>
       </c>
       <c r="AQ101">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR101">
         <v>2.06</v>
@@ -21930,7 +21936,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22008,7 +22014,7 @@
         <v>0</v>
       </c>
       <c r="AP102">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ102">
         <v>0</v>
@@ -22136,7 +22142,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22548,7 +22554,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22960,7 +22966,7 @@
         <v>91</v>
       </c>
       <c r="P107" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23578,7 +23584,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23784,7 +23790,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -23990,7 +23996,7 @@
         <v>91</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q112">
         <v>5</v>
@@ -24146,6 +24152,212 @@
         <v>2.4</v>
       </c>
       <c r="BP112">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7785290</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45856.54166666666</v>
+      </c>
+      <c r="F113">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s">
+        <v>79</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113">
+        <v>3</v>
+      </c>
+      <c r="L113">
+        <v>2</v>
+      </c>
+      <c r="M113">
+        <v>2</v>
+      </c>
+      <c r="N113">
+        <v>4</v>
+      </c>
+      <c r="O113" t="s">
+        <v>165</v>
+      </c>
+      <c r="P113" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q113">
+        <v>2.9</v>
+      </c>
+      <c r="R113">
+        <v>2.2</v>
+      </c>
+      <c r="S113">
+        <v>3.1</v>
+      </c>
+      <c r="T113">
+        <v>1.3</v>
+      </c>
+      <c r="U113">
+        <v>3.2</v>
+      </c>
+      <c r="V113">
+        <v>2.3</v>
+      </c>
+      <c r="W113">
+        <v>1.55</v>
+      </c>
+      <c r="X113">
+        <v>5.5</v>
+      </c>
+      <c r="Y113">
+        <v>1.08</v>
+      </c>
+      <c r="Z113">
+        <v>2.45</v>
+      </c>
+      <c r="AA113">
+        <v>3.34</v>
+      </c>
+      <c r="AB113">
+        <v>2.43</v>
+      </c>
+      <c r="AC113">
+        <v>1.04</v>
+      </c>
+      <c r="AD113">
+        <v>10</v>
+      </c>
+      <c r="AE113">
+        <v>1.2</v>
+      </c>
+      <c r="AF113">
+        <v>4.33</v>
+      </c>
+      <c r="AG113">
+        <v>1.55</v>
+      </c>
+      <c r="AH113">
+        <v>2.2</v>
+      </c>
+      <c r="AI113">
+        <v>1.48</v>
+      </c>
+      <c r="AJ113">
+        <v>2.4</v>
+      </c>
+      <c r="AK113">
+        <v>1.45</v>
+      </c>
+      <c r="AL113">
+        <v>1.25</v>
+      </c>
+      <c r="AM113">
+        <v>1.5</v>
+      </c>
+      <c r="AN113">
+        <v>1.33</v>
+      </c>
+      <c r="AO113">
+        <v>1.43</v>
+      </c>
+      <c r="AP113">
+        <v>1.29</v>
+      </c>
+      <c r="AQ113">
+        <v>1.38</v>
+      </c>
+      <c r="AR113">
+        <v>1.76</v>
+      </c>
+      <c r="AS113">
+        <v>1.3</v>
+      </c>
+      <c r="AT113">
+        <v>3.06</v>
+      </c>
+      <c r="AU113">
+        <v>7</v>
+      </c>
+      <c r="AV113">
+        <v>6</v>
+      </c>
+      <c r="AW113">
+        <v>12</v>
+      </c>
+      <c r="AX113">
+        <v>6</v>
+      </c>
+      <c r="AY113">
+        <v>19</v>
+      </c>
+      <c r="AZ113">
+        <v>12</v>
+      </c>
+      <c r="BA113">
+        <v>4</v>
+      </c>
+      <c r="BB113">
+        <v>1</v>
+      </c>
+      <c r="BC113">
+        <v>5</v>
+      </c>
+      <c r="BD113">
+        <v>2.15</v>
+      </c>
+      <c r="BE113">
+        <v>6.75</v>
+      </c>
+      <c r="BF113">
+        <v>1.84</v>
+      </c>
+      <c r="BG113">
+        <v>1.21</v>
+      </c>
+      <c r="BH113">
+        <v>3.9</v>
+      </c>
+      <c r="BI113">
+        <v>1.36</v>
+      </c>
+      <c r="BJ113">
+        <v>2.8</v>
+      </c>
+      <c r="BK113">
+        <v>1.58</v>
+      </c>
+      <c r="BL113">
+        <v>2.18</v>
+      </c>
+      <c r="BM113">
+        <v>1.93</v>
+      </c>
+      <c r="BN113">
+        <v>1.76</v>
+      </c>
+      <c r="BO113">
+        <v>2.4</v>
+      </c>
+      <c r="BP113">
         <v>1.49</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -22459,13 +22459,13 @@
         <v>4</v>
       </c>
       <c r="BA104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB104">
         <v>1</v>
       </c>
       <c r="BC104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD104">
         <v>1.14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -514,6 +514,15 @@
     <t>['20', '87']</t>
   </si>
   <si>
+    <t>['31', '45']</t>
+  </si>
+  <si>
+    <t>['11', '20', '41', '51']</t>
+  </si>
+  <si>
+    <t>['6', '22']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -719,6 +728,9 @@
   </si>
   <si>
     <t>['5', '34']</t>
+  </si>
+  <si>
+    <t>['1', '14', '38', '70']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP113"/>
+  <dimension ref="A1:BP116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1336,7 +1348,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1623,7 +1635,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ3">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1748,7 +1760,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1954,7 +1966,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2160,7 +2172,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2238,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ6">
         <v>0.43</v>
@@ -2366,7 +2378,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2444,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>1.86</v>
@@ -2859,7 +2871,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ9">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3602,7 +3614,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4014,7 +4026,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4095,7 +4107,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ15">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4220,7 +4232,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4426,7 +4438,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4504,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17">
         <v>1.14</v>
@@ -4838,7 +4850,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4916,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ19">
         <v>1.38</v>
@@ -5044,7 +5056,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5125,7 +5137,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR20">
         <v>1.82</v>
@@ -5250,7 +5262,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5456,7 +5468,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5662,7 +5674,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5743,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR23">
         <v>1.32</v>
@@ -5868,7 +5880,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6074,7 +6086,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6280,7 +6292,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6486,7 +6498,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6564,7 +6576,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ27">
         <v>1.86</v>
@@ -6692,7 +6704,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -6770,10 +6782,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>1.35</v>
@@ -7310,7 +7322,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7722,7 +7734,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8134,7 +8146,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8215,7 +8227,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ35">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR35">
         <v>1.51</v>
@@ -8340,7 +8352,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8418,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ36">
         <v>2.29</v>
@@ -8546,7 +8558,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8624,7 +8636,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ37">
         <v>0</v>
@@ -8752,7 +8764,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -9164,7 +9176,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9245,7 +9257,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ40">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR40">
         <v>2.08</v>
@@ -9448,7 +9460,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ41">
         <v>1.86</v>
@@ -9576,7 +9588,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9782,7 +9794,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -10066,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
         <v>0</v>
@@ -10606,7 +10618,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10812,7 +10824,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -10890,7 +10902,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ48">
         <v>2.29</v>
@@ -11224,7 +11236,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11636,7 +11648,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11842,7 +11854,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -11920,7 +11932,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ53">
         <v>0.43</v>
@@ -12129,7 +12141,7 @@
         <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR54">
         <v>1.59</v>
@@ -12460,7 +12472,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12538,7 +12550,7 @@
         <v>1.4</v>
       </c>
       <c r="AP56">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -12666,7 +12678,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12872,7 +12884,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13284,7 +13296,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13490,7 +13502,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13902,7 +13914,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -14314,7 +14326,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14520,7 +14532,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14601,7 +14613,7 @@
         <v>3</v>
       </c>
       <c r="AQ66">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR66">
         <v>1.95</v>
@@ -14726,7 +14738,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14807,7 +14819,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ67">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR67">
         <v>1.35</v>
@@ -14932,7 +14944,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15010,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ68">
         <v>1.25</v>
@@ -15138,7 +15150,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15344,7 +15356,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15550,7 +15562,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15756,7 +15768,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15962,7 +15974,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16168,7 +16180,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16374,7 +16386,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16580,7 +16592,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16786,7 +16798,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -16867,7 +16879,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ77">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR77">
         <v>1.3</v>
@@ -16992,7 +17004,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17198,7 +17210,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17276,7 +17288,7 @@
         <v>2.4</v>
       </c>
       <c r="AP79">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ79">
         <v>2</v>
@@ -17485,7 +17497,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR80">
         <v>2.02</v>
@@ -17610,7 +17622,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -18022,7 +18034,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18228,7 +18240,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18434,7 +18446,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18718,10 +18730,10 @@
         <v>1.5</v>
       </c>
       <c r="AP86">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR86">
         <v>1.15</v>
@@ -18924,7 +18936,7 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ87">
         <v>0.83</v>
@@ -19052,7 +19064,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19464,7 +19476,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19670,7 +19682,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19876,7 +19888,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20082,7 +20094,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20160,7 +20172,7 @@
         <v>0.4</v>
       </c>
       <c r="AP93">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
         <v>1.14</v>
@@ -20288,7 +20300,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20700,7 +20712,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20781,7 +20793,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ96">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR96">
         <v>1.39</v>
@@ -20984,10 +20996,10 @@
         <v>1.2</v>
       </c>
       <c r="AP97">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ97">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR97">
         <v>2.35</v>
@@ -21112,7 +21124,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21318,7 +21330,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21399,7 +21411,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ99">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR99">
         <v>1.51</v>
@@ -21936,7 +21948,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22142,7 +22154,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22220,7 +22232,7 @@
         <v>0.8</v>
       </c>
       <c r="AP103">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ103">
         <v>0.83</v>
@@ -22554,7 +22566,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22966,7 +22978,7 @@
         <v>91</v>
       </c>
       <c r="P107" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23584,7 +23596,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23790,7 +23802,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -23996,7 +24008,7 @@
         <v>91</v>
       </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q112">
         <v>5</v>
@@ -24077,7 +24089,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ112">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AR112">
         <v>1.37</v>
@@ -24202,7 +24214,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q113">
         <v>2.9</v>
@@ -24358,6 +24370,624 @@
         <v>2.4</v>
       </c>
       <c r="BP113">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7785287</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45857.375</v>
+      </c>
+      <c r="F114">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>74</v>
+      </c>
+      <c r="H114" t="s">
+        <v>80</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>2</v>
+      </c>
+      <c r="O114" t="s">
+        <v>166</v>
+      </c>
+      <c r="P114" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q114">
+        <v>3.5</v>
+      </c>
+      <c r="R114">
+        <v>2</v>
+      </c>
+      <c r="S114">
+        <v>2.95</v>
+      </c>
+      <c r="T114">
+        <v>1.4</v>
+      </c>
+      <c r="U114">
+        <v>2.7</v>
+      </c>
+      <c r="V114">
+        <v>2.8</v>
+      </c>
+      <c r="W114">
+        <v>1.38</v>
+      </c>
+      <c r="X114">
+        <v>7.3</v>
+      </c>
+      <c r="Y114">
+        <v>1.03</v>
+      </c>
+      <c r="Z114">
+        <v>2.88</v>
+      </c>
+      <c r="AA114">
+        <v>3.11</v>
+      </c>
+      <c r="AB114">
+        <v>2.22</v>
+      </c>
+      <c r="AC114">
+        <v>1.06</v>
+      </c>
+      <c r="AD114">
+        <v>8.5</v>
+      </c>
+      <c r="AE114">
+        <v>1.3</v>
+      </c>
+      <c r="AF114">
+        <v>3.45</v>
+      </c>
+      <c r="AG114">
+        <v>1.89</v>
+      </c>
+      <c r="AH114">
+        <v>1.81</v>
+      </c>
+      <c r="AI114">
+        <v>1.65</v>
+      </c>
+      <c r="AJ114">
+        <v>2.05</v>
+      </c>
+      <c r="AK114">
+        <v>1.55</v>
+      </c>
+      <c r="AL114">
+        <v>1.25</v>
+      </c>
+      <c r="AM114">
+        <v>1.38</v>
+      </c>
+      <c r="AN114">
+        <v>1.17</v>
+      </c>
+      <c r="AO114">
+        <v>1.67</v>
+      </c>
+      <c r="AP114">
+        <v>1.43</v>
+      </c>
+      <c r="AQ114">
+        <v>1.43</v>
+      </c>
+      <c r="AR114">
+        <v>1.4</v>
+      </c>
+      <c r="AS114">
+        <v>1.75</v>
+      </c>
+      <c r="AT114">
+        <v>3.15</v>
+      </c>
+      <c r="AU114">
+        <v>4</v>
+      </c>
+      <c r="AV114">
+        <v>2</v>
+      </c>
+      <c r="AW114">
+        <v>6</v>
+      </c>
+      <c r="AX114">
+        <v>13</v>
+      </c>
+      <c r="AY114">
+        <v>10</v>
+      </c>
+      <c r="AZ114">
+        <v>15</v>
+      </c>
+      <c r="BA114">
+        <v>4</v>
+      </c>
+      <c r="BB114">
+        <v>11</v>
+      </c>
+      <c r="BC114">
+        <v>15</v>
+      </c>
+      <c r="BD114">
+        <v>2</v>
+      </c>
+      <c r="BE114">
+        <v>6.75</v>
+      </c>
+      <c r="BF114">
+        <v>1.95</v>
+      </c>
+      <c r="BG114">
+        <v>1.23</v>
+      </c>
+      <c r="BH114">
+        <v>3.7</v>
+      </c>
+      <c r="BI114">
+        <v>1.4</v>
+      </c>
+      <c r="BJ114">
+        <v>2.7</v>
+      </c>
+      <c r="BK114">
+        <v>1.65</v>
+      </c>
+      <c r="BL114">
+        <v>2.08</v>
+      </c>
+      <c r="BM114">
+        <v>2</v>
+      </c>
+      <c r="BN114">
+        <v>1.71</v>
+      </c>
+      <c r="BO114">
+        <v>2.5</v>
+      </c>
+      <c r="BP114">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7785288</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45857.45833333334</v>
+      </c>
+      <c r="F115">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>75</v>
+      </c>
+      <c r="H115" t="s">
+        <v>70</v>
+      </c>
+      <c r="I115">
+        <v>3</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>4</v>
+      </c>
+      <c r="L115">
+        <v>4</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>5</v>
+      </c>
+      <c r="O115" t="s">
+        <v>167</v>
+      </c>
+      <c r="P115" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q115">
+        <v>1.88</v>
+      </c>
+      <c r="R115">
+        <v>2.65</v>
+      </c>
+      <c r="S115">
+        <v>5.45</v>
+      </c>
+      <c r="T115">
+        <v>1.16</v>
+      </c>
+      <c r="U115">
+        <v>4.1</v>
+      </c>
+      <c r="V115">
+        <v>2.03</v>
+      </c>
+      <c r="W115">
+        <v>1.7</v>
+      </c>
+      <c r="X115">
+        <v>4.4</v>
+      </c>
+      <c r="Y115">
+        <v>1.14</v>
+      </c>
+      <c r="Z115">
+        <v>1.47</v>
+      </c>
+      <c r="AA115">
+        <v>4.2</v>
+      </c>
+      <c r="AB115">
+        <v>4.9</v>
+      </c>
+      <c r="AC115">
+        <v>1.01</v>
+      </c>
+      <c r="AD115">
+        <v>17</v>
+      </c>
+      <c r="AE115">
+        <v>1.06</v>
+      </c>
+      <c r="AF115">
+        <v>6.25</v>
+      </c>
+      <c r="AG115">
+        <v>1.55</v>
+      </c>
+      <c r="AH115">
+        <v>2.2</v>
+      </c>
+      <c r="AI115">
+        <v>1.51</v>
+      </c>
+      <c r="AJ115">
+        <v>2.39</v>
+      </c>
+      <c r="AK115">
+        <v>1.12</v>
+      </c>
+      <c r="AL115">
+        <v>1.17</v>
+      </c>
+      <c r="AM115">
+        <v>2.74</v>
+      </c>
+      <c r="AN115">
+        <v>0.67</v>
+      </c>
+      <c r="AO115">
+        <v>1</v>
+      </c>
+      <c r="AP115">
+        <v>1</v>
+      </c>
+      <c r="AQ115">
+        <v>0.86</v>
+      </c>
+      <c r="AR115">
+        <v>1.6</v>
+      </c>
+      <c r="AS115">
+        <v>1.35</v>
+      </c>
+      <c r="AT115">
+        <v>2.95</v>
+      </c>
+      <c r="AU115">
+        <v>4</v>
+      </c>
+      <c r="AV115">
+        <v>4</v>
+      </c>
+      <c r="AW115">
+        <v>7</v>
+      </c>
+      <c r="AX115">
+        <v>4</v>
+      </c>
+      <c r="AY115">
+        <v>11</v>
+      </c>
+      <c r="AZ115">
+        <v>8</v>
+      </c>
+      <c r="BA115">
+        <v>6</v>
+      </c>
+      <c r="BB115">
+        <v>5</v>
+      </c>
+      <c r="BC115">
+        <v>11</v>
+      </c>
+      <c r="BD115">
+        <v>1.34</v>
+      </c>
+      <c r="BE115">
+        <v>8</v>
+      </c>
+      <c r="BF115">
+        <v>3.45</v>
+      </c>
+      <c r="BG115">
+        <v>1.13</v>
+      </c>
+      <c r="BH115">
+        <v>4.9</v>
+      </c>
+      <c r="BI115">
+        <v>1.24</v>
+      </c>
+      <c r="BJ115">
+        <v>3.55</v>
+      </c>
+      <c r="BK115">
+        <v>1.41</v>
+      </c>
+      <c r="BL115">
+        <v>2.65</v>
+      </c>
+      <c r="BM115">
+        <v>1.65</v>
+      </c>
+      <c r="BN115">
+        <v>2.1</v>
+      </c>
+      <c r="BO115">
+        <v>1.98</v>
+      </c>
+      <c r="BP115">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7785292</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45857.54166666666</v>
+      </c>
+      <c r="F116">
+        <v>14</v>
+      </c>
+      <c r="G116" t="s">
+        <v>85</v>
+      </c>
+      <c r="H116" t="s">
+        <v>78</v>
+      </c>
+      <c r="I116">
+        <v>2</v>
+      </c>
+      <c r="J116">
+        <v>3</v>
+      </c>
+      <c r="K116">
+        <v>5</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="M116">
+        <v>4</v>
+      </c>
+      <c r="N116">
+        <v>6</v>
+      </c>
+      <c r="O116" t="s">
+        <v>168</v>
+      </c>
+      <c r="P116" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q116">
+        <v>3.3</v>
+      </c>
+      <c r="R116">
+        <v>2.35</v>
+      </c>
+      <c r="S116">
+        <v>2.55</v>
+      </c>
+      <c r="T116">
+        <v>1.25</v>
+      </c>
+      <c r="U116">
+        <v>3.55</v>
+      </c>
+      <c r="V116">
+        <v>2.15</v>
+      </c>
+      <c r="W116">
+        <v>1.62</v>
+      </c>
+      <c r="X116">
+        <v>4.4</v>
+      </c>
+      <c r="Y116">
+        <v>1.14</v>
+      </c>
+      <c r="Z116">
+        <v>2.77</v>
+      </c>
+      <c r="AA116">
+        <v>3.79</v>
+      </c>
+      <c r="AB116">
+        <v>2.02</v>
+      </c>
+      <c r="AC116">
+        <v>1.01</v>
+      </c>
+      <c r="AD116">
+        <v>15.5</v>
+      </c>
+      <c r="AE116">
+        <v>1.15</v>
+      </c>
+      <c r="AF116">
+        <v>5.25</v>
+      </c>
+      <c r="AG116">
+        <v>1.48</v>
+      </c>
+      <c r="AH116">
+        <v>2.45</v>
+      </c>
+      <c r="AI116">
+        <v>1.42</v>
+      </c>
+      <c r="AJ116">
+        <v>2.62</v>
+      </c>
+      <c r="AK116">
+        <v>1.67</v>
+      </c>
+      <c r="AL116">
+        <v>1.2</v>
+      </c>
+      <c r="AM116">
+        <v>1.38</v>
+      </c>
+      <c r="AN116">
+        <v>2.5</v>
+      </c>
+      <c r="AO116">
+        <v>1.83</v>
+      </c>
+      <c r="AP116">
+        <v>2.22</v>
+      </c>
+      <c r="AQ116">
+        <v>2</v>
+      </c>
+      <c r="AR116">
+        <v>2.37</v>
+      </c>
+      <c r="AS116">
+        <v>1.91</v>
+      </c>
+      <c r="AT116">
+        <v>4.28</v>
+      </c>
+      <c r="AU116">
+        <v>6</v>
+      </c>
+      <c r="AV116">
+        <v>10</v>
+      </c>
+      <c r="AW116">
+        <v>9</v>
+      </c>
+      <c r="AX116">
+        <v>7</v>
+      </c>
+      <c r="AY116">
+        <v>15</v>
+      </c>
+      <c r="AZ116">
+        <v>17</v>
+      </c>
+      <c r="BA116">
+        <v>4</v>
+      </c>
+      <c r="BB116">
+        <v>4</v>
+      </c>
+      <c r="BC116">
+        <v>8</v>
+      </c>
+      <c r="BD116">
+        <v>1.97</v>
+      </c>
+      <c r="BE116">
+        <v>6.75</v>
+      </c>
+      <c r="BF116">
+        <v>1.98</v>
+      </c>
+      <c r="BG116">
+        <v>1.2</v>
+      </c>
+      <c r="BH116">
+        <v>3.95</v>
+      </c>
+      <c r="BI116">
+        <v>1.35</v>
+      </c>
+      <c r="BJ116">
+        <v>2.9</v>
+      </c>
+      <c r="BK116">
+        <v>1.58</v>
+      </c>
+      <c r="BL116">
+        <v>2.18</v>
+      </c>
+      <c r="BM116">
+        <v>1.93</v>
+      </c>
+      <c r="BN116">
+        <v>1.77</v>
+      </c>
+      <c r="BO116">
+        <v>2.4</v>
+      </c>
+      <c r="BP116">
         <v>1.49</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Norway Eliteserien_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="244">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -523,6 +523,18 @@
     <t>['6', '22']</t>
   </si>
   <si>
+    <t>['64', '84', '90+1']</t>
+  </si>
+  <si>
+    <t>['45+1', '55', '58']</t>
+  </si>
+  <si>
+    <t>['8', '22', '39', '45', '66', '86']</t>
+  </si>
+  <si>
+    <t>['12']</t>
+  </si>
+  <si>
     <t>['39', '49']</t>
   </si>
   <si>
@@ -731,6 +743,9 @@
   </si>
   <si>
     <t>['1', '14', '38', '70']</t>
+  </si>
+  <si>
+    <t>['52']</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP116"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1348,7 +1363,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="Q2">
         <v>3.75</v>
@@ -1760,7 +1775,7 @@
         <v>88</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1838,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
         <v>2</v>
@@ -1966,7 +1981,7 @@
         <v>89</v>
       </c>
       <c r="P5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -2044,10 +2059,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2172,7 +2187,7 @@
         <v>90</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q6">
         <v>2.88</v>
@@ -2378,7 +2393,7 @@
         <v>91</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q7">
         <v>1.91</v>
@@ -2662,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ8">
         <v>0</v>
@@ -3283,7 +3298,7 @@
         <v>2</v>
       </c>
       <c r="AQ11">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3614,7 +3629,7 @@
         <v>96</v>
       </c>
       <c r="P13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4026,7 +4041,7 @@
         <v>91</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q15">
         <v>3.25</v>
@@ -4232,7 +4247,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4313,7 +4328,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ16">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4438,7 +4453,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q17">
         <v>2.25</v>
@@ -4850,7 +4865,7 @@
         <v>101</v>
       </c>
       <c r="P19" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q19">
         <v>1.91</v>
@@ -4931,7 +4946,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ19">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR19">
         <v>2.02</v>
@@ -5056,7 +5071,7 @@
         <v>102</v>
       </c>
       <c r="P20" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q20">
         <v>1.9</v>
@@ -5262,7 +5277,7 @@
         <v>103</v>
       </c>
       <c r="P21" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q21">
         <v>2.25</v>
@@ -5340,10 +5355,10 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR21">
         <v>1.94</v>
@@ -5468,7 +5483,7 @@
         <v>91</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
@@ -5546,7 +5561,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22">
         <v>1.38</v>
@@ -5674,7 +5689,7 @@
         <v>104</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>3.4</v>
@@ -5880,7 +5895,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q24">
         <v>2.5</v>
@@ -6086,7 +6101,7 @@
         <v>106</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q25">
         <v>2.63</v>
@@ -6292,7 +6307,7 @@
         <v>107</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>3.75</v>
@@ -6370,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ26">
         <v>2</v>
@@ -6498,7 +6513,7 @@
         <v>108</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -6704,7 +6719,7 @@
         <v>109</v>
       </c>
       <c r="P28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q28">
         <v>3.5</v>
@@ -7322,7 +7337,7 @@
         <v>111</v>
       </c>
       <c r="P31" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>1.8</v>
@@ -7403,7 +7418,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ31">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR31">
         <v>1.79</v>
@@ -7609,7 +7624,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ32">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR32">
         <v>1.53</v>
@@ -7734,7 +7749,7 @@
         <v>91</v>
       </c>
       <c r="P33" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q33">
         <v>3.5</v>
@@ -8146,7 +8161,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q35">
         <v>2.44</v>
@@ -8352,7 +8367,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -8558,7 +8573,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q37">
         <v>1.73</v>
@@ -8764,7 +8779,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
@@ -8845,7 +8860,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR38">
         <v>1.75</v>
@@ -9048,7 +9063,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ39">
         <v>1.14</v>
@@ -9176,7 +9191,7 @@
         <v>117</v>
       </c>
       <c r="P40" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q40">
         <v>3.4</v>
@@ -9254,7 +9269,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ40">
         <v>1.43</v>
@@ -9588,7 +9603,7 @@
         <v>91</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q42">
         <v>2.4</v>
@@ -9666,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ42">
         <v>0.43</v>
@@ -9794,7 +9809,7 @@
         <v>118</v>
       </c>
       <c r="P43" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -9875,7 +9890,7 @@
         <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR43">
         <v>1.63</v>
@@ -10287,7 +10302,7 @@
         <v>2</v>
       </c>
       <c r="AQ45">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR45">
         <v>2.27</v>
@@ -10618,7 +10633,7 @@
         <v>91</v>
       </c>
       <c r="P47" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>4</v>
@@ -10824,7 +10839,7 @@
         <v>121</v>
       </c>
       <c r="P48" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>3.25</v>
@@ -11111,7 +11126,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ49">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR49">
         <v>1.56</v>
@@ -11236,7 +11251,7 @@
         <v>122</v>
       </c>
       <c r="P50" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q50">
         <v>2.88</v>
@@ -11648,7 +11663,7 @@
         <v>124</v>
       </c>
       <c r="P52" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>5</v>
@@ -11854,7 +11869,7 @@
         <v>125</v>
       </c>
       <c r="P53" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q53">
         <v>2</v>
@@ -12138,7 +12153,7 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ54">
         <v>2</v>
@@ -12472,7 +12487,7 @@
         <v>91</v>
       </c>
       <c r="P56" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q56">
         <v>1.8</v>
@@ -12553,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -12678,7 +12693,7 @@
         <v>91</v>
       </c>
       <c r="P57" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -12759,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="AQ57">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -12884,7 +12899,7 @@
         <v>89</v>
       </c>
       <c r="P58" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q58">
         <v>2.2</v>
@@ -13296,7 +13311,7 @@
         <v>129</v>
       </c>
       <c r="P60" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13374,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ60">
         <v>0.71</v>
@@ -13502,7 +13517,7 @@
         <v>130</v>
       </c>
       <c r="P61" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q61">
         <v>3.55</v>
@@ -13583,7 +13598,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ61">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR61">
         <v>1.27</v>
@@ -13914,7 +13929,7 @@
         <v>132</v>
       </c>
       <c r="P63" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q63">
         <v>4.5</v>
@@ -13992,7 +14007,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ63">
         <v>1.25</v>
@@ -14326,7 +14341,7 @@
         <v>91</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>4.33</v>
@@ -14532,7 +14547,7 @@
         <v>133</v>
       </c>
       <c r="P66" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>2.63</v>
@@ -14738,7 +14753,7 @@
         <v>91</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>6</v>
@@ -14944,7 +14959,7 @@
         <v>91</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>3.4</v>
@@ -15150,7 +15165,7 @@
         <v>91</v>
       </c>
       <c r="P69" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q69">
         <v>3.75</v>
@@ -15356,7 +15371,7 @@
         <v>134</v>
       </c>
       <c r="P70" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q70">
         <v>1.95</v>
@@ -15562,7 +15577,7 @@
         <v>91</v>
       </c>
       <c r="P71" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q71">
         <v>2.4</v>
@@ -15768,7 +15783,7 @@
         <v>91</v>
       </c>
       <c r="P72" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -15974,7 +15989,7 @@
         <v>135</v>
       </c>
       <c r="P73" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q73">
         <v>2.6</v>
@@ -16052,7 +16067,7 @@
         <v>1.4</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ73">
         <v>1.25</v>
@@ -16180,7 +16195,7 @@
         <v>124</v>
       </c>
       <c r="P74" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q74">
         <v>2.5</v>
@@ -16386,7 +16401,7 @@
         <v>136</v>
       </c>
       <c r="P75" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q75">
         <v>1.65</v>
@@ -16467,7 +16482,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ75">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR75">
         <v>1.99</v>
@@ -16592,7 +16607,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q76">
         <v>3.1</v>
@@ -16798,7 +16813,7 @@
         <v>91</v>
       </c>
       <c r="P77" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q77">
         <v>9</v>
@@ -17004,7 +17019,7 @@
         <v>138</v>
       </c>
       <c r="P78" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q78">
         <v>1.83</v>
@@ -17210,7 +17225,7 @@
         <v>91</v>
       </c>
       <c r="P79" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q79">
         <v>2.62</v>
@@ -17622,7 +17637,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>3</v>
@@ -17700,7 +17715,7 @@
         <v>1.4</v>
       </c>
       <c r="AP81">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ81">
         <v>1.25</v>
@@ -18034,7 +18049,7 @@
         <v>142</v>
       </c>
       <c r="P83" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q83">
         <v>4.75</v>
@@ -18240,7 +18255,7 @@
         <v>143</v>
       </c>
       <c r="P84" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q84">
         <v>2.1</v>
@@ -18321,7 +18336,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ84">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR84">
         <v>1.74</v>
@@ -18446,7 +18461,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q85">
         <v>3.75</v>
@@ -18524,7 +18539,7 @@
         <v>1.75</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ85">
         <v>2.29</v>
@@ -18939,7 +18954,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ87">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR87">
         <v>2.49</v>
@@ -19064,7 +19079,7 @@
         <v>147</v>
       </c>
       <c r="P88" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q88">
         <v>2.83</v>
@@ -19351,7 +19366,7 @@
         <v>0.29</v>
       </c>
       <c r="AQ89">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR89">
         <v>1.3</v>
@@ -19476,7 +19491,7 @@
         <v>148</v>
       </c>
       <c r="P90" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q90">
         <v>1.57</v>
@@ -19682,7 +19697,7 @@
         <v>149</v>
       </c>
       <c r="P91" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q91">
         <v>2.45</v>
@@ -19888,7 +19903,7 @@
         <v>91</v>
       </c>
       <c r="P92" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20094,7 +20109,7 @@
         <v>150</v>
       </c>
       <c r="P93" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20300,7 +20315,7 @@
         <v>91</v>
       </c>
       <c r="P94" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q94">
         <v>2.95</v>
@@ -20712,7 +20727,7 @@
         <v>152</v>
       </c>
       <c r="P96" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q96">
         <v>4.33</v>
@@ -20790,7 +20805,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ96">
         <v>1.43</v>
@@ -21124,7 +21139,7 @@
         <v>154</v>
       </c>
       <c r="P98" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21202,10 +21217,10 @@
         <v>0.8</v>
       </c>
       <c r="AP98">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AQ98">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR98">
         <v>2.13</v>
@@ -21330,7 +21345,7 @@
         <v>155</v>
       </c>
       <c r="P99" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q99">
         <v>6.5</v>
@@ -21614,7 +21629,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ100">
         <v>1.25</v>
@@ -21948,7 +21963,7 @@
         <v>158</v>
       </c>
       <c r="P102" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q102">
         <v>1.73</v>
@@ -22154,7 +22169,7 @@
         <v>124</v>
       </c>
       <c r="P103" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q103">
         <v>2.38</v>
@@ -22235,7 +22250,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ103">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR103">
         <v>1.27</v>
@@ -22566,7 +22581,7 @@
         <v>160</v>
       </c>
       <c r="P105" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q105">
         <v>3.1</v>
@@ -22978,7 +22993,7 @@
         <v>91</v>
       </c>
       <c r="P107" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23596,7 +23611,7 @@
         <v>163</v>
       </c>
       <c r="P110" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q110">
         <v>4</v>
@@ -23802,7 +23817,7 @@
         <v>164</v>
       </c>
       <c r="P111" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q111">
         <v>2.75</v>
@@ -24008,7 +24023,7 @@
         <v>91</v>
       </c>
       <c r="P112" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q112">
         <v>5</v>
@@ -24214,7 +24229,7 @@
         <v>165</v>
       </c>
       <c r="P113" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q113">
         <v>2.9</v>
@@ -24832,7 +24847,7 @@
         <v>168</v>
       </c>
       <c r="P116" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q116">
         <v>3.3</v>
@@ -24989,6 +25004,830 @@
       </c>
       <c r="BP116">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7785293</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45858.39583333334</v>
+      </c>
+      <c r="F117">
+        <v>14</v>
+      </c>
+      <c r="G117" t="s">
+        <v>72</v>
+      </c>
+      <c r="H117" t="s">
+        <v>83</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>3</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>3</v>
+      </c>
+      <c r="O117" t="s">
+        <v>169</v>
+      </c>
+      <c r="P117" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q117">
+        <v>1.73</v>
+      </c>
+      <c r="R117">
+        <v>2.75</v>
+      </c>
+      <c r="S117">
+        <v>7.5</v>
+      </c>
+      <c r="T117">
+        <v>1.25</v>
+      </c>
+      <c r="U117">
+        <v>3.75</v>
+      </c>
+      <c r="V117">
+        <v>2.1</v>
+      </c>
+      <c r="W117">
+        <v>1.67</v>
+      </c>
+      <c r="X117">
+        <v>5</v>
+      </c>
+      <c r="Y117">
+        <v>1.17</v>
+      </c>
+      <c r="Z117">
+        <v>1.28</v>
+      </c>
+      <c r="AA117">
+        <v>4.8</v>
+      </c>
+      <c r="AB117">
+        <v>7.7</v>
+      </c>
+      <c r="AC117">
+        <v>1.03</v>
+      </c>
+      <c r="AD117">
+        <v>11</v>
+      </c>
+      <c r="AE117">
+        <v>1.15</v>
+      </c>
+      <c r="AF117">
+        <v>5.25</v>
+      </c>
+      <c r="AG117">
+        <v>1.4</v>
+      </c>
+      <c r="AH117">
+        <v>2.82</v>
+      </c>
+      <c r="AI117">
+        <v>1.8</v>
+      </c>
+      <c r="AJ117">
+        <v>1.95</v>
+      </c>
+      <c r="AK117">
+        <v>1.07</v>
+      </c>
+      <c r="AL117">
+        <v>1.15</v>
+      </c>
+      <c r="AM117">
+        <v>3.25</v>
+      </c>
+      <c r="AN117">
+        <v>0.83</v>
+      </c>
+      <c r="AO117">
+        <v>0</v>
+      </c>
+      <c r="AP117">
+        <v>1.14</v>
+      </c>
+      <c r="AQ117">
+        <v>0</v>
+      </c>
+      <c r="AR117">
+        <v>2.04</v>
+      </c>
+      <c r="AS117">
+        <v>1.19</v>
+      </c>
+      <c r="AT117">
+        <v>3.23</v>
+      </c>
+      <c r="AU117">
+        <v>13</v>
+      </c>
+      <c r="AV117">
+        <v>4</v>
+      </c>
+      <c r="AW117">
+        <v>14</v>
+      </c>
+      <c r="AX117">
+        <v>3</v>
+      </c>
+      <c r="AY117">
+        <v>27</v>
+      </c>
+      <c r="AZ117">
+        <v>7</v>
+      </c>
+      <c r="BA117">
+        <v>10</v>
+      </c>
+      <c r="BB117">
+        <v>7</v>
+      </c>
+      <c r="BC117">
+        <v>17</v>
+      </c>
+      <c r="BD117">
+        <v>1.16</v>
+      </c>
+      <c r="BE117">
+        <v>10</v>
+      </c>
+      <c r="BF117">
+        <v>5.3</v>
+      </c>
+      <c r="BG117">
+        <v>1.16</v>
+      </c>
+      <c r="BH117">
+        <v>4.5</v>
+      </c>
+      <c r="BI117">
+        <v>1.28</v>
+      </c>
+      <c r="BJ117">
+        <v>3.3</v>
+      </c>
+      <c r="BK117">
+        <v>1.46</v>
+      </c>
+      <c r="BL117">
+        <v>2.5</v>
+      </c>
+      <c r="BM117">
+        <v>1.72</v>
+      </c>
+      <c r="BN117">
+        <v>1.98</v>
+      </c>
+      <c r="BO117">
+        <v>2.07</v>
+      </c>
+      <c r="BP117">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7785291</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45858.5</v>
+      </c>
+      <c r="F118">
+        <v>14</v>
+      </c>
+      <c r="G118" t="s">
+        <v>76</v>
+      </c>
+      <c r="H118" t="s">
+        <v>77</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>3</v>
+      </c>
+      <c r="M118">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>4</v>
+      </c>
+      <c r="O118" t="s">
+        <v>170</v>
+      </c>
+      <c r="P118" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q118">
+        <v>2.2</v>
+      </c>
+      <c r="R118">
+        <v>2.3</v>
+      </c>
+      <c r="S118">
+        <v>5.5</v>
+      </c>
+      <c r="T118">
+        <v>1.36</v>
+      </c>
+      <c r="U118">
+        <v>3</v>
+      </c>
+      <c r="V118">
+        <v>2.63</v>
+      </c>
+      <c r="W118">
+        <v>1.44</v>
+      </c>
+      <c r="X118">
+        <v>7</v>
+      </c>
+      <c r="Y118">
+        <v>1.1</v>
+      </c>
+      <c r="Z118">
+        <v>1.65</v>
+      </c>
+      <c r="AA118">
+        <v>3.29</v>
+      </c>
+      <c r="AB118">
+        <v>4.75</v>
+      </c>
+      <c r="AC118">
+        <v>1.05</v>
+      </c>
+      <c r="AD118">
+        <v>9.5</v>
+      </c>
+      <c r="AE118">
+        <v>1.28</v>
+      </c>
+      <c r="AF118">
+        <v>3.55</v>
+      </c>
+      <c r="AG118">
+        <v>1.8</v>
+      </c>
+      <c r="AH118">
+        <v>1.9</v>
+      </c>
+      <c r="AI118">
+        <v>1.91</v>
+      </c>
+      <c r="AJ118">
+        <v>1.91</v>
+      </c>
+      <c r="AK118">
+        <v>1.16</v>
+      </c>
+      <c r="AL118">
+        <v>1.25</v>
+      </c>
+      <c r="AM118">
+        <v>2.2</v>
+      </c>
+      <c r="AN118">
+        <v>2</v>
+      </c>
+      <c r="AO118">
+        <v>0.83</v>
+      </c>
+      <c r="AP118">
+        <v>2.14</v>
+      </c>
+      <c r="AQ118">
+        <v>0.71</v>
+      </c>
+      <c r="AR118">
+        <v>1.36</v>
+      </c>
+      <c r="AS118">
+        <v>1.07</v>
+      </c>
+      <c r="AT118">
+        <v>2.43</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
+        <v>7</v>
+      </c>
+      <c r="AW118">
+        <v>7</v>
+      </c>
+      <c r="AX118">
+        <v>4</v>
+      </c>
+      <c r="AY118">
+        <v>14</v>
+      </c>
+      <c r="AZ118">
+        <v>11</v>
+      </c>
+      <c r="BA118">
+        <v>5</v>
+      </c>
+      <c r="BB118">
+        <v>3</v>
+      </c>
+      <c r="BC118">
+        <v>8</v>
+      </c>
+      <c r="BD118">
+        <v>1.38</v>
+      </c>
+      <c r="BE118">
+        <v>7</v>
+      </c>
+      <c r="BF118">
+        <v>3.3</v>
+      </c>
+      <c r="BG118">
+        <v>1.21</v>
+      </c>
+      <c r="BH118">
+        <v>3.9</v>
+      </c>
+      <c r="BI118">
+        <v>1.38</v>
+      </c>
+      <c r="BJ118">
+        <v>2.8</v>
+      </c>
+      <c r="BK118">
+        <v>1.6</v>
+      </c>
+      <c r="BL118">
+        <v>2.17</v>
+      </c>
+      <c r="BM118">
+        <v>1.94</v>
+      </c>
+      <c r="BN118">
+        <v>1.76</v>
+      </c>
+      <c r="BO118">
+        <v>2.4</v>
+      </c>
+      <c r="BP118">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7785289</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45858.5</v>
+      </c>
+      <c r="F119">
+        <v>14</v>
+      </c>
+      <c r="G119" t="s">
+        <v>82</v>
+      </c>
+      <c r="H119" t="s">
+        <v>84</v>
+      </c>
+      <c r="I119">
+        <v>4</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>4</v>
+      </c>
+      <c r="L119">
+        <v>6</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>6</v>
+      </c>
+      <c r="O119" t="s">
+        <v>171</v>
+      </c>
+      <c r="P119" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q119">
+        <v>2.1</v>
+      </c>
+      <c r="R119">
+        <v>2.5</v>
+      </c>
+      <c r="S119">
+        <v>5</v>
+      </c>
+      <c r="T119">
+        <v>1.29</v>
+      </c>
+      <c r="U119">
+        <v>3.5</v>
+      </c>
+      <c r="V119">
+        <v>2.25</v>
+      </c>
+      <c r="W119">
+        <v>1.57</v>
+      </c>
+      <c r="X119">
+        <v>5.5</v>
+      </c>
+      <c r="Y119">
+        <v>1.14</v>
+      </c>
+      <c r="Z119">
+        <v>1.62</v>
+      </c>
+      <c r="AA119">
+        <v>3.69</v>
+      </c>
+      <c r="AB119">
+        <v>4.3</v>
+      </c>
+      <c r="AC119">
+        <v>1.03</v>
+      </c>
+      <c r="AD119">
+        <v>11</v>
+      </c>
+      <c r="AE119">
+        <v>1.2</v>
+      </c>
+      <c r="AF119">
+        <v>4.33</v>
+      </c>
+      <c r="AG119">
+        <v>1.6</v>
+      </c>
+      <c r="AH119">
+        <v>2.1</v>
+      </c>
+      <c r="AI119">
+        <v>1.67</v>
+      </c>
+      <c r="AJ119">
+        <v>2.1</v>
+      </c>
+      <c r="AK119">
+        <v>1.19</v>
+      </c>
+      <c r="AL119">
+        <v>1.22</v>
+      </c>
+      <c r="AM119">
+        <v>2.15</v>
+      </c>
+      <c r="AN119">
+        <v>3</v>
+      </c>
+      <c r="AO119">
+        <v>1.38</v>
+      </c>
+      <c r="AP119">
+        <v>3</v>
+      </c>
+      <c r="AQ119">
+        <v>1.22</v>
+      </c>
+      <c r="AR119">
+        <v>2.01</v>
+      </c>
+      <c r="AS119">
+        <v>1.2</v>
+      </c>
+      <c r="AT119">
+        <v>3.21</v>
+      </c>
+      <c r="AU119">
+        <v>8</v>
+      </c>
+      <c r="AV119">
+        <v>4</v>
+      </c>
+      <c r="AW119">
+        <v>9</v>
+      </c>
+      <c r="AX119">
+        <v>5</v>
+      </c>
+      <c r="AY119">
+        <v>17</v>
+      </c>
+      <c r="AZ119">
+        <v>9</v>
+      </c>
+      <c r="BA119">
+        <v>6</v>
+      </c>
+      <c r="BB119">
+        <v>7</v>
+      </c>
+      <c r="BC119">
+        <v>13</v>
+      </c>
+      <c r="BD119">
+        <v>1.42</v>
+      </c>
+      <c r="BE119">
+        <v>7</v>
+      </c>
+      <c r="BF119">
+        <v>3.15</v>
+      </c>
+      <c r="BG119">
+        <v>1.23</v>
+      </c>
+      <c r="BH119">
+        <v>3.65</v>
+      </c>
+      <c r="BI119">
+        <v>1.4</v>
+      </c>
+      <c r="BJ119">
+        <v>2.65</v>
+      </c>
+      <c r="BK119">
+        <v>1.66</v>
+      </c>
+      <c r="BL119">
+        <v>2.08</v>
+      </c>
+      <c r="BM119">
+        <v>2.02</v>
+      </c>
+      <c r="BN119">
+        <v>1.7</v>
+      </c>
+      <c r="BO119">
+        <v>2.55</v>
+      </c>
+      <c r="BP119">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7785286</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45858.59375</v>
+      </c>
+      <c r="F120">
+        <v>14</v>
+      </c>
+      <c r="G120" t="s">
+        <v>73</v>
+      </c>
+      <c r="H120" t="s">
+        <v>71</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>1</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="M120">
+        <v>1</v>
+      </c>
+      <c r="N120">
+        <v>2</v>
+      </c>
+      <c r="O120" t="s">
+        <v>172</v>
+      </c>
+      <c r="P120" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q120">
+        <v>3.4</v>
+      </c>
+      <c r="R120">
+        <v>2.1</v>
+      </c>
+      <c r="S120">
+        <v>3.1</v>
+      </c>
+      <c r="T120">
+        <v>1.4</v>
+      </c>
+      <c r="U120">
+        <v>2.75</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+      <c r="W120">
+        <v>1.36</v>
+      </c>
+      <c r="X120">
+        <v>8</v>
+      </c>
+      <c r="Y120">
+        <v>1.08</v>
+      </c>
+      <c r="Z120">
+        <v>2.78</v>
+      </c>
+      <c r="AA120">
+        <v>3.34</v>
+      </c>
+      <c r="AB120">
+        <v>2.17</v>
+      </c>
+      <c r="AC120">
+        <v>1.07</v>
+      </c>
+      <c r="AD120">
+        <v>8</v>
+      </c>
+      <c r="AE120">
+        <v>1.33</v>
+      </c>
+      <c r="AF120">
+        <v>3.25</v>
+      </c>
+      <c r="AG120">
+        <v>1.8</v>
+      </c>
+      <c r="AH120">
+        <v>1.9</v>
+      </c>
+      <c r="AI120">
+        <v>1.8</v>
+      </c>
+      <c r="AJ120">
+        <v>1.95</v>
+      </c>
+      <c r="AK120">
+        <v>1.48</v>
+      </c>
+      <c r="AL120">
+        <v>1.3</v>
+      </c>
+      <c r="AM120">
+        <v>1.42</v>
+      </c>
+      <c r="AN120">
+        <v>1.33</v>
+      </c>
+      <c r="AO120">
+        <v>0.83</v>
+      </c>
+      <c r="AP120">
+        <v>1.29</v>
+      </c>
+      <c r="AQ120">
+        <v>0.86</v>
+      </c>
+      <c r="AR120">
+        <v>1.36</v>
+      </c>
+      <c r="AS120">
+        <v>1.3</v>
+      </c>
+      <c r="AT120">
+        <v>2.66</v>
+      </c>
+      <c r="AU120">
+        <v>3</v>
+      </c>
+      <c r="AV120">
+        <v>8</v>
+      </c>
+      <c r="AW120">
+        <v>9</v>
+      </c>
+      <c r="AX120">
+        <v>4</v>
+      </c>
+      <c r="AY120">
+        <v>12</v>
+      </c>
+      <c r="AZ120">
+        <v>12</v>
+      </c>
+      <c r="BA120">
+        <v>9</v>
+      </c>
+      <c r="BB120">
+        <v>4</v>
+      </c>
+      <c r="BC120">
+        <v>13</v>
+      </c>
+      <c r="BD120">
+        <v>2.07</v>
+      </c>
+      <c r="BE120">
+        <v>7</v>
+      </c>
+      <c r="BF120">
+        <v>1.88</v>
+      </c>
+      <c r="BG120">
+        <v>1.16</v>
+      </c>
+      <c r="BH120">
+        <v>4.4</v>
+      </c>
+      <c r="BI120">
+        <v>1.29</v>
+      </c>
+      <c r="BJ120">
+        <v>3.2</v>
+      </c>
+      <c r="BK120">
+        <v>1.49</v>
+      </c>
+      <c r="BL120">
+        <v>2.4</v>
+      </c>
+      <c r="BM120">
+        <v>1.77</v>
+      </c>
+      <c r="BN120">
+        <v>1.93</v>
+      </c>
+      <c r="BO120">
+        <v>2.17</v>
+      </c>
+      <c r="BP120">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
